--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3358" uniqueCount="1339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3353" uniqueCount="1336">
   <si>
     <t>ID</t>
   </si>
@@ -3803,15 +3803,6 @@
   </si>
   <si>
     <t>中秋禮品</t>
-  </si>
-  <si>
-    <t>ID1788841035775</t>
-  </si>
-  <si>
-    <t>GFCKM-TY-C</t>
-  </si>
-  <si>
-    <t>26#13</t>
   </si>
   <si>
     <t>ID1788853989803</t>
@@ -13684,7 +13675,7 @@
         <v>12</v>
       </c>
       <c r="D405" s="2">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="E405" s="2" t="s">
         <v>805</v>
@@ -18586,7 +18577,7 @@
         <v>12</v>
       </c>
       <c r="D610" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E610" s="2" t="s">
         <v>1025</v>
@@ -19186,7 +19177,7 @@
         <v>12</v>
       </c>
       <c r="D637" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E637" s="2" t="s">
         <v>1036</v>
@@ -19514,22 +19505,20 @@
         <v>12</v>
       </c>
       <c r="D651" s="2">
-        <v>17.0</v>
+        <v>3.0</v>
       </c>
       <c r="E651" s="2" t="s">
         <v>1265</v>
       </c>
       <c r="F651" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="G651" s="7">
-        <v>46322.0</v>
-      </c>
+        <v>704</v>
+      </c>
+      <c r="G651" s="7"/>
       <c r="H651" s="2"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>702</v>
@@ -19541,7 +19530,7 @@
         <v>3.0</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F652" s="3" t="s">
         <v>704</v>
@@ -19551,7 +19540,7 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>702</v>
@@ -19563,7 +19552,7 @@
         <v>3.0</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="F653" s="3" t="s">
         <v>704</v>
@@ -19573,7 +19562,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>702</v>
@@ -19582,10 +19571,10 @@
         <v>12</v>
       </c>
       <c r="D654" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="F654" s="3" t="s">
         <v>704</v>
@@ -19595,7 +19584,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>702</v>
@@ -19607,7 +19596,7 @@
         <v>2.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="F655" s="3" t="s">
         <v>704</v>
@@ -19617,29 +19606,31 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D656" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F656" s="3" t="s">
         <v>1275</v>
       </c>
-      <c r="B656" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="C656" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D656" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E656" s="2" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F656" s="3" t="s">
-        <v>704</v>
-      </c>
-      <c r="G656" s="7"/>
+      <c r="G656" s="7">
+        <v>46982.0</v>
+      </c>
       <c r="H656" s="2"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>34</v>
@@ -19648,37 +19639,37 @@
         <v>12</v>
       </c>
       <c r="D657" s="2">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1165</v>
+        <v>1277</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="G657" s="7">
-        <v>46982.0</v>
+        <v>46914.0</v>
       </c>
       <c r="H657" s="2"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C658" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D658" s="2">
-        <v>10.0</v>
+        <v>15.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="G658" s="7">
         <v>46914.0</v>
@@ -19687,31 +19678,31 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B659" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D659" s="2">
         <v>15.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1282</v>
+        <v>1038</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1278</v>
+        <v>1281</v>
       </c>
       <c r="G659" s="7">
-        <v>46914.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H659" s="2"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>45</v>
@@ -19720,13 +19711,13 @@
         <v>12</v>
       </c>
       <c r="D660" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G660" s="7">
         <v>46963.0</v>
@@ -19735,7 +19726,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>45</v>
@@ -19744,22 +19735,22 @@
         <v>12</v>
       </c>
       <c r="D661" s="2">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1040</v>
+        <v>1284</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G661" s="7">
-        <v>46963.0</v>
+        <v>46421.0</v>
       </c>
       <c r="H661" s="2"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>45</v>
@@ -19768,22 +19759,22 @@
         <v>12</v>
       </c>
       <c r="D662" s="2">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G662" s="7">
-        <v>46421.0</v>
+        <v>46710.0</v>
       </c>
       <c r="H662" s="2"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>45</v>
@@ -19795,43 +19786,43 @@
         <v>12.0</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>1289</v>
+        <v>1286</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G663" s="7">
-        <v>46710.0</v>
+        <v>46722.0</v>
       </c>
       <c r="H663" s="2"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C664" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D664" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1289</v>
+        <v>901</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G664" s="7">
-        <v>46722.0</v>
+        <v>46620.0</v>
       </c>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>45</v>
@@ -19840,37 +19831,37 @@
         <v>27</v>
       </c>
       <c r="D665" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>901</v>
+        <v>1168</v>
       </c>
       <c r="F665" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G665" s="7">
-        <v>46620.0</v>
+        <v>46757.0</v>
       </c>
       <c r="H665" s="2"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D666" s="2">
-        <v>16.0</v>
+        <v>12.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1168</v>
+        <v>1291</v>
       </c>
       <c r="F666" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G666" s="7">
         <v>46757.0</v>
@@ -19879,7 +19870,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>45</v>
@@ -19888,22 +19879,22 @@
         <v>12</v>
       </c>
       <c r="D667" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1294</v>
+        <v>1031</v>
       </c>
       <c r="F667" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G667" s="7">
-        <v>46757.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H667" s="2"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>45</v>
@@ -19912,46 +19903,46 @@
         <v>12</v>
       </c>
       <c r="D668" s="2">
-        <v>13.0</v>
+        <v>11.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1031</v>
+        <v>1294</v>
       </c>
       <c r="F668" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G668" s="7">
-        <v>46530.0</v>
+        <v>46911.0</v>
       </c>
       <c r="H668" s="2"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D669" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G669" s="7">
-        <v>46911.0</v>
+        <v>46480.0</v>
       </c>
       <c r="H669" s="2"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>45</v>
@@ -19963,10 +19954,10 @@
         <v>15.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="F670" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G670" s="7">
         <v>46480.0</v>
@@ -19975,7 +19966,7 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>45</v>
@@ -19987,19 +19978,19 @@
         <v>15.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="F671" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G671" s="7">
-        <v>46480.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H671" s="2"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>45</v>
@@ -20011,10 +20002,10 @@
         <v>15.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1303</v>
+        <v>1042</v>
       </c>
       <c r="F672" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G672" s="7">
         <v>46793.0</v>
@@ -20023,31 +20014,31 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D673" s="2">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1042</v>
+        <v>1303</v>
       </c>
       <c r="F673" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G673" s="7">
-        <v>46793.0</v>
+        <v>46794.0</v>
       </c>
       <c r="H673" s="2"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>45</v>
@@ -20059,43 +20050,43 @@
         <v>13.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="F674" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G674" s="7">
-        <v>46794.0</v>
+        <v>46487.0</v>
       </c>
       <c r="H674" s="2"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D675" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="F675" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G675" s="7">
-        <v>46487.0</v>
+        <v>46424.0</v>
       </c>
       <c r="H675" s="2"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>45</v>
@@ -20107,43 +20098,39 @@
         <v>15.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="F676" s="3" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="G676" s="7">
-        <v>46424.0</v>
+        <v>46757.0</v>
       </c>
       <c r="H676" s="2"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>45</v>
+        <v>702</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D677" s="2">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>1312</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G677" s="7">
-        <v>46757.0</v>
-      </c>
+        <v>1036</v>
+      </c>
+      <c r="F677" s="3"/>
+      <c r="G677" s="7"/>
       <c r="H677" s="2"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>702</v>
@@ -20155,7 +20142,7 @@
         <v>10.0</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1036</v>
+        <v>439</v>
       </c>
       <c r="F678" s="3"/>
       <c r="G678" s="7"/>
@@ -20163,7 +20150,7 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>702</v>
@@ -20175,7 +20162,7 @@
         <v>10.0</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>439</v>
+        <v>1313</v>
       </c>
       <c r="F679" s="3"/>
       <c r="G679" s="7"/>
@@ -20183,7 +20170,7 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>702</v>
@@ -20195,7 +20182,7 @@
         <v>10.0</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
       <c r="F680" s="3"/>
       <c r="G680" s="7"/>
@@ -20203,7 +20190,7 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>702</v>
@@ -20215,7 +20202,7 @@
         <v>10.0</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="F681" s="3"/>
       <c r="G681" s="7"/>
@@ -20223,7 +20210,7 @@
     </row>
     <row r="682">
       <c r="A682" s="2" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>702</v>
@@ -20235,7 +20222,7 @@
         <v>10.0</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="F682" s="3"/>
       <c r="G682" s="7"/>
@@ -20243,7 +20230,7 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>702</v>
@@ -20252,18 +20239,20 @@
         <v>27</v>
       </c>
       <c r="D683" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="F683" s="3"/>
+        <v>397</v>
+      </c>
+      <c r="F683" s="3" t="s">
+        <v>1321</v>
+      </c>
       <c r="G683" s="7"/>
       <c r="H683" s="2"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>702</v>
@@ -20275,17 +20264,17 @@
         <v>3.0</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>397</v>
+        <v>1323</v>
       </c>
       <c r="F684" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G684" s="7"/>
       <c r="H684" s="2"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>702</v>
@@ -20297,17 +20286,17 @@
         <v>3.0</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>1326</v>
+        <v>765</v>
       </c>
       <c r="F685" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G685" s="7"/>
       <c r="H685" s="2"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B686" s="2" t="s">
         <v>702</v>
@@ -20319,17 +20308,17 @@
         <v>3.0</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>765</v>
+        <v>1326</v>
       </c>
       <c r="F686" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G686" s="7"/>
       <c r="H686" s="2"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>702</v>
@@ -20341,17 +20330,17 @@
         <v>3.0</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="F687" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G687" s="7"/>
       <c r="H687" s="2"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>702</v>
@@ -20363,39 +20352,39 @@
         <v>3.0</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="F688" s="3" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="G688" s="7"/>
       <c r="H688" s="2"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>702</v>
+        <v>45</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D689" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>1333</v>
+        <v>1205</v>
       </c>
       <c r="F689" s="3" t="s">
-        <v>1324</v>
+        <v>1281</v>
       </c>
       <c r="G689" s="7"/>
       <c r="H689" s="2"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="s">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>45</v>
@@ -20404,63 +20393,51 @@
         <v>12</v>
       </c>
       <c r="D690" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>1205</v>
+        <v>1333</v>
       </c>
       <c r="F690" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="G690" s="7"/>
+        <v>1281</v>
+      </c>
+      <c r="G690" s="7">
+        <v>46620.0</v>
+      </c>
       <c r="H690" s="2"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D691" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E691" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F691" s="3" t="s">
         <v>1335</v>
       </c>
-      <c r="B691" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C691" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D691" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="E691" s="2" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F691" s="3" t="s">
-        <v>1284</v>
-      </c>
       <c r="G691" s="7">
-        <v>46620.0</v>
+        <v>46982.0</v>
       </c>
       <c r="H691" s="2"/>
     </row>
     <row r="692">
-      <c r="A692" s="2" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B692" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C692" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D692" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="E692" s="2" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F692" s="3" t="s">
-        <v>1338</v>
-      </c>
-      <c r="G692" s="7">
-        <v>46982.0</v>
-      </c>
+      <c r="A692" s="2"/>
+      <c r="B692" s="2"/>
+      <c r="C692" s="2"/>
+      <c r="D692" s="2"/>
+      <c r="E692" s="2"/>
+      <c r="F692" s="3"/>
+      <c r="G692" s="7"/>
       <c r="H692" s="2"/>
     </row>
     <row r="693">
@@ -26973,16 +26950,6 @@
       <c r="G1343" s="7"/>
       <c r="H1343" s="2"/>
     </row>
-    <row r="1344">
-      <c r="A1344" s="2"/>
-      <c r="B1344" s="2"/>
-      <c r="C1344" s="2"/>
-      <c r="D1344" s="2"/>
-      <c r="E1344" s="2"/>
-      <c r="F1344" s="3"/>
-      <c r="G1344" s="7"/>
-      <c r="H1344" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3408" uniqueCount="1358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1378">
   <si>
     <t>ID</t>
   </si>
@@ -2863,30 +2863,12 @@
     <t>10Q</t>
   </si>
   <si>
-    <t>ID1787194275587</t>
-  </si>
-  <si>
-    <t>MFV25(G9預定)</t>
-  </si>
-  <si>
     <t>ID1787194287329</t>
   </si>
   <si>
     <t>MFV10(G9預定)</t>
   </si>
   <si>
-    <t>ID1787194302354</t>
-  </si>
-  <si>
-    <t>MFR250(G9預定)</t>
-  </si>
-  <si>
-    <t>ID1787194331734</t>
-  </si>
-  <si>
-    <t>IABS500(G9預定)</t>
-  </si>
-  <si>
     <t>ID1787195263221</t>
   </si>
   <si>
@@ -3793,12 +3775,6 @@
     <t>1150430K</t>
   </si>
   <si>
-    <t>ID1788840807493</t>
-  </si>
-  <si>
-    <t>中秋禮品</t>
-  </si>
-  <si>
     <t>ID1788853989803</t>
   </si>
   <si>
@@ -4085,6 +4061,90 @@
   </si>
   <si>
     <t>GSTDL-TY-C</t>
+  </si>
+  <si>
+    <t>ID1789359528826</t>
+  </si>
+  <si>
+    <t>CHSRL-YK-K</t>
+  </si>
+  <si>
+    <t>1141027K</t>
+  </si>
+  <si>
+    <t>ID1789359549949</t>
+  </si>
+  <si>
+    <t>ID1789359562229</t>
+  </si>
+  <si>
+    <t>SA5S80</t>
+  </si>
+  <si>
+    <t>ID1789359579715</t>
+  </si>
+  <si>
+    <t>M9RER-KR-C</t>
+  </si>
+  <si>
+    <t>ID1789359596188</t>
+  </si>
+  <si>
+    <t>ACTDL-TY-C</t>
+  </si>
+  <si>
+    <t>ID1789359610729</t>
+  </si>
+  <si>
+    <t>M89OB-KR-C</t>
+  </si>
+  <si>
+    <t>ID1789359622586</t>
+  </si>
+  <si>
+    <t>ID1789359630465</t>
+  </si>
+  <si>
+    <t>ID1789359647163</t>
+  </si>
+  <si>
+    <t>ID1789359679757</t>
+  </si>
+  <si>
+    <t>GFTUE-TY-K</t>
+  </si>
+  <si>
+    <t>1140926K</t>
+  </si>
+  <si>
+    <t>ID1789359690483</t>
+  </si>
+  <si>
+    <t>BJUC</t>
+  </si>
+  <si>
+    <t>ID1789359711003</t>
+  </si>
+  <si>
+    <t>ID1789370001528</t>
+  </si>
+  <si>
+    <t>ID1789370523286</t>
+  </si>
+  <si>
+    <t>M89RER-KR-K</t>
+  </si>
+  <si>
+    <t>1150508K</t>
+  </si>
+  <si>
+    <t>ID1789370533458</t>
+  </si>
+  <si>
+    <t>1150620K</t>
+  </si>
+  <si>
+    <t>ID1789370551793</t>
   </si>
 </sst>
 </file>
@@ -7992,10 +8052,10 @@
         <v>45</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D154" s="2">
-        <v>4.0</v>
+        <v>18.0</v>
       </c>
       <c r="E154" s="2" t="s">
         <v>318</v>
@@ -8096,10 +8156,10 @@
         <v>34</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D159" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>350</v>
@@ -8119,10 +8179,10 @@
         <v>34</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D160" s="2">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="E160" s="2" t="s">
         <v>352</v>
@@ -12250,7 +12310,9 @@
       <c r="G342" s="7">
         <v>46872.0</v>
       </c>
-      <c r="H342" s="2"/>
+      <c r="H342" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
@@ -15437,21 +15499,23 @@
         <v>952</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>11</v>
+        <v>701</v>
       </c>
       <c r="C476" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D476" s="2">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="E476" s="2" t="s">
         <v>953</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G476" s="7"/>
+        <v>703</v>
+      </c>
+      <c r="G476" s="7">
+        <v>46363.0</v>
+      </c>
       <c r="H476" s="2"/>
     </row>
     <row r="477">
@@ -15459,21 +15523,23 @@
         <v>954</v>
       </c>
       <c r="B477" s="2" t="s">
-        <v>11</v>
+        <v>332</v>
       </c>
       <c r="C477" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D477" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E477" s="2" t="s">
         <v>955</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G477" s="7"/>
+        <v>263</v>
+      </c>
+      <c r="G477" s="7">
+        <v>46382.0</v>
+      </c>
       <c r="H477" s="2"/>
     </row>
     <row r="478">
@@ -15481,21 +15547,23 @@
         <v>956</v>
       </c>
       <c r="B478" s="2" t="s">
-        <v>11</v>
+        <v>332</v>
       </c>
       <c r="C478" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D478" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E478" s="2" t="s">
         <v>957</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G478" s="7"/>
+        <v>263</v>
+      </c>
+      <c r="G478" s="7">
+        <v>46581.0</v>
+      </c>
       <c r="H478" s="2"/>
     </row>
     <row r="479">
@@ -15503,28 +15571,28 @@
         <v>958</v>
       </c>
       <c r="B479" s="2" t="s">
-        <v>701</v>
+        <v>332</v>
       </c>
       <c r="C479" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D479" s="2">
-        <v>14.0</v>
+        <v>6.0</v>
       </c>
       <c r="E479" s="2" t="s">
-        <v>959</v>
+        <v>570</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>703</v>
+        <v>263</v>
       </c>
       <c r="G479" s="7">
-        <v>46363.0</v>
+        <v>46392.0</v>
       </c>
       <c r="H479" s="2"/>
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>332</v>
@@ -15536,19 +15604,19 @@
         <v>6.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>263</v>
       </c>
       <c r="G480" s="7">
-        <v>46382.0</v>
+        <v>46356.0</v>
       </c>
       <c r="H480" s="2"/>
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>332</v>
@@ -15557,64 +15625,64 @@
         <v>12</v>
       </c>
       <c r="D481" s="2">
-        <v>3.0</v>
+        <v>12.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>963</v>
+        <v>894</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>263</v>
+        <v>810</v>
       </c>
       <c r="G481" s="7">
-        <v>46581.0</v>
+        <v>46291.0</v>
       </c>
       <c r="H481" s="2"/>
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="B482" s="2" t="s">
-        <v>332</v>
+        <v>815</v>
       </c>
       <c r="C482" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D482" s="2">
-        <v>6.0</v>
+        <v>14.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>570</v>
+        <v>963</v>
       </c>
       <c r="F482" s="3" t="s">
         <v>263</v>
       </c>
       <c r="G482" s="7">
-        <v>46392.0</v>
+        <v>46409.0</v>
       </c>
       <c r="H482" s="2"/>
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
+        <v>964</v>
+      </c>
+      <c r="B483" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C483" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D483" s="2">
+        <v>21.0</v>
+      </c>
+      <c r="E483" s="2" t="s">
         <v>965</v>
       </c>
-      <c r="B483" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C483" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D483" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E483" s="2" t="s">
+      <c r="F483" s="3" t="s">
         <v>966</v>
       </c>
-      <c r="F483" s="3" t="s">
-        <v>263</v>
-      </c>
       <c r="G483" s="7">
-        <v>46356.0</v>
+        <v>46764.0</v>
       </c>
       <c r="H483" s="2"/>
     </row>
@@ -15623,22 +15691,22 @@
         <v>967</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>332</v>
+        <v>45</v>
       </c>
       <c r="C484" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D484" s="2">
-        <v>12.0</v>
+        <v>9.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>894</v>
+        <v>435</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>810</v>
+        <v>306</v>
       </c>
       <c r="G484" s="7">
-        <v>46291.0</v>
+        <v>46875.0</v>
       </c>
       <c r="H484" s="2"/>
     </row>
@@ -15647,22 +15715,22 @@
         <v>968</v>
       </c>
       <c r="B485" s="2" t="s">
-        <v>815</v>
+        <v>45</v>
       </c>
       <c r="C485" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D485" s="2">
-        <v>14.0</v>
+        <v>9.0</v>
       </c>
       <c r="E485" s="2" t="s">
         <v>969</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>263</v>
+        <v>966</v>
       </c>
       <c r="G485" s="7">
-        <v>46409.0</v>
+        <v>46899.0</v>
       </c>
       <c r="H485" s="2"/>
     </row>
@@ -15671,52 +15739,52 @@
         <v>970</v>
       </c>
       <c r="B486" s="2" t="s">
-        <v>442</v>
+        <v>45</v>
       </c>
       <c r="C486" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D486" s="2">
-        <v>21.0</v>
+        <v>9.0</v>
       </c>
       <c r="E486" s="2" t="s">
         <v>971</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="G486" s="7">
-        <v>46764.0</v>
+        <v>46745.0</v>
       </c>
       <c r="H486" s="2"/>
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
+        <v>972</v>
+      </c>
+      <c r="B487" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C487" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D487" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E487" s="2" t="s">
         <v>973</v>
       </c>
-      <c r="B487" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C487" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D487" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="E487" s="2" t="s">
-        <v>435</v>
-      </c>
       <c r="F487" s="3" t="s">
-        <v>306</v>
+        <v>974</v>
       </c>
       <c r="G487" s="7">
-        <v>46875.0</v>
+        <v>46953.0</v>
       </c>
       <c r="H487" s="2"/>
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>45</v>
@@ -15728,91 +15796,89 @@
         <v>9.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="G488" s="7">
-        <v>46899.0</v>
+        <v>46901.0</v>
       </c>
       <c r="H488" s="2"/>
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D489" s="2">
-        <v>9.0</v>
+        <v>21.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>972</v>
+        <v>156</v>
       </c>
       <c r="G489" s="7">
-        <v>46745.0</v>
-      </c>
-      <c r="H489" s="2"/>
+        <v>46737.0</v>
+      </c>
+      <c r="H489" s="2" t="s">
+        <v>979</v>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B490" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C490" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D490" s="2">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>979</v>
-      </c>
-      <c r="F490" s="3" t="s">
-        <v>980</v>
-      </c>
+        <v>981</v>
+      </c>
+      <c r="F490" s="3"/>
       <c r="G490" s="7">
-        <v>46953.0</v>
+        <v>46954.0</v>
       </c>
       <c r="H490" s="2"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C491" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D491" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>982</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>972</v>
-      </c>
+        <v>983</v>
+      </c>
+      <c r="F491" s="3"/>
       <c r="G491" s="7">
-        <v>46901.0</v>
+        <v>46949.0</v>
       </c>
       <c r="H491" s="2"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>45</v>
@@ -15821,20 +15887,18 @@
         <v>12</v>
       </c>
       <c r="D492" s="2">
-        <v>21.0</v>
+        <v>11.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>156</v>
+        <v>274</v>
       </c>
       <c r="G492" s="7">
-        <v>46737.0</v>
-      </c>
-      <c r="H492" s="2" t="s">
-        <v>985</v>
-      </c>
+        <v>46794.0</v>
+      </c>
+      <c r="H492" s="2"/>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
@@ -15847,84 +15911,88 @@
         <v>12</v>
       </c>
       <c r="D493" s="2">
-        <v>7.0</v>
+        <v>14.0</v>
       </c>
       <c r="E493" s="2" t="s">
         <v>987</v>
       </c>
-      <c r="F493" s="3"/>
+      <c r="F493" s="3" t="s">
+        <v>988</v>
+      </c>
       <c r="G493" s="7">
-        <v>46954.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H493" s="2"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B494" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C494" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D494" s="2">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>989</v>
-      </c>
-      <c r="F494" s="3"/>
+        <v>990</v>
+      </c>
+      <c r="F494" s="3" t="s">
+        <v>156</v>
+      </c>
       <c r="G494" s="7">
-        <v>46949.0</v>
+        <v>48157.0</v>
       </c>
       <c r="H494" s="2"/>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B495" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C495" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D495" s="2">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>274</v>
+        <v>156</v>
       </c>
       <c r="G495" s="7">
-        <v>46794.0</v>
+        <v>48332.0</v>
       </c>
       <c r="H495" s="2"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B496" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C496" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D496" s="2">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F496" s="3" t="s">
-        <v>994</v>
+        <v>156</v>
       </c>
       <c r="G496" s="7">
-        <v>46793.0</v>
+        <v>47574.0</v>
       </c>
       <c r="H496" s="2"/>
     </row>
@@ -15933,13 +16001,13 @@
         <v>995</v>
       </c>
       <c r="B497" s="2" t="s">
-        <v>11</v>
+        <v>815</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D497" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E497" s="2" t="s">
         <v>996</v>
@@ -15948,7 +16016,7 @@
         <v>156</v>
       </c>
       <c r="G497" s="7">
-        <v>48157.0</v>
+        <v>48198.0</v>
       </c>
       <c r="H497" s="2"/>
     </row>
@@ -15957,79 +16025,79 @@
         <v>997</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>11</v>
+        <v>998</v>
       </c>
       <c r="C498" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D498" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>998</v>
-      </c>
-      <c r="F498" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G498" s="7">
-        <v>48332.0</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="F498" s="3"/>
+      <c r="G498" s="7"/>
       <c r="H498" s="2"/>
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B499" s="2" t="s">
-        <v>11</v>
+        <v>998</v>
       </c>
       <c r="C499" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D499" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>156</v>
+        <v>703</v>
       </c>
       <c r="G499" s="7">
-        <v>47574.0</v>
-      </c>
-      <c r="H499" s="2"/>
+        <v>46363.0</v>
+      </c>
+      <c r="H499" s="2" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B500" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C500" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D500" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E500" s="2" t="s">
         <v>1001</v>
       </c>
-      <c r="B500" s="2" t="s">
-        <v>815</v>
-      </c>
-      <c r="C500" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D500" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E500" s="2" t="s">
-        <v>1002</v>
-      </c>
       <c r="F500" s="3" t="s">
-        <v>156</v>
+        <v>703</v>
       </c>
       <c r="G500" s="7">
-        <v>48198.0</v>
-      </c>
-      <c r="H500" s="2"/>
+        <v>46363.0</v>
+      </c>
+      <c r="H500" s="2" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="B501" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C501" s="2" t="s">
         <v>12</v>
@@ -16038,18 +16106,24 @@
         <v>1.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F501" s="3"/>
-      <c r="G501" s="7"/>
-      <c r="H501" s="2"/>
+        <v>953</v>
+      </c>
+      <c r="F501" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="G501" s="7">
+        <v>46363.0</v>
+      </c>
+      <c r="H501" s="2" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
         <v>1006</v>
       </c>
       <c r="B502" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C502" s="2" t="s">
         <v>12</v>
@@ -16058,59 +16132,49 @@
         <v>1.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F502" s="3" t="s">
-        <v>703</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="F502" s="3"/>
       <c r="G502" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H502" s="2" t="s">
-        <v>1008</v>
-      </c>
+        <v>46286.0</v>
+      </c>
+      <c r="H502" s="2"/>
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="B503" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C503" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D503" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F503" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G503" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H503" s="2" t="s">
-        <v>1010</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="F503" s="3"/>
+      <c r="G503" s="7"/>
+      <c r="H503" s="2"/>
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="B504" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C504" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D504" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>959</v>
+        <v>801</v>
       </c>
       <c r="F504" s="3" t="s">
         <v>703</v>
@@ -16119,37 +16183,41 @@
         <v>46363.0</v>
       </c>
       <c r="H504" s="2" t="s">
-        <v>1010</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C505" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D505" s="2">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F505" s="3"/>
+        <v>1001</v>
+      </c>
+      <c r="F505" s="3" t="s">
+        <v>703</v>
+      </c>
       <c r="G505" s="7">
-        <v>46286.0</v>
-      </c>
-      <c r="H505" s="2"/>
+        <v>46363.0</v>
+      </c>
+      <c r="H505" s="2" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="B506" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C506" s="2" t="s">
         <v>12</v>
@@ -16158,18 +16226,24 @@
         <v>2.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="F506" s="3"/>
-      <c r="G506" s="7"/>
-      <c r="H506" s="2"/>
+        <v>953</v>
+      </c>
+      <c r="F506" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="G506" s="7">
+        <v>46363.0</v>
+      </c>
+      <c r="H506" s="2" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="B507" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C507" s="2" t="s">
         <v>12</v>
@@ -16178,59 +16252,49 @@
         <v>2.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F507" s="3" t="s">
-        <v>703</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="F507" s="3"/>
       <c r="G507" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H507" s="2" t="s">
-        <v>1008</v>
-      </c>
+        <v>46286.0</v>
+      </c>
+      <c r="H507" s="2"/>
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="B508" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C508" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D508" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F508" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G508" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H508" s="2" t="s">
-        <v>1008</v>
-      </c>
+        <v>1014</v>
+      </c>
+      <c r="F508" s="3"/>
+      <c r="G508" s="7"/>
+      <c r="H508" s="2"/>
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="B509" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C509" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D509" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>959</v>
+        <v>801</v>
       </c>
       <c r="F509" s="3" t="s">
         <v>703</v>
@@ -16239,37 +16303,41 @@
         <v>46363.0</v>
       </c>
       <c r="H509" s="2" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="B510" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C510" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D510" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F510" s="3"/>
+        <v>1017</v>
+      </c>
+      <c r="F510" s="3" t="s">
+        <v>703</v>
+      </c>
       <c r="G510" s="7">
-        <v>46286.0</v>
-      </c>
-      <c r="H510" s="2"/>
+        <v>46363.0</v>
+      </c>
+      <c r="H510" s="2" t="s">
+        <v>1002</v>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B511" s="2" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="C511" s="2" t="s">
         <v>12</v>
@@ -16278,111 +16346,111 @@
         <v>3.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1020</v>
+        <v>1002</v>
       </c>
       <c r="F511" s="3"/>
-      <c r="G511" s="7"/>
+      <c r="G511" s="7">
+        <v>46286.0</v>
+      </c>
       <c r="H511" s="2"/>
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="B512" s="2" t="s">
+        <v>998</v>
+      </c>
+      <c r="C512" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D512" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E512" s="2" t="s">
         <v>1004</v>
       </c>
-      <c r="C512" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D512" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E512" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F512" s="3" t="s">
-        <v>703</v>
-      </c>
+      <c r="F512" s="3"/>
       <c r="G512" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H512" s="2" t="s">
-        <v>1008</v>
-      </c>
+        <v>46303.0</v>
+      </c>
+      <c r="H512" s="2"/>
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>1004</v>
+        <v>45</v>
       </c>
       <c r="C513" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D513" s="2">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F513" s="3" t="s">
-        <v>703</v>
-      </c>
+        <v>1021</v>
+      </c>
+      <c r="F513" s="3"/>
       <c r="G513" s="7">
-        <v>46363.0</v>
-      </c>
-      <c r="H513" s="2" t="s">
-        <v>1008</v>
-      </c>
+        <v>46948.0</v>
+      </c>
+      <c r="H513" s="2"/>
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B514" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C514" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D514" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E514" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F514" s="3" t="s">
         <v>1024</v>
       </c>
-      <c r="B514" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C514" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D514" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E514" s="2" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F514" s="3"/>
       <c r="G514" s="7">
-        <v>46286.0</v>
-      </c>
-      <c r="H514" s="2"/>
+        <v>46530.0</v>
+      </c>
+      <c r="H514" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
         <v>1025</v>
       </c>
       <c r="B515" s="2" t="s">
-        <v>1004</v>
+        <v>45</v>
       </c>
       <c r="C515" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D515" s="2">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F515" s="3"/>
+        <v>1026</v>
+      </c>
+      <c r="F515" s="3" t="s">
+        <v>1024</v>
+      </c>
       <c r="G515" s="7">
-        <v>46303.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H515" s="2"/>
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>45</v>
@@ -16391,20 +16459,22 @@
         <v>12</v>
       </c>
       <c r="D516" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1027</v>
-      </c>
-      <c r="F516" s="3"/>
+        <v>1028</v>
+      </c>
+      <c r="F516" s="3" t="s">
+        <v>400</v>
+      </c>
       <c r="G516" s="7">
-        <v>46948.0</v>
+        <v>46771.0</v>
       </c>
       <c r="H516" s="2"/>
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>45</v>
@@ -16413,16 +16483,16 @@
         <v>12</v>
       </c>
       <c r="D517" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G517" s="7">
-        <v>46530.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H517" s="2"/>
     </row>
@@ -16437,16 +16507,16 @@
         <v>12</v>
       </c>
       <c r="D518" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E518" s="2" t="s">
         <v>1032</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G518" s="7">
-        <v>46530.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H518" s="2"/>
     </row>
@@ -16458,19 +16528,19 @@
         <v>45</v>
       </c>
       <c r="C519" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D519" s="2">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="E519" s="2" t="s">
         <v>1034</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>400</v>
+        <v>1024</v>
       </c>
       <c r="G519" s="7">
-        <v>46771.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H519" s="2"/>
     </row>
@@ -16479,22 +16549,22 @@
         <v>1035</v>
       </c>
       <c r="B520" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C520" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D520" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="E520" s="2" t="s">
         <v>1036</v>
       </c>
       <c r="F520" s="3" t="s">
-        <v>1030</v>
+        <v>20</v>
       </c>
       <c r="G520" s="7">
-        <v>46963.0</v>
+        <v>46424.0</v>
       </c>
       <c r="H520" s="2"/>
     </row>
@@ -16506,19 +16576,19 @@
         <v>45</v>
       </c>
       <c r="C521" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D521" s="2">
-        <v>16.0</v>
+        <v>21.0</v>
       </c>
       <c r="E521" s="2" t="s">
         <v>1038</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>1030</v>
+        <v>941</v>
       </c>
       <c r="G521" s="7">
-        <v>46963.0</v>
+        <v>46480.0</v>
       </c>
       <c r="H521" s="2"/>
     </row>
@@ -16530,19 +16600,19 @@
         <v>45</v>
       </c>
       <c r="C522" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D522" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E522" s="2" t="s">
         <v>1040</v>
       </c>
       <c r="F522" s="3" t="s">
-        <v>1030</v>
+        <v>687</v>
       </c>
       <c r="G522" s="7">
-        <v>46793.0</v>
+        <v>47074.0</v>
       </c>
       <c r="H522" s="2"/>
     </row>
@@ -16551,22 +16621,22 @@
         <v>1041</v>
       </c>
       <c r="B523" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C523" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D523" s="2">
-        <v>15.0</v>
+        <v>21.0</v>
       </c>
       <c r="E523" s="2" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F523" s="3" t="s">
         <v>1042</v>
       </c>
-      <c r="F523" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G523" s="7">
-        <v>46424.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H523" s="2"/>
     </row>
@@ -16587,10 +16657,10 @@
         <v>1044</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="G524" s="7">
-        <v>46480.0</v>
+        <v>46886.0</v>
       </c>
       <c r="H524" s="2"/>
     </row>
@@ -16608,19 +16678,19 @@
         <v>21.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>687</v>
+        <v>946</v>
       </c>
       <c r="G525" s="7">
-        <v>47074.0</v>
+        <v>46913.0</v>
       </c>
       <c r="H525" s="2"/>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>45</v>
@@ -16632,91 +16702,91 @@
         <v>21.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1046</v>
+        <v>397</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G526" s="7">
-        <v>46792.0</v>
+        <v>47158.0</v>
       </c>
       <c r="H526" s="2"/>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B527" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C527" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D527" s="2">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1050</v>
+        <v>344</v>
       </c>
       <c r="F527" s="3" t="s">
-        <v>944</v>
+        <v>80</v>
       </c>
       <c r="G527" s="7">
-        <v>46886.0</v>
+        <v>46607.0</v>
       </c>
       <c r="H527" s="2"/>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B528" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C528" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D528" s="2">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="E528" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F528" s="3" t="s">
         <v>1050</v>
       </c>
-      <c r="F528" s="3" t="s">
-        <v>946</v>
-      </c>
       <c r="G528" s="7">
-        <v>46913.0</v>
+        <v>46628.0</v>
       </c>
       <c r="H528" s="2"/>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B529" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C529" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D529" s="2">
-        <v>21.0</v>
+        <v>10.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>397</v>
+        <v>344</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G529" s="7">
-        <v>47158.0</v>
+        <v>46649.0</v>
       </c>
       <c r="H529" s="2"/>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>34</v>
@@ -16731,10 +16801,10 @@
         <v>344</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>80</v>
+        <v>1054</v>
       </c>
       <c r="G530" s="7">
-        <v>46607.0</v>
+        <v>46649.0</v>
       </c>
       <c r="H530" s="2"/>
     </row>
@@ -16758,7 +16828,7 @@
         <v>1056</v>
       </c>
       <c r="G531" s="7">
-        <v>46628.0</v>
+        <v>46775.0</v>
       </c>
       <c r="H531" s="2"/>
     </row>
@@ -16779,16 +16849,16 @@
         <v>344</v>
       </c>
       <c r="F532" s="3" t="s">
-        <v>1058</v>
+        <v>360</v>
       </c>
       <c r="G532" s="7">
-        <v>46649.0</v>
+        <v>46775.0</v>
       </c>
       <c r="H532" s="2"/>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>34</v>
@@ -16803,16 +16873,16 @@
         <v>344</v>
       </c>
       <c r="F533" s="3" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="G533" s="7">
-        <v>46649.0</v>
+        <v>46859.0</v>
       </c>
       <c r="H533" s="2"/>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>34</v>
@@ -16827,16 +16897,16 @@
         <v>344</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="G534" s="7">
-        <v>46775.0</v>
+        <v>46880.0</v>
       </c>
       <c r="H534" s="2"/>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>34</v>
@@ -16848,13 +16918,13 @@
         <v>10.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F535" s="3" t="s">
-        <v>360</v>
+        <v>1063</v>
       </c>
       <c r="G535" s="7">
-        <v>46775.0</v>
+        <v>46421.0</v>
       </c>
       <c r="H535" s="2"/>
     </row>
@@ -16872,19 +16942,19 @@
         <v>10.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F536" s="3" t="s">
-        <v>1065</v>
+        <v>204</v>
       </c>
       <c r="G536" s="7">
-        <v>46859.0</v>
+        <v>46596.0</v>
       </c>
       <c r="H536" s="2"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>34</v>
@@ -16896,19 +16966,19 @@
         <v>10.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>1067</v>
+        <v>87</v>
       </c>
       <c r="G537" s="7">
-        <v>46880.0</v>
+        <v>46613.0</v>
       </c>
       <c r="H537" s="2"/>
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>34</v>
@@ -16923,16 +16993,16 @@
         <v>352</v>
       </c>
       <c r="F538" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="G538" s="7">
-        <v>46421.0</v>
+        <v>46725.0</v>
       </c>
       <c r="H538" s="2"/>
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>34</v>
@@ -16947,16 +17017,16 @@
         <v>352</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>204</v>
+        <v>1069</v>
       </c>
       <c r="G539" s="7">
-        <v>46596.0</v>
+        <v>46635.0</v>
       </c>
       <c r="H539" s="2"/>
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>34</v>
@@ -16968,13 +17038,13 @@
         <v>10.0</v>
       </c>
       <c r="E540" s="2" t="s">
-        <v>352</v>
+        <v>1071</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>87</v>
+        <v>974</v>
       </c>
       <c r="G540" s="7">
-        <v>46613.0</v>
+        <v>46953.0</v>
       </c>
       <c r="H540" s="2"/>
     </row>
@@ -16983,70 +17053,70 @@
         <v>1072</v>
       </c>
       <c r="B541" s="2" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="C541" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D541" s="2">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>352</v>
+        <v>1073</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="G541" s="7">
-        <v>46725.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H541" s="2"/>
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B542" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C542" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D542" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E542" s="2" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F542" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="B542" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C542" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D542" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E542" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F542" s="3" t="s">
-        <v>1075</v>
-      </c>
       <c r="G542" s="7">
-        <v>46635.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H542" s="2"/>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B543" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C543" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D543" s="2">
+        <v>8.0</v>
+      </c>
+      <c r="E543" s="2" t="s">
         <v>1076</v>
       </c>
-      <c r="B543" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C543" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D543" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E543" s="2" t="s">
-        <v>1077</v>
-      </c>
       <c r="F543" s="3" t="s">
-        <v>980</v>
+        <v>1074</v>
       </c>
       <c r="G543" s="7">
-        <v>46953.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H543" s="2"/>
     </row>
@@ -17061,22 +17131,22 @@
         <v>12</v>
       </c>
       <c r="D544" s="2">
-        <v>6.0</v>
+        <v>9.0</v>
       </c>
       <c r="E544" s="2" t="s">
         <v>1079</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1080</v>
+        <v>726</v>
       </c>
       <c r="G544" s="7">
-        <v>46333.0</v>
+        <v>46941.0</v>
       </c>
       <c r="H544" s="2"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>701</v>
@@ -17085,22 +17155,24 @@
         <v>12</v>
       </c>
       <c r="D545" s="2">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F545" s="3" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="G545" s="7">
-        <v>46333.0</v>
-      </c>
-      <c r="H545" s="2"/>
+        <v>46324.0</v>
+      </c>
+      <c r="H545" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>701</v>
@@ -17109,192 +17181,190 @@
         <v>12</v>
       </c>
       <c r="D546" s="2">
-        <v>8.0</v>
+        <v>3.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>1080</v>
+        <v>703</v>
       </c>
       <c r="G546" s="7">
-        <v>46333.0</v>
-      </c>
-      <c r="H546" s="2"/>
+        <v>46349.0</v>
+      </c>
+      <c r="H546" s="2" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
         <v>1084</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C547" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D547" s="2">
-        <v>9.0</v>
+        <v>7.0</v>
       </c>
       <c r="E547" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="F547" s="3">
+        <v>11508.0</v>
+      </c>
+      <c r="G547" s="7">
+        <v>46967.0</v>
+      </c>
+      <c r="H547" s="2" t="s">
         <v>1085</v>
       </c>
-      <c r="F547" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="G547" s="7">
-        <v>46941.0</v>
-      </c>
-      <c r="H547" s="2"/>
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
         <v>1086</v>
       </c>
       <c r="B548" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C548" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D548" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E548" s="2" t="s">
         <v>1087</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>1080</v>
+        <v>1024</v>
       </c>
       <c r="G548" s="7">
-        <v>46324.0</v>
-      </c>
-      <c r="H548" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>46544.0</v>
+      </c>
+      <c r="H548" s="2"/>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
         <v>1088</v>
       </c>
       <c r="B549" s="2" t="s">
-        <v>701</v>
+        <v>1089</v>
       </c>
       <c r="C549" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D549" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>703</v>
+        <v>1024</v>
       </c>
       <c r="G549" s="7">
-        <v>46349.0</v>
+        <v>46949.0</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>241</v>
+        <v>138</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B550" s="2" t="s">
-        <v>45</v>
+        <v>1089</v>
       </c>
       <c r="C550" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D550" s="2">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>987</v>
-      </c>
-      <c r="F550" s="3">
-        <v>11508.0</v>
+        <v>1092</v>
+      </c>
+      <c r="F550" s="3" t="s">
+        <v>1024</v>
       </c>
       <c r="G550" s="7">
-        <v>46967.0</v>
-      </c>
-      <c r="H550" s="2" t="s">
-        <v>1091</v>
-      </c>
+        <v>46793.0</v>
+      </c>
+      <c r="H550" s="2"/>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B551" s="2" t="s">
-        <v>45</v>
+        <v>1089</v>
       </c>
       <c r="C551" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D551" s="2">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F551" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G551" s="7">
-        <v>46544.0</v>
+        <v>46767.0</v>
       </c>
       <c r="H551" s="2"/>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B552" s="2" t="s">
-        <v>1095</v>
+        <v>45</v>
       </c>
       <c r="C552" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D552" s="2">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="E552" s="2" t="s">
         <v>1096</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G552" s="7">
-        <v>46949.0</v>
-      </c>
-      <c r="H552" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>46662.0</v>
+      </c>
+      <c r="H552" s="2"/>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
         <v>1097</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>1095</v>
+        <v>45</v>
       </c>
       <c r="C553" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D553" s="2">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="E553" s="2" t="s">
         <v>1098</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="G553" s="7">
-        <v>46793.0</v>
+        <v>46711.0</v>
       </c>
       <c r="H553" s="2"/>
     </row>
@@ -17303,22 +17373,22 @@
         <v>1099</v>
       </c>
       <c r="B554" s="2" t="s">
-        <v>1095</v>
+        <v>34</v>
       </c>
       <c r="C554" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D554" s="2">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
       <c r="E554" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F554" s="3" t="s">
         <v>1100</v>
       </c>
-      <c r="F554" s="3" t="s">
-        <v>1030</v>
-      </c>
       <c r="G554" s="7">
-        <v>46767.0</v>
+        <v>46908.0</v>
       </c>
       <c r="H554" s="2"/>
     </row>
@@ -17327,46 +17397,46 @@
         <v>1101</v>
       </c>
       <c r="B555" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C555" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D555" s="2">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1102</v>
+        <v>679</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>1030</v>
+        <v>1100</v>
       </c>
       <c r="G555" s="7">
-        <v>46662.0</v>
+        <v>46911.0</v>
       </c>
       <c r="H555" s="2"/>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B556" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C556" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D556" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E556" s="2" t="s">
         <v>1103</v>
       </c>
-      <c r="B556" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C556" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D556" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E556" s="2" t="s">
+      <c r="F556" s="3" t="s">
         <v>1104</v>
       </c>
-      <c r="F556" s="3" t="s">
-        <v>1030</v>
-      </c>
       <c r="G556" s="7">
-        <v>46711.0</v>
+        <v>46463.0</v>
       </c>
       <c r="H556" s="2"/>
     </row>
@@ -17375,22 +17445,22 @@
         <v>1105</v>
       </c>
       <c r="B557" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C557" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D557" s="2">
-        <v>15.0</v>
+        <v>8.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>350</v>
+        <v>1106</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="G557" s="7">
-        <v>46908.0</v>
+        <v>46432.0</v>
       </c>
       <c r="H557" s="2"/>
     </row>
@@ -17399,22 +17469,22 @@
         <v>1107</v>
       </c>
       <c r="B558" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C558" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D558" s="2">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>679</v>
+        <v>1106</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1106</v>
+        <v>594</v>
       </c>
       <c r="G558" s="7">
-        <v>46911.0</v>
+        <v>46484.0</v>
       </c>
       <c r="H558" s="2"/>
     </row>
@@ -17423,28 +17493,28 @@
         <v>1108</v>
       </c>
       <c r="B559" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C559" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D559" s="2">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1109</v>
+        <v>1106</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>1110</v>
+        <v>418</v>
       </c>
       <c r="G559" s="7">
-        <v>46463.0</v>
+        <v>46488.0</v>
       </c>
       <c r="H559" s="2"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>45</v>
@@ -17456,19 +17526,19 @@
         <v>8.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="F560" s="3" t="s">
         <v>1110</v>
       </c>
       <c r="G560" s="7">
-        <v>46432.0</v>
+        <v>46551.0</v>
       </c>
       <c r="H560" s="2"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>45</v>
@@ -17480,19 +17550,19 @@
         <v>8.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>594</v>
+        <v>400</v>
       </c>
       <c r="G561" s="7">
-        <v>46484.0</v>
+        <v>46768.0</v>
       </c>
       <c r="H561" s="2"/>
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>45</v>
@@ -17504,91 +17574,91 @@
         <v>8.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>418</v>
+        <v>1059</v>
       </c>
       <c r="G562" s="7">
-        <v>46488.0</v>
+        <v>46877.0</v>
       </c>
       <c r="H562" s="2"/>
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="B563" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C563" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D563" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1116</v>
+        <v>118</v>
       </c>
       <c r="G563" s="7">
-        <v>46551.0</v>
+        <v>46477.0</v>
       </c>
       <c r="H563" s="2"/>
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="B564" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C564" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D564" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="G564" s="7">
-        <v>46768.0</v>
+        <v>46484.0</v>
       </c>
       <c r="H564" s="2"/>
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="B565" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C565" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D565" s="2">
-        <v>8.0</v>
+        <v>19.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>1065</v>
+        <v>1110</v>
       </c>
       <c r="G565" s="7">
-        <v>46877.0</v>
+        <v>46551.0</v>
       </c>
       <c r="H565" s="2"/>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>34</v>
@@ -17600,19 +17670,19 @@
         <v>19.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>118</v>
+        <v>1118</v>
       </c>
       <c r="G566" s="7">
-        <v>46477.0</v>
+        <v>46578.0</v>
       </c>
       <c r="H566" s="2"/>
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1121</v>
+        <v>1119</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>34</v>
@@ -17624,19 +17694,19 @@
         <v>19.0</v>
       </c>
       <c r="E567" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F567" s="3" t="s">
         <v>1120</v>
       </c>
-      <c r="F567" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="G567" s="7">
-        <v>46484.0</v>
+        <v>46624.0</v>
       </c>
       <c r="H567" s="2"/>
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>34</v>
@@ -17648,13 +17718,13 @@
         <v>19.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="F568" s="3" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="G568" s="7">
-        <v>46551.0</v>
+        <v>46624.0</v>
       </c>
       <c r="H568" s="2"/>
     </row>
@@ -17672,13 +17742,13 @@
         <v>19.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="F569" s="3" t="s">
         <v>1124</v>
       </c>
       <c r="G569" s="7">
-        <v>46578.0</v>
+        <v>46743.0</v>
       </c>
       <c r="H569" s="2"/>
     </row>
@@ -17696,13 +17766,13 @@
         <v>19.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="F570" s="3" t="s">
         <v>1126</v>
       </c>
       <c r="G570" s="7">
-        <v>46624.0</v>
+        <v>46813.0</v>
       </c>
       <c r="H570" s="2"/>
     </row>
@@ -17720,13 +17790,13 @@
         <v>19.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1128</v>
+        <v>944</v>
       </c>
       <c r="G571" s="7">
-        <v>46624.0</v>
+        <v>46688.0</v>
       </c>
       <c r="H571" s="2"/>
     </row>
@@ -17744,37 +17814,37 @@
         <v>19.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="F572" s="3" t="s">
-        <v>1130</v>
+        <v>1042</v>
       </c>
       <c r="G572" s="7">
-        <v>46743.0</v>
+        <v>46745.0</v>
       </c>
       <c r="H572" s="2"/>
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B573" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C573" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D573" s="2">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1120</v>
+        <v>1131</v>
       </c>
       <c r="F573" s="3" t="s">
         <v>1132</v>
       </c>
       <c r="G573" s="7">
-        <v>46813.0</v>
+        <v>46578.0</v>
       </c>
       <c r="H573" s="2"/>
     </row>
@@ -17783,22 +17853,22 @@
         <v>1133</v>
       </c>
       <c r="B574" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C574" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D574" s="2">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="E574" s="2" t="s">
         <v>1134</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>944</v>
+        <v>594</v>
       </c>
       <c r="G574" s="7">
-        <v>46688.0</v>
+        <v>46484.0</v>
       </c>
       <c r="H574" s="2"/>
     </row>
@@ -17807,22 +17877,22 @@
         <v>1135</v>
       </c>
       <c r="B575" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C575" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D575" s="2">
-        <v>19.0</v>
+        <v>8.0</v>
       </c>
       <c r="E575" s="2" t="s">
         <v>1134</v>
       </c>
       <c r="F575" s="3" t="s">
-        <v>1048</v>
+        <v>418</v>
       </c>
       <c r="G575" s="7">
-        <v>46745.0</v>
+        <v>46488.0</v>
       </c>
       <c r="H575" s="2"/>
     </row>
@@ -17840,19 +17910,19 @@
         <v>8.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1138</v>
+        <v>1122</v>
       </c>
       <c r="G576" s="7">
-        <v>46578.0</v>
+        <v>46613.0</v>
       </c>
       <c r="H576" s="2"/>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>45</v>
@@ -17864,19 +17934,19 @@
         <v>8.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>594</v>
+        <v>1069</v>
       </c>
       <c r="G577" s="7">
-        <v>46484.0</v>
+        <v>46635.0</v>
       </c>
       <c r="H577" s="2"/>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1141</v>
+        <v>1138</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>45</v>
@@ -17888,19 +17958,19 @@
         <v>8.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="F578" s="3" t="s">
-        <v>418</v>
+        <v>1067</v>
       </c>
       <c r="G578" s="7">
-        <v>46488.0</v>
+        <v>46725.0</v>
       </c>
       <c r="H578" s="2"/>
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1142</v>
+        <v>1139</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>45</v>
@@ -17915,16 +17985,16 @@
         <v>1140</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1128</v>
+        <v>1069</v>
       </c>
       <c r="G579" s="7">
-        <v>46613.0</v>
+        <v>46635.0</v>
       </c>
       <c r="H579" s="2"/>
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>45</v>
@@ -17939,16 +18009,16 @@
         <v>1140</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1075</v>
+        <v>1067</v>
       </c>
       <c r="G580" s="7">
-        <v>46635.0</v>
+        <v>46725.0</v>
       </c>
       <c r="H580" s="2"/>
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>45</v>
@@ -17963,16 +18033,16 @@
         <v>1140</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1073</v>
+        <v>1124</v>
       </c>
       <c r="G581" s="7">
-        <v>46725.0</v>
+        <v>46743.0</v>
       </c>
       <c r="H581" s="2"/>
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>45</v>
@@ -17984,19 +18054,19 @@
         <v>8.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1075</v>
+        <v>1056</v>
       </c>
       <c r="G582" s="7">
-        <v>46635.0</v>
+        <v>46743.0</v>
       </c>
       <c r="H582" s="2"/>
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1147</v>
+        <v>1144</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>45</v>
@@ -18008,19 +18078,19 @@
         <v>8.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1073</v>
+        <v>944</v>
       </c>
       <c r="G583" s="7">
-        <v>46725.0</v>
+        <v>46834.0</v>
       </c>
       <c r="H583" s="2"/>
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1148</v>
+        <v>1145</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>45</v>
@@ -18032,19 +18102,19 @@
         <v>8.0</v>
       </c>
       <c r="E584" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F584" s="3" t="s">
         <v>1146</v>
       </c>
-      <c r="F584" s="3" t="s">
-        <v>1130</v>
-      </c>
       <c r="G584" s="7">
-        <v>46743.0</v>
+        <v>46872.0</v>
       </c>
       <c r="H584" s="2"/>
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>45</v>
@@ -18053,40 +18123,40 @@
         <v>27</v>
       </c>
       <c r="D585" s="2">
-        <v>8.0</v>
+        <v>21.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F585" s="3" t="s">
-        <v>1062</v>
+        <v>730</v>
+      </c>
+      <c r="F585" s="3">
+        <v>11506.0</v>
       </c>
       <c r="G585" s="7">
-        <v>46743.0</v>
+        <v>46877.0</v>
       </c>
       <c r="H585" s="2"/>
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B586" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C586" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D586" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E586" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F586" s="3" t="s">
         <v>1150</v>
       </c>
-      <c r="B586" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C586" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D586" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E586" s="2" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F586" s="3" t="s">
-        <v>944</v>
-      </c>
       <c r="G586" s="7">
-        <v>46834.0</v>
+        <v>46365.0</v>
       </c>
       <c r="H586" s="2"/>
     </row>
@@ -18095,22 +18165,22 @@
         <v>1151</v>
       </c>
       <c r="B587" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C587" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D587" s="2">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="G587" s="7">
-        <v>46872.0</v>
+        <v>46363.0</v>
       </c>
       <c r="H587" s="2"/>
     </row>
@@ -18119,122 +18189,122 @@
         <v>1153</v>
       </c>
       <c r="B588" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C588" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D588" s="2">
-        <v>21.0</v>
+        <v>13.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="F588" s="3">
-        <v>11506.0</v>
+        <v>1154</v>
+      </c>
+      <c r="F588" s="3" t="s">
+        <v>1155</v>
       </c>
       <c r="G588" s="7">
-        <v>46877.0</v>
+        <v>46332.0</v>
       </c>
       <c r="H588" s="2"/>
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>701</v>
+        <v>34</v>
       </c>
       <c r="C589" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D589" s="2">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="G589" s="7">
-        <v>46365.0</v>
-      </c>
-      <c r="H589" s="2"/>
+        <v>46926.0</v>
+      </c>
+      <c r="H589" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D590" s="2">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1156</v>
+        <v>743</v>
       </c>
       <c r="G590" s="7">
-        <v>46363.0</v>
+        <v>46457.0</v>
       </c>
       <c r="H590" s="2"/>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B591" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C591" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D591" s="2">
-        <v>13.0</v>
+        <v>16.0</v>
       </c>
       <c r="E591" s="2" t="s">
         <v>1160</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="G591" s="7">
-        <v>46332.0</v>
+        <v>46457.0</v>
       </c>
       <c r="H591" s="2"/>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B592" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C592" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D592" s="2">
-        <v>11.0</v>
+        <v>8.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1164</v>
+        <v>156</v>
       </c>
       <c r="G592" s="7">
-        <v>46926.0</v>
-      </c>
-      <c r="H592" s="2" t="s">
-        <v>138</v>
-      </c>
+        <v>46781.0</v>
+      </c>
+      <c r="H592" s="2"/>
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
@@ -18247,22 +18317,20 @@
         <v>27</v>
       </c>
       <c r="D593" s="2">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1166</v>
+        <v>943</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="G593" s="7">
-        <v>46457.0</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="G593" s="7"/>
       <c r="H593" s="2"/>
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>45</v>
@@ -18271,22 +18339,20 @@
         <v>27</v>
       </c>
       <c r="D594" s="2">
-        <v>16.0</v>
+        <v>9.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1166</v>
+        <v>943</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G594" s="7">
-        <v>46457.0</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="G594" s="7"/>
       <c r="H594" s="2"/>
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>45</v>
@@ -18295,22 +18361,22 @@
         <v>12</v>
       </c>
       <c r="D595" s="2">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>156</v>
+        <v>1169</v>
       </c>
       <c r="G595" s="7">
-        <v>46781.0</v>
+        <v>46397.0</v>
       </c>
       <c r="H595" s="2"/>
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>45</v>
@@ -18319,20 +18385,22 @@
         <v>27</v>
       </c>
       <c r="D596" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>943</v>
+        <v>874</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="G596" s="7"/>
+        <v>1132</v>
+      </c>
+      <c r="G596" s="7">
+        <v>46578.0</v>
+      </c>
       <c r="H596" s="2"/>
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>45</v>
@@ -18341,44 +18409,46 @@
         <v>27</v>
       </c>
       <c r="D597" s="2">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>943</v>
+        <v>874</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>687</v>
-      </c>
-      <c r="G597" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="G597" s="7">
+        <v>46613.0</v>
+      </c>
       <c r="H597" s="2"/>
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C598" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D598" s="2">
-        <v>22.0</v>
+        <v>10.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1174</v>
+        <v>874</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1175</v>
+        <v>1069</v>
       </c>
       <c r="G598" s="7">
-        <v>46397.0</v>
+        <v>46635.0</v>
       </c>
       <c r="H598" s="2"/>
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>45</v>
@@ -18393,16 +18463,16 @@
         <v>874</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1138</v>
+        <v>1067</v>
       </c>
       <c r="G599" s="7">
-        <v>46578.0</v>
+        <v>46725.0</v>
       </c>
       <c r="H599" s="2"/>
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>45</v>
@@ -18417,83 +18487,79 @@
         <v>874</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>87</v>
+        <v>400</v>
       </c>
       <c r="G600" s="7">
-        <v>46613.0</v>
+        <v>46768.0</v>
       </c>
       <c r="H600" s="2"/>
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C601" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D601" s="2">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>874</v>
+        <v>1176</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1075</v>
+        <v>274</v>
       </c>
       <c r="G601" s="7">
-        <v>46635.0</v>
+        <v>46934.0</v>
       </c>
       <c r="H601" s="2"/>
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="D602" s="2">
-        <v>10.0</v>
+        <v>18.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>874</v>
+        <v>1178</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1073</v>
-      </c>
-      <c r="G602" s="7">
-        <v>46725.0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G602" s="7"/>
       <c r="H602" s="2"/>
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B603" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C603" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D603" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E603" s="2" t="s">
         <v>1180</v>
       </c>
-      <c r="B603" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C603" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D603" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E603" s="2" t="s">
-        <v>874</v>
-      </c>
       <c r="F603" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="G603" s="7">
-        <v>46768.0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G603" s="7"/>
       <c r="H603" s="2"/>
     </row>
     <row r="604">
@@ -18501,23 +18567,21 @@
         <v>1181</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D604" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E604" s="2" t="s">
         <v>1182</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G604" s="7">
-        <v>46934.0</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="G604" s="7"/>
       <c r="H604" s="2"/>
     </row>
     <row r="605">
@@ -18528,132 +18592,132 @@
         <v>34</v>
       </c>
       <c r="C605" s="2" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="D605" s="2">
-        <v>18.0</v>
+        <v>15.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1184</v>
+        <v>1071</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G605" s="7"/>
+        <v>875</v>
+      </c>
+      <c r="G605" s="7">
+        <v>46892.0</v>
+      </c>
       <c r="H605" s="2"/>
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B606" s="2" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="C606" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D606" s="2">
-        <v>18.0</v>
+        <v>16.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1186</v>
+        <v>1017</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G606" s="7"/>
+        <v>703</v>
+      </c>
+      <c r="G606" s="7">
+        <v>46363.0</v>
+      </c>
       <c r="H606" s="2"/>
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C607" s="2" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="D607" s="2">
-        <v>13.0</v>
+        <v>8.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1188</v>
+        <v>861</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>17</v>
+        <v>156</v>
       </c>
       <c r="G607" s="7"/>
       <c r="H607" s="2"/>
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1189</v>
+        <v>1186</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C608" s="2" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="D608" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F608" s="3" t="s">
-        <v>875</v>
-      </c>
-      <c r="G608" s="7">
-        <v>46892.0</v>
-      </c>
+        <v>1187</v>
+      </c>
+      <c r="F608" s="3"/>
+      <c r="G608" s="7"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C609" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D609" s="2">
-        <v>16.0</v>
+        <v>7.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F609" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G609" s="7">
-        <v>46363.0</v>
-      </c>
+        <v>1189</v>
+      </c>
+      <c r="F609" s="3">
+        <v>11507.0</v>
+      </c>
+      <c r="G609" s="7"/>
       <c r="H609" s="2"/>
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B610" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C610" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D610" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E610" s="2" t="s">
         <v>1191</v>
       </c>
-      <c r="B610" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C610" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D610" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="E610" s="2" t="s">
-        <v>861</v>
-      </c>
-      <c r="F610" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="G610" s="7"/>
+      <c r="F610" s="3">
+        <v>11508.0</v>
+      </c>
+      <c r="G610" s="7">
+        <v>46947.0</v>
+      </c>
       <c r="H610" s="2"/>
     </row>
     <row r="611">
@@ -18664,15 +18728,17 @@
         <v>34</v>
       </c>
       <c r="C611" s="2" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="D611" s="2">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="E611" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="F611" s="3" t="s">
         <v>1193</v>
       </c>
-      <c r="F611" s="3"/>
       <c r="G611" s="7"/>
       <c r="H611" s="2"/>
     </row>
@@ -18687,112 +18753,110 @@
         <v>29</v>
       </c>
       <c r="D612" s="2">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F612" s="3">
-        <v>11507.0</v>
+        <v>1164</v>
+      </c>
+      <c r="F612" s="3" t="s">
+        <v>156</v>
       </c>
       <c r="G612" s="7"/>
       <c r="H612" s="2"/>
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C613" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D613" s="2">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F613" s="3">
-        <v>11508.0</v>
+        <v>338</v>
+      </c>
+      <c r="F613" s="3" t="s">
+        <v>274</v>
       </c>
       <c r="G613" s="7">
-        <v>46947.0</v>
+        <v>46929.0</v>
       </c>
       <c r="H613" s="2"/>
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C614" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D614" s="2">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>602</v>
+        <v>1197</v>
       </c>
       <c r="F614" s="3" t="s">
-        <v>1199</v>
+        <v>1024</v>
       </c>
       <c r="G614" s="7"/>
       <c r="H614" s="2"/>
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C615" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D615" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>156</v>
+        <v>1024</v>
       </c>
       <c r="G615" s="7"/>
       <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D616" s="2">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>338</v>
+        <v>1200</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G616" s="7">
-        <v>46929.0</v>
-      </c>
+        <v>1024</v>
+      </c>
+      <c r="G616" s="7"/>
       <c r="H616" s="2"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>45</v>
@@ -18804,17 +18868,19 @@
         <v>11.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>1203</v>
+        <v>1200</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G617" s="7"/>
+        <v>921</v>
+      </c>
+      <c r="G617" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>45</v>
@@ -18826,17 +18892,19 @@
         <v>11.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G618" s="7"/>
+        <v>921</v>
+      </c>
+      <c r="G618" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>45</v>
@@ -18848,17 +18916,19 @@
         <v>11.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G619" s="7"/>
+        <v>1024</v>
+      </c>
+      <c r="G619" s="7">
+        <v>46767.0</v>
+      </c>
       <c r="H619" s="2"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>45</v>
@@ -18873,16 +18943,16 @@
         <v>1206</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>921</v>
+        <v>1024</v>
       </c>
       <c r="G620" s="7">
-        <v>46792.0</v>
+        <v>46711.0</v>
       </c>
       <c r="H620" s="2"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>45</v>
@@ -18891,22 +18961,20 @@
         <v>12</v>
       </c>
       <c r="D621" s="2">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F621" s="3" t="s">
-        <v>921</v>
-      </c>
-      <c r="G621" s="7">
-        <v>46792.0</v>
-      </c>
-      <c r="H621" s="2"/>
+        <v>1208</v>
+      </c>
+      <c r="F621" s="3"/>
+      <c r="G621" s="7"/>
+      <c r="H621" s="2" t="s">
+        <v>1209</v>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>45</v>
@@ -18914,18 +18982,10 @@
       <c r="C622" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D622" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E622" s="2" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F622" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G622" s="7">
-        <v>46767.0</v>
-      </c>
+      <c r="D622" s="2"/>
+      <c r="E622" s="2"/>
+      <c r="F622" s="3"/>
+      <c r="G622" s="7"/>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
@@ -18938,61 +18998,59 @@
       <c r="C623" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D623" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E623" s="2" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F623" s="3" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G623" s="7">
-        <v>46711.0</v>
-      </c>
+      <c r="D623" s="2"/>
+      <c r="E623" s="2"/>
+      <c r="F623" s="3"/>
+      <c r="G623" s="7"/>
       <c r="H623" s="2"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B624" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C624" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D624" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E624" s="2" t="s">
         <v>1213</v>
       </c>
-      <c r="B624" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C624" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D624" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E624" s="2" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F624" s="3"/>
+      <c r="F624" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G624" s="7"/>
-      <c r="H624" s="2" t="s">
-        <v>1215</v>
-      </c>
+      <c r="H624" s="2"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D625" s="2"/>
-      <c r="E625" s="2"/>
-      <c r="F625" s="3"/>
+        <v>27</v>
+      </c>
+      <c r="D625" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="E625" s="2" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F625" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="G625" s="7"/>
       <c r="H625" s="2"/>
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>45</v>
@@ -19008,62 +19066,74 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D627" s="2">
-        <v>18.0</v>
+        <v>5.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1219</v>
+        <v>836</v>
       </c>
       <c r="F627" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G627" s="7"/>
+        <v>156</v>
+      </c>
+      <c r="G627" s="7">
+        <v>46884.0</v>
+      </c>
       <c r="H627" s="2"/>
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B628" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C628" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D628" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E628" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F628" s="3" t="s">
         <v>1220</v>
       </c>
-      <c r="B628" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C628" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D628" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="E628" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F628" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G628" s="7"/>
+      <c r="G628" s="7">
+        <v>46620.0</v>
+      </c>
       <c r="H628" s="2"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D629" s="2"/>
-      <c r="E629" s="2"/>
-      <c r="F629" s="3"/>
-      <c r="G629" s="7"/>
+        <v>29</v>
+      </c>
+      <c r="D629" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E629" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="F629" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G629" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H629" s="2"/>
     </row>
     <row r="630">
@@ -19071,187 +19141,187 @@
         <v>1223</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D630" s="2">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>836</v>
+        <v>1224</v>
       </c>
       <c r="F630" s="3" t="s">
-        <v>156</v>
+        <v>1225</v>
       </c>
       <c r="G630" s="7">
-        <v>46884.0</v>
+        <v>46670.0</v>
       </c>
       <c r="H630" s="2"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D631" s="2">
-        <v>19.0</v>
+        <v>15.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G631" s="7">
-        <v>46620.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H631" s="2"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C632" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D632" s="2">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>894</v>
+        <v>1230</v>
       </c>
       <c r="F632" s="3" t="s">
         <v>1228</v>
       </c>
       <c r="G632" s="7">
-        <v>46792.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H632" s="2"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="B633" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C633" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D633" s="2">
-        <v>20.0</v>
+        <v>15.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1230</v>
+        <v>1028</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G633" s="7">
-        <v>46670.0</v>
-      </c>
+        <v>1232</v>
+      </c>
+      <c r="G633" s="7"/>
       <c r="H633" s="2"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B634" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C634" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D634" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E634" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F634" s="3" t="s">
         <v>1232</v>
       </c>
-      <c r="B634" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C634" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D634" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E634" s="2" t="s">
-        <v>1233</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G634" s="7">
-        <v>46963.0</v>
-      </c>
+      <c r="G634" s="7"/>
       <c r="H634" s="2"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B635" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C635" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D635" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E635" s="2" t="s">
         <v>1235</v>
       </c>
-      <c r="B635" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C635" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D635" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E635" s="2" t="s">
-        <v>1236</v>
-      </c>
       <c r="F635" s="3" t="s">
-        <v>1234</v>
+        <v>274</v>
       </c>
       <c r="G635" s="7">
-        <v>46963.0</v>
+        <v>47231.0</v>
       </c>
       <c r="H635" s="2"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B636" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C636" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D636" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E636" s="2" t="s">
         <v>1237</v>
       </c>
-      <c r="B636" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C636" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D636" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E636" s="2" t="s">
-        <v>1034</v>
-      </c>
       <c r="F636" s="3" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G636" s="7"/>
+        <v>274</v>
+      </c>
+      <c r="G636" s="7">
+        <v>47231.0</v>
+      </c>
       <c r="H636" s="2"/>
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B637" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C637" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D637" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="E637" s="2" t="s">
         <v>1239</v>
       </c>
-      <c r="B637" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C637" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D637" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E637" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="F637" s="3" t="s">
-        <v>1238</v>
-      </c>
-      <c r="G637" s="7"/>
+        <v>274</v>
+      </c>
+      <c r="G637" s="7">
+        <v>47313.0</v>
+      </c>
       <c r="H637" s="2"/>
     </row>
     <row r="638">
@@ -19274,7 +19344,7 @@
         <v>274</v>
       </c>
       <c r="G638" s="7">
-        <v>47231.0</v>
+        <v>47229.0</v>
       </c>
       <c r="H638" s="2"/>
     </row>
@@ -19298,7 +19368,7 @@
         <v>274</v>
       </c>
       <c r="G639" s="7">
-        <v>47231.0</v>
+        <v>47248.0</v>
       </c>
       <c r="H639" s="2"/>
     </row>
@@ -19307,22 +19377,22 @@
         <v>1244</v>
       </c>
       <c r="B640" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="C640" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D640" s="2">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="E640" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F640" s="3" t="s">
         <v>1245</v>
       </c>
-      <c r="F640" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="G640" s="7">
-        <v>47313.0</v>
+        <v>46461.0</v>
       </c>
       <c r="H640" s="2"/>
     </row>
@@ -19331,22 +19401,22 @@
         <v>1246</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C641" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D641" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E641" s="2" t="s">
         <v>1247</v>
       </c>
       <c r="F641" s="3" t="s">
-        <v>274</v>
+        <v>703</v>
       </c>
       <c r="G641" s="7">
-        <v>47229.0</v>
+        <v>46352.0</v>
       </c>
       <c r="H641" s="2"/>
     </row>
@@ -19355,143 +19425,139 @@
         <v>1248</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>45</v>
+        <v>332</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D642" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1249</v>
+        <v>665</v>
       </c>
       <c r="F642" s="3" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="G642" s="7">
-        <v>47248.0</v>
+        <v>46384.0</v>
       </c>
       <c r="H642" s="2"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B643" s="2" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="C643" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D643" s="2">
         <v>1.0</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>339</v>
+        <v>1028</v>
       </c>
       <c r="F643" s="3" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G643" s="7">
-        <v>46461.0</v>
+        <v>46316.0</v>
       </c>
       <c r="H643" s="2"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C644" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D644" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1253</v>
+        <v>679</v>
       </c>
       <c r="F644" s="3" t="s">
-        <v>703</v>
+        <v>1250</v>
       </c>
       <c r="G644" s="7">
-        <v>46352.0</v>
+        <v>46320.0</v>
       </c>
       <c r="H644" s="2"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>332</v>
+        <v>45</v>
       </c>
       <c r="C645" s="2" t="s">
-        <v>12</v>
+        <v>101</v>
       </c>
       <c r="D645" s="2">
-        <v>11.0</v>
+        <v>19.0</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>665</v>
+        <v>1044</v>
       </c>
       <c r="F645" s="3" t="s">
-        <v>263</v>
+        <v>1253</v>
       </c>
       <c r="G645" s="7">
-        <v>46384.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H645" s="2"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C646" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D646" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1034</v>
+        <v>1255</v>
       </c>
       <c r="F646" s="3" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G646" s="7">
-        <v>46316.0</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G646" s="7"/>
       <c r="H646" s="2"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C647" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D647" s="2">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>679</v>
+        <v>1257</v>
       </c>
       <c r="F647" s="3" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G647" s="7">
-        <v>46320.0</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G647" s="7"/>
       <c r="H647" s="2"/>
     </row>
     <row r="648">
@@ -19499,23 +19565,21 @@
         <v>1258</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C648" s="2" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="D648" s="2">
-        <v>19.0</v>
+        <v>3.0</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>1050</v>
+        <v>1259</v>
       </c>
       <c r="F648" s="3" t="s">
-        <v>1259</v>
-      </c>
-      <c r="G648" s="7">
-        <v>46792.0</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G648" s="7"/>
       <c r="H648" s="2"/>
     </row>
     <row r="649">
@@ -19523,18 +19587,20 @@
         <v>1260</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>34</v>
+        <v>701</v>
       </c>
       <c r="C649" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D649" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E649" s="2" t="s">
         <v>1261</v>
       </c>
-      <c r="F649" s="3"/>
+      <c r="F649" s="3" t="s">
+        <v>703</v>
+      </c>
       <c r="G649" s="7"/>
       <c r="H649" s="2"/>
     </row>
@@ -19549,7 +19615,7 @@
         <v>12</v>
       </c>
       <c r="D650" s="2">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="E650" s="2" t="s">
         <v>1263</v>
@@ -19565,21 +19631,23 @@
         <v>1264</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>701</v>
+        <v>34</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D651" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E651" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F651" s="3" t="s">
         <v>1265</v>
       </c>
-      <c r="F651" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G651" s="7"/>
+      <c r="G651" s="7">
+        <v>46982.0</v>
+      </c>
       <c r="H651" s="2"/>
     </row>
     <row r="652">
@@ -19587,21 +19655,23 @@
         <v>1266</v>
       </c>
       <c r="B652" s="2" t="s">
-        <v>701</v>
+        <v>34</v>
       </c>
       <c r="C652" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D652" s="2">
-        <v>3.0</v>
+        <v>10.0</v>
       </c>
       <c r="E652" s="2" t="s">
         <v>1267</v>
       </c>
       <c r="F652" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G652" s="7"/>
+        <v>1265</v>
+      </c>
+      <c r="G652" s="7">
+        <v>46914.0</v>
+      </c>
       <c r="H652" s="2"/>
     </row>
     <row r="653">
@@ -19609,21 +19679,23 @@
         <v>1268</v>
       </c>
       <c r="B653" s="2" t="s">
-        <v>701</v>
+        <v>34</v>
       </c>
       <c r="C653" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D653" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E653" s="2" t="s">
         <v>1269</v>
       </c>
       <c r="F653" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G653" s="7"/>
+        <v>1265</v>
+      </c>
+      <c r="G653" s="7">
+        <v>46914.0</v>
+      </c>
       <c r="H653" s="2"/>
     </row>
     <row r="654">
@@ -19631,21 +19703,23 @@
         <v>1270</v>
       </c>
       <c r="B654" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C654" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D654" s="2">
-        <v>2.0</v>
+        <v>15.0</v>
       </c>
       <c r="E654" s="2" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F654" s="3" t="s">
         <v>1271</v>
       </c>
-      <c r="F654" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="G654" s="7"/>
+      <c r="G654" s="7">
+        <v>46963.0</v>
+      </c>
       <c r="H654" s="2"/>
     </row>
     <row r="655">
@@ -19653,76 +19727,76 @@
         <v>1272</v>
       </c>
       <c r="B655" s="2" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C655" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D655" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1163</v>
+        <v>1032</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G655" s="7">
-        <v>46982.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H655" s="2"/>
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D656" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E656" s="2" t="s">
         <v>1274</v>
       </c>
-      <c r="B656" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C656" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D656" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E656" s="2" t="s">
-        <v>1275</v>
-      </c>
       <c r="F656" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G656" s="7">
-        <v>46914.0</v>
+        <v>46421.0</v>
       </c>
       <c r="H656" s="2"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D657" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E657" s="2" t="s">
         <v>1276</v>
       </c>
-      <c r="B657" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C657" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D657" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="E657" s="2" t="s">
-        <v>1277</v>
-      </c>
       <c r="F657" s="3" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="G657" s="7">
-        <v>46914.0</v>
+        <v>46710.0</v>
       </c>
       <c r="H657" s="2"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>45</v>
@@ -19731,70 +19805,70 @@
         <v>12</v>
       </c>
       <c r="D658" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1036</v>
+        <v>1276</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G658" s="7">
-        <v>46963.0</v>
+        <v>46722.0</v>
       </c>
       <c r="H658" s="2"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C659" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D659" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1038</v>
+        <v>899</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G659" s="7">
-        <v>46963.0</v>
+        <v>46620.0</v>
       </c>
       <c r="H659" s="2"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C660" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D660" s="2">
-        <v>11.0</v>
+        <v>16.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1282</v>
+        <v>1160</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G660" s="7">
-        <v>46421.0</v>
+        <v>46757.0</v>
       </c>
       <c r="H660" s="2"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1283</v>
+        <v>1280</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>45</v>
@@ -19806,19 +19880,19 @@
         <v>12.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1284</v>
+        <v>1281</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G661" s="7">
-        <v>46710.0</v>
+        <v>46757.0</v>
       </c>
       <c r="H661" s="2"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1285</v>
+        <v>1282</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>45</v>
@@ -19827,46 +19901,46 @@
         <v>12</v>
       </c>
       <c r="D662" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1284</v>
+        <v>1023</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G662" s="7">
-        <v>46722.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H662" s="2"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1286</v>
+        <v>1283</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C663" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D663" s="2">
-        <v>15.0</v>
+        <v>11.0</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>899</v>
+        <v>1284</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G663" s="7">
-        <v>46620.0</v>
+        <v>46911.0</v>
       </c>
       <c r="H663" s="2"/>
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>45</v>
@@ -19875,64 +19949,64 @@
         <v>27</v>
       </c>
       <c r="D664" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1166</v>
+        <v>1286</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G664" s="7">
-        <v>46757.0</v>
+        <v>46480.0</v>
       </c>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C665" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D665" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="F665" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G665" s="7">
-        <v>46757.0</v>
+        <v>46480.0</v>
       </c>
       <c r="H665" s="2"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C666" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D666" s="2">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1029</v>
+        <v>1290</v>
       </c>
       <c r="F666" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G666" s="7">
-        <v>46530.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H666" s="2"/>
     </row>
@@ -19944,73 +20018,73 @@
         <v>45</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D667" s="2">
-        <v>11.0</v>
+        <v>15.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1292</v>
+        <v>1034</v>
       </c>
       <c r="F667" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G667" s="7">
-        <v>46911.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H667" s="2"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C668" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D668" s="2">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F668" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G668" s="7">
-        <v>46480.0</v>
+        <v>46794.0</v>
       </c>
       <c r="H668" s="2"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C669" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D669" s="2">
-        <v>15.0</v>
+        <v>13.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G669" s="7">
-        <v>46480.0</v>
+        <v>46487.0</v>
       </c>
       <c r="H669" s="2"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>45</v>
@@ -20022,19 +20096,19 @@
         <v>15.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F670" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G670" s="7">
-        <v>46793.0</v>
+        <v>46424.0</v>
       </c>
       <c r="H670" s="2"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>45</v>
@@ -20043,16 +20117,16 @@
         <v>27</v>
       </c>
       <c r="D671" s="2">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1040</v>
+        <v>1299</v>
       </c>
       <c r="F671" s="3" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="G671" s="7">
-        <v>46793.0</v>
+        <v>46757.0</v>
       </c>
       <c r="H671" s="2"/>
     </row>
@@ -20061,100 +20135,84 @@
         <v>1300</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D672" s="2">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1301</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G672" s="7">
-        <v>46794.0</v>
-      </c>
+        <v>1028</v>
+      </c>
+      <c r="F672" s="3"/>
+      <c r="G672" s="7"/>
       <c r="H672" s="2"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D673" s="2">
-        <v>13.0</v>
+        <v>10.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1303</v>
-      </c>
-      <c r="F673" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G673" s="7">
-        <v>46487.0</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="F673" s="3"/>
+      <c r="G673" s="7"/>
       <c r="H673" s="2"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C674" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D674" s="2">
-        <v>15.0</v>
+        <v>10.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1305</v>
-      </c>
-      <c r="F674" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G674" s="7">
-        <v>46424.0</v>
-      </c>
+        <v>1303</v>
+      </c>
+      <c r="F674" s="3"/>
+      <c r="G674" s="7"/>
       <c r="H674" s="2"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>45</v>
+        <v>701</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D675" s="2">
-        <v>16.0</v>
+        <v>10.0</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G675" s="7">
-        <v>46757.0</v>
-      </c>
+        <v>1305</v>
+      </c>
+      <c r="F675" s="3"/>
+      <c r="G675" s="7"/>
       <c r="H675" s="2"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="s">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>701</v>
@@ -20166,7 +20224,7 @@
         <v>10.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1034</v>
+        <v>1307</v>
       </c>
       <c r="F676" s="3"/>
       <c r="G676" s="7"/>
@@ -20174,7 +20232,7 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>701</v>
@@ -20186,7 +20244,7 @@
         <v>10.0</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>438</v>
+        <v>1309</v>
       </c>
       <c r="F677" s="3"/>
       <c r="G677" s="7"/>
@@ -20203,18 +20261,20 @@
         <v>27</v>
       </c>
       <c r="D678" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E678" s="2" t="s">
         <v>1311</v>
       </c>
-      <c r="F678" s="3"/>
+      <c r="F678" s="3" t="s">
+        <v>1312</v>
+      </c>
       <c r="G678" s="7"/>
       <c r="H678" s="2"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>701</v>
@@ -20223,18 +20283,20 @@
         <v>27</v>
       </c>
       <c r="D679" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1313</v>
-      </c>
-      <c r="F679" s="3"/>
+        <v>1314</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>1312</v>
+      </c>
       <c r="G679" s="7"/>
       <c r="H679" s="2"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>701</v>
@@ -20243,12 +20305,14 @@
         <v>27</v>
       </c>
       <c r="D680" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F680" s="3"/>
+        <v>763</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>1312</v>
+      </c>
       <c r="G680" s="7"/>
       <c r="H680" s="2"/>
     </row>
@@ -20263,12 +20327,14 @@
         <v>27</v>
       </c>
       <c r="D681" s="2">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="E681" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="F681" s="3"/>
+      <c r="F681" s="3" t="s">
+        <v>1312</v>
+      </c>
       <c r="G681" s="7"/>
       <c r="H681" s="2"/>
     </row>
@@ -20289,14 +20355,14 @@
         <v>1319</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="G682" s="7"/>
       <c r="H682" s="2"/>
     </row>
     <row r="683">
       <c r="A683" s="2" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>701</v>
@@ -20308,122 +20374,130 @@
         <v>3.0</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="G683" s="7"/>
       <c r="H683" s="2"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>701</v>
+        <v>45</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D684" s="2">
-        <v>3.0</v>
+        <v>11.0</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>763</v>
+        <v>1197</v>
       </c>
       <c r="F684" s="3" t="s">
-        <v>1320</v>
+        <v>1271</v>
       </c>
       <c r="G684" s="7"/>
       <c r="H684" s="2"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B685" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C685" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D685" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="E685" s="2" t="s">
         <v>1324</v>
       </c>
-      <c r="B685" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C685" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D685" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E685" s="2" t="s">
-        <v>1325</v>
-      </c>
       <c r="F685" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G685" s="7"/>
+        <v>1271</v>
+      </c>
+      <c r="G685" s="7">
+        <v>46620.0</v>
+      </c>
       <c r="H685" s="2"/>
     </row>
     <row r="686">
       <c r="A686" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B686" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C686" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D686" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E686" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F686" s="3" t="s">
         <v>1326</v>
       </c>
-      <c r="B686" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C686" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D686" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E686" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="F686" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G686" s="7"/>
+      <c r="G686" s="7">
+        <v>46982.0</v>
+      </c>
       <c r="H686" s="2"/>
     </row>
     <row r="687">
       <c r="A687" s="2" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C687" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D687" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E687" s="2" t="s">
         <v>1328</v>
       </c>
-      <c r="B687" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="C687" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D687" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E687" s="2" t="s">
-        <v>1329</v>
-      </c>
       <c r="F687" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="G687" s="7"/>
+        <v>156</v>
+      </c>
+      <c r="G687" s="7">
+        <v>46661.0</v>
+      </c>
       <c r="H687" s="2"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B688" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C688" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D688" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E688" s="2" t="s">
         <v>1330</v>
       </c>
-      <c r="B688" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C688" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D688" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E688" s="2" t="s">
-        <v>1203</v>
-      </c>
       <c r="F688" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="G688" s="7"/>
+        <v>156</v>
+      </c>
+      <c r="G688" s="7">
+        <v>46494.0</v>
+      </c>
       <c r="H688" s="2"/>
     </row>
     <row r="689">
@@ -20431,22 +20505,22 @@
         <v>1331</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C689" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D689" s="2">
-        <v>16.0</v>
+        <v>2.0</v>
       </c>
       <c r="E689" s="2" t="s">
         <v>1332</v>
       </c>
       <c r="F689" s="3" t="s">
-        <v>1279</v>
+        <v>156</v>
       </c>
       <c r="G689" s="7">
-        <v>46620.0</v>
+        <v>46717.0</v>
       </c>
       <c r="H689" s="2"/>
     </row>
@@ -20455,22 +20529,22 @@
         <v>1333</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D690" s="2">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>1163</v>
+        <v>1334</v>
       </c>
       <c r="F690" s="3" t="s">
-        <v>1334</v>
+        <v>156</v>
       </c>
       <c r="G690" s="7">
-        <v>46982.0</v>
+        <v>46659.0</v>
       </c>
       <c r="H690" s="2"/>
     </row>
@@ -20494,7 +20568,7 @@
         <v>156</v>
       </c>
       <c r="G691" s="7">
-        <v>46661.0</v>
+        <v>46604.0</v>
       </c>
       <c r="H691" s="2"/>
     </row>
@@ -20518,7 +20592,7 @@
         <v>156</v>
       </c>
       <c r="G692" s="7">
-        <v>46494.0</v>
+        <v>46688.0</v>
       </c>
       <c r="H692" s="2"/>
     </row>
@@ -20527,22 +20601,22 @@
         <v>1339</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>11</v>
+        <v>701</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D693" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E693" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F693" s="3" t="s">
         <v>1340</v>
       </c>
-      <c r="F693" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="G693" s="7">
-        <v>46717.0</v>
+        <v>46399.0</v>
       </c>
       <c r="H693" s="2"/>
     </row>
@@ -20551,76 +20625,76 @@
         <v>1341</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>11</v>
+        <v>701</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D694" s="2">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>1342</v>
+        <v>1149</v>
       </c>
       <c r="F694" s="3" t="s">
-        <v>156</v>
+        <v>1340</v>
       </c>
       <c r="G694" s="7">
-        <v>46659.0</v>
+        <v>46398.0</v>
       </c>
       <c r="H694" s="2"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D695" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E695" s="2" t="s">
         <v>1343</v>
       </c>
-      <c r="B695" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C695" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D695" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E695" s="2" t="s">
-        <v>1344</v>
-      </c>
       <c r="F695" s="3" t="s">
-        <v>156</v>
+        <v>1340</v>
       </c>
       <c r="G695" s="7">
-        <v>46604.0</v>
+        <v>46399.0</v>
       </c>
       <c r="H695" s="2"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D696" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E696" s="2" t="s">
         <v>1345</v>
       </c>
-      <c r="B696" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C696" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D696" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E696" s="2" t="s">
-        <v>1346</v>
-      </c>
       <c r="F696" s="3" t="s">
-        <v>156</v>
+        <v>1340</v>
       </c>
       <c r="G696" s="7">
-        <v>46688.0</v>
+        <v>46328.0</v>
       </c>
       <c r="H696" s="2"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>701</v>
@@ -20632,19 +20706,19 @@
         <v>1.0</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>1158</v>
+        <v>1347</v>
       </c>
       <c r="F697" s="3" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="G697" s="7">
-        <v>46399.0</v>
+        <v>46335.0</v>
       </c>
       <c r="H697" s="2"/>
     </row>
     <row r="698">
       <c r="A698" s="2" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>701</v>
@@ -20656,10 +20730,10 @@
         <v>1.0</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>1155</v>
+        <v>1349</v>
       </c>
       <c r="F698" s="3" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="G698" s="7">
         <v>46398.0</v>
@@ -20674,44 +20748,42 @@
         <v>701</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D699" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="E699" s="2" t="s">
         <v>1351</v>
       </c>
       <c r="F699" s="3" t="s">
-        <v>1348</v>
+        <v>1352</v>
       </c>
       <c r="G699" s="7">
-        <v>46399.0</v>
+        <v>46641.0</v>
       </c>
       <c r="H699" s="2"/>
     </row>
     <row r="700">
       <c r="A700" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>701</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D700" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>1353</v>
+        <v>373</v>
       </c>
       <c r="F700" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="G700" s="7">
-        <v>46328.0</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="G700" s="7"/>
       <c r="H700" s="2"/>
     </row>
     <row r="701">
@@ -20722,20 +20794,18 @@
         <v>701</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D701" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="E701" s="2" t="s">
         <v>1355</v>
       </c>
       <c r="F701" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="G701" s="7">
-        <v>46335.0</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="G701" s="7"/>
       <c r="H701" s="2"/>
     </row>
     <row r="702">
@@ -20746,140 +20816,286 @@
         <v>701</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D702" s="2">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="E702" s="2" t="s">
         <v>1357</v>
       </c>
       <c r="F702" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="G702" s="7">
-        <v>46398.0</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="G702" s="7"/>
       <c r="H702" s="2"/>
     </row>
     <row r="703">
-      <c r="A703" s="2"/>
-      <c r="B703" s="2"/>
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
-      <c r="E703" s="2"/>
-      <c r="F703" s="3"/>
+      <c r="A703" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D703" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E703" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>1150</v>
+      </c>
       <c r="G703" s="7"/>
       <c r="H703" s="2"/>
     </row>
     <row r="704">
-      <c r="A704" s="2"/>
-      <c r="B704" s="2"/>
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
-      <c r="E704" s="2"/>
-      <c r="F704" s="3"/>
+      <c r="A704" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D704" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E704" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>703</v>
+      </c>
       <c r="G704" s="7"/>
       <c r="H704" s="2"/>
     </row>
     <row r="705">
-      <c r="A705" s="2"/>
-      <c r="B705" s="2"/>
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
-      <c r="E705" s="2"/>
-      <c r="F705" s="3"/>
+      <c r="A705" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D705" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E705" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="G705" s="7"/>
       <c r="H705" s="2"/>
     </row>
     <row r="706">
-      <c r="A706" s="2"/>
-      <c r="B706" s="2"/>
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
-      <c r="E706" s="2"/>
-      <c r="F706" s="3"/>
+      <c r="A706" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D706" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E706" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="G706" s="7"/>
       <c r="H706" s="2"/>
     </row>
     <row r="707">
-      <c r="A707" s="2"/>
-      <c r="B707" s="2"/>
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
-      <c r="E707" s="2"/>
-      <c r="F707" s="3"/>
+      <c r="A707" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D707" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E707" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>274</v>
+      </c>
       <c r="G707" s="7"/>
       <c r="H707" s="2"/>
     </row>
     <row r="708">
-      <c r="A708" s="2"/>
-      <c r="B708" s="2"/>
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
-      <c r="E708" s="2"/>
-      <c r="F708" s="3"/>
+      <c r="A708" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D708" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E708" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1367</v>
+      </c>
       <c r="G708" s="7"/>
       <c r="H708" s="2"/>
     </row>
     <row r="709">
-      <c r="A709" s="2"/>
-      <c r="B709" s="2"/>
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
-      <c r="E709" s="2"/>
+      <c r="A709" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D709" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E709" s="2" t="s">
+        <v>1369</v>
+      </c>
       <c r="F709" s="3"/>
       <c r="G709" s="7"/>
       <c r="H709" s="2"/>
     </row>
     <row r="710">
-      <c r="A710" s="2"/>
-      <c r="B710" s="2"/>
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
-      <c r="E710" s="2"/>
-      <c r="F710" s="3"/>
+      <c r="A710" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D710" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="E710" s="2" t="s">
+        <v>960</v>
+      </c>
+      <c r="F710" s="3" t="s">
+        <v>266</v>
+      </c>
       <c r="G710" s="7"/>
       <c r="H710" s="2"/>
     </row>
     <row r="711">
-      <c r="A711" s="2"/>
-      <c r="B711" s="2"/>
-      <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
-      <c r="E711" s="2"/>
-      <c r="F711" s="3"/>
+      <c r="A711" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C711" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D711" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E711" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="F711" s="3">
+        <v>11504.0</v>
+      </c>
       <c r="G711" s="7"/>
       <c r="H711" s="2"/>
     </row>
     <row r="712">
-      <c r="A712" s="2"/>
-      <c r="B712" s="2"/>
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
-      <c r="E712" s="2"/>
-      <c r="F712" s="3"/>
-      <c r="G712" s="7"/>
+      <c r="A712" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D712" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E712" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G712" s="7">
+        <v>46432.0</v>
+      </c>
       <c r="H712" s="2"/>
     </row>
     <row r="713">
-      <c r="A713" s="2"/>
-      <c r="B713" s="2"/>
-      <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
-      <c r="E713" s="2"/>
-      <c r="F713" s="3"/>
-      <c r="G713" s="7"/>
+      <c r="A713" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C713" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D713" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E713" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="G713" s="7">
+        <v>46477.0</v>
+      </c>
       <c r="H713" s="2"/>
     </row>
     <row r="714">
-      <c r="A714" s="2"/>
-      <c r="B714" s="2"/>
-      <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
-      <c r="E714" s="2"/>
-      <c r="F714" s="3"/>
-      <c r="G714" s="7"/>
+      <c r="A714" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D714" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="E714" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="G714" s="7">
+        <v>46488.0</v>
+      </c>
       <c r="H714" s="2"/>
     </row>
     <row r="715">
@@ -27122,46 +27338,6 @@
       <c r="G1338" s="7"/>
       <c r="H1338" s="2"/>
     </row>
-    <row r="1339">
-      <c r="A1339" s="2"/>
-      <c r="B1339" s="2"/>
-      <c r="C1339" s="2"/>
-      <c r="D1339" s="2"/>
-      <c r="E1339" s="2"/>
-      <c r="F1339" s="3"/>
-      <c r="G1339" s="7"/>
-      <c r="H1339" s="2"/>
-    </row>
-    <row r="1340">
-      <c r="A1340" s="2"/>
-      <c r="B1340" s="2"/>
-      <c r="C1340" s="2"/>
-      <c r="D1340" s="2"/>
-      <c r="E1340" s="2"/>
-      <c r="F1340" s="3"/>
-      <c r="G1340" s="7"/>
-      <c r="H1340" s="2"/>
-    </row>
-    <row r="1341">
-      <c r="A1341" s="2"/>
-      <c r="B1341" s="2"/>
-      <c r="C1341" s="2"/>
-      <c r="D1341" s="2"/>
-      <c r="E1341" s="2"/>
-      <c r="F1341" s="3"/>
-      <c r="G1341" s="7"/>
-      <c r="H1341" s="2"/>
-    </row>
-    <row r="1342">
-      <c r="A1342" s="2"/>
-      <c r="B1342" s="2"/>
-      <c r="C1342" s="2"/>
-      <c r="D1342" s="2"/>
-      <c r="E1342" s="2"/>
-      <c r="F1342" s="3"/>
-      <c r="G1342" s="7"/>
-      <c r="H1342" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3469" uniqueCount="1378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3470" uniqueCount="1378">
   <si>
     <t>ID</t>
   </si>
@@ -13434,7 +13434,9 @@
       <c r="G389" s="7">
         <v>46925.0</v>
       </c>
-      <c r="H389" s="2"/>
+      <c r="H389" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3281" uniqueCount="1309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3281" uniqueCount="1308">
   <si>
     <t>ID</t>
   </si>
@@ -2126,9 +2126,6 @@
   </si>
   <si>
     <t>24-26B</t>
-  </si>
-  <si>
-    <t>1b</t>
   </si>
   <si>
     <t>ID1784079992534</t>
@@ -12430,12 +12427,12 @@
         <v>46926.0</v>
       </c>
       <c r="H354" s="2" t="s">
-        <v>705</v>
+        <v>196</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B355" s="2" t="s">
         <v>665</v>
@@ -12447,7 +12444,7 @@
         <v>12.0</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F355" s="3" t="s">
         <v>667</v>
@@ -12459,7 +12456,7 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B356" s="2" t="s">
         <v>665</v>
@@ -12471,7 +12468,7 @@
         <v>12.0</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F356" s="3" t="s">
         <v>667</v>
@@ -12483,7 +12480,7 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B357" s="2" t="s">
         <v>34</v>
@@ -12495,10 +12492,10 @@
         <v>22.0</v>
       </c>
       <c r="E357" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F357" s="3" t="s">
         <v>711</v>
-      </c>
-      <c r="F357" s="3" t="s">
-        <v>712</v>
       </c>
       <c r="G357" s="7">
         <v>46834.0</v>
@@ -12507,7 +12504,7 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B358" s="2" t="s">
         <v>34</v>
@@ -12519,17 +12516,17 @@
         <v>11.0</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="F358" s="3"/>
       <c r="G358" s="7"/>
       <c r="H358" s="2" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B359" s="2" t="s">
         <v>397</v>
@@ -12541,10 +12538,10 @@
         <v>21.0</v>
       </c>
       <c r="E359" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="F359" s="3" t="s">
         <v>717</v>
-      </c>
-      <c r="F359" s="3" t="s">
-        <v>718</v>
       </c>
       <c r="G359" s="7">
         <v>46689.0</v>
@@ -12553,7 +12550,7 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B360" s="2" t="s">
         <v>397</v>
@@ -12565,7 +12562,7 @@
         <v>21.0</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="F360" s="3" t="s">
         <v>51</v>
@@ -12577,7 +12574,7 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B361" s="2" t="s">
         <v>397</v>
@@ -12589,7 +12586,7 @@
         <v>21.0</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="F361" s="3" t="s">
         <v>391</v>
@@ -12601,7 +12598,7 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B362" s="2" t="s">
         <v>397</v>
@@ -12613,7 +12610,7 @@
         <v>21.0</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F362" s="3" t="s">
         <v>355</v>
@@ -12625,7 +12622,7 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B363" s="2" t="s">
         <v>34</v>
@@ -12637,7 +12634,7 @@
         <v>22.0</v>
       </c>
       <c r="E363" s="2" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="F363" s="3" t="s">
         <v>626</v>
@@ -12649,7 +12646,7 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B364" s="2" t="s">
         <v>34</v>
@@ -12661,7 +12658,7 @@
         <v>22.0</v>
       </c>
       <c r="E364" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="F364" s="3" t="s">
         <v>564</v>
@@ -12673,7 +12670,7 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B365" s="2" t="s">
         <v>34</v>
@@ -12685,7 +12682,7 @@
         <v>15.0</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F365" s="3" t="s">
         <v>233</v>
@@ -12697,7 +12694,7 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B366" s="2" t="s">
         <v>42</v>
@@ -12709,10 +12706,10 @@
         <v>4.0</v>
       </c>
       <c r="E366" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="F366" s="3" t="s">
         <v>732</v>
-      </c>
-      <c r="F366" s="3" t="s">
-        <v>733</v>
       </c>
       <c r="G366" s="7">
         <v>46722.0</v>
@@ -12721,7 +12718,7 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>665</v>
@@ -12733,7 +12730,7 @@
         <v>17.0</v>
       </c>
       <c r="E367" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F367" s="3" t="s">
         <v>690</v>
@@ -12745,7 +12742,7 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>42</v>
@@ -12757,7 +12754,7 @@
         <v>6.0</v>
       </c>
       <c r="E368" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="F368" s="3">
         <v>11507.0</v>
@@ -12766,12 +12763,12 @@
         <v>46923.0</v>
       </c>
       <c r="H368" s="2" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>42</v>
@@ -12783,10 +12780,10 @@
         <v>15.0</v>
       </c>
       <c r="E369" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="F369" s="3" t="s">
         <v>740</v>
-      </c>
-      <c r="F369" s="3" t="s">
-        <v>741</v>
       </c>
       <c r="G369" s="7">
         <v>46479.0</v>
@@ -12795,10 +12792,10 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B370" s="2" t="s">
         <v>742</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>743</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>12</v>
@@ -12807,22 +12804,22 @@
         <v>1.0</v>
       </c>
       <c r="E370" s="2" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="F370" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G370" s="7"/>
       <c r="H370" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>12</v>
@@ -12831,22 +12828,22 @@
         <v>1.0</v>
       </c>
       <c r="E371" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F371" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G371" s="7"/>
       <c r="H371" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>12</v>
@@ -12855,22 +12852,22 @@
         <v>1.0</v>
       </c>
       <c r="E372" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F372" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G372" s="7"/>
       <c r="H372" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C373" s="2" t="s">
         <v>12</v>
@@ -12879,22 +12876,22 @@
         <v>1.0</v>
       </c>
       <c r="E373" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F373" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G373" s="7"/>
       <c r="H373" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>12</v>
@@ -12903,22 +12900,22 @@
         <v>1.0</v>
       </c>
       <c r="E374" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F374" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G374" s="7"/>
       <c r="H374" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>12</v>
@@ -12927,19 +12924,19 @@
         <v>1.0</v>
       </c>
       <c r="E375" s="2" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="F375" s="3" t="s">
         <v>143</v>
       </c>
       <c r="G375" s="7"/>
       <c r="H375" s="2" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>42</v>
@@ -12951,10 +12948,10 @@
         <v>20.0</v>
       </c>
       <c r="E376" s="2" t="s">
+        <v>756</v>
+      </c>
+      <c r="F376" s="3" t="s">
         <v>757</v>
-      </c>
-      <c r="F376" s="3" t="s">
-        <v>758</v>
       </c>
       <c r="G376" s="7">
         <v>46764.0</v>
@@ -12963,7 +12960,7 @@
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>42</v>
@@ -12975,10 +12972,10 @@
         <v>22.0</v>
       </c>
       <c r="E377" s="2" t="s">
+        <v>759</v>
+      </c>
+      <c r="F377" s="3" t="s">
         <v>760</v>
-      </c>
-      <c r="F377" s="3" t="s">
-        <v>761</v>
       </c>
       <c r="G377" s="7">
         <v>46390.0</v>
@@ -12987,7 +12984,7 @@
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>34</v>
@@ -12999,7 +12996,7 @@
         <v>4.0</v>
       </c>
       <c r="E378" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="F378" s="3" t="s">
         <v>143</v>
@@ -13011,7 +13008,7 @@
     </row>
     <row r="379">
       <c r="A379" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>34</v>
@@ -13023,7 +13020,7 @@
         <v>4.0</v>
       </c>
       <c r="E379" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F379" s="3" t="s">
         <v>143</v>
@@ -13035,7 +13032,7 @@
     </row>
     <row r="380">
       <c r="A380" s="2" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>34</v>
@@ -13059,7 +13056,7 @@
     </row>
     <row r="381">
       <c r="A381" s="2" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>34</v>
@@ -13071,7 +13068,7 @@
         <v>4.0</v>
       </c>
       <c r="E381" s="2" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="F381" s="3" t="s">
         <v>143</v>
@@ -13083,7 +13080,7 @@
     </row>
     <row r="382">
       <c r="A382" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>34</v>
@@ -13095,7 +13092,7 @@
         <v>4.0</v>
       </c>
       <c r="E382" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="F382" s="3" t="s">
         <v>143</v>
@@ -13107,7 +13104,7 @@
     </row>
     <row r="383">
       <c r="A383" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>34</v>
@@ -13119,7 +13116,7 @@
         <v>16.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>143</v>
@@ -13131,7 +13128,7 @@
     </row>
     <row r="384">
       <c r="A384" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>34</v>
@@ -13143,7 +13140,7 @@
         <v>1.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>143</v>
@@ -13155,7 +13152,7 @@
     </row>
     <row r="385">
       <c r="A385" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>34</v>
@@ -13167,7 +13164,7 @@
         <v>1.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>143</v>
@@ -13179,7 +13176,7 @@
     </row>
     <row r="386">
       <c r="A386" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>34</v>
@@ -13191,7 +13188,7 @@
         <v>7.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>143</v>
@@ -13203,7 +13200,7 @@
     </row>
     <row r="387">
       <c r="A387" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B387" s="2" t="s">
         <v>34</v>
@@ -13215,7 +13212,7 @@
         <v>2.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>143</v>
@@ -13227,7 +13224,7 @@
     </row>
     <row r="388">
       <c r="A388" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B388" s="2" t="s">
         <v>34</v>
@@ -13239,7 +13236,7 @@
         <v>2.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="F388" s="3" t="s">
         <v>143</v>
@@ -13251,7 +13248,7 @@
     </row>
     <row r="389">
       <c r="A389" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B389" s="2" t="s">
         <v>34</v>
@@ -13263,7 +13260,7 @@
         <v>1.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>143</v>
@@ -13272,12 +13269,12 @@
         <v>46521.0</v>
       </c>
       <c r="H389" s="2" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B390" s="2" t="s">
         <v>34</v>
@@ -13289,7 +13286,7 @@
         <v>2.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>143</v>
@@ -13301,7 +13298,7 @@
     </row>
     <row r="391">
       <c r="A391" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B391" s="2" t="s">
         <v>34</v>
@@ -13313,7 +13310,7 @@
         <v>1.0</v>
       </c>
       <c r="E391" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F391" s="3" t="s">
         <v>143</v>
@@ -13325,7 +13322,7 @@
     </row>
     <row r="392">
       <c r="A392" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="B392" s="2" t="s">
         <v>34</v>
@@ -13337,7 +13334,7 @@
         <v>7.0</v>
       </c>
       <c r="E392" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F392" s="3" t="s">
         <v>143</v>
@@ -13349,7 +13346,7 @@
     </row>
     <row r="393">
       <c r="A393" s="2" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B393" s="2" t="s">
         <v>34</v>
@@ -13361,7 +13358,7 @@
         <v>1.0</v>
       </c>
       <c r="E393" s="2" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F393" s="3" t="s">
         <v>143</v>
@@ -13373,7 +13370,7 @@
     </row>
     <row r="394">
       <c r="A394" s="2" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="B394" s="2" t="s">
         <v>42</v>
@@ -13385,7 +13382,7 @@
         <v>14.0</v>
       </c>
       <c r="E394" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F394" s="3" t="s">
         <v>241</v>
@@ -13397,7 +13394,7 @@
     </row>
     <row r="395">
       <c r="A395" s="2" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B395" s="2" t="s">
         <v>42</v>
@@ -13409,7 +13406,7 @@
         <v>11.0</v>
       </c>
       <c r="E395" s="2" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F395" s="3" t="s">
         <v>241</v>
@@ -13421,7 +13418,7 @@
     </row>
     <row r="396">
       <c r="A396" s="2" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B396" s="2" t="s">
         <v>42</v>
@@ -13433,7 +13430,7 @@
         <v>11.0</v>
       </c>
       <c r="E396" s="2" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F396" s="3" t="s">
         <v>241</v>
@@ -13445,7 +13442,7 @@
     </row>
     <row r="397">
       <c r="A397" s="2" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B397" s="2" t="s">
         <v>42</v>
@@ -13457,7 +13454,7 @@
         <v>11.0</v>
       </c>
       <c r="E397" s="2" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F397" s="3" t="s">
         <v>241</v>
@@ -13469,7 +13466,7 @@
     </row>
     <row r="398">
       <c r="A398" s="2" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B398" s="2" t="s">
         <v>42</v>
@@ -13493,7 +13490,7 @@
     </row>
     <row r="399">
       <c r="A399" s="2" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B399" s="2" t="s">
         <v>34</v>
@@ -13505,10 +13502,10 @@
         <v>15.0</v>
       </c>
       <c r="E399" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="F399" s="3" t="s">
         <v>803</v>
-      </c>
-      <c r="F399" s="3" t="s">
-        <v>804</v>
       </c>
       <c r="G399" s="7">
         <v>46877.0</v>
@@ -13517,7 +13514,7 @@
     </row>
     <row r="400">
       <c r="A400" s="2" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B400" s="2" t="s">
         <v>34</v>
@@ -13529,10 +13526,10 @@
         <v>15.0</v>
       </c>
       <c r="E400" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F400" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G400" s="7">
         <v>46877.0</v>
@@ -13541,7 +13538,7 @@
     </row>
     <row r="401">
       <c r="A401" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B401" s="2" t="s">
         <v>34</v>
@@ -13556,7 +13553,7 @@
         <v>649</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G401" s="7">
         <v>46877.0</v>
@@ -13565,7 +13562,7 @@
     </row>
     <row r="402">
       <c r="A402" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B402" s="2" t="s">
         <v>34</v>
@@ -13577,10 +13574,10 @@
         <v>15.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="F402" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G402" s="7">
         <v>46877.0</v>
@@ -13589,7 +13586,7 @@
     </row>
     <row r="403">
       <c r="A403" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B403" s="2" t="s">
         <v>34</v>
@@ -13601,10 +13598,10 @@
         <v>15.0</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="F403" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G403" s="7">
         <v>46892.0</v>
@@ -13613,7 +13610,7 @@
     </row>
     <row r="404">
       <c r="A404" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B404" s="2" t="s">
         <v>34</v>
@@ -13625,10 +13622,10 @@
         <v>15.0</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="F404" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G404" s="7">
         <v>46891.0</v>
@@ -13637,7 +13634,7 @@
     </row>
     <row r="405">
       <c r="A405" s="2" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B405" s="2" t="s">
         <v>42</v>
@@ -13649,7 +13646,7 @@
         <v>13.0</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F405" s="3" t="s">
         <v>241</v>
@@ -13661,7 +13658,7 @@
     </row>
     <row r="406">
       <c r="A406" s="2" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B406" s="2" t="s">
         <v>42</v>
@@ -13673,7 +13670,7 @@
         <v>8.0</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="F406" s="3" t="s">
         <v>143</v>
@@ -13685,7 +13682,7 @@
     </row>
     <row r="407">
       <c r="A407" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B407" s="2" t="s">
         <v>42</v>
@@ -13697,7 +13694,7 @@
         <v>19.0</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="F407" s="3" t="s">
         <v>20</v>
@@ -13709,7 +13706,7 @@
     </row>
     <row r="408">
       <c r="A408" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B408" s="2" t="s">
         <v>42</v>
@@ -13721,10 +13718,10 @@
         <v>20.0</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F408" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G408" s="7">
         <v>46764.0</v>
@@ -13733,7 +13730,7 @@
     </row>
     <row r="409">
       <c r="A409" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B409" s="2" t="s">
         <v>42</v>
@@ -13745,10 +13742,10 @@
         <v>16.0</v>
       </c>
       <c r="E409" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="F409" s="3" t="s">
         <v>822</v>
-      </c>
-      <c r="F409" s="3" t="s">
-        <v>823</v>
       </c>
       <c r="G409" s="7">
         <v>46488.0</v>
@@ -13757,7 +13754,7 @@
     </row>
     <row r="410">
       <c r="A410" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B410" s="2" t="s">
         <v>42</v>
@@ -13769,10 +13766,10 @@
         <v>16.0</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G410" s="7">
         <v>46441.0</v>
@@ -13781,7 +13778,7 @@
     </row>
     <row r="411">
       <c r="A411" s="2" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B411" s="2" t="s">
         <v>42</v>
@@ -13793,10 +13790,10 @@
         <v>15.0</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G411" s="7">
         <v>46544.0</v>
@@ -13805,7 +13802,7 @@
     </row>
     <row r="412">
       <c r="A412" s="2" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B412" s="2" t="s">
         <v>42</v>
@@ -13817,10 +13814,10 @@
         <v>14.0</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G412" s="7">
         <v>46792.0</v>
@@ -13829,7 +13826,7 @@
     </row>
     <row r="413">
       <c r="A413" s="2" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B413" s="2" t="s">
         <v>42</v>
@@ -13841,10 +13838,10 @@
         <v>14.0</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F413" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G413" s="7">
         <v>46886.0</v>
@@ -13853,7 +13850,7 @@
     </row>
     <row r="414">
       <c r="A414" s="2" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B414" s="2" t="s">
         <v>42</v>
@@ -13865,7 +13862,7 @@
         <v>8.0</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="F414" s="3" t="s">
         <v>633</v>
@@ -13877,7 +13874,7 @@
     </row>
     <row r="415">
       <c r="A415" s="2" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B415" s="2" t="s">
         <v>42</v>
@@ -13889,7 +13886,7 @@
         <v>6.0</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F415" s="3" t="s">
         <v>20</v>
@@ -13898,12 +13895,12 @@
         <v>46422.0</v>
       </c>
       <c r="H415" s="2" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B416" s="2" t="s">
         <v>42</v>
@@ -13915,17 +13912,17 @@
         <v>14.0</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F416" s="3" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G416" s="7"/>
       <c r="H416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="B417" s="2" t="s">
         <v>42</v>
@@ -13937,10 +13934,10 @@
         <v>20.0</v>
       </c>
       <c r="E417" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="F417" s="3" t="s">
         <v>840</v>
-      </c>
-      <c r="F417" s="3" t="s">
-        <v>841</v>
       </c>
       <c r="G417" s="7">
         <v>46925.0</v>
@@ -13949,7 +13946,7 @@
     </row>
     <row r="418">
       <c r="A418" s="2" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="B418" s="2" t="s">
         <v>34</v>
@@ -13961,7 +13958,7 @@
         <v>16.0</v>
       </c>
       <c r="E418" s="2" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="F418" s="3" t="s">
         <v>472</v>
@@ -13971,7 +13968,7 @@
     </row>
     <row r="419">
       <c r="A419" s="2" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B419" s="2" t="s">
         <v>42</v>
@@ -13983,10 +13980,10 @@
         <v>9.0</v>
       </c>
       <c r="E419" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="F419" s="3" t="s">
         <v>845</v>
-      </c>
-      <c r="F419" s="3" t="s">
-        <v>846</v>
       </c>
       <c r="G419" s="7">
         <v>46792.0</v>
@@ -13995,7 +13992,7 @@
     </row>
     <row r="420">
       <c r="A420" s="2" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B420" s="2" t="s">
         <v>42</v>
@@ -14007,10 +14004,10 @@
         <v>9.0</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="G420" s="7">
         <v>46843.0</v>
@@ -14019,7 +14016,7 @@
     </row>
     <row r="421">
       <c r="A421" s="2" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B421" s="2" t="s">
         <v>42</v>
@@ -14034,7 +14031,7 @@
         <v>549</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G421" s="7">
         <v>46529.0</v>
@@ -14043,7 +14040,7 @@
     </row>
     <row r="422">
       <c r="A422" s="2" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>42</v>
@@ -14055,10 +14052,10 @@
         <v>9.0</v>
       </c>
       <c r="E422" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="F422" s="3" t="s">
         <v>852</v>
-      </c>
-      <c r="F422" s="3" t="s">
-        <v>853</v>
       </c>
       <c r="G422" s="7">
         <v>46872.0</v>
@@ -14067,7 +14064,7 @@
     </row>
     <row r="423">
       <c r="A423" s="2" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>42</v>
@@ -14091,7 +14088,7 @@
     </row>
     <row r="424">
       <c r="A424" s="2" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>42</v>
@@ -14103,10 +14100,10 @@
         <v>9.0</v>
       </c>
       <c r="E424" s="2" t="s">
+        <v>855</v>
+      </c>
+      <c r="F424" s="3" t="s">
         <v>856</v>
-      </c>
-      <c r="F424" s="3" t="s">
-        <v>857</v>
       </c>
       <c r="G424" s="7">
         <v>46480.0</v>
@@ -14115,7 +14112,7 @@
     </row>
     <row r="425">
       <c r="A425" s="2" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>42</v>
@@ -14127,10 +14124,10 @@
         <v>18.0</v>
       </c>
       <c r="E425" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F425" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="F425" s="3" t="s">
-        <v>860</v>
       </c>
       <c r="G425" s="7">
         <v>46849.0</v>
@@ -14139,7 +14136,7 @@
     </row>
     <row r="426">
       <c r="A426" s="2" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>42</v>
@@ -14151,10 +14148,10 @@
         <v>18.0</v>
       </c>
       <c r="E426" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G426" s="7">
         <v>46913.0</v>
@@ -14163,7 +14160,7 @@
     </row>
     <row r="427">
       <c r="A427" s="2" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>34</v>
@@ -14187,7 +14184,7 @@
     </row>
     <row r="428">
       <c r="A428" s="2" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>42</v>
@@ -14199,7 +14196,7 @@
         <v>2.0</v>
       </c>
       <c r="E428" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F428" s="3"/>
       <c r="G428" s="7">
@@ -14209,7 +14206,7 @@
     </row>
     <row r="429">
       <c r="A429" s="2" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>11</v>
@@ -14221,7 +14218,7 @@
         <v>2.0</v>
       </c>
       <c r="E429" s="2" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F429" s="3" t="s">
         <v>143</v>
@@ -14231,7 +14228,7 @@
     </row>
     <row r="430">
       <c r="A430" s="2" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>665</v>
@@ -14243,7 +14240,7 @@
         <v>14.0</v>
       </c>
       <c r="E430" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F430" s="3" t="s">
         <v>690</v>
@@ -14255,7 +14252,7 @@
     </row>
     <row r="431">
       <c r="A431" s="2" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>292</v>
@@ -14267,7 +14264,7 @@
         <v>6.0</v>
       </c>
       <c r="E431" s="2" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F431" s="3" t="s">
         <v>521</v>
@@ -14279,7 +14276,7 @@
     </row>
     <row r="432">
       <c r="A432" s="2" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>292</v>
@@ -14291,7 +14288,7 @@
         <v>3.0</v>
       </c>
       <c r="E432" s="2" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F432" s="3" t="s">
         <v>521</v>
@@ -14303,7 +14300,7 @@
     </row>
     <row r="433">
       <c r="A433" s="2" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>292</v>
@@ -14315,7 +14312,7 @@
         <v>6.0</v>
       </c>
       <c r="E433" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="F433" s="3" t="s">
         <v>521</v>
@@ -14327,7 +14324,7 @@
     </row>
     <row r="434">
       <c r="A434" s="2" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>292</v>
@@ -14339,7 +14336,7 @@
         <v>6.0</v>
       </c>
       <c r="E434" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F434" s="3" t="s">
         <v>521</v>
@@ -14351,7 +14348,7 @@
     </row>
     <row r="435">
       <c r="A435" s="2" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>292</v>
@@ -14363,10 +14360,10 @@
         <v>12.0</v>
       </c>
       <c r="E435" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F435" s="3" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G435" s="7">
         <v>46291.0</v>
@@ -14375,10 +14372,10 @@
     </row>
     <row r="436">
       <c r="A436" s="2" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B436" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C436" s="2" t="s">
         <v>12</v>
@@ -14387,7 +14384,7 @@
         <v>14.0</v>
       </c>
       <c r="E436" s="2" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F436" s="3" t="s">
         <v>521</v>
@@ -14399,7 +14396,7 @@
     </row>
     <row r="437">
       <c r="A437" s="2" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>397</v>
@@ -14411,10 +14408,10 @@
         <v>21.0</v>
       </c>
       <c r="E437" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="F437" s="3" t="s">
         <v>883</v>
-      </c>
-      <c r="F437" s="3" t="s">
-        <v>884</v>
       </c>
       <c r="G437" s="7">
         <v>46764.0</v>
@@ -14423,7 +14420,7 @@
     </row>
     <row r="438">
       <c r="A438" s="2" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>42</v>
@@ -14447,7 +14444,7 @@
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>42</v>
@@ -14459,10 +14456,10 @@
         <v>9.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F439" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G439" s="7">
         <v>46899.0</v>
@@ -14471,7 +14468,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>42</v>
@@ -14483,10 +14480,10 @@
         <v>9.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="F440" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G440" s="7">
         <v>46745.0</v>
@@ -14495,7 +14492,7 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>34</v>
@@ -14507,10 +14504,10 @@
         <v>8.0</v>
       </c>
       <c r="E441" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="F441" s="3" t="s">
         <v>891</v>
-      </c>
-      <c r="F441" s="3" t="s">
-        <v>892</v>
       </c>
       <c r="G441" s="7">
         <v>46953.0</v>
@@ -14519,7 +14516,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>42</v>
@@ -14531,10 +14528,10 @@
         <v>9.0</v>
       </c>
       <c r="E442" s="2" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="G442" s="7">
         <v>46901.0</v>
@@ -14543,7 +14540,7 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>42</v>
@@ -14555,7 +14552,7 @@
         <v>21.0</v>
       </c>
       <c r="E443" s="2" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="F443" s="3" t="s">
         <v>143</v>
@@ -14569,7 +14566,7 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>42</v>
@@ -14581,7 +14578,7 @@
         <v>11.0</v>
       </c>
       <c r="E444" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="F444" s="3" t="s">
         <v>241</v>
@@ -14593,7 +14590,7 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>42</v>
@@ -14605,10 +14602,10 @@
         <v>14.0</v>
       </c>
       <c r="E445" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="F445" s="3" t="s">
         <v>900</v>
-      </c>
-      <c r="F445" s="3" t="s">
-        <v>901</v>
       </c>
       <c r="G445" s="7">
         <v>46793.0</v>
@@ -14617,7 +14614,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>11</v>
@@ -14629,7 +14626,7 @@
         <v>2.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>143</v>
@@ -14641,7 +14638,7 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>11</v>
@@ -14653,7 +14650,7 @@
         <v>3.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>143</v>
@@ -14665,7 +14662,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>11</v>
@@ -14677,7 +14674,7 @@
         <v>3.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>143</v>
@@ -14689,10 +14686,10 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>27</v>
@@ -14701,7 +14698,7 @@
         <v>3.0</v>
       </c>
       <c r="E449" s="2" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F449" s="3" t="s">
         <v>143</v>
@@ -14713,10 +14710,10 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="B450" s="2" t="s">
         <v>910</v>
-      </c>
-      <c r="B450" s="2" t="s">
-        <v>911</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>12</v>
@@ -14725,7 +14722,7 @@
         <v>1.0</v>
       </c>
       <c r="E450" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F450" s="3"/>
       <c r="G450" s="7"/>
@@ -14733,10 +14730,10 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>12</v>
@@ -14745,7 +14742,7 @@
         <v>1.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F451" s="3" t="s">
         <v>690</v>
@@ -14754,15 +14751,15 @@
         <v>46363.0</v>
       </c>
       <c r="H451" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>12</v>
@@ -14771,7 +14768,7 @@
         <v>1.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F452" s="3" t="s">
         <v>690</v>
@@ -14780,15 +14777,15 @@
         <v>46363.0</v>
       </c>
       <c r="H452" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>12</v>
@@ -14797,7 +14794,7 @@
         <v>1.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F453" s="3" t="s">
         <v>690</v>
@@ -14806,15 +14803,15 @@
         <v>46363.0</v>
       </c>
       <c r="H453" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>12</v>
@@ -14823,7 +14820,7 @@
         <v>1.0</v>
       </c>
       <c r="E454" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F454" s="3"/>
       <c r="G454" s="7">
@@ -14833,10 +14830,10 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>12</v>
@@ -14845,7 +14842,7 @@
         <v>2.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F455" s="3"/>
       <c r="G455" s="7"/>
@@ -14853,10 +14850,10 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C456" s="2" t="s">
         <v>12</v>
@@ -14865,7 +14862,7 @@
         <v>2.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F456" s="3" t="s">
         <v>690</v>
@@ -14874,15 +14871,15 @@
         <v>46363.0</v>
       </c>
       <c r="H456" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C457" s="2" t="s">
         <v>12</v>
@@ -14891,7 +14888,7 @@
         <v>2.0</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F457" s="3" t="s">
         <v>690</v>
@@ -14900,15 +14897,15 @@
         <v>46363.0</v>
       </c>
       <c r="H457" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C458" s="2" t="s">
         <v>12</v>
@@ -14917,7 +14914,7 @@
         <v>2.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F458" s="3" t="s">
         <v>690</v>
@@ -14926,15 +14923,15 @@
         <v>46363.0</v>
       </c>
       <c r="H458" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C459" s="2" t="s">
         <v>12</v>
@@ -14943,7 +14940,7 @@
         <v>2.0</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F459" s="3"/>
       <c r="G459" s="7">
@@ -14953,10 +14950,10 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C460" s="2" t="s">
         <v>12</v>
@@ -14965,7 +14962,7 @@
         <v>3.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F460" s="3"/>
       <c r="G460" s="7"/>
@@ -14973,10 +14970,10 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C461" s="2" t="s">
         <v>12</v>
@@ -14985,7 +14982,7 @@
         <v>3.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F461" s="3" t="s">
         <v>690</v>
@@ -14994,15 +14991,15 @@
         <v>46363.0</v>
       </c>
       <c r="H461" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C462" s="2" t="s">
         <v>12</v>
@@ -15011,7 +15008,7 @@
         <v>3.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F462" s="3" t="s">
         <v>690</v>
@@ -15020,15 +15017,15 @@
         <v>46363.0</v>
       </c>
       <c r="H462" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C463" s="2" t="s">
         <v>12</v>
@@ -15037,7 +15034,7 @@
         <v>3.0</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F463" s="3"/>
       <c r="G463" s="7">
@@ -15047,10 +15044,10 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="C464" s="2" t="s">
         <v>12</v>
@@ -15059,7 +15056,7 @@
         <v>1.0</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F464" s="3"/>
       <c r="G464" s="7">
@@ -15069,7 +15066,7 @@
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>42</v>
@@ -15081,7 +15078,7 @@
         <v>8.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F465" s="3"/>
       <c r="G465" s="7">
@@ -15091,7 +15088,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>42</v>
@@ -15103,10 +15100,10 @@
         <v>15.0</v>
       </c>
       <c r="E466" s="2" t="s">
+        <v>935</v>
+      </c>
+      <c r="F466" s="3" t="s">
         <v>936</v>
-      </c>
-      <c r="F466" s="3" t="s">
-        <v>937</v>
       </c>
       <c r="G466" s="7">
         <v>46530.0</v>
@@ -15115,7 +15112,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>42</v>
@@ -15127,21 +15124,21 @@
         <v>16.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F467" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G467" s="7">
         <v>46963.0</v>
       </c>
       <c r="H467" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>42</v>
@@ -15153,10 +15150,10 @@
         <v>15.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G468" s="7">
         <v>46793.0</v>
@@ -15165,7 +15162,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>34</v>
@@ -15177,7 +15174,7 @@
         <v>14.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>20</v>
@@ -15189,7 +15186,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>42</v>
@@ -15201,10 +15198,10 @@
         <v>21.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G470" s="7">
         <v>46480.0</v>
@@ -15213,7 +15210,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>42</v>
@@ -15225,7 +15222,7 @@
         <v>21.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>633</v>
@@ -15237,7 +15234,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>42</v>
@@ -15249,10 +15246,10 @@
         <v>21.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G472" s="7">
         <v>46792.0</v>
@@ -15261,7 +15258,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>42</v>
@@ -15273,10 +15270,10 @@
         <v>21.0</v>
       </c>
       <c r="E473" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="F473" s="3" t="s">
         <v>859</v>
-      </c>
-      <c r="F473" s="3" t="s">
-        <v>860</v>
       </c>
       <c r="G473" s="7">
         <v>46886.0</v>
@@ -15285,7 +15282,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>42</v>
@@ -15297,10 +15294,10 @@
         <v>21.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G474" s="7">
         <v>46913.0</v>
@@ -15309,7 +15306,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>42</v>
@@ -15324,7 +15321,7 @@
         <v>352</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G475" s="7">
         <v>47158.0</v>
@@ -15333,7 +15330,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>34</v>
@@ -15357,7 +15354,7 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>34</v>
@@ -15372,7 +15369,7 @@
         <v>304</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G477" s="7">
         <v>46628.0</v>
@@ -15381,7 +15378,7 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>34</v>
@@ -15396,7 +15393,7 @@
         <v>304</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G478" s="7">
         <v>46649.0</v>
@@ -15405,7 +15402,7 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>34</v>
@@ -15420,7 +15417,7 @@
         <v>304</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G479" s="7">
         <v>46649.0</v>
@@ -15429,7 +15426,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>34</v>
@@ -15444,7 +15441,7 @@
         <v>304</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G480" s="7">
         <v>46775.0</v>
@@ -15453,7 +15450,7 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>34</v>
@@ -15477,7 +15474,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>34</v>
@@ -15492,7 +15489,7 @@
         <v>304</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G482" s="7">
         <v>46859.0</v>
@@ -15501,7 +15498,7 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>34</v>
@@ -15516,7 +15513,7 @@
         <v>304</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G483" s="7">
         <v>46880.0</v>
@@ -15525,7 +15522,7 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>34</v>
@@ -15540,7 +15537,7 @@
         <v>652</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G484" s="7">
         <v>46421.0</v>
@@ -15549,7 +15546,7 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>34</v>
@@ -15573,7 +15570,7 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>34</v>
@@ -15597,7 +15594,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>34</v>
@@ -15612,7 +15609,7 @@
         <v>652</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G487" s="7">
         <v>46725.0</v>
@@ -15621,7 +15618,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>34</v>
@@ -15636,7 +15633,7 @@
         <v>652</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G488" s="7">
         <v>46635.0</v>
@@ -15645,7 +15642,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>34</v>
@@ -15657,10 +15654,10 @@
         <v>10.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="G489" s="7">
         <v>46953.0</v>
@@ -15669,7 +15666,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>665</v>
@@ -15681,10 +15678,10 @@
         <v>6.0</v>
       </c>
       <c r="E490" s="2" t="s">
+        <v>979</v>
+      </c>
+      <c r="F490" s="3" t="s">
         <v>980</v>
-      </c>
-      <c r="F490" s="3" t="s">
-        <v>981</v>
       </c>
       <c r="G490" s="7">
         <v>46333.0</v>
@@ -15695,7 +15692,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>665</v>
@@ -15707,10 +15704,10 @@
         <v>7.0</v>
       </c>
       <c r="E491" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="F491" s="3" t="s">
         <v>983</v>
-      </c>
-      <c r="F491" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="G491" s="7">
         <v>46333.0</v>
@@ -15721,7 +15718,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>665</v>
@@ -15733,10 +15730,10 @@
         <v>8.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="G492" s="7">
         <v>46333.0</v>
@@ -15747,7 +15744,7 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>665</v>
@@ -15759,7 +15756,7 @@
         <v>9.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F493" s="3" t="s">
         <v>667</v>
@@ -15771,7 +15768,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>665</v>
@@ -15783,7 +15780,7 @@
         <v>3.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>690</v>
@@ -15797,7 +15794,7 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>42</v>
@@ -15809,7 +15806,7 @@
         <v>7.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F495" s="3">
         <v>11508.0</v>
@@ -15821,7 +15818,7 @@
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>42</v>
@@ -15833,10 +15830,10 @@
         <v>12.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F496" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G496" s="7">
         <v>46544.0</v>
@@ -15845,10 +15842,10 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
+        <v>994</v>
+      </c>
+      <c r="B497" s="2" t="s">
         <v>995</v>
-      </c>
-      <c r="B497" s="2" t="s">
-        <v>996</v>
       </c>
       <c r="C497" s="2" t="s">
         <v>12</v>
@@ -15857,10 +15854,10 @@
         <v>1.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G497" s="7">
         <v>46793.0</v>
@@ -15869,10 +15866,10 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B498" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="C498" s="2" t="s">
         <v>12</v>
@@ -15881,10 +15878,10 @@
         <v>1.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G498" s="7">
         <v>46767.0</v>
@@ -15893,7 +15890,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>42</v>
@@ -15905,10 +15902,10 @@
         <v>11.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G499" s="7">
         <v>46662.0</v>
@@ -15917,7 +15914,7 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>42</v>
@@ -15929,10 +15926,10 @@
         <v>11.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G500" s="7">
         <v>46711.0</v>
@@ -15941,7 +15938,7 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>34</v>
@@ -15956,7 +15953,7 @@
         <v>310</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G501" s="7">
         <v>46908.0</v>
@@ -15965,7 +15962,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>34</v>
@@ -15980,7 +15977,7 @@
         <v>625</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G502" s="7">
         <v>46911.0</v>
@@ -15989,7 +15986,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>34</v>
@@ -16001,10 +15998,10 @@
         <v>19.0</v>
       </c>
       <c r="E503" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F503" s="3" t="s">
         <v>1008</v>
-      </c>
-      <c r="F503" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="G503" s="7">
         <v>46463.0</v>
@@ -16013,7 +16010,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>42</v>
@@ -16025,10 +16022,10 @@
         <v>8.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G504" s="7">
         <v>46432.0</v>
@@ -16037,7 +16034,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>42</v>
@@ -16049,7 +16046,7 @@
         <v>8.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F505" s="3" t="s">
         <v>547</v>
@@ -16061,7 +16058,7 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>42</v>
@@ -16073,7 +16070,7 @@
         <v>8.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>373</v>
@@ -16085,7 +16082,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>42</v>
@@ -16097,10 +16094,10 @@
         <v>8.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F507" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G507" s="7">
         <v>46551.0</v>
@@ -16109,7 +16106,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>42</v>
@@ -16121,7 +16118,7 @@
         <v>8.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F508" s="3" t="s">
         <v>355</v>
@@ -16133,7 +16130,7 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>42</v>
@@ -16145,10 +16142,10 @@
         <v>8.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F509" s="3" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G509" s="7">
         <v>46877.0</v>
@@ -16157,7 +16154,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>34</v>
@@ -16169,7 +16166,7 @@
         <v>19.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>111</v>
@@ -16181,7 +16178,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>34</v>
@@ -16193,7 +16190,7 @@
         <v>19.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>373</v>
@@ -16205,7 +16202,7 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>34</v>
@@ -16217,10 +16214,10 @@
         <v>19.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F512" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G512" s="7">
         <v>46551.0</v>
@@ -16229,7 +16226,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>34</v>
@@ -16241,10 +16238,10 @@
         <v>19.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="G513" s="7">
         <v>46578.0</v>
@@ -16253,7 +16250,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>34</v>
@@ -16265,10 +16262,10 @@
         <v>19.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="G514" s="7">
         <v>46624.0</v>
@@ -16277,7 +16274,7 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>34</v>
@@ -16289,10 +16286,10 @@
         <v>19.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F515" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G515" s="7">
         <v>46624.0</v>
@@ -16301,7 +16298,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>34</v>
@@ -16313,10 +16310,10 @@
         <v>19.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G516" s="7">
         <v>46743.0</v>
@@ -16325,7 +16322,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>34</v>
@@ -16337,10 +16334,10 @@
         <v>19.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G517" s="7">
         <v>46813.0</v>
@@ -16349,7 +16346,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>34</v>
@@ -16361,10 +16358,10 @@
         <v>19.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G518" s="7">
         <v>46688.0</v>
@@ -16373,7 +16370,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>34</v>
@@ -16385,10 +16382,10 @@
         <v>19.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G519" s="7">
         <v>46745.0</v>
@@ -16397,7 +16394,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>42</v>
@@ -16409,10 +16406,10 @@
         <v>8.0</v>
       </c>
       <c r="E520" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F520" s="3" t="s">
         <v>1036</v>
-      </c>
-      <c r="F520" s="3" t="s">
-        <v>1037</v>
       </c>
       <c r="G520" s="7">
         <v>46578.0</v>
@@ -16421,7 +16418,7 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>42</v>
@@ -16433,7 +16430,7 @@
         <v>8.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>547</v>
@@ -16445,7 +16442,7 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>42</v>
@@ -16457,7 +16454,7 @@
         <v>8.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>373</v>
@@ -16469,7 +16466,7 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>42</v>
@@ -16481,10 +16478,10 @@
         <v>8.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F523" s="3" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G523" s="7">
         <v>46613.0</v>
@@ -16493,7 +16490,7 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>42</v>
@@ -16505,10 +16502,10 @@
         <v>8.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G524" s="7">
         <v>46635.0</v>
@@ -16517,7 +16514,7 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>42</v>
@@ -16529,10 +16526,10 @@
         <v>8.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G525" s="7">
         <v>46725.0</v>
@@ -16541,7 +16538,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>42</v>
@@ -16553,10 +16550,10 @@
         <v>8.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F526" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G526" s="7">
         <v>46635.0</v>
@@ -16565,7 +16562,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>42</v>
@@ -16577,10 +16574,10 @@
         <v>8.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F527" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G527" s="7">
         <v>46725.0</v>
@@ -16589,7 +16586,7 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>42</v>
@@ -16601,10 +16598,10 @@
         <v>8.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F528" s="3" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G528" s="7">
         <v>46743.0</v>
@@ -16613,7 +16610,7 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>42</v>
@@ -16625,10 +16622,10 @@
         <v>8.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F529" s="3" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G529" s="7">
         <v>46743.0</v>
@@ -16637,7 +16634,7 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>42</v>
@@ -16649,10 +16646,10 @@
         <v>8.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F530" s="3" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G530" s="7">
         <v>46834.0</v>
@@ -16661,7 +16658,7 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>42</v>
@@ -16673,10 +16670,10 @@
         <v>8.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="F531" s="3" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G531" s="7">
         <v>46872.0</v>
@@ -16685,7 +16682,7 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>42</v>
@@ -16697,7 +16694,7 @@
         <v>3.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F532" s="3">
         <v>11506.0</v>
@@ -16709,7 +16706,7 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>665</v>
@@ -16721,10 +16718,10 @@
         <v>4.0</v>
       </c>
       <c r="E533" s="2" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F533" s="3" t="s">
         <v>1055</v>
-      </c>
-      <c r="F533" s="3" t="s">
-        <v>1056</v>
       </c>
       <c r="G533" s="7">
         <v>46365.0</v>
@@ -16733,7 +16730,7 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>665</v>
@@ -16745,10 +16742,10 @@
         <v>5.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G534" s="7">
         <v>46363.0</v>
@@ -16757,7 +16754,7 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>665</v>
@@ -16769,10 +16766,10 @@
         <v>13.0</v>
       </c>
       <c r="E535" s="2" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F535" s="3" t="s">
         <v>1060</v>
-      </c>
-      <c r="F535" s="3" t="s">
-        <v>1061</v>
       </c>
       <c r="G535" s="7">
         <v>46332.0</v>
@@ -16783,7 +16780,7 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>42</v>
@@ -16795,7 +16792,7 @@
         <v>16.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F536" s="3" t="s">
         <v>680</v>
@@ -16807,7 +16804,7 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>42</v>
@@ -16819,10 +16816,10 @@
         <v>16.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="G537" s="7">
         <v>46457.0</v>
@@ -16831,7 +16828,7 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>42</v>
@@ -16843,7 +16840,7 @@
         <v>8.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F538" s="3" t="s">
         <v>143</v>
@@ -16855,7 +16852,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>42</v>
@@ -16867,7 +16864,7 @@
         <v>18.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F539" s="3" t="s">
         <v>633</v>
@@ -16879,7 +16876,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>42</v>
@@ -16891,10 +16888,10 @@
         <v>22.0</v>
       </c>
       <c r="E540" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F540" s="3" t="s">
         <v>1070</v>
-      </c>
-      <c r="F540" s="3" t="s">
-        <v>1071</v>
       </c>
       <c r="G540" s="7">
         <v>46397.0</v>
@@ -16903,7 +16900,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>42</v>
@@ -16915,10 +16912,10 @@
         <v>10.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="G541" s="7">
         <v>46578.0</v>
@@ -16927,7 +16924,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>42</v>
@@ -16939,7 +16936,7 @@
         <v>10.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>85</v>
@@ -16951,7 +16948,7 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>42</v>
@@ -16963,10 +16960,10 @@
         <v>10.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G543" s="7">
         <v>46635.0</v>
@@ -16975,7 +16972,7 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>42</v>
@@ -16987,10 +16984,10 @@
         <v>10.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G544" s="7">
         <v>46725.0</v>
@@ -16999,7 +16996,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>42</v>
@@ -17011,7 +17008,7 @@
         <v>10.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>355</v>
@@ -17023,7 +17020,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>42</v>
@@ -17035,7 +17032,7 @@
         <v>11.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>241</v>
@@ -17047,7 +17044,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>34</v>
@@ -17059,7 +17056,7 @@
         <v>18.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="F547" s="3" t="s">
         <v>17</v>
@@ -17069,7 +17066,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>34</v>
@@ -17081,7 +17078,7 @@
         <v>18.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="F548" s="3" t="s">
         <v>17</v>
@@ -17091,7 +17088,7 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>34</v>
@@ -17103,7 +17100,7 @@
         <v>13.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F549" s="3" t="s">
         <v>17</v>
@@ -17113,7 +17110,7 @@
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>34</v>
@@ -17125,10 +17122,10 @@
         <v>15.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G550" s="7">
         <v>46892.0</v>
@@ -17137,7 +17134,7 @@
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>665</v>
@@ -17149,7 +17146,7 @@
         <v>16.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F551" s="3" t="s">
         <v>690</v>
@@ -17161,7 +17158,7 @@
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>34</v>
@@ -17173,7 +17170,7 @@
         <v>8.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F552" s="3" t="s">
         <v>143</v>
@@ -17183,7 +17180,7 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>34</v>
@@ -17195,17 +17192,17 @@
         <v>12.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F553" s="3"/>
       <c r="G553" s="7"/>
       <c r="H553" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>42</v>
@@ -17217,7 +17214,7 @@
         <v>18.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="F554" s="3"/>
       <c r="G554" s="7"/>
@@ -17225,7 +17222,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>34</v>
@@ -17240,7 +17237,7 @@
         <v>555</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G555" s="7">
         <v>46403.0</v>
@@ -17249,7 +17246,7 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>42</v>
@@ -17261,7 +17258,7 @@
         <v>15.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F556" s="3" t="s">
         <v>143</v>
@@ -17273,7 +17270,7 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>42</v>
@@ -17297,7 +17294,7 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>42</v>
@@ -17309,17 +17306,17 @@
         <v>11.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G558" s="7"/>
       <c r="H558" s="2"/>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>42</v>
@@ -17331,17 +17328,17 @@
         <v>11.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G559" s="7"/>
       <c r="H559" s="2"/>
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>42</v>
@@ -17353,17 +17350,17 @@
         <v>11.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G560" s="7"/>
       <c r="H560" s="2"/>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>42</v>
@@ -17375,10 +17372,10 @@
         <v>11.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G561" s="7">
         <v>46792.0</v>
@@ -17387,7 +17384,7 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>42</v>
@@ -17399,10 +17396,10 @@
         <v>11.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G562" s="7">
         <v>46792.0</v>
@@ -17411,7 +17408,7 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>42</v>
@@ -17423,10 +17420,10 @@
         <v>11.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G563" s="7">
         <v>46767.0</v>
@@ -17435,7 +17432,7 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>42</v>
@@ -17447,10 +17444,10 @@
         <v>11.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G564" s="7">
         <v>46711.0</v>
@@ -17459,7 +17456,7 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>42</v>
@@ -17471,17 +17468,17 @@
         <v>13.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F565" s="3"/>
       <c r="G565" s="7"/>
       <c r="H565" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>34</v>
@@ -17493,7 +17490,7 @@
         <v>18.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F566" s="3" t="s">
         <v>17</v>
@@ -17503,7 +17500,7 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>34</v>
@@ -17515,7 +17512,7 @@
         <v>18.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F567" s="3" t="s">
         <v>17</v>
@@ -17525,7 +17522,7 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>34</v>
@@ -17537,7 +17534,7 @@
         <v>5.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="F568" s="3" t="s">
         <v>143</v>
@@ -17549,7 +17546,7 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>42</v>
@@ -17561,10 +17558,10 @@
         <v>19.0</v>
       </c>
       <c r="E569" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F569" s="3" t="s">
         <v>1118</v>
-      </c>
-      <c r="F569" s="3" t="s">
-        <v>1119</v>
       </c>
       <c r="G569" s="7">
         <v>46620.0</v>
@@ -17573,7 +17570,7 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>42</v>
@@ -17585,10 +17582,10 @@
         <v>20.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="G570" s="7">
         <v>46792.0</v>
@@ -17597,7 +17594,7 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>42</v>
@@ -17609,10 +17606,10 @@
         <v>20.0</v>
       </c>
       <c r="E571" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F571" s="3" t="s">
         <v>1123</v>
-      </c>
-      <c r="F571" s="3" t="s">
-        <v>1124</v>
       </c>
       <c r="G571" s="7">
         <v>46670.0</v>
@@ -17621,7 +17618,7 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>34</v>
@@ -17633,10 +17630,10 @@
         <v>15.0</v>
       </c>
       <c r="E572" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F572" s="3" t="s">
         <v>1126</v>
-      </c>
-      <c r="F572" s="3" t="s">
-        <v>1127</v>
       </c>
       <c r="G572" s="7">
         <v>46963.0</v>
@@ -17645,7 +17642,7 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>665</v>
@@ -17657,17 +17654,17 @@
         <v>15.0</v>
       </c>
       <c r="E573" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F573" s="3" t="s">
         <v>1129</v>
-      </c>
-      <c r="F573" s="3" t="s">
-        <v>1130</v>
       </c>
       <c r="G573" s="7"/>
       <c r="H573" s="2"/>
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>665</v>
@@ -17682,14 +17679,14 @@
         <v>310</v>
       </c>
       <c r="F574" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G574" s="7"/>
       <c r="H574" s="2"/>
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>42</v>
@@ -17701,7 +17698,7 @@
         <v>3.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="F575" s="3" t="s">
         <v>241</v>
@@ -17713,7 +17710,7 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>42</v>
@@ -17725,7 +17722,7 @@
         <v>3.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="F576" s="3" t="s">
         <v>241</v>
@@ -17737,7 +17734,7 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>42</v>
@@ -17749,7 +17746,7 @@
         <v>3.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="F577" s="3" t="s">
         <v>241</v>
@@ -17761,7 +17758,7 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>42</v>
@@ -17773,7 +17770,7 @@
         <v>3.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F578" s="3" t="s">
         <v>241</v>
@@ -17785,7 +17782,7 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>42</v>
@@ -17797,7 +17794,7 @@
         <v>3.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="F579" s="3" t="s">
         <v>241</v>
@@ -17809,7 +17806,7 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>34</v>
@@ -17824,7 +17821,7 @@
         <v>299</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="G580" s="7">
         <v>46461.0</v>
@@ -17833,7 +17830,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>292</v>
@@ -17857,7 +17854,7 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>665</v>
@@ -17869,10 +17866,10 @@
         <v>1.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G582" s="7">
         <v>46316.0</v>
@@ -17881,7 +17878,7 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>665</v>
@@ -17896,7 +17893,7 @@
         <v>625</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="G583" s="7">
         <v>46320.0</v>
@@ -17905,7 +17902,7 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>665</v>
@@ -17917,7 +17914,7 @@
         <v>3.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F584" s="3" t="s">
         <v>690</v>
@@ -17927,7 +17924,7 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>665</v>
@@ -17939,7 +17936,7 @@
         <v>3.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="F585" s="3" t="s">
         <v>690</v>
@@ -17949,7 +17946,7 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>665</v>
@@ -17961,7 +17958,7 @@
         <v>3.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F586" s="3" t="s">
         <v>690</v>
@@ -17971,7 +17968,7 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>665</v>
@@ -17983,7 +17980,7 @@
         <v>2.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="F587" s="3" t="s">
         <v>690</v>
@@ -17993,7 +17990,7 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>665</v>
@@ -18005,7 +18002,7 @@
         <v>2.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="F588" s="3" t="s">
         <v>690</v>
@@ -18015,7 +18012,7 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>34</v>
@@ -18027,10 +18024,10 @@
         <v>11.0</v>
       </c>
       <c r="E589" s="2" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F589" s="3" t="s">
         <v>1159</v>
-      </c>
-      <c r="F589" s="3" t="s">
-        <v>1160</v>
       </c>
       <c r="G589" s="7">
         <v>46982.0</v>
@@ -18039,7 +18036,7 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>34</v>
@@ -18051,10 +18048,10 @@
         <v>10.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G590" s="7">
         <v>46914.0</v>
@@ -18063,7 +18060,7 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>34</v>
@@ -18075,10 +18072,10 @@
         <v>15.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G591" s="7">
         <v>46914.0</v>
@@ -18087,7 +18084,7 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>42</v>
@@ -18099,10 +18096,10 @@
         <v>15.0</v>
       </c>
       <c r="E592" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F592" s="3" t="s">
         <v>1166</v>
-      </c>
-      <c r="F592" s="3" t="s">
-        <v>1167</v>
       </c>
       <c r="G592" s="7">
         <v>46963.0</v>
@@ -18111,7 +18108,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>42</v>
@@ -18123,10 +18120,10 @@
         <v>16.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F593" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G593" s="7">
         <v>46963.0</v>
@@ -18135,7 +18132,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>42</v>
@@ -18147,10 +18144,10 @@
         <v>11.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G594" s="7">
         <v>46421.0</v>
@@ -18159,7 +18156,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>42</v>
@@ -18171,10 +18168,10 @@
         <v>12.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="F595" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G595" s="7">
         <v>46710.0</v>
@@ -18183,7 +18180,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>42</v>
@@ -18195,10 +18192,10 @@
         <v>12.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G596" s="7">
         <v>46722.0</v>
@@ -18207,7 +18204,7 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>42</v>
@@ -18219,10 +18216,10 @@
         <v>15.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G597" s="7">
         <v>46620.0</v>
@@ -18231,7 +18228,7 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>42</v>
@@ -18243,10 +18240,10 @@
         <v>16.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G598" s="7">
         <v>46757.0</v>
@@ -18255,7 +18252,7 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>42</v>
@@ -18267,10 +18264,10 @@
         <v>12.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G599" s="7">
         <v>46757.0</v>
@@ -18279,7 +18276,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>42</v>
@@ -18291,10 +18288,10 @@
         <v>13.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G600" s="7">
         <v>46530.0</v>
@@ -18303,7 +18300,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>42</v>
@@ -18315,10 +18312,10 @@
         <v>11.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="F601" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G601" s="7">
         <v>46911.0</v>
@@ -18327,7 +18324,7 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>42</v>
@@ -18339,10 +18336,10 @@
         <v>15.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G602" s="7">
         <v>46480.0</v>
@@ -18351,7 +18348,7 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>42</v>
@@ -18363,10 +18360,10 @@
         <v>15.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G603" s="7">
         <v>46480.0</v>
@@ -18375,7 +18372,7 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>42</v>
@@ -18387,10 +18384,10 @@
         <v>15.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G604" s="7">
         <v>46793.0</v>
@@ -18399,7 +18396,7 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>42</v>
@@ -18411,10 +18408,10 @@
         <v>15.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="F605" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G605" s="7">
         <v>46793.0</v>
@@ -18423,7 +18420,7 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>42</v>
@@ -18435,10 +18432,10 @@
         <v>13.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F606" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G606" s="7">
         <v>46794.0</v>
@@ -18447,7 +18444,7 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>42</v>
@@ -18459,10 +18456,10 @@
         <v>13.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F607" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G607" s="7">
         <v>46487.0</v>
@@ -18471,7 +18468,7 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>42</v>
@@ -18483,10 +18480,10 @@
         <v>15.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G608" s="7">
         <v>46424.0</v>
@@ -18495,7 +18492,7 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>42</v>
@@ -18507,10 +18504,10 @@
         <v>16.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G609" s="7">
         <v>46757.0</v>
@@ -18519,7 +18516,7 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>665</v>
@@ -18531,7 +18528,7 @@
         <v>10.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="F610" s="3"/>
       <c r="G610" s="7"/>
@@ -18539,7 +18536,7 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>665</v>
@@ -18559,7 +18556,7 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>665</v>
@@ -18571,7 +18568,7 @@
         <v>10.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F612" s="3"/>
       <c r="G612" s="7"/>
@@ -18579,7 +18576,7 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>665</v>
@@ -18591,7 +18588,7 @@
         <v>10.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F613" s="3"/>
       <c r="G613" s="7"/>
@@ -18599,7 +18596,7 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>665</v>
@@ -18611,7 +18608,7 @@
         <v>10.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F614" s="3"/>
       <c r="G614" s="7"/>
@@ -18619,7 +18616,7 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>665</v>
@@ -18631,7 +18628,7 @@
         <v>10.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F615" s="3"/>
       <c r="G615" s="7"/>
@@ -18639,7 +18636,7 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>42</v>
@@ -18651,10 +18648,10 @@
         <v>12.0</v>
       </c>
       <c r="E616" s="2" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F616" s="3" t="s">
         <v>1208</v>
-      </c>
-      <c r="F616" s="3" t="s">
-        <v>1209</v>
       </c>
       <c r="G616" s="7">
         <v>46670.0</v>
@@ -18663,7 +18660,7 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>665</v>
@@ -18675,17 +18672,17 @@
         <v>3.0</v>
       </c>
       <c r="E617" s="2" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F617" s="3" t="s">
         <v>1211</v>
-      </c>
-      <c r="F617" s="3" t="s">
-        <v>1212</v>
       </c>
       <c r="G617" s="7"/>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>665</v>
@@ -18700,14 +18697,14 @@
         <v>701</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G618" s="7"/>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>42</v>
@@ -18719,10 +18716,10 @@
         <v>14.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G619" s="7">
         <v>46792.0</v>
@@ -18731,7 +18728,7 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>665</v>
@@ -18743,17 +18740,17 @@
         <v>3.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G620" s="7"/>
       <c r="H620" s="2"/>
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>665</v>
@@ -18765,17 +18762,17 @@
         <v>3.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F621" s="3" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G621" s="7"/>
       <c r="H621" s="2"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>42</v>
@@ -18787,17 +18784,17 @@
         <v>11.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F622" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G622" s="7"/>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>42</v>
@@ -18809,10 +18806,10 @@
         <v>16.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="F623" s="3" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G623" s="7">
         <v>46620.0</v>
@@ -18821,7 +18818,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>34</v>
@@ -18833,10 +18830,10 @@
         <v>16.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F624" s="3" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G624" s="7">
         <v>46982.0</v>
@@ -18845,7 +18842,7 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>11</v>
@@ -18857,7 +18854,7 @@
         <v>2.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="F625" s="3" t="s">
         <v>143</v>
@@ -18869,7 +18866,7 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>11</v>
@@ -18881,7 +18878,7 @@
         <v>2.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="F626" s="3" t="s">
         <v>143</v>
@@ -18893,7 +18890,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>11</v>
@@ -18905,7 +18902,7 @@
         <v>2.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="F627" s="3" t="s">
         <v>143</v>
@@ -18917,7 +18914,7 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>11</v>
@@ -18929,7 +18926,7 @@
         <v>2.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="F628" s="3" t="s">
         <v>143</v>
@@ -18941,7 +18938,7 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>11</v>
@@ -18953,7 +18950,7 @@
         <v>2.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="F629" s="3" t="s">
         <v>143</v>
@@ -18965,7 +18962,7 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>11</v>
@@ -18977,7 +18974,7 @@
         <v>2.0</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="F630" s="3" t="s">
         <v>143</v>
@@ -18989,7 +18986,7 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>665</v>
@@ -19001,10 +18998,10 @@
         <v>1.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G631" s="7">
         <v>46399.0</v>
@@ -19013,7 +19010,7 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>665</v>
@@ -19025,10 +19022,10 @@
         <v>1.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G632" s="7">
         <v>46398.0</v>
@@ -19037,7 +19034,7 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>665</v>
@@ -19049,10 +19046,10 @@
         <v>1.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G633" s="7">
         <v>46399.0</v>
@@ -19061,7 +19058,7 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>665</v>
@@ -19073,10 +19070,10 @@
         <v>1.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="F634" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G634" s="7">
         <v>46328.0</v>
@@ -19085,7 +19082,7 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>665</v>
@@ -19097,10 +19094,10 @@
         <v>1.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="F635" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G635" s="7">
         <v>46335.0</v>
@@ -19109,7 +19106,7 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>665</v>
@@ -19121,10 +19118,10 @@
         <v>1.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="F636" s="3" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="G636" s="7">
         <v>46398.0</v>
@@ -19133,7 +19130,7 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>665</v>
@@ -19155,7 +19152,7 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>665</v>
@@ -19167,7 +19164,7 @@
         <v>12.0</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="F638" s="3" t="s">
         <v>241</v>
@@ -19177,7 +19174,7 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>665</v>
@@ -19189,7 +19186,7 @@
         <v>12.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="F639" s="3" t="s">
         <v>690</v>
@@ -19199,7 +19196,7 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>665</v>
@@ -19211,17 +19208,17 @@
         <v>12.0</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F640" s="3" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G640" s="7"/>
       <c r="H640" s="2"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>665</v>
@@ -19233,7 +19230,7 @@
         <v>12.0</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="F641" s="3" t="s">
         <v>690</v>
@@ -19243,7 +19240,7 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>665</v>
@@ -19265,7 +19262,7 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>665</v>
@@ -19287,7 +19284,7 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>665</v>
@@ -19309,7 +19306,7 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>665</v>
@@ -19321,17 +19318,17 @@
         <v>12.0</v>
       </c>
       <c r="E645" s="2" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F645" s="3" t="s">
         <v>1261</v>
-      </c>
-      <c r="F645" s="3" t="s">
-        <v>1262</v>
       </c>
       <c r="G645" s="7"/>
       <c r="H645" s="2"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>665</v>
@@ -19343,7 +19340,7 @@
         <v>12.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="F646" s="3"/>
       <c r="G646" s="7"/>
@@ -19351,7 +19348,7 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>665</v>
@@ -19363,7 +19360,7 @@
         <v>12.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="F647" s="3" t="s">
         <v>233</v>
@@ -19373,7 +19370,7 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>42</v>
@@ -19385,7 +19382,7 @@
         <v>6.0</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F648" s="3">
         <v>11504.0</v>
@@ -19395,7 +19392,7 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>34</v>
@@ -19407,10 +19404,10 @@
         <v>15.0</v>
       </c>
       <c r="E649" s="2" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F649" s="3" t="s">
         <v>1268</v>
-      </c>
-      <c r="F649" s="3" t="s">
-        <v>1269</v>
       </c>
       <c r="G649" s="7">
         <v>46432.0</v>
@@ -19419,7 +19416,7 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>34</v>
@@ -19431,10 +19428,10 @@
         <v>15.0</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F650" s="3" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="G650" s="7">
         <v>46477.0</v>
@@ -19443,7 +19440,7 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>34</v>
@@ -19455,7 +19452,7 @@
         <v>15.0</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="F651" s="3" t="s">
         <v>376</v>
@@ -19467,7 +19464,7 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>34</v>
@@ -19479,21 +19476,21 @@
         <v>12.0</v>
       </c>
       <c r="E652" s="2" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F652" s="3" t="s">
         <v>1274</v>
-      </c>
-      <c r="F652" s="3" t="s">
-        <v>1275</v>
       </c>
       <c r="G652" s="7">
         <v>46949.0</v>
       </c>
       <c r="H652" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>34</v>
@@ -19505,17 +19502,17 @@
         <v>13.0</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F653" s="3"/>
       <c r="G653" s="7"/>
       <c r="H653" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>34</v>
@@ -19539,7 +19536,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>34</v>
@@ -19554,7 +19551,7 @@
         <v>310</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G655" s="7">
         <v>46908.0</v>
@@ -19563,7 +19560,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>34</v>
@@ -19575,7 +19572,7 @@
         <v>22.0</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="F656" s="3"/>
       <c r="G656" s="7"/>
@@ -19583,7 +19580,7 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>42</v>
@@ -19595,10 +19592,10 @@
         <v>22.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G657" s="7">
         <v>46670.0</v>
@@ -19607,7 +19604,7 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>42</v>
@@ -19619,10 +19616,10 @@
         <v>22.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G658" s="7">
         <v>46432.0</v>
@@ -19631,7 +19628,7 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>42</v>
@@ -19643,10 +19640,10 @@
         <v>22.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G659" s="7">
         <v>46913.0</v>
@@ -19655,7 +19652,7 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>42</v>
@@ -19670,7 +19667,7 @@
         <v>701</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G660" s="7">
         <v>46641.0</v>
@@ -19679,7 +19676,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>42</v>
@@ -19691,10 +19688,10 @@
         <v>18.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G661" s="7">
         <v>47158.0</v>
@@ -19703,7 +19700,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>42</v>
@@ -19715,10 +19712,10 @@
         <v>18.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="G662" s="7">
         <v>46792.0</v>
@@ -19727,7 +19724,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>42</v>
@@ -19739,10 +19736,10 @@
         <v>12.0</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G663" s="7">
         <v>46670.0</v>
@@ -19751,7 +19748,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>42</v>
@@ -19763,17 +19760,17 @@
         <v>12.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="G664" s="7"/>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>42</v>
@@ -19793,7 +19790,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>34</v>
@@ -19805,7 +19802,7 @@
         <v>20.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F666" s="3" t="s">
         <v>667</v>
@@ -19817,7 +19814,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>34</v>
@@ -19829,7 +19826,7 @@
         <v>20.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="F667" s="3" t="s">
         <v>667</v>
@@ -19841,7 +19838,7 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>34</v>
@@ -19865,7 +19862,7 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>34</v>
@@ -19877,10 +19874,10 @@
         <v>17.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="G669" s="7">
         <v>46988.0</v>
@@ -19889,7 +19886,7 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>34</v>
@@ -19901,17 +19898,17 @@
         <v>13.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="F670" s="3"/>
       <c r="G670" s="7"/>
       <c r="H670" s="2" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>42</v>
@@ -19923,10 +19920,10 @@
         <v>12.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F671" s="3" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G671" s="7">
         <v>46757.0</v>
@@ -19935,7 +19932,7 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>665</v>
@@ -19947,17 +19944,17 @@
         <v>9.0</v>
       </c>
       <c r="E672" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="F672" s="3" t="s">
         <v>1304</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>1305</v>
       </c>
       <c r="G672" s="7"/>
       <c r="H672" s="2"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>42</v>
@@ -19969,7 +19966,7 @@
         <v>1.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F673" s="3">
         <v>11508.0</v>
@@ -19979,7 +19976,7 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>34</v>
@@ -19994,7 +19991,7 @@
         <v>555</v>
       </c>
       <c r="F674" s="3" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="G674" s="7">
         <v>46338.0</v>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="1285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3337" uniqueCount="1335">
   <si>
     <t>ID</t>
   </si>
@@ -3866,6 +3866,156 @@
   </si>
   <si>
     <t>MM4-12入 媽媽咪亞義大利西洋梨果汁飲 250 ML</t>
+  </si>
+  <si>
+    <t>ID1790218789359</t>
+  </si>
+  <si>
+    <t>流動庫位區</t>
+  </si>
+  <si>
+    <t>CHRER-SS-K</t>
+  </si>
+  <si>
+    <t>1150923K6</t>
+  </si>
+  <si>
+    <t>ID1790229789879</t>
+  </si>
+  <si>
+    <t>亞里士EP335</t>
+  </si>
+  <si>
+    <t>ID1790230880553</t>
+  </si>
+  <si>
+    <t>CHRER-YK-K</t>
+  </si>
+  <si>
+    <t>ID1790230921449</t>
+  </si>
+  <si>
+    <t>ID1790231028666</t>
+  </si>
+  <si>
+    <t>26B-9/29 G9</t>
+  </si>
+  <si>
+    <t>ID1790231063409</t>
+  </si>
+  <si>
+    <t>TUE-KR-K G9</t>
+  </si>
+  <si>
+    <t>ID1790231137693</t>
+  </si>
+  <si>
+    <t>1141229K</t>
+  </si>
+  <si>
+    <t>ID1790231151539</t>
+  </si>
+  <si>
+    <t>ID1790231272737</t>
+  </si>
+  <si>
+    <t>1141027K</t>
+  </si>
+  <si>
+    <t>ID1790231504226</t>
+  </si>
+  <si>
+    <t>CKC2 G9</t>
+  </si>
+  <si>
+    <t>ID1790231506745</t>
+  </si>
+  <si>
+    <t>PRCFT-GO G9</t>
+  </si>
+  <si>
+    <t>ID1790231547197</t>
+  </si>
+  <si>
+    <t>RFM-KR-K G9</t>
+  </si>
+  <si>
+    <t>ID1790240251682</t>
+  </si>
+  <si>
+    <t>BLR20</t>
+  </si>
+  <si>
+    <t>ID1790240867862</t>
+  </si>
+  <si>
+    <t>26B 10/01 鴨車</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>ID1790240890309</t>
+  </si>
+  <si>
+    <t>ID1790240905379</t>
+  </si>
+  <si>
+    <t>30-32B 10/01 鴨車</t>
+  </si>
+  <si>
+    <t>ID1790240908607</t>
+  </si>
+  <si>
+    <t>TS 10/01 鴨車</t>
+  </si>
+  <si>
+    <t>ID1790240945365</t>
+  </si>
+  <si>
+    <t>ID1790240950818</t>
+  </si>
+  <si>
+    <t>12S 10/01 鴨車</t>
+  </si>
+  <si>
+    <t>ID1790240962705</t>
+  </si>
+  <si>
+    <t>60S 10/01 鴨車</t>
+  </si>
+  <si>
+    <t>ID1790240998134</t>
+  </si>
+  <si>
+    <t>ID1790241377413</t>
+  </si>
+  <si>
+    <t>PRSRM-GO-C</t>
+  </si>
+  <si>
+    <t>26#9</t>
+  </si>
+  <si>
+    <t>ID1790241391796</t>
+  </si>
+  <si>
+    <t>PRTDL-GO-C</t>
+  </si>
+  <si>
+    <t>ID1790241413190</t>
+  </si>
+  <si>
+    <t>ID1790241426045</t>
+  </si>
+  <si>
+    <t>CHTDL-GO-C</t>
+  </si>
+  <si>
+    <t>ID1790241449453</t>
+  </si>
+  <si>
+    <t>GO 9/29</t>
   </si>
 </sst>
 </file>
@@ -17195,7 +17345,9 @@
       <c r="G555" s="7">
         <v>46530.0</v>
       </c>
-      <c r="H555" s="2"/>
+      <c r="H555" s="2" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
@@ -18605,7 +18757,7 @@
         <v>644</v>
       </c>
       <c r="C616" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D616" s="2">
         <v>10.0</v>
@@ -19528,262 +19680,592 @@
       </c>
     </row>
     <row r="655">
-      <c r="A655" s="2"/>
-      <c r="B655" s="2"/>
-      <c r="C655" s="2"/>
-      <c r="D655" s="2"/>
-      <c r="E655" s="2"/>
-      <c r="F655" s="3"/>
-      <c r="G655" s="7"/>
+      <c r="A655" s="2" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B655" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C655" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D655" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E655" s="2" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F655" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G655" s="7">
+        <v>46941.0</v>
+      </c>
       <c r="H655" s="2"/>
     </row>
     <row r="656">
-      <c r="A656" s="2"/>
-      <c r="B656" s="2"/>
-      <c r="C656" s="2"/>
-      <c r="D656" s="2"/>
-      <c r="E656" s="2"/>
-      <c r="F656" s="3"/>
-      <c r="G656" s="7"/>
+      <c r="A656" s="2" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B656" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C656" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D656" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E656" s="2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F656" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G656" s="7">
+        <v>46535.0</v>
+      </c>
       <c r="H656" s="2"/>
     </row>
     <row r="657">
-      <c r="A657" s="2"/>
-      <c r="B657" s="2"/>
-      <c r="C657" s="2"/>
-      <c r="D657" s="2"/>
-      <c r="E657" s="2"/>
-      <c r="F657" s="3"/>
-      <c r="G657" s="7"/>
+      <c r="A657" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B657" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C657" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D657" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="E657" s="2" t="s">
+        <v>1292</v>
+      </c>
+      <c r="F657" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G657" s="7">
+        <v>46941.0</v>
+      </c>
       <c r="H657" s="2"/>
     </row>
     <row r="658">
-      <c r="A658" s="2"/>
-      <c r="B658" s="2"/>
-      <c r="C658" s="2"/>
-      <c r="D658" s="2"/>
-      <c r="E658" s="2"/>
-      <c r="F658" s="3"/>
-      <c r="G658" s="7"/>
+      <c r="A658" s="2" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B658" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C658" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D658" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="E658" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="F658" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="G658" s="7">
+        <v>46910.0</v>
+      </c>
       <c r="H658" s="2"/>
     </row>
     <row r="659">
-      <c r="A659" s="2"/>
-      <c r="B659" s="2"/>
-      <c r="C659" s="2"/>
-      <c r="D659" s="2"/>
-      <c r="E659" s="2"/>
-      <c r="F659" s="3"/>
+      <c r="A659" s="2" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B659" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C659" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D659" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E659" s="2" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F659" s="3">
+        <v>11508.0</v>
+      </c>
       <c r="G659" s="7"/>
       <c r="H659" s="2"/>
     </row>
     <row r="660">
-      <c r="A660" s="2"/>
-      <c r="B660" s="2"/>
-      <c r="C660" s="2"/>
-      <c r="D660" s="2"/>
-      <c r="E660" s="2"/>
-      <c r="F660" s="3"/>
+      <c r="A660" s="2" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B660" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C660" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D660" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E660" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F660" s="3" t="s">
+        <v>318</v>
+      </c>
       <c r="G660" s="7"/>
       <c r="H660" s="2"/>
     </row>
     <row r="661">
-      <c r="A661" s="2"/>
-      <c r="B661" s="2"/>
-      <c r="C661" s="2"/>
-      <c r="D661" s="2"/>
-      <c r="E661" s="2"/>
-      <c r="F661" s="3"/>
+      <c r="A661" s="2" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B661" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C661" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D661" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E661" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F661" s="3" t="s">
+        <v>1299</v>
+      </c>
       <c r="G661" s="7"/>
       <c r="H661" s="2"/>
     </row>
     <row r="662">
-      <c r="A662" s="2"/>
-      <c r="B662" s="2"/>
-      <c r="C662" s="2"/>
-      <c r="D662" s="2"/>
-      <c r="E662" s="2"/>
-      <c r="F662" s="3"/>
+      <c r="A662" s="2" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B662" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D662" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E662" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F662" s="3" t="s">
+        <v>897</v>
+      </c>
       <c r="G662" s="7"/>
       <c r="H662" s="2"/>
     </row>
     <row r="663">
-      <c r="A663" s="2"/>
-      <c r="B663" s="2"/>
-      <c r="C663" s="2"/>
-      <c r="D663" s="2"/>
-      <c r="E663" s="2"/>
-      <c r="F663" s="3"/>
+      <c r="A663" s="2" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B663" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C663" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D663" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E663" s="2" t="s">
+        <v>1297</v>
+      </c>
+      <c r="F663" s="3" t="s">
+        <v>1302</v>
+      </c>
       <c r="G663" s="7"/>
       <c r="H663" s="2"/>
     </row>
     <row r="664">
-      <c r="A664" s="2"/>
-      <c r="B664" s="2"/>
-      <c r="C664" s="2"/>
-      <c r="D664" s="2"/>
-      <c r="E664" s="2"/>
-      <c r="F664" s="3"/>
+      <c r="A664" s="2" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B664" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C664" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D664" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E664" s="2" t="s">
+        <v>1304</v>
+      </c>
+      <c r="F664" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="G664" s="7"/>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
-      <c r="A665" s="2"/>
-      <c r="B665" s="2"/>
-      <c r="C665" s="2"/>
-      <c r="D665" s="2"/>
-      <c r="E665" s="2"/>
-      <c r="F665" s="3"/>
+      <c r="A665" s="2" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B665" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C665" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D665" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E665" s="2" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F665" s="3" t="s">
+        <v>234</v>
+      </c>
       <c r="G665" s="7"/>
       <c r="H665" s="2"/>
     </row>
     <row r="666">
-      <c r="A666" s="2"/>
-      <c r="B666" s="2"/>
-      <c r="C666" s="2"/>
-      <c r="D666" s="2"/>
-      <c r="E666" s="2"/>
-      <c r="F666" s="3"/>
+      <c r="A666" s="2" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B666" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C666" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D666" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E666" s="2" t="s">
+        <v>1308</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>946</v>
+      </c>
       <c r="G666" s="7"/>
       <c r="H666" s="2"/>
     </row>
     <row r="667">
-      <c r="A667" s="2"/>
-      <c r="B667" s="2"/>
-      <c r="C667" s="2"/>
-      <c r="D667" s="2"/>
-      <c r="E667" s="2"/>
-      <c r="F667" s="3"/>
-      <c r="G667" s="7"/>
+      <c r="A667" s="2" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B667" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C667" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D667" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E667" s="2" t="s">
+        <v>1310</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G667" s="7">
+        <v>46707.0</v>
+      </c>
       <c r="H667" s="2"/>
     </row>
     <row r="668">
-      <c r="A668" s="2"/>
-      <c r="B668" s="2"/>
-      <c r="C668" s="2"/>
-      <c r="D668" s="2"/>
-      <c r="E668" s="2"/>
-      <c r="F668" s="3"/>
+      <c r="A668" s="2" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B668" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C668" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D668" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E668" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G668" s="7"/>
       <c r="H668" s="2"/>
     </row>
     <row r="669">
-      <c r="A669" s="2"/>
-      <c r="B669" s="2"/>
-      <c r="C669" s="2"/>
-      <c r="D669" s="2"/>
-      <c r="E669" s="2"/>
-      <c r="F669" s="3"/>
+      <c r="A669" s="2" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D669" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E669" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G669" s="7"/>
       <c r="H669" s="2"/>
     </row>
     <row r="670">
-      <c r="A670" s="2"/>
-      <c r="B670" s="2"/>
-      <c r="C670" s="2"/>
-      <c r="D670" s="2"/>
-      <c r="E670" s="2"/>
-      <c r="F670" s="3"/>
+      <c r="A670" s="2" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D670" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E670" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="F670" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G670" s="7"/>
       <c r="H670" s="2"/>
     </row>
     <row r="671">
-      <c r="A671" s="2"/>
-      <c r="B671" s="2"/>
-      <c r="C671" s="2"/>
-      <c r="D671" s="2"/>
-      <c r="E671" s="2"/>
-      <c r="F671" s="3"/>
+      <c r="A671" s="2" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D671" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E671" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F671" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G671" s="7"/>
       <c r="H671" s="2"/>
     </row>
     <row r="672">
-      <c r="A672" s="2"/>
-      <c r="B672" s="2"/>
-      <c r="C672" s="2"/>
-      <c r="D672" s="2"/>
-      <c r="E672" s="2"/>
-      <c r="F672" s="3"/>
+      <c r="A672" s="2" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D672" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E672" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G672" s="7"/>
       <c r="H672" s="2"/>
     </row>
     <row r="673">
-      <c r="A673" s="2"/>
-      <c r="B673" s="2"/>
-      <c r="C673" s="2"/>
-      <c r="D673" s="2"/>
-      <c r="E673" s="2"/>
-      <c r="F673" s="3"/>
+      <c r="A673" s="2" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D673" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E673" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G673" s="7"/>
       <c r="H673" s="2"/>
     </row>
     <row r="674">
-      <c r="A674" s="2"/>
-      <c r="B674" s="2"/>
-      <c r="C674" s="2"/>
-      <c r="D674" s="2"/>
-      <c r="E674" s="2"/>
-      <c r="F674" s="3"/>
+      <c r="A674" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B674" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C674" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D674" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E674" s="2" t="s">
+        <v>1323</v>
+      </c>
+      <c r="F674" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G674" s="7"/>
       <c r="H674" s="2"/>
     </row>
     <row r="675">
-      <c r="A675" s="2"/>
-      <c r="B675" s="2"/>
-      <c r="C675" s="2"/>
-      <c r="D675" s="2"/>
-      <c r="E675" s="2"/>
-      <c r="F675" s="3"/>
+      <c r="A675" s="2" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B675" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C675" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D675" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E675" s="2" t="s">
+        <v>1312</v>
+      </c>
+      <c r="F675" s="3" t="s">
+        <v>1313</v>
+      </c>
       <c r="G675" s="7"/>
       <c r="H675" s="2"/>
     </row>
     <row r="676">
-      <c r="A676" s="2"/>
-      <c r="B676" s="2"/>
-      <c r="C676" s="2"/>
-      <c r="D676" s="2"/>
-      <c r="E676" s="2"/>
-      <c r="F676" s="3"/>
-      <c r="G676" s="7"/>
+      <c r="A676" s="2" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B676" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C676" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D676" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E676" s="2" t="s">
+        <v>1326</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G676" s="7">
+        <v>46405.0</v>
+      </c>
       <c r="H676" s="2"/>
     </row>
     <row r="677">
-      <c r="A677" s="2"/>
-      <c r="B677" s="2"/>
-      <c r="C677" s="2"/>
-      <c r="D677" s="2"/>
-      <c r="E677" s="2"/>
-      <c r="F677" s="3"/>
-      <c r="G677" s="7"/>
+      <c r="A677" s="2" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B677" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C677" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D677" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E677" s="2" t="s">
+        <v>1329</v>
+      </c>
+      <c r="F677" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G677" s="7">
+        <v>46405.0</v>
+      </c>
       <c r="H677" s="2"/>
     </row>
     <row r="678">
-      <c r="A678" s="2"/>
-      <c r="B678" s="2"/>
-      <c r="C678" s="2"/>
-      <c r="D678" s="2"/>
-      <c r="E678" s="2"/>
-      <c r="F678" s="3"/>
-      <c r="G678" s="7"/>
+      <c r="A678" s="2" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B678" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C678" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D678" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E678" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="F678" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G678" s="7">
+        <v>46402.0</v>
+      </c>
       <c r="H678" s="2"/>
     </row>
     <row r="679">
-      <c r="A679" s="2"/>
-      <c r="B679" s="2"/>
-      <c r="C679" s="2"/>
-      <c r="D679" s="2"/>
-      <c r="E679" s="2"/>
-      <c r="F679" s="3"/>
-      <c r="G679" s="7"/>
+      <c r="A679" s="2" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B679" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C679" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D679" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E679" s="2" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F679" s="3" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G679" s="7">
+        <v>46402.0</v>
+      </c>
       <c r="H679" s="2"/>
     </row>
     <row r="680">
-      <c r="A680" s="2"/>
-      <c r="B680" s="2"/>
-      <c r="C680" s="2"/>
-      <c r="D680" s="2"/>
-      <c r="E680" s="2"/>
-      <c r="F680" s="3"/>
+      <c r="A680" s="2" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B680" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="C680" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D680" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>1327</v>
+      </c>
       <c r="G680" s="7"/>
       <c r="H680" s="2"/>
     </row>
@@ -24537,186 +25019,6 @@
       <c r="G1155" s="7"/>
       <c r="H1155" s="2"/>
     </row>
-    <row r="1156">
-      <c r="A1156" s="2"/>
-      <c r="B1156" s="2"/>
-      <c r="C1156" s="2"/>
-      <c r="D1156" s="2"/>
-      <c r="E1156" s="2"/>
-      <c r="F1156" s="3"/>
-      <c r="G1156" s="7"/>
-      <c r="H1156" s="2"/>
-    </row>
-    <row r="1157">
-      <c r="A1157" s="2"/>
-      <c r="B1157" s="2"/>
-      <c r="C1157" s="2"/>
-      <c r="D1157" s="2"/>
-      <c r="E1157" s="2"/>
-      <c r="F1157" s="3"/>
-      <c r="G1157" s="7"/>
-      <c r="H1157" s="2"/>
-    </row>
-    <row r="1158">
-      <c r="A1158" s="2"/>
-      <c r="B1158" s="2"/>
-      <c r="C1158" s="2"/>
-      <c r="D1158" s="2"/>
-      <c r="E1158" s="2"/>
-      <c r="F1158" s="3"/>
-      <c r="G1158" s="7"/>
-      <c r="H1158" s="2"/>
-    </row>
-    <row r="1159">
-      <c r="A1159" s="2"/>
-      <c r="B1159" s="2"/>
-      <c r="C1159" s="2"/>
-      <c r="D1159" s="2"/>
-      <c r="E1159" s="2"/>
-      <c r="F1159" s="3"/>
-      <c r="G1159" s="7"/>
-      <c r="H1159" s="2"/>
-    </row>
-    <row r="1160">
-      <c r="A1160" s="2"/>
-      <c r="B1160" s="2"/>
-      <c r="C1160" s="2"/>
-      <c r="D1160" s="2"/>
-      <c r="E1160" s="2"/>
-      <c r="F1160" s="3"/>
-      <c r="G1160" s="7"/>
-      <c r="H1160" s="2"/>
-    </row>
-    <row r="1161">
-      <c r="A1161" s="2"/>
-      <c r="B1161" s="2"/>
-      <c r="C1161" s="2"/>
-      <c r="D1161" s="2"/>
-      <c r="E1161" s="2"/>
-      <c r="F1161" s="3"/>
-      <c r="G1161" s="7"/>
-      <c r="H1161" s="2"/>
-    </row>
-    <row r="1162">
-      <c r="A1162" s="2"/>
-      <c r="B1162" s="2"/>
-      <c r="C1162" s="2"/>
-      <c r="D1162" s="2"/>
-      <c r="E1162" s="2"/>
-      <c r="F1162" s="3"/>
-      <c r="G1162" s="7"/>
-      <c r="H1162" s="2"/>
-    </row>
-    <row r="1163">
-      <c r="A1163" s="2"/>
-      <c r="B1163" s="2"/>
-      <c r="C1163" s="2"/>
-      <c r="D1163" s="2"/>
-      <c r="E1163" s="2"/>
-      <c r="F1163" s="3"/>
-      <c r="G1163" s="7"/>
-      <c r="H1163" s="2"/>
-    </row>
-    <row r="1164">
-      <c r="A1164" s="2"/>
-      <c r="B1164" s="2"/>
-      <c r="C1164" s="2"/>
-      <c r="D1164" s="2"/>
-      <c r="E1164" s="2"/>
-      <c r="F1164" s="3"/>
-      <c r="G1164" s="7"/>
-      <c r="H1164" s="2"/>
-    </row>
-    <row r="1165">
-      <c r="A1165" s="2"/>
-      <c r="B1165" s="2"/>
-      <c r="C1165" s="2"/>
-      <c r="D1165" s="2"/>
-      <c r="E1165" s="2"/>
-      <c r="F1165" s="3"/>
-      <c r="G1165" s="7"/>
-      <c r="H1165" s="2"/>
-    </row>
-    <row r="1166">
-      <c r="A1166" s="2"/>
-      <c r="B1166" s="2"/>
-      <c r="C1166" s="2"/>
-      <c r="D1166" s="2"/>
-      <c r="E1166" s="2"/>
-      <c r="F1166" s="3"/>
-      <c r="G1166" s="7"/>
-      <c r="H1166" s="2"/>
-    </row>
-    <row r="1167">
-      <c r="A1167" s="2"/>
-      <c r="B1167" s="2"/>
-      <c r="C1167" s="2"/>
-      <c r="D1167" s="2"/>
-      <c r="E1167" s="2"/>
-      <c r="F1167" s="3"/>
-      <c r="G1167" s="7"/>
-      <c r="H1167" s="2"/>
-    </row>
-    <row r="1168">
-      <c r="A1168" s="2"/>
-      <c r="B1168" s="2"/>
-      <c r="C1168" s="2"/>
-      <c r="D1168" s="2"/>
-      <c r="E1168" s="2"/>
-      <c r="F1168" s="3"/>
-      <c r="G1168" s="7"/>
-      <c r="H1168" s="2"/>
-    </row>
-    <row r="1169">
-      <c r="A1169" s="2"/>
-      <c r="B1169" s="2"/>
-      <c r="C1169" s="2"/>
-      <c r="D1169" s="2"/>
-      <c r="E1169" s="2"/>
-      <c r="F1169" s="3"/>
-      <c r="G1169" s="7"/>
-      <c r="H1169" s="2"/>
-    </row>
-    <row r="1170">
-      <c r="A1170" s="2"/>
-      <c r="B1170" s="2"/>
-      <c r="C1170" s="2"/>
-      <c r="D1170" s="2"/>
-      <c r="E1170" s="2"/>
-      <c r="F1170" s="3"/>
-      <c r="G1170" s="7"/>
-      <c r="H1170" s="2"/>
-    </row>
-    <row r="1171">
-      <c r="A1171" s="2"/>
-      <c r="B1171" s="2"/>
-      <c r="C1171" s="2"/>
-      <c r="D1171" s="2"/>
-      <c r="E1171" s="2"/>
-      <c r="F1171" s="3"/>
-      <c r="G1171" s="7"/>
-      <c r="H1171" s="2"/>
-    </row>
-    <row r="1172">
-      <c r="A1172" s="2"/>
-      <c r="B1172" s="2"/>
-      <c r="C1172" s="2"/>
-      <c r="D1172" s="2"/>
-      <c r="E1172" s="2"/>
-      <c r="F1172" s="3"/>
-      <c r="G1172" s="7"/>
-      <c r="H1172" s="2"/>
-    </row>
-    <row r="1173">
-      <c r="A1173" s="2"/>
-      <c r="B1173" s="2"/>
-      <c r="C1173" s="2"/>
-      <c r="D1173" s="2"/>
-      <c r="E1173" s="2"/>
-      <c r="F1173" s="3"/>
-      <c r="G1173" s="7"/>
-      <c r="H1173" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3398" uniqueCount="1360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3407" uniqueCount="1365">
   <si>
     <t>ID</t>
   </si>
@@ -4091,6 +4091,21 @@
   </si>
   <si>
     <t>YK 冷藏牛 10/6</t>
+  </si>
+  <si>
+    <t>ID1790827548413</t>
+  </si>
+  <si>
+    <t>TS</t>
+  </si>
+  <si>
+    <t>ID1790827587466</t>
+  </si>
+  <si>
+    <t>12S</t>
+  </si>
+  <si>
+    <t>手推車</t>
   </si>
 </sst>
 </file>
@@ -20639,24 +20654,50 @@
       <c r="H693" s="2"/>
     </row>
     <row r="694">
-      <c r="A694" s="2"/>
-      <c r="B694" s="2"/>
-      <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
-      <c r="E694" s="2"/>
-      <c r="F694" s="3"/>
+      <c r="A694" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D694" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E694" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F694" s="3">
+        <v>11509.0</v>
+      </c>
       <c r="G694" s="7"/>
       <c r="H694" s="2"/>
     </row>
     <row r="695">
-      <c r="A695" s="2"/>
-      <c r="B695" s="2"/>
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
-      <c r="E695" s="2"/>
-      <c r="F695" s="3"/>
+      <c r="A695" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D695" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="F695" s="3">
+        <v>11509.0</v>
+      </c>
       <c r="G695" s="7"/>
-      <c r="H695" s="2"/>
+      <c r="H695" s="2" t="s">
+        <v>1364</v>
+      </c>
     </row>
     <row r="696">
       <c r="A696" s="2"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3342" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3354" uniqueCount="1338">
   <si>
     <t>ID</t>
   </si>
@@ -3928,6 +3928,9 @@
     <t>ID1790755358925</t>
   </si>
   <si>
+    <t>26#30</t>
+  </si>
+  <si>
     <t>ID1790755368205</t>
   </si>
   <si>
@@ -3955,12 +3958,6 @@
     <t>CHTDL-YK-C</t>
   </si>
   <si>
-    <t>ID1790755449100</t>
-  </si>
-  <si>
-    <t>YK 冷藏牛 10/6</t>
-  </si>
-  <si>
     <t>ID1790827548413</t>
   </si>
   <si>
@@ -4019,6 +4016,15 @@
   </si>
   <si>
     <t>26#84</t>
+  </si>
+  <si>
+    <t>ID1791282403166</t>
+  </si>
+  <si>
+    <t>DCC</t>
+  </si>
+  <si>
+    <t>ID1791282433375</t>
   </si>
 </sst>
 </file>
@@ -19938,13 +19944,17 @@
       <c r="E664" s="2" t="s">
         <v>1207</v>
       </c>
-      <c r="F664" s="3"/>
-      <c r="G664" s="7"/>
+      <c r="F664" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G664" s="7">
+        <v>46366.0</v>
+      </c>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>1281</v>
@@ -19958,13 +19968,17 @@
       <c r="E665" s="2" t="s">
         <v>956</v>
       </c>
-      <c r="F665" s="3"/>
-      <c r="G665" s="7"/>
+      <c r="F665" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G665" s="7">
+        <v>46366.0</v>
+      </c>
       <c r="H665" s="2"/>
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>1281</v>
@@ -19976,15 +19990,19 @@
         <v>3.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F666" s="3"/>
-      <c r="G666" s="7"/>
+        <v>1308</v>
+      </c>
+      <c r="F666" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G666" s="7">
+        <v>46367.0</v>
+      </c>
       <c r="H666" s="2"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>1281</v>
@@ -19996,15 +20014,19 @@
         <v>3.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1309</v>
-      </c>
-      <c r="F667" s="3"/>
-      <c r="G667" s="7"/>
+        <v>1310</v>
+      </c>
+      <c r="F667" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G667" s="7">
+        <v>46366.0</v>
+      </c>
       <c r="H667" s="2"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>1281</v>
@@ -20016,15 +20038,19 @@
         <v>3.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F668" s="3"/>
-      <c r="G668" s="7"/>
+        <v>1312</v>
+      </c>
+      <c r="F668" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G668" s="7">
+        <v>46366.0</v>
+      </c>
       <c r="H668" s="2"/>
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>1281</v>
@@ -20036,143 +20062,149 @@
         <v>3.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1313</v>
-      </c>
-      <c r="F669" s="3"/>
-      <c r="G669" s="7"/>
+        <v>1314</v>
+      </c>
+      <c r="F669" s="3" t="s">
+        <v>1305</v>
+      </c>
+      <c r="G669" s="7">
+        <v>46366.0</v>
+      </c>
       <c r="H669" s="2"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1281</v>
+        <v>32</v>
       </c>
       <c r="C670" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D670" s="2">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F670" s="3"/>
-      <c r="G670" s="7"/>
+        <v>1316</v>
+      </c>
+      <c r="F670" s="3">
+        <v>11509.0</v>
+      </c>
+      <c r="G670" s="7">
+        <v>46826.0</v>
+      </c>
       <c r="H670" s="2"/>
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>32</v>
+        <v>701</v>
       </c>
       <c r="C671" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D671" s="2">
-        <v>20.0</v>
+        <v>9.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F671" s="3">
         <v>11509.0</v>
       </c>
-      <c r="G671" s="7">
-        <v>46826.0</v>
-      </c>
-      <c r="H671" s="2"/>
+      <c r="G671" s="7"/>
+      <c r="H671" s="2" t="s">
+        <v>1319</v>
+      </c>
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>701</v>
+        <v>32</v>
       </c>
       <c r="C672" s="2" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="D672" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="F672" s="3">
-        <v>11509.0</v>
+        <v>11508.0</v>
       </c>
       <c r="G672" s="7"/>
-      <c r="H672" s="2" t="s">
-        <v>1320</v>
-      </c>
+      <c r="H672" s="2"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D673" s="2">
-        <v>6.0</v>
+        <v>21.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="F673" s="3">
-        <v>11508.0</v>
+        <v>1323</v>
+      </c>
+      <c r="F673" s="3" t="s">
+        <v>1324</v>
       </c>
       <c r="G673" s="7"/>
       <c r="H673" s="2"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="D674" s="2">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="F674" s="3" t="s">
-        <v>1325</v>
-      </c>
-      <c r="G674" s="7"/>
+        <v>141</v>
+      </c>
+      <c r="G674" s="7">
+        <v>46522.0</v>
+      </c>
       <c r="H674" s="2"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>40</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="D675" s="2">
-        <v>1.0</v>
+        <v>22.0</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="F675" s="3" t="s">
-        <v>141</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="F675" s="3"/>
       <c r="G675" s="7">
         <v>46522.0</v>
       </c>
@@ -20186,41 +20218,43 @@
         <v>40</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D676" s="2">
-        <v>22.0</v>
+        <v>18.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F676" s="3"/>
+        <v>1329</v>
+      </c>
+      <c r="F676" s="3" t="s">
+        <v>858</v>
+      </c>
       <c r="G676" s="7">
-        <v>46522.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H676" s="2"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>40</v>
+        <v>701</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D677" s="2">
-        <v>18.0</v>
+        <v>10.0</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>1330</v>
+        <v>589</v>
       </c>
       <c r="F677" s="3" t="s">
-        <v>858</v>
+        <v>233</v>
       </c>
       <c r="G677" s="7">
-        <v>46963.0</v>
+        <v>47022.0</v>
       </c>
       <c r="H677" s="2"/>
     </row>
@@ -20229,83 +20263,97 @@
         <v>1331</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>701</v>
+        <v>628</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D678" s="2">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>589</v>
+        <v>1295</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>233</v>
+        <v>1287</v>
       </c>
       <c r="G678" s="7">
-        <v>47022.0</v>
-      </c>
-      <c r="H678" s="2"/>
+        <v>46348.0</v>
+      </c>
+      <c r="H678" s="2" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
         <v>1332</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>628</v>
+        <v>40</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D679" s="2">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1295</v>
+        <v>1333</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>1287</v>
+        <v>1334</v>
       </c>
       <c r="G679" s="7">
-        <v>46348.0</v>
-      </c>
-      <c r="H679" s="2" t="s">
-        <v>587</v>
-      </c>
+        <v>46830.0</v>
+      </c>
+      <c r="H679" s="2"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="B680" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C680" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D680" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E680" s="2" t="s">
+        <v>1336</v>
+      </c>
+      <c r="F680" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G680" s="7">
+        <v>46662.0</v>
+      </c>
+      <c r="H680" s="2"/>
+    </row>
+    <row r="681">
+      <c r="A681" s="2" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B681" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C680" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D680" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E680" s="2" t="s">
-        <v>1334</v>
-      </c>
-      <c r="F680" s="3" t="s">
-        <v>1335</v>
-      </c>
-      <c r="G680" s="7">
-        <v>46830.0</v>
-      </c>
-      <c r="H680" s="2"/>
-    </row>
-    <row r="681">
-      <c r="A681" s="2"/>
-      <c r="B681" s="2"/>
-      <c r="C681" s="2"/>
-      <c r="D681" s="2"/>
-      <c r="E681" s="2"/>
-      <c r="F681" s="3"/>
-      <c r="G681" s="7"/>
+      <c r="C681" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D681" s="2">
+        <v>22.0</v>
+      </c>
+      <c r="E681" s="2" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F681" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="G681" s="7">
+        <v>47181.0</v>
+      </c>
       <c r="H681" s="2"/>
     </row>
     <row r="682">
@@ -24488,16 +24536,6 @@
       <c r="G1099" s="7"/>
       <c r="H1099" s="2"/>
     </row>
-    <row r="1100">
-      <c r="A1100" s="2"/>
-      <c r="B1100" s="2"/>
-      <c r="C1100" s="2"/>
-      <c r="D1100" s="2"/>
-      <c r="E1100" s="2"/>
-      <c r="F1100" s="3"/>
-      <c r="G1100" s="7"/>
-      <c r="H1100" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -24017,16 +24017,6 @@
       <c r="G1048" s="7"/>
       <c r="H1048" s="2"/>
     </row>
-    <row r="1049">
-      <c r="A1049" s="2"/>
-      <c r="B1049" s="2"/>
-      <c r="C1049" s="2"/>
-      <c r="D1049" s="2"/>
-      <c r="E1049" s="2"/>
-      <c r="F1049" s="3"/>
-      <c r="G1049" s="7"/>
-      <c r="H1049" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -23970,16 +23970,6 @@
       <c r="G1024" s="7"/>
       <c r="H1024" s="2"/>
     </row>
-    <row r="1025">
-      <c r="A1025" s="2"/>
-      <c r="B1025" s="2"/>
-      <c r="C1025" s="2"/>
-      <c r="D1025" s="2"/>
-      <c r="E1025" s="2"/>
-      <c r="F1025" s="3"/>
-      <c r="G1025" s="7"/>
-      <c r="H1025" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3405" uniqueCount="1351">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3415" uniqueCount="1355">
   <si>
     <t>ID</t>
   </si>
@@ -4064,6 +4064,18 @@
   </si>
   <si>
     <t>ID1791790184915</t>
+  </si>
+  <si>
+    <t>ID1792030856013</t>
+  </si>
+  <si>
+    <t>1180415S</t>
+  </si>
+  <si>
+    <t>ID1792030867014</t>
+  </si>
+  <si>
+    <t>1180819S</t>
   </si>
 </sst>
 </file>
@@ -20671,23 +20683,51 @@
       <c r="H694" s="2"/>
     </row>
     <row r="695">
-      <c r="A695" s="2"/>
-      <c r="B695" s="2"/>
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
-      <c r="E695" s="2"/>
-      <c r="F695" s="3"/>
-      <c r="G695" s="7"/>
+      <c r="A695" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D695" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>1352</v>
+      </c>
+      <c r="G695" s="7">
+        <v>46794.0</v>
+      </c>
       <c r="H695" s="2"/>
     </row>
     <row r="696">
-      <c r="A696" s="2"/>
-      <c r="B696" s="2"/>
-      <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
-      <c r="E696" s="2"/>
-      <c r="F696" s="3"/>
-      <c r="G696" s="7"/>
+      <c r="A696" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D696" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E696" s="2" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="G696" s="7">
+        <v>46793.0</v>
+      </c>
       <c r="H696" s="2"/>
     </row>
     <row r="697">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3325" uniqueCount="1329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="1326">
   <si>
     <t>ID</t>
   </si>
@@ -3910,39 +3910,39 @@
     <t>ID1791789970422</t>
   </si>
   <si>
+    <t>ID1791790034642</t>
+  </si>
+  <si>
+    <t>ID1791790057648</t>
+  </si>
+  <si>
+    <t>PRRER-280-320-YK</t>
+  </si>
+  <si>
+    <t>ID1791790088657</t>
+  </si>
+  <si>
+    <t>ID1791790114880</t>
+  </si>
+  <si>
+    <t>PRSRL-260-300-GO</t>
+  </si>
+  <si>
+    <t>ID1791790146072</t>
+  </si>
+  <si>
+    <t>TL-4CM-KR</t>
+  </si>
+  <si>
+    <t>ID1791790184915</t>
+  </si>
+  <si>
+    <t>ID1792030856013</t>
+  </si>
+  <si>
     <t>PRCER-十字切-GO</t>
   </si>
   <si>
-    <t>ID1791790034642</t>
-  </si>
-  <si>
-    <t>ID1791790057648</t>
-  </si>
-  <si>
-    <t>PRRER-280-320-YK</t>
-  </si>
-  <si>
-    <t>ID1791790088657</t>
-  </si>
-  <si>
-    <t>ID1791790114880</t>
-  </si>
-  <si>
-    <t>PRSRL-260-300-GO</t>
-  </si>
-  <si>
-    <t>ID1791790146072</t>
-  </si>
-  <si>
-    <t>TL-4CM-KR</t>
-  </si>
-  <si>
-    <t>ID1791790184915</t>
-  </si>
-  <si>
-    <t>ID1792030856013</t>
-  </si>
-  <si>
     <t>1180415S</t>
   </si>
   <si>
@@ -3982,22 +3982,13 @@
     <t>ID1792046535549</t>
   </si>
   <si>
-    <t>ID1792046551582</t>
-  </si>
-  <si>
-    <t>PRCFT-GO</t>
-  </si>
-  <si>
     <t>ID1792046579229</t>
   </si>
   <si>
     <t>PSRER-HF</t>
   </si>
   <si>
-    <t>ID1792046634040</t>
-  </si>
-  <si>
-    <t>10/15 G9</t>
+    <t>手推車</t>
   </si>
 </sst>
 </file>
@@ -19782,7 +19773,7 @@
         <v>13.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1299</v>
+        <v>286</v>
       </c>
       <c r="F660" s="3" t="s">
         <v>1286</v>
@@ -19794,7 +19785,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>37</v>
@@ -19818,7 +19809,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>37</v>
@@ -19830,7 +19821,7 @@
         <v>12.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F662" s="3" t="s">
         <v>1286</v>
@@ -19842,7 +19833,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>37</v>
@@ -19866,7 +19857,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>37</v>
@@ -19878,7 +19869,7 @@
         <v>13.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
       <c r="F664" s="3" t="s">
         <v>1286</v>
@@ -19890,7 +19881,7 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>37</v>
@@ -19902,7 +19893,7 @@
         <v>13.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F665" s="3" t="s">
         <v>1286</v>
@@ -19914,7 +19905,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>37</v>
@@ -19938,7 +19929,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>37</v>
@@ -19950,7 +19941,7 @@
         <v>19.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="F667" s="3" t="s">
         <v>1310</v>
@@ -19974,7 +19965,7 @@
         <v>19.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1299</v>
+        <v>1309</v>
       </c>
       <c r="F668" s="3" t="s">
         <v>1312</v>
@@ -20125,13 +20116,13 @@
         <v>1322</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1272</v>
+        <v>37</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D675" s="2">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="E675" s="2" t="s">
         <v>45</v>
@@ -20149,13 +20140,13 @@
         <v>1323</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1272</v>
+        <v>640</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D676" s="2">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="E676" s="2" t="s">
         <v>1324</v>
@@ -20164,50 +20155,28 @@
         <v>218</v>
       </c>
       <c r="G676" s="7">
-        <v>46759.0</v>
-      </c>
-      <c r="H676" s="2"/>
+        <v>47231.0</v>
+      </c>
+      <c r="H676" s="2" t="s">
+        <v>1325</v>
+      </c>
     </row>
     <row r="677">
-      <c r="A677" s="2" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B677" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C677" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D677" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E677" s="2" t="s">
-        <v>1326</v>
-      </c>
-      <c r="F677" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="G677" s="7">
-        <v>47231.0</v>
-      </c>
+      <c r="A677" s="2"/>
+      <c r="B677" s="2"/>
+      <c r="C677" s="2"/>
+      <c r="D677" s="2"/>
+      <c r="E677" s="2"/>
+      <c r="F677" s="3"/>
+      <c r="G677" s="7"/>
       <c r="H677" s="2"/>
     </row>
     <row r="678">
-      <c r="A678" s="2" t="s">
-        <v>1327</v>
-      </c>
-      <c r="B678" s="2" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C678" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D678" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E678" s="2" t="s">
-        <v>1328</v>
-      </c>
+      <c r="A678" s="2"/>
+      <c r="B678" s="2"/>
+      <c r="C678" s="2"/>
+      <c r="D678" s="2"/>
+      <c r="E678" s="2"/>
       <c r="F678" s="3"/>
       <c r="G678" s="7"/>
       <c r="H678" s="2"/>
@@ -23372,26 +23341,6 @@
       <c r="G994" s="7"/>
       <c r="H994" s="2"/>
     </row>
-    <row r="995">
-      <c r="A995" s="2"/>
-      <c r="B995" s="2"/>
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
-      <c r="E995" s="2"/>
-      <c r="F995" s="3"/>
-      <c r="G995" s="7"/>
-      <c r="H995" s="2"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="2"/>
-      <c r="B996" s="2"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="F996" s="3"/>
-      <c r="G996" s="7"/>
-      <c r="H996" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3317" uniqueCount="1326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="1327">
   <si>
     <t>ID</t>
   </si>
@@ -373,6 +373,9 @@
     <t>QB(鴨骨)</t>
   </si>
   <si>
+    <t>產品出清</t>
+  </si>
+  <si>
     <t>ID39835414951126</t>
   </si>
   <si>
@@ -877,9 +880,6 @@
     <t>1150409S</t>
   </si>
   <si>
-    <t>產品出清</t>
-  </si>
-  <si>
     <t>BLR20-HF</t>
   </si>
   <si>
@@ -2845,6 +2845,9 @@
     <t>26#72</t>
   </si>
   <si>
+    <t>[產品異常] 轉凍 1151019K6  2028.07.29</t>
+  </si>
+  <si>
     <t>ID1788854015329</t>
   </si>
   <si>
@@ -3274,7 +3277,7 @@
     <t>26#74</t>
   </si>
   <si>
-    <t>【30日】</t>
+    <t>[產品異常] 轉凍 1151019K6  2028.07.30</t>
   </si>
   <si>
     <t>ID1790136818504</t>
@@ -5344,11 +5347,13 @@
       <c r="G44" s="14">
         <v>46917.0</v>
       </c>
-      <c r="H44" s="11"/>
+      <c r="H44" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B45" s="11" t="s">
         <v>37</v>
@@ -5360,7 +5365,7 @@
         <v>9.0</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F45" s="17"/>
       <c r="G45" s="14">
@@ -5370,7 +5375,7 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>37</v>
@@ -5382,7 +5387,7 @@
         <v>9.0</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F46" s="13">
         <v>11504.0</v>
@@ -5391,12 +5396,12 @@
         <v>46848.0</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="10" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B47" s="11" t="s">
         <v>37</v>
@@ -5408,7 +5413,7 @@
         <v>6.0</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F47" s="17"/>
       <c r="G47" s="14">
@@ -5418,7 +5423,7 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B48" s="11" t="s">
         <v>37</v>
@@ -5430,7 +5435,7 @@
         <v>16.0</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F48" s="13">
         <v>11504.0</v>
@@ -5440,7 +5445,7 @@
     </row>
     <row r="49">
       <c r="A49" s="10" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B49" s="11" t="s">
         <v>37</v>
@@ -5460,7 +5465,7 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>37</v>
@@ -5472,17 +5477,17 @@
         <v>4.0</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F50" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G50" s="15"/>
       <c r="H50" s="15"/>
     </row>
     <row r="51">
       <c r="A51" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B51" s="11" t="s">
         <v>37</v>
@@ -5494,7 +5499,7 @@
         <v>6.0</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F51" s="13" t="s">
         <v>17</v>
@@ -5506,7 +5511,7 @@
     </row>
     <row r="52">
       <c r="A52" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B52" s="11" t="s">
         <v>32</v>
@@ -5518,7 +5523,7 @@
         <v>13.0</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="14">
@@ -5528,7 +5533,7 @@
     </row>
     <row r="53">
       <c r="A53" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B53" s="11" t="s">
         <v>37</v>
@@ -5540,10 +5545,10 @@
         <v>2.0</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G53" s="14">
         <v>46949.0</v>
@@ -5552,7 +5557,7 @@
     </row>
     <row r="54">
       <c r="A54" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B54" s="11" t="s">
         <v>37</v>
@@ -5564,10 +5569,10 @@
         <v>2.0</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F54" s="13" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G54" s="14">
         <v>46757.0</v>
@@ -5576,7 +5581,7 @@
     </row>
     <row r="55">
       <c r="A55" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B55" s="11" t="s">
         <v>32</v>
@@ -5588,18 +5593,18 @@
         <v>12.0</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F55" s="17"/>
       <c r="G55" s="14"/>
       <c r="H55" s="11"/>
       <c r="I55" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>32</v>
@@ -5611,7 +5616,7 @@
         <v>12.0</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F56" s="17"/>
       <c r="G56" s="14">
@@ -5621,7 +5626,7 @@
     </row>
     <row r="57">
       <c r="A57" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>32</v>
@@ -5633,7 +5638,7 @@
         <v>9.0</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F57" s="13" t="s">
         <v>20</v>
@@ -5643,7 +5648,7 @@
     </row>
     <row r="58">
       <c r="A58" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>32</v>
@@ -5655,10 +5660,10 @@
         <v>2.0</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G58" s="14">
         <v>46716.0</v>
@@ -5667,7 +5672,7 @@
     </row>
     <row r="59">
       <c r="A59" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B59" s="11" t="s">
         <v>32</v>
@@ -5679,10 +5684,10 @@
         <v>8.0</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G59" s="14">
         <v>46675.0</v>
@@ -5691,7 +5696,7 @@
     </row>
     <row r="60">
       <c r="A60" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>32</v>
@@ -5703,10 +5708,10 @@
         <v>8.0</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G60" s="14">
         <v>46703.0</v>
@@ -5715,7 +5720,7 @@
     </row>
     <row r="61">
       <c r="A61" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B61" s="11" t="s">
         <v>32</v>
@@ -5730,7 +5735,7 @@
         <v>61</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G61" s="14">
         <v>46703.0</v>
@@ -5739,7 +5744,7 @@
     </row>
     <row r="62">
       <c r="A62" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>32</v>
@@ -5751,10 +5756,10 @@
         <v>7.0</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F62" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="G62" s="14">
         <v>46577.0</v>
@@ -5763,7 +5768,7 @@
     </row>
     <row r="63">
       <c r="A63" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B63" s="11" t="s">
         <v>32</v>
@@ -5775,10 +5780,10 @@
         <v>7.0</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F63" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G63" s="14">
         <v>46612.0</v>
@@ -5787,7 +5792,7 @@
     </row>
     <row r="64">
       <c r="A64" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B64" s="11" t="s">
         <v>32</v>
@@ -5799,10 +5804,10 @@
         <v>7.0</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F64" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G64" s="14">
         <v>46634.0</v>
@@ -5811,7 +5816,7 @@
     </row>
     <row r="65">
       <c r="A65" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B65" s="11" t="s">
         <v>32</v>
@@ -5823,24 +5828,24 @@
         <v>11.0</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F65" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G65" s="14">
         <v>46157.0</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>32</v>
@@ -5852,24 +5857,24 @@
         <v>11.0</v>
       </c>
       <c r="E66" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F66" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G66" s="14">
         <v>46152.0</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B67" s="11" t="s">
         <v>32</v>
@@ -5881,24 +5886,24 @@
         <v>11.0</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F67" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G67" s="14">
         <v>46148.0</v>
       </c>
       <c r="H67" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I67" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B68" s="11" t="s">
         <v>32</v>
@@ -5910,24 +5915,24 @@
         <v>11.0</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F68" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G68" s="14">
         <v>46148.0</v>
       </c>
       <c r="H68" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B69" s="11" t="s">
         <v>32</v>
@@ -5939,10 +5944,10 @@
         <v>20.0</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F69" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G69" s="14">
         <v>46999.0</v>
@@ -5951,7 +5956,7 @@
     </row>
     <row r="70">
       <c r="A70" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>32</v>
@@ -5963,7 +5968,7 @@
         <v>19.0</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F70" s="13" t="s">
         <v>20</v>
@@ -5975,7 +5980,7 @@
     </row>
     <row r="71">
       <c r="A71" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B71" s="11" t="s">
         <v>32</v>
@@ -5987,7 +5992,7 @@
         <v>17.0</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F71" s="13" t="s">
         <v>20</v>
@@ -5999,7 +6004,7 @@
     </row>
     <row r="72">
       <c r="A72" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>32</v>
@@ -6011,10 +6016,10 @@
         <v>15.0</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F72" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G72" s="14">
         <v>46626.0</v>
@@ -6023,7 +6028,7 @@
     </row>
     <row r="73">
       <c r="A73" s="10" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B73" s="11" t="s">
         <v>32</v>
@@ -6035,7 +6040,7 @@
         <v>14.0</v>
       </c>
       <c r="E73" s="11" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F73" s="13" t="s">
         <v>20</v>
@@ -6047,7 +6052,7 @@
     </row>
     <row r="74">
       <c r="A74" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B74" s="11" t="s">
         <v>32</v>
@@ -6059,7 +6064,7 @@
         <v>14.0</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F74" s="13" t="s">
         <v>17</v>
@@ -6071,7 +6076,7 @@
     </row>
     <row r="75">
       <c r="A75" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B75" s="11" t="s">
         <v>32</v>
@@ -6083,7 +6088,7 @@
         <v>14.0</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F75" s="13" t="s">
         <v>20</v>
@@ -6095,7 +6100,7 @@
     </row>
     <row r="76">
       <c r="A76" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>32</v>
@@ -6107,7 +6112,7 @@
         <v>12.0</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F76" s="13" t="s">
         <v>20</v>
@@ -6119,7 +6124,7 @@
     </row>
     <row r="77">
       <c r="A77" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B77" s="11" t="s">
         <v>32</v>
@@ -6131,10 +6136,10 @@
         <v>12.0</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F77" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G77" s="14">
         <v>46662.0</v>
@@ -6143,7 +6148,7 @@
     </row>
     <row r="78">
       <c r="A78" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B78" s="11" t="s">
         <v>32</v>
@@ -6158,14 +6163,14 @@
         <v>52</v>
       </c>
       <c r="F78" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G78" s="15"/>
       <c r="H78" s="11"/>
     </row>
     <row r="79">
       <c r="A79" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B79" s="11" t="s">
         <v>37</v>
@@ -6177,7 +6182,7 @@
         <v>5.0</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F79" s="13" t="s">
         <v>17</v>
@@ -6189,7 +6194,7 @@
     </row>
     <row r="80">
       <c r="A80" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>32</v>
@@ -6201,7 +6206,7 @@
         <v>9.0</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F80" s="13" t="s">
         <v>20</v>
@@ -6213,7 +6218,7 @@
     </row>
     <row r="81">
       <c r="A81" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B81" s="11" t="s">
         <v>32</v>
@@ -6225,17 +6230,17 @@
         <v>8.0</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F81" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G81" s="15"/>
       <c r="H81" s="15"/>
     </row>
     <row r="82">
       <c r="A82" s="10" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>32</v>
@@ -6247,10 +6252,10 @@
         <v>7.0</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F82" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G82" s="14">
         <v>46549.0</v>
@@ -6259,7 +6264,7 @@
     </row>
     <row r="83">
       <c r="A83" s="10" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>32</v>
@@ -6271,10 +6276,10 @@
         <v>7.0</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F83" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G83" s="14">
         <v>46760.0</v>
@@ -6283,7 +6288,7 @@
     </row>
     <row r="84">
       <c r="A84" s="10" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>32</v>
@@ -6295,21 +6300,21 @@
         <v>6.0</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G84" s="14">
         <v>46631.0</v>
       </c>
       <c r="H84" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B85" s="11" t="s">
         <v>32</v>
@@ -6321,10 +6326,10 @@
         <v>5.0</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F85" s="13" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G85" s="14">
         <v>46711.0</v>
@@ -6333,7 +6338,7 @@
     </row>
     <row r="86">
       <c r="A86" s="10" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>32</v>
@@ -6345,10 +6350,10 @@
         <v>5.0</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F86" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G86" s="14">
         <v>47182.0</v>
@@ -6357,7 +6362,7 @@
     </row>
     <row r="87">
       <c r="A87" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B87" s="11" t="s">
         <v>32</v>
@@ -6369,19 +6374,19 @@
         <v>3.0</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F87" s="17"/>
       <c r="G87" s="14">
         <v>46662.0</v>
       </c>
       <c r="H87" s="11" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B88" s="11" t="s">
         <v>32</v>
@@ -6393,7 +6398,7 @@
         <v>3.0</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F88" s="17"/>
       <c r="G88" s="14">
@@ -6403,7 +6408,7 @@
     </row>
     <row r="89">
       <c r="A89" s="10" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B89" s="11" t="s">
         <v>32</v>
@@ -6415,7 +6420,7 @@
         <v>1.0</v>
       </c>
       <c r="E89" s="15" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F89" s="17"/>
       <c r="G89" s="15"/>
@@ -6423,7 +6428,7 @@
     </row>
     <row r="90">
       <c r="A90" s="10" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>32</v>
@@ -6435,10 +6440,10 @@
         <v>4.0</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F90" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G90" s="14">
         <v>46731.0</v>
@@ -6447,7 +6452,7 @@
     </row>
     <row r="91">
       <c r="A91" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B91" s="11" t="s">
         <v>32</v>
@@ -6459,7 +6464,7 @@
         <v>10.0</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F91" s="13" t="s">
         <v>20</v>
@@ -6471,7 +6476,7 @@
     </row>
     <row r="92">
       <c r="A92" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>32</v>
@@ -6483,7 +6488,7 @@
         <v>17.0</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F92" s="13" t="s">
         <v>20</v>
@@ -6495,7 +6500,7 @@
     </row>
     <row r="93">
       <c r="A93" s="10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>32</v>
@@ -6510,7 +6515,7 @@
         <v>68</v>
       </c>
       <c r="F93" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G93" s="14">
         <v>46767.0</v>
@@ -6519,7 +6524,7 @@
     </row>
     <row r="94">
       <c r="A94" s="10" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B94" s="11" t="s">
         <v>37</v>
@@ -6534,7 +6539,7 @@
         <v>97</v>
       </c>
       <c r="F94" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G94" s="14">
         <v>46691.0</v>
@@ -6543,7 +6548,7 @@
     </row>
     <row r="95">
       <c r="A95" s="10" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B95" s="11" t="s">
         <v>37</v>
@@ -6558,16 +6563,16 @@
         <v>65</v>
       </c>
       <c r="F95" s="13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G95" s="15"/>
       <c r="H95" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>32</v>
@@ -6579,24 +6584,24 @@
         <v>11.0</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F96" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G96" s="14">
         <v>46162.0</v>
       </c>
       <c r="H96" s="11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B97" s="11" t="s">
         <v>37</v>
@@ -6608,10 +6613,10 @@
         <v>16.0</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F97" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G97" s="14">
         <v>46481.0</v>
@@ -6620,7 +6625,7 @@
     </row>
     <row r="98">
       <c r="A98" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B98" s="11" t="s">
         <v>37</v>
@@ -6632,7 +6637,7 @@
         <v>3.0</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F98" s="13" t="s">
         <v>17</v>
@@ -6644,7 +6649,7 @@
     </row>
     <row r="99">
       <c r="A99" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B99" s="11" t="s">
         <v>37</v>
@@ -6656,10 +6661,10 @@
         <v>21.0</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F99" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G99" s="14">
         <v>46759.0</v>
@@ -6668,7 +6673,7 @@
     </row>
     <row r="100">
       <c r="A100" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>37</v>
@@ -6680,10 +6685,10 @@
         <v>15.0</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F100" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G100" s="14">
         <v>46544.0</v>
@@ -6692,7 +6697,7 @@
     </row>
     <row r="101">
       <c r="A101" s="10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B101" s="11" t="s">
         <v>37</v>
@@ -6704,10 +6709,10 @@
         <v>19.0</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F101" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G101" s="14">
         <v>46394.0</v>
@@ -6716,7 +6721,7 @@
     </row>
     <row r="102">
       <c r="A102" s="10" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B102" s="11" t="s">
         <v>32</v>
@@ -6728,10 +6733,10 @@
         <v>16.0</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F102" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="G102" s="14">
         <v>46949.0</v>
@@ -6740,7 +6745,7 @@
     </row>
     <row r="103">
       <c r="A103" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B103" s="11" t="s">
         <v>37</v>
@@ -6752,7 +6757,7 @@
         <v>19.0</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F103" s="13" t="s">
         <v>17</v>
@@ -6764,7 +6769,7 @@
     </row>
     <row r="104">
       <c r="A104" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B104" s="11" t="s">
         <v>37</v>
@@ -6776,10 +6781,10 @@
         <v>18.0</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F104" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G104" s="14">
         <v>46530.0</v>
@@ -6788,7 +6793,7 @@
     </row>
     <row r="105">
       <c r="A105" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B105" s="11" t="s">
         <v>37</v>
@@ -6800,7 +6805,7 @@
         <v>17.0</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F105" s="17"/>
       <c r="G105" s="14">
@@ -6810,7 +6815,7 @@
     </row>
     <row r="106">
       <c r="A106" s="10" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>32</v>
@@ -6822,7 +6827,7 @@
         <v>13.0</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F106" s="17"/>
       <c r="G106" s="14">
@@ -6835,7 +6840,7 @@
         <v>1.774363425608E12</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>12</v>
@@ -6844,11 +6849,11 @@
         <v>1.0</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F107" s="4"/>
       <c r="H107" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108">
@@ -6856,7 +6861,7 @@
         <v>1.774363487217E12</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>12</v>
@@ -6865,11 +6870,11 @@
         <v>2.0</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F108" s="4"/>
       <c r="H108" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109">
@@ -6886,7 +6891,7 @@
         <v>6.0</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>17</v>
@@ -6909,10 +6914,10 @@
         <v>21.0</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G110" s="7">
         <v>46929.0</v>
@@ -6933,7 +6938,7 @@
         <v>1.0</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>55</v>
@@ -6956,7 +6961,7 @@
         <v>13.0</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F112" s="4"/>
       <c r="G112" s="7">
@@ -6978,7 +6983,7 @@
         <v>11.0</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F113" s="4"/>
       <c r="G113" s="7">
@@ -6999,7 +7004,7 @@
         <v>12.0</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F114" s="4"/>
       <c r="G114" s="7">
@@ -7023,7 +7028,7 @@
         <v>45</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G115" s="7">
         <v>46949.0</v>
@@ -7043,10 +7048,10 @@
         <v>1.0</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G116" s="7">
         <v>46752.0</v>
@@ -7066,7 +7071,7 @@
         <v>12.0</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F117" s="4"/>
       <c r="G117" s="7">
@@ -7087,7 +7092,7 @@
         <v>13.0</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F118" s="4"/>
       <c r="G118" s="7">
@@ -7108,7 +7113,7 @@
         <v>18.0</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>17</v>
@@ -7131,7 +7136,7 @@
         <v>3.0</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>17</v>
@@ -7151,10 +7156,10 @@
         <v>16.0</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="122">
@@ -7171,10 +7176,10 @@
         <v>15.0</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G122" s="7">
         <v>46681.0</v>
@@ -7194,10 +7199,10 @@
         <v>17.0</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G123" s="7">
         <v>46947.0</v>
@@ -7217,7 +7222,7 @@
         <v>2.0</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F124" s="3">
         <v>11506.0</v>
@@ -7238,10 +7243,10 @@
         <v>8.0</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G125" s="7">
         <v>46949.0</v>
@@ -7261,10 +7266,10 @@
         <v>19.0</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G126" s="7">
         <v>46794.0</v>
@@ -7287,13 +7292,13 @@
         <v>45</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G127" s="7">
         <v>46794.0</v>
       </c>
       <c r="H127" s="2" t="s">
-        <v>288</v>
+        <v>120</v>
       </c>
     </row>
     <row r="128">
@@ -7365,7 +7370,7 @@
         <v>46769.0</v>
       </c>
       <c r="H130" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="131">
@@ -7385,7 +7390,7 @@
         <v>292</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G131" s="7">
         <v>46794.0</v>
@@ -7476,7 +7481,7 @@
         <v>298</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G135" s="7">
         <v>47286.0</v>
@@ -7849,7 +7854,7 @@
         <v>4.0</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>313</v>
@@ -7872,7 +7877,7 @@
         <v>5.0</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>314</v>
@@ -7898,7 +7903,7 @@
         <v>315</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G153" s="7">
         <v>46771.0</v>
@@ -7967,7 +7972,7 @@
         <v>319</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G156" s="7">
         <v>46947.0</v>
@@ -8126,7 +8131,7 @@
         <v>334</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G164" s="7">
         <v>46716.0</v>
@@ -8192,7 +8197,7 @@
         <v>342</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G167" s="7">
         <v>46716.0</v>
@@ -8430,13 +8435,13 @@
         <v>365</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="G177" s="7">
         <v>46162.0</v>
       </c>
       <c r="H177" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="178">
@@ -8474,13 +8479,13 @@
         <v>369</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G179" s="7">
         <v>46152.0</v>
       </c>
       <c r="H179" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="180">
@@ -8546,7 +8551,7 @@
         <v>315</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G182" s="7">
         <v>46771.0</v>
@@ -8569,7 +8574,7 @@
         <v>378</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G183" s="7">
         <v>46738.0</v>
@@ -8742,7 +8747,7 @@
         <v>393</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G191" s="7">
         <v>46488.0</v>
@@ -8766,7 +8771,7 @@
         <v>395</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G192" s="7">
         <v>46408.0</v>
@@ -8790,7 +8795,7 @@
         <v>397</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G193" s="7">
         <v>46473.0</v>
@@ -8814,7 +8819,7 @@
         <v>399</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G194" s="7">
         <v>46758.0</v>
@@ -8838,7 +8843,7 @@
         <v>401</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G195" s="7">
         <v>47154.0</v>
@@ -8862,7 +8867,7 @@
         <v>403</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G196" s="7">
         <v>47146.0</v>
@@ -8885,7 +8890,7 @@
         <v>405</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G197" s="7">
         <v>46988.0</v>
@@ -8927,7 +8932,7 @@
         <v>409</v>
       </c>
       <c r="F199" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G199" s="7">
         <v>47123.0</v>
@@ -8973,7 +8978,7 @@
         <v>411</v>
       </c>
       <c r="F201" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G201" s="7">
         <v>46752.0</v>
@@ -8999,7 +9004,7 @@
         <v>321</v>
       </c>
       <c r="H202" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="203">
@@ -9016,7 +9021,7 @@
         <v>1.0</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>417</v>
@@ -9479,7 +9484,7 @@
         <v>459</v>
       </c>
       <c r="F225" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G225" s="7">
         <v>46759.0</v>
@@ -9491,7 +9496,7 @@
         <v>460</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>12</v>
@@ -9503,7 +9508,7 @@
         <v>461</v>
       </c>
       <c r="F226" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G226" s="7">
         <v>46406.0</v>
@@ -9514,7 +9519,7 @@
         <v>462</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>12</v>
@@ -9526,7 +9531,7 @@
         <v>463</v>
       </c>
       <c r="F227" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G227" s="7">
         <v>46406.0</v>
@@ -9537,7 +9542,7 @@
         <v>464</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>12</v>
@@ -9549,7 +9554,7 @@
         <v>465</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G228" s="7">
         <v>46406.0</v>
@@ -9560,7 +9565,7 @@
         <v>466</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>12</v>
@@ -9572,7 +9577,7 @@
         <v>467</v>
       </c>
       <c r="F229" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G229" s="7">
         <v>46387.0</v>
@@ -9583,7 +9588,7 @@
         <v>468</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>12</v>
@@ -9595,7 +9600,7 @@
         <v>469</v>
       </c>
       <c r="F230" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G230" s="7">
         <v>46387.0</v>
@@ -9606,7 +9611,7 @@
         <v>470</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>12</v>
@@ -9618,7 +9623,7 @@
         <v>471</v>
       </c>
       <c r="F231" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G231" s="7">
         <v>46387.0</v>
@@ -9629,7 +9634,7 @@
         <v>472</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>12</v>
@@ -9641,7 +9646,7 @@
         <v>473</v>
       </c>
       <c r="F232" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G232" s="7">
         <v>46387.0</v>
@@ -9652,7 +9657,7 @@
         <v>474</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>12</v>
@@ -9676,7 +9681,7 @@
         <v>477</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>12</v>
@@ -9699,7 +9704,7 @@
         <v>479</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>12</v>
@@ -9722,7 +9727,7 @@
         <v>481</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>12</v>
@@ -9745,7 +9750,7 @@
         <v>483</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C237" s="2" t="s">
         <v>12</v>
@@ -9757,7 +9762,7 @@
         <v>484</v>
       </c>
       <c r="F237" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G237" s="7">
         <v>46392.0</v>
@@ -9769,7 +9774,7 @@
         <v>485</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>12</v>
@@ -9781,7 +9786,7 @@
         <v>486</v>
       </c>
       <c r="F238" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G238" s="7">
         <v>46366.0</v>
@@ -10095,7 +10100,7 @@
         <v>512</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G252" s="7">
         <v>46766.0</v>
@@ -10212,7 +10217,7 @@
         <v>22</v>
       </c>
       <c r="F257" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G257" s="7">
         <v>47531.0</v>
@@ -10236,7 +10241,7 @@
         <v>22</v>
       </c>
       <c r="F258" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G258" s="7">
         <v>47531.0</v>
@@ -10260,7 +10265,7 @@
         <v>22</v>
       </c>
       <c r="F259" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G259" s="7">
         <v>47531.0</v>
@@ -10284,7 +10289,7 @@
         <v>527</v>
       </c>
       <c r="F260" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G260" s="7">
         <v>46767.0</v>
@@ -10356,7 +10361,7 @@
         <v>533</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>12</v>
@@ -10368,7 +10373,7 @@
         <v>534</v>
       </c>
       <c r="F264" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G264" s="7">
         <v>46387.0</v>
@@ -10380,7 +10385,7 @@
         <v>535</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>12</v>
@@ -10392,7 +10397,7 @@
         <v>536</v>
       </c>
       <c r="F265" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G265" s="7">
         <v>46387.0</v>
@@ -10404,7 +10409,7 @@
         <v>537</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>12</v>
@@ -10416,7 +10421,7 @@
         <v>538</v>
       </c>
       <c r="F266" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G266" s="7">
         <v>46387.0</v>
@@ -10428,7 +10433,7 @@
         <v>539</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>12</v>
@@ -10440,7 +10445,7 @@
         <v>540</v>
       </c>
       <c r="F267" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G267" s="7">
         <v>46387.0</v>
@@ -10452,7 +10457,7 @@
         <v>541</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>12</v>
@@ -10464,7 +10469,7 @@
         <v>542</v>
       </c>
       <c r="F268" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G268" s="7">
         <v>46387.0</v>
@@ -10476,7 +10481,7 @@
         <v>543</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>12</v>
@@ -10488,7 +10493,7 @@
         <v>463</v>
       </c>
       <c r="F269" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G269" s="7">
         <v>46521.0</v>
@@ -10500,7 +10505,7 @@
         <v>544</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>12</v>
@@ -10512,7 +10517,7 @@
         <v>545</v>
       </c>
       <c r="F270" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G270" s="7">
         <v>46525.0</v>
@@ -10524,7 +10529,7 @@
         <v>546</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>12</v>
@@ -10536,7 +10541,7 @@
         <v>461</v>
       </c>
       <c r="F271" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G271" s="7">
         <v>46521.0</v>
@@ -10548,7 +10553,7 @@
         <v>547</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>12</v>
@@ -10560,7 +10565,7 @@
         <v>465</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G272" s="7">
         <v>46521.0</v>
@@ -10572,7 +10577,7 @@
         <v>548</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>12</v>
@@ -10584,7 +10589,7 @@
         <v>549</v>
       </c>
       <c r="F273" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G273" s="7">
         <v>46527.0</v>
@@ -10596,7 +10601,7 @@
         <v>550</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>12</v>
@@ -10608,7 +10613,7 @@
         <v>551</v>
       </c>
       <c r="F274" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G274" s="7">
         <v>46356.0</v>
@@ -10620,7 +10625,7 @@
         <v>552</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>12</v>
@@ -10632,7 +10637,7 @@
         <v>553</v>
       </c>
       <c r="F275" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G275" s="7">
         <v>46366.0</v>
@@ -10644,7 +10649,7 @@
         <v>554</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>12</v>
@@ -10656,7 +10661,7 @@
         <v>555</v>
       </c>
       <c r="F276" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G276" s="7">
         <v>46336.0</v>
@@ -10668,7 +10673,7 @@
         <v>556</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>12</v>
@@ -10680,7 +10685,7 @@
         <v>557</v>
       </c>
       <c r="F277" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G277" s="7">
         <v>46354.0</v>
@@ -10692,7 +10697,7 @@
         <v>558</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>12</v>
@@ -10704,7 +10709,7 @@
         <v>559</v>
       </c>
       <c r="F278" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G278" s="7">
         <v>46360.0</v>
@@ -10716,7 +10721,7 @@
         <v>560</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>12</v>
@@ -10742,7 +10747,7 @@
         <v>563</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>12</v>
@@ -10754,7 +10759,7 @@
         <v>564</v>
       </c>
       <c r="F280" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G280" s="7">
         <v>46343.0</v>
@@ -10799,7 +10804,7 @@
         <v>22.0</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>39</v>
@@ -10874,7 +10879,7 @@
         <v>415</v>
       </c>
       <c r="F285" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G285" s="7">
         <v>46675.0</v>
@@ -10922,7 +10927,7 @@
         <v>578</v>
       </c>
       <c r="F287" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G287" s="7">
         <v>46341.0</v>
@@ -11162,7 +11167,7 @@
         <v>597</v>
       </c>
       <c r="F297" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G297" s="7">
         <v>46530.0</v>
@@ -11186,7 +11191,7 @@
         <v>597</v>
       </c>
       <c r="F298" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G298" s="7">
         <v>46530.0</v>
@@ -11512,7 +11517,7 @@
         <v>635</v>
       </c>
       <c r="F312" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G312" s="7">
         <v>46729.0</v>
@@ -11560,7 +11565,7 @@
         <v>641</v>
       </c>
       <c r="F314" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G314" s="7"/>
       <c r="H314" s="2" t="s">
@@ -11584,7 +11589,7 @@
         <v>644</v>
       </c>
       <c r="F315" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G315" s="7"/>
       <c r="H315" s="2" t="s">
@@ -11608,7 +11613,7 @@
         <v>646</v>
       </c>
       <c r="F316" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G316" s="7"/>
       <c r="H316" s="2" t="s">
@@ -11632,7 +11637,7 @@
         <v>648</v>
       </c>
       <c r="F317" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G317" s="7"/>
       <c r="H317" s="2" t="s">
@@ -11656,7 +11661,7 @@
         <v>650</v>
       </c>
       <c r="F318" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G318" s="7"/>
       <c r="H318" s="2" t="s">
@@ -11680,7 +11685,7 @@
         <v>652</v>
       </c>
       <c r="F319" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G319" s="7"/>
       <c r="H319" s="2" t="s">
@@ -11752,7 +11757,7 @@
         <v>635</v>
       </c>
       <c r="F322" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G322" s="7">
         <v>46851.0</v>
@@ -11776,7 +11781,7 @@
         <v>661</v>
       </c>
       <c r="F323" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G323" s="7">
         <v>46884.0</v>
@@ -11800,7 +11805,7 @@
         <v>527</v>
       </c>
       <c r="F324" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G324" s="7">
         <v>46874.0</v>
@@ -11824,7 +11829,7 @@
         <v>664</v>
       </c>
       <c r="F325" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G325" s="7">
         <v>46871.0</v>
@@ -11848,7 +11853,7 @@
         <v>666</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G326" s="7">
         <v>46462.0</v>
@@ -11872,7 +11877,7 @@
         <v>668</v>
       </c>
       <c r="F327" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G327" s="7">
         <v>46858.0</v>
@@ -11896,7 +11901,7 @@
         <v>670</v>
       </c>
       <c r="F328" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G328" s="7">
         <v>46871.0</v>
@@ -11920,7 +11925,7 @@
         <v>672</v>
       </c>
       <c r="F329" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G329" s="7">
         <v>46865.0</v>
@@ -11944,7 +11949,7 @@
         <v>674</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G330" s="7">
         <v>46884.0</v>
@@ -11968,7 +11973,7 @@
         <v>676</v>
       </c>
       <c r="F331" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G331" s="7">
         <v>46887.0</v>
@@ -11992,7 +11997,7 @@
         <v>678</v>
       </c>
       <c r="F332" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G332" s="7">
         <v>46887.0</v>
@@ -12016,7 +12021,7 @@
         <v>680</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G333" s="7">
         <v>46521.0</v>
@@ -12042,7 +12047,7 @@
         <v>683</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G334" s="7">
         <v>46874.0</v>
@@ -12066,7 +12071,7 @@
         <v>685</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G335" s="7">
         <v>46874.0</v>
@@ -12090,7 +12095,7 @@
         <v>687</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G336" s="7">
         <v>46580.0</v>
@@ -12114,7 +12119,7 @@
         <v>689</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G337" s="7">
         <v>46942.0</v>
@@ -12138,7 +12143,7 @@
         <v>691</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G338" s="7">
         <v>46942.0</v>
@@ -12162,7 +12167,7 @@
         <v>693</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G339" s="7">
         <v>46934.0</v>
@@ -12183,10 +12188,10 @@
         <v>13.0</v>
       </c>
       <c r="E340" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G340" s="7">
         <v>46929.0</v>
@@ -12354,7 +12359,7 @@
         <v>708</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G347" s="7">
         <v>47159.0</v>
@@ -12722,7 +12727,7 @@
         <v>745</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>12</v>
@@ -12746,7 +12751,7 @@
         <v>747</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>12</v>
@@ -12770,7 +12775,7 @@
         <v>749</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>12</v>
@@ -12794,7 +12799,7 @@
         <v>751</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>12</v>
@@ -12818,7 +12823,7 @@
         <v>753</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C367" s="2" t="s">
         <v>12</v>
@@ -13000,7 +13005,7 @@
         <v>771</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G374" s="7">
         <v>48157.0</v>
@@ -13024,7 +13029,7 @@
         <v>773</v>
       </c>
       <c r="F375" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G375" s="7">
         <v>48332.0</v>
@@ -13048,7 +13053,7 @@
         <v>775</v>
       </c>
       <c r="F376" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G376" s="7">
         <v>47574.0</v>
@@ -13072,7 +13077,7 @@
         <v>777</v>
       </c>
       <c r="F377" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G377" s="7">
         <v>48198.0</v>
@@ -13211,7 +13216,7 @@
         <v>10.0</v>
       </c>
       <c r="E383" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F383" s="3" t="s">
         <v>69</v>
@@ -13235,7 +13240,7 @@
         <v>10.0</v>
       </c>
       <c r="E384" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F384" s="3" t="s">
         <v>791</v>
@@ -13259,7 +13264,7 @@
         <v>10.0</v>
       </c>
       <c r="E385" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F385" s="3" t="s">
         <v>793</v>
@@ -13283,7 +13288,7 @@
         <v>10.0</v>
       </c>
       <c r="E386" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F386" s="3" t="s">
         <v>795</v>
@@ -13307,7 +13312,7 @@
         <v>10.0</v>
       </c>
       <c r="E387" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F387" s="3" t="s">
         <v>797</v>
@@ -13331,10 +13336,10 @@
         <v>10.0</v>
       </c>
       <c r="E388" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F388" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G388" s="7">
         <v>46775.0</v>
@@ -13355,7 +13360,7 @@
         <v>10.0</v>
       </c>
       <c r="E389" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F389" s="3" t="s">
         <v>800</v>
@@ -13379,7 +13384,7 @@
         <v>10.0</v>
       </c>
       <c r="E390" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F390" s="3" t="s">
         <v>802</v>
@@ -13671,7 +13676,7 @@
         <v>15.0</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F402" s="3" t="s">
         <v>827</v>
@@ -14418,7 +14423,7 @@
         <v>882</v>
       </c>
       <c r="F433" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G433" s="7">
         <v>46781.0</v>
@@ -14610,7 +14615,7 @@
         <v>894</v>
       </c>
       <c r="F441" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G441" s="7">
         <v>46934.0</v>
@@ -14748,7 +14753,7 @@
         <v>905</v>
       </c>
       <c r="F447" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G447" s="7">
         <v>46739.0</v>
@@ -14818,7 +14823,7 @@
         <v>882</v>
       </c>
       <c r="F450" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G450" s="7">
         <v>46669.0</v>
@@ -14839,10 +14844,10 @@
         <v>12.0</v>
       </c>
       <c r="E451" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F451" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G451" s="7">
         <v>46929.0</v>
@@ -14984,7 +14989,7 @@
         <v>661</v>
       </c>
       <c r="F457" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G457" s="7">
         <v>46884.0</v>
@@ -15080,7 +15085,7 @@
         <v>933</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G461" s="7">
         <v>47231.0</v>
@@ -15104,7 +15109,7 @@
         <v>935</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G462" s="7">
         <v>47313.0</v>
@@ -15128,7 +15133,7 @@
         <v>937</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G463" s="7">
         <v>47229.0</v>
@@ -15152,7 +15157,7 @@
         <v>939</v>
       </c>
       <c r="F464" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G464" s="7">
         <v>47248.0</v>
@@ -15173,7 +15178,7 @@
         <v>1.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F465" s="3" t="s">
         <v>941</v>
@@ -15206,12 +15211,12 @@
         <v>46320.0</v>
       </c>
       <c r="H466" s="2" t="s">
-        <v>562</v>
+        <v>944</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>602</v>
@@ -15223,7 +15228,7 @@
         <v>3.0</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F467" s="3" t="s">
         <v>604</v>
@@ -15235,7 +15240,7 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>602</v>
@@ -15247,7 +15252,7 @@
         <v>3.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F468" s="3" t="s">
         <v>604</v>
@@ -15259,7 +15264,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>602</v>
@@ -15271,7 +15276,7 @@
         <v>3.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F469" s="3" t="s">
         <v>604</v>
@@ -15285,7 +15290,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>32</v>
@@ -15297,10 +15302,10 @@
         <v>11.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G470" s="7">
         <v>46982.0</v>
@@ -15309,7 +15314,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>32</v>
@@ -15321,10 +15326,10 @@
         <v>10.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F471" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G471" s="7">
         <v>46914.0</v>
@@ -15333,7 +15338,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>32</v>
@@ -15345,10 +15350,10 @@
         <v>15.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F472" s="3" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="G472" s="7">
         <v>46914.0</v>
@@ -15357,7 +15362,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>37</v>
@@ -15369,10 +15374,10 @@
         <v>11.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F473" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G473" s="7">
         <v>46421.0</v>
@@ -15381,7 +15386,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>37</v>
@@ -15396,7 +15401,7 @@
         <v>718</v>
       </c>
       <c r="F474" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G474" s="7">
         <v>46620.0</v>
@@ -15405,7 +15410,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>37</v>
@@ -15420,7 +15425,7 @@
         <v>879</v>
       </c>
       <c r="F475" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G475" s="7">
         <v>46757.0</v>
@@ -15429,7 +15434,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>37</v>
@@ -15441,10 +15446,10 @@
         <v>15.0</v>
       </c>
       <c r="E476" s="2" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F476" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G476" s="7">
         <v>46480.0</v>
@@ -15453,7 +15458,7 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>37</v>
@@ -15465,10 +15470,10 @@
         <v>15.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G477" s="7">
         <v>46480.0</v>
@@ -15477,7 +15482,7 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>37</v>
@@ -15489,10 +15494,10 @@
         <v>15.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G478" s="7">
         <v>46793.0</v>
@@ -15501,7 +15506,7 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>37</v>
@@ -15516,7 +15521,7 @@
         <v>784</v>
       </c>
       <c r="F479" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G479" s="7">
         <v>46793.0</v>
@@ -15525,7 +15530,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>37</v>
@@ -15537,10 +15542,10 @@
         <v>14.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F480" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G480" s="7">
         <v>46794.0</v>
@@ -15549,7 +15554,7 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>37</v>
@@ -15561,10 +15566,10 @@
         <v>15.0</v>
       </c>
       <c r="E481" s="2" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F481" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G481" s="7">
         <v>46424.0</v>
@@ -15573,7 +15578,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>37</v>
@@ -15585,10 +15590,10 @@
         <v>16.0</v>
       </c>
       <c r="E482" s="2" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F482" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G482" s="7">
         <v>46757.0</v>
@@ -15597,7 +15602,7 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>37</v>
@@ -15609,10 +15614,10 @@
         <v>12.0</v>
       </c>
       <c r="E483" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F483" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G483" s="7">
         <v>46670.0</v>
@@ -15621,7 +15626,7 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>37</v>
@@ -15633,10 +15638,10 @@
         <v>14.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G484" s="7">
         <v>46792.0</v>
@@ -15645,7 +15650,7 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>37</v>
@@ -15657,10 +15662,10 @@
         <v>16.0</v>
       </c>
       <c r="E485" s="2" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F485" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G485" s="7">
         <v>46620.0</v>
@@ -15669,7 +15674,7 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>32</v>
@@ -15681,10 +15686,10 @@
         <v>16.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F486" s="3" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="G486" s="7">
         <v>46982.0</v>
@@ -15693,7 +15698,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>11</v>
@@ -15705,10 +15710,10 @@
         <v>2.0</v>
       </c>
       <c r="E487" s="2" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F487" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G487" s="7">
         <v>46661.0</v>
@@ -15717,7 +15722,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>11</v>
@@ -15729,10 +15734,10 @@
         <v>2.0</v>
       </c>
       <c r="E488" s="2" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G488" s="7">
         <v>46494.0</v>
@@ -15741,7 +15746,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>11</v>
@@ -15753,10 +15758,10 @@
         <v>2.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F489" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G489" s="7">
         <v>46659.0</v>
@@ -15765,7 +15770,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>11</v>
@@ -15777,10 +15782,10 @@
         <v>2.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F490" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G490" s="7">
         <v>46604.0</v>
@@ -15789,7 +15794,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>11</v>
@@ -15801,10 +15806,10 @@
         <v>2.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G491" s="7">
         <v>46688.0</v>
@@ -15813,7 +15818,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>602</v>
@@ -15825,10 +15830,10 @@
         <v>2.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G492" s="7">
         <v>46399.0</v>
@@ -15837,7 +15842,7 @@
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>602</v>
@@ -15849,10 +15854,10 @@
         <v>1.0</v>
       </c>
       <c r="E493" s="2" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F493" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G493" s="7">
         <v>46398.0</v>
@@ -15861,7 +15866,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>602</v>
@@ -15873,10 +15878,10 @@
         <v>1.0</v>
       </c>
       <c r="E494" s="2" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F494" s="3" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="G494" s="7">
         <v>46398.0</v>
@@ -15885,7 +15890,7 @@
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>602</v>
@@ -15900,14 +15905,14 @@
         <v>298</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G495" s="7"/>
       <c r="H495" s="2"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>602</v>
@@ -15919,17 +15924,17 @@
         <v>12.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F496" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G496" s="7"/>
       <c r="H496" s="2"/>
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>602</v>
@@ -15941,17 +15946,17 @@
         <v>12.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="G497" s="7"/>
       <c r="H497" s="2"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>602</v>
@@ -15963,7 +15968,7 @@
         <v>12.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F498" s="3" t="s">
         <v>604</v>
@@ -15973,7 +15978,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>602</v>
@@ -15988,14 +15993,14 @@
         <v>545</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G499" s="7"/>
       <c r="H499" s="2"/>
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>602</v>
@@ -16010,14 +16015,14 @@
         <v>557</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G500" s="7"/>
       <c r="H500" s="2"/>
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>602</v>
@@ -16029,17 +16034,17 @@
         <v>12.0</v>
       </c>
       <c r="E501" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F501" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G501" s="7"/>
       <c r="H501" s="2"/>
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>32</v>
@@ -16051,10 +16056,10 @@
         <v>15.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="G502" s="7">
         <v>46432.0</v>
@@ -16063,7 +16068,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>32</v>
@@ -16075,7 +16080,7 @@
         <v>15.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>340</v>
@@ -16087,7 +16092,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>32</v>
@@ -16099,10 +16104,10 @@
         <v>12.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G504" s="7">
         <v>46949.0</v>
@@ -16113,7 +16118,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>32</v>
@@ -16125,7 +16130,7 @@
         <v>13.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F505" s="3"/>
       <c r="G505" s="7"/>
@@ -16135,7 +16140,7 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>32</v>
@@ -16147,7 +16152,7 @@
         <v>15.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>39</v>
@@ -16159,7 +16164,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>32</v>
@@ -16171,7 +16176,7 @@
         <v>15.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>827</v>
@@ -16183,7 +16188,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>32</v>
@@ -16195,7 +16200,7 @@
         <v>22.0</v>
       </c>
       <c r="E508" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F508" s="3"/>
       <c r="G508" s="7"/>
@@ -16203,7 +16208,7 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>37</v>
@@ -16215,10 +16220,10 @@
         <v>16.0</v>
       </c>
       <c r="E509" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F509" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G509" s="7">
         <v>46432.0</v>
@@ -16227,7 +16232,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>37</v>
@@ -16239,10 +16244,10 @@
         <v>15.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F510" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G510" s="7">
         <v>46913.0</v>
@@ -16251,7 +16256,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>37</v>
@@ -16263,10 +16268,10 @@
         <v>21.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F511" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G511" s="7">
         <v>46641.0</v>
@@ -16277,7 +16282,7 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>37</v>
@@ -16301,7 +16306,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>37</v>
@@ -16316,7 +16321,7 @@
         <v>739</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="G513" s="7">
         <v>46792.0</v>
@@ -16325,7 +16330,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>37</v>
@@ -16337,17 +16342,17 @@
         <v>12.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G514" s="7"/>
       <c r="H514" s="2"/>
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>37</v>
@@ -16367,7 +16372,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>32</v>
@@ -16379,10 +16384,10 @@
         <v>20.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G516" s="7">
         <v>46926.0</v>
@@ -16391,7 +16396,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>32</v>
@@ -16403,10 +16408,10 @@
         <v>20.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G517" s="7">
         <v>46926.0</v>
@@ -16415,7 +16420,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>32</v>
@@ -16427,10 +16432,10 @@
         <v>20.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F518" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="G518" s="7">
         <v>46925.0</v>
@@ -16439,7 +16444,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>32</v>
@@ -16451,10 +16456,10 @@
         <v>17.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G519" s="7">
         <v>46988.0</v>
@@ -16463,7 +16468,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>32</v>
@@ -16475,7 +16480,7 @@
         <v>13.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F520" s="3"/>
       <c r="G520" s="7"/>
@@ -16485,7 +16490,7 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>37</v>
@@ -16497,10 +16502,10 @@
         <v>19.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F521" s="3" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G521" s="7">
         <v>46940.0</v>
@@ -16509,7 +16514,7 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>32</v>
@@ -16521,7 +16526,7 @@
         <v>15.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>697</v>
@@ -16533,7 +16538,7 @@
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>32</v>
@@ -16545,7 +16550,7 @@
         <v>20.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F523" s="3"/>
       <c r="G523" s="7"/>
@@ -16553,7 +16558,7 @@
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>602</v>
@@ -16565,10 +16570,10 @@
         <v>17.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F524" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G524" s="7">
         <v>46398.0</v>
@@ -16577,7 +16582,7 @@
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>602</v>
@@ -16589,10 +16594,10 @@
         <v>16.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F525" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G525" s="7">
         <v>46398.0</v>
@@ -16601,7 +16606,7 @@
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>640</v>
@@ -16623,7 +16628,7 @@
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>640</v>
@@ -16635,7 +16640,7 @@
         <v>3.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>489</v>
@@ -16645,7 +16650,7 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>640</v>
@@ -16667,7 +16672,7 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>640</v>
@@ -16689,7 +16694,7 @@
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>640</v>
@@ -16711,7 +16716,7 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>640</v>
@@ -16733,10 +16738,10 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B532" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C532" s="2" t="s">
         <v>12</v>
@@ -16745,7 +16750,7 @@
         <v>6.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>489</v>
@@ -16757,7 +16762,7 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>640</v>
@@ -16779,7 +16784,7 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>602</v>
@@ -16791,10 +16796,10 @@
         <v>4.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F534" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G534" s="7">
         <v>46384.0</v>
@@ -16803,7 +16808,7 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>602</v>
@@ -16815,17 +16820,17 @@
         <v>11.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F535" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G535" s="7"/>
       <c r="H535" s="2"/>
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>602</v>
@@ -16837,17 +16842,17 @@
         <v>11.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F536" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G536" s="7"/>
       <c r="H536" s="2"/>
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>602</v>
@@ -16859,10 +16864,10 @@
         <v>4.0</v>
       </c>
       <c r="E537" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G537" s="7">
         <v>46384.0</v>
@@ -16871,7 +16876,7 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>602</v>
@@ -16883,10 +16888,10 @@
         <v>4.0</v>
       </c>
       <c r="E538" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F538" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="G538" s="7">
         <v>46384.0</v>
@@ -16895,7 +16900,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>37</v>
@@ -16907,10 +16912,10 @@
         <v>19.0</v>
       </c>
       <c r="E539" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="G539" s="7">
         <v>46940.0</v>
@@ -16919,7 +16924,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>37</v>
@@ -16934,7 +16939,7 @@
         <v>597</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G540" s="7">
         <v>46536.0</v>
@@ -16943,7 +16948,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>602</v>
@@ -16955,7 +16960,7 @@
         <v>16.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F541" s="3" t="s">
         <v>604</v>
@@ -16967,7 +16972,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>602</v>
@@ -16979,21 +16984,21 @@
         <v>14.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F542" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G542" s="7">
         <v>46323.0</v>
       </c>
       <c r="H542" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>602</v>
@@ -17005,10 +17010,10 @@
         <v>13.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F543" s="3" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="G543" s="7">
         <v>46321.0</v>
@@ -17019,7 +17024,7 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>37</v>
@@ -17031,7 +17036,7 @@
         <v>7.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F544" s="3" t="s">
         <v>875</v>
@@ -17043,7 +17048,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>602</v>
@@ -17055,7 +17060,7 @@
         <v>3.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>604</v>
@@ -17069,7 +17074,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>37</v>
@@ -17081,10 +17086,10 @@
         <v>20.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F546" s="3" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="G546" s="7">
         <v>46865.0</v>
@@ -17093,7 +17098,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>37</v>
@@ -17105,10 +17110,10 @@
         <v>1.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F547" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G547" s="7">
         <v>46758.0</v>
@@ -17117,7 +17122,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>640</v>
@@ -17129,21 +17134,21 @@
         <v>4.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F548" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G548" s="7">
         <v>46550.0</v>
       </c>
       <c r="H548" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>640</v>
@@ -17155,21 +17160,21 @@
         <v>4.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F549" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G549" s="7">
         <v>46554.0</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>640</v>
@@ -17181,21 +17186,21 @@
         <v>4.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G550" s="7">
         <v>46549.0</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>640</v>
@@ -17207,21 +17212,21 @@
         <v>2.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F551" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G551" s="7">
         <v>46549.0</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>640</v>
@@ -17233,21 +17238,21 @@
         <v>6.0</v>
       </c>
       <c r="E552" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G552" s="7">
         <v>46549.0</v>
       </c>
       <c r="H552" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>640</v>
@@ -17259,21 +17264,21 @@
         <v>2.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G553" s="7">
         <v>46494.0</v>
       </c>
       <c r="H553" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>640</v>
@@ -17285,10 +17290,10 @@
         <v>7.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G554" s="7">
         <v>46661.0</v>
@@ -17299,7 +17304,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>640</v>
@@ -17311,21 +17316,21 @@
         <v>6.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G555" s="7">
         <v>46707.0</v>
       </c>
       <c r="H555" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>640</v>
@@ -17337,21 +17342,21 @@
         <v>6.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G556" s="7">
         <v>46604.0</v>
       </c>
       <c r="H556" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>640</v>
@@ -17363,10 +17368,10 @@
         <v>5.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G557" s="7">
         <v>46688.0</v>
@@ -17377,7 +17382,7 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>640</v>
@@ -17389,21 +17394,21 @@
         <v>6.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G558" s="7">
         <v>46659.0</v>
       </c>
       <c r="H558" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>32</v>
@@ -17415,7 +17420,7 @@
         <v>3.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F559" s="3">
         <v>11508.0</v>
@@ -17425,7 +17430,7 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>640</v>
@@ -17437,21 +17442,21 @@
         <v>4.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G560" s="7">
         <v>46549.0</v>
       </c>
       <c r="H560" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>32</v>
@@ -17463,10 +17468,10 @@
         <v>13.0</v>
       </c>
       <c r="E561" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F561" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G561" s="7">
         <v>46535.0</v>
@@ -17475,7 +17480,7 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>37</v>
@@ -17487,10 +17492,10 @@
         <v>22.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G562" s="7">
         <v>46941.0</v>
@@ -17499,7 +17504,7 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>37</v>
@@ -17514,7 +17519,7 @@
         <v>761</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="G563" s="7">
         <v>46910.0</v>
@@ -17523,7 +17528,7 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>32</v>
@@ -17547,7 +17552,7 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>32</v>
@@ -17562,7 +17567,7 @@
         <v>855</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="G565" s="7">
         <v>46675.0</v>
@@ -17571,7 +17576,7 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>32</v>
@@ -17595,7 +17600,7 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>32</v>
@@ -17610,7 +17615,7 @@
         <v>855</v>
       </c>
       <c r="F567" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="G567" s="7">
         <v>46612.0</v>
@@ -17619,7 +17624,7 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>32</v>
@@ -17631,7 +17636,7 @@
         <v>3.0</v>
       </c>
       <c r="E568" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F568" s="3" t="s">
         <v>837</v>
@@ -17643,7 +17648,7 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>32</v>
@@ -17655,7 +17660,7 @@
         <v>17.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="F569" s="3" t="s">
         <v>20</v>
@@ -17667,7 +17672,7 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>37</v>
@@ -17679,17 +17684,17 @@
         <v>7.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G570" s="7"/>
       <c r="H570" s="2"/>
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>32</v>
@@ -17701,7 +17706,7 @@
         <v>3.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F571" s="3" t="s">
         <v>340</v>
@@ -17713,7 +17718,7 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>32</v>
@@ -17725,7 +17730,7 @@
         <v>3.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="F572" s="3" t="s">
         <v>837</v>
@@ -17737,7 +17742,7 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>32</v>
@@ -17749,7 +17754,7 @@
         <v>3.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F573" s="3" t="s">
         <v>340</v>
@@ -17761,7 +17766,7 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>32</v>
@@ -17773,7 +17778,7 @@
         <v>3.0</v>
       </c>
       <c r="E574" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F574" s="3" t="s">
         <v>837</v>
@@ -17785,7 +17790,7 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>640</v>
@@ -17797,17 +17802,17 @@
         <v>16.0</v>
       </c>
       <c r="E575" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="F575" s="3"/>
       <c r="G575" s="7"/>
       <c r="H575" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>640</v>
@@ -17819,21 +17824,21 @@
         <v>8.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F576" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="G576" s="7">
         <v>46376.0</v>
       </c>
       <c r="H576" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>640</v>
@@ -17845,21 +17850,21 @@
         <v>8.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="F577" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="G577" s="7">
         <v>46376.0</v>
       </c>
       <c r="H577" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>640</v>
@@ -17881,7 +17886,7 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>602</v>
@@ -17893,10 +17898,10 @@
         <v>12.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F579" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G579" s="7">
         <v>46338.0</v>
@@ -17905,7 +17910,7 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>602</v>
@@ -17917,10 +17922,10 @@
         <v>11.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G580" s="7">
         <v>46348.0</v>
@@ -17929,7 +17934,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>602</v>
@@ -17941,10 +17946,10 @@
         <v>14.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G581" s="7">
         <v>46347.0</v>
@@ -17953,7 +17958,7 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>602</v>
@@ -17965,10 +17970,10 @@
         <v>11.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="F582" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G582" s="7">
         <v>46349.0</v>
@@ -17977,7 +17982,7 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>602</v>
@@ -17989,10 +17994,10 @@
         <v>15.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F583" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="G583" s="7">
         <v>46341.0</v>
@@ -18001,7 +18006,7 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>602</v>
@@ -18013,10 +18018,10 @@
         <v>8.0</v>
       </c>
       <c r="E584" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F584" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G584" s="7">
         <v>46402.0</v>
@@ -18025,7 +18030,7 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>602</v>
@@ -18037,10 +18042,10 @@
         <v>9.0</v>
       </c>
       <c r="E585" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="F585" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G585" s="7">
         <v>46405.0</v>
@@ -18049,7 +18054,7 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>602</v>
@@ -18061,10 +18066,10 @@
         <v>10.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="G586" s="7">
         <v>46402.0</v>
@@ -18073,7 +18078,7 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>37</v>
@@ -18088,7 +18093,7 @@
         <v>722</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="G587" s="7">
         <v>46792.0</v>
@@ -18097,7 +18102,7 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>602</v>
@@ -18109,10 +18114,10 @@
         <v>6.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G588" s="7">
         <v>46366.0</v>
@@ -18121,7 +18126,7 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>602</v>
@@ -18133,10 +18138,10 @@
         <v>7.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G589" s="7">
         <v>46366.0</v>
@@ -18145,7 +18150,7 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>602</v>
@@ -18157,10 +18162,10 @@
         <v>5.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G590" s="7">
         <v>46366.0</v>
@@ -18169,7 +18174,7 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>602</v>
@@ -18181,10 +18186,10 @@
         <v>5.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G591" s="7">
         <v>46366.0</v>
@@ -18193,7 +18198,7 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>602</v>
@@ -18205,10 +18210,10 @@
         <v>7.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="G592" s="7">
         <v>46366.0</v>
@@ -18217,7 +18222,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>32</v>
@@ -18229,7 +18234,7 @@
         <v>20.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="F593" s="3">
         <v>11509.0</v>
@@ -18241,7 +18246,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>37</v>
@@ -18253,10 +18258,10 @@
         <v>1.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F594" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G594" s="7">
         <v>46522.0</v>
@@ -18265,7 +18270,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>37</v>
@@ -18287,7 +18292,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>640</v>
@@ -18302,7 +18307,7 @@
         <v>564</v>
       </c>
       <c r="F596" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G596" s="7">
         <v>47022.0</v>
@@ -18311,7 +18316,7 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>602</v>
@@ -18323,10 +18328,10 @@
         <v>12.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F597" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G597" s="7">
         <v>46348.0</v>
@@ -18337,7 +18342,7 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>37</v>
@@ -18349,10 +18354,10 @@
         <v>1.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G598" s="7">
         <v>46830.0</v>
@@ -18361,7 +18366,7 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>32</v>
@@ -18373,10 +18378,10 @@
         <v>14.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F599" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G599" s="7">
         <v>46662.0</v>
@@ -18385,7 +18390,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>37</v>
@@ -18397,10 +18402,10 @@
         <v>22.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F600" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G600" s="7">
         <v>47098.0</v>
@@ -18409,10 +18414,10 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C601" s="2" t="s">
         <v>29</v>
@@ -18433,10 +18438,10 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B602" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C602" s="2" t="s">
         <v>29</v>
@@ -18457,10 +18462,10 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B603" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C603" s="2" t="s">
         <v>12</v>
@@ -18477,10 +18482,10 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B604" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C604" s="2" t="s">
         <v>29</v>
@@ -18501,7 +18506,7 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>37</v>
@@ -18513,7 +18518,7 @@
         <v>7.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>875</v>
@@ -18525,7 +18530,7 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>37</v>
@@ -18537,7 +18542,7 @@
         <v>7.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>875</v>
@@ -18549,7 +18554,7 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>37</v>
@@ -18561,7 +18566,7 @@
         <v>7.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>875</v>
@@ -18573,7 +18578,7 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>37</v>
@@ -18585,17 +18590,17 @@
         <v>5.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F608" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G608" s="7"/>
       <c r="H608" s="2"/>
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>32</v>
@@ -18607,10 +18612,10 @@
         <v>15.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G609" s="7">
         <v>46725.0</v>
@@ -18619,7 +18624,7 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>32</v>
@@ -18631,7 +18636,7 @@
         <v>14.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="F610" s="3"/>
       <c r="G610" s="7"/>
@@ -18639,7 +18644,7 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>32</v>
@@ -18651,7 +18656,7 @@
         <v>6.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="F611" s="3"/>
       <c r="G611" s="7"/>
@@ -18659,7 +18664,7 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>32</v>
@@ -18683,7 +18688,7 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>32</v>
@@ -18707,7 +18712,7 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>32</v>
@@ -18729,7 +18734,7 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>602</v>
@@ -18741,10 +18746,10 @@
         <v>12.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="G615" s="7">
         <v>46349.0</v>
@@ -18753,7 +18758,7 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>602</v>
@@ -18768,7 +18773,7 @@
         <v>512</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="G616" s="7">
         <v>46336.0</v>
@@ -18777,7 +18782,7 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>37</v>
@@ -18799,7 +18804,7 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>640</v>
@@ -18811,10 +18816,10 @@
         <v>11.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G618" s="7">
         <v>46349.0</v>
@@ -18825,7 +18830,7 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>640</v>
@@ -18837,10 +18842,10 @@
         <v>11.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="G619" s="7">
         <v>46356.0</v>
@@ -18851,7 +18856,7 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>32</v>
@@ -18863,19 +18868,19 @@
         <v>21.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G620" s="7"/>
       <c r="H620" s="2" t="s">
-        <v>288</v>
+        <v>120</v>
       </c>
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>32</v>
@@ -18887,19 +18892,19 @@
         <v>21.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F621" s="3" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="G621" s="7"/>
       <c r="H621" s="2" t="s">
-        <v>288</v>
+        <v>120</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>32</v>
@@ -18911,7 +18916,7 @@
         <v>21.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F622" s="3" t="s">
         <v>69</v>
@@ -18921,7 +18926,7 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>32</v>
@@ -18933,7 +18938,7 @@
         <v>21.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F623" s="3" t="s">
         <v>791</v>
@@ -18943,7 +18948,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>32</v>
@@ -18955,7 +18960,7 @@
         <v>21.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F624" s="3"/>
       <c r="G624" s="7"/>
@@ -18963,7 +18968,7 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>32</v>
@@ -18975,7 +18980,7 @@
         <v>21.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F625" s="3" t="s">
         <v>791</v>
@@ -18985,7 +18990,7 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>32</v>
@@ -18997,7 +19002,7 @@
         <v>21.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F626" s="3"/>
       <c r="G626" s="7"/>
@@ -19005,7 +19010,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>32</v>
@@ -19017,10 +19022,10 @@
         <v>20.0</v>
       </c>
       <c r="E627" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F627" s="3" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="G627" s="7">
         <v>46554.0</v>
@@ -19029,7 +19034,7 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>11</v>
@@ -19041,7 +19046,7 @@
         <v>4.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="F628" s="3"/>
       <c r="G628" s="7"/>
@@ -19049,7 +19054,7 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>640</v>
@@ -19064,7 +19069,7 @@
         <v>644</v>
       </c>
       <c r="F629" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G629" s="7">
         <v>47300.0</v>
@@ -19073,7 +19078,7 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>640</v>
@@ -19085,10 +19090,10 @@
         <v>14.0</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F630" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G630" s="7">
         <v>47178.0</v>
@@ -19097,7 +19102,7 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>640</v>
@@ -19112,7 +19117,7 @@
         <v>641</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G631" s="7">
         <v>47300.0</v>
@@ -19121,7 +19126,7 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>640</v>
@@ -19133,10 +19138,10 @@
         <v>14.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G632" s="7">
         <v>46997.0</v>
@@ -19145,7 +19150,7 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>640</v>
@@ -19157,10 +19162,10 @@
         <v>14.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G633" s="7">
         <v>46874.0</v>
@@ -19169,7 +19174,7 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>640</v>
@@ -19181,10 +19186,10 @@
         <v>14.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F634" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G634" s="7">
         <v>47370.0</v>
@@ -19193,7 +19198,7 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>640</v>
@@ -19205,10 +19210,10 @@
         <v>15.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="F635" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G635" s="7"/>
       <c r="H635" s="2" t="s">
@@ -19217,7 +19222,7 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>640</v>
@@ -19229,10 +19234,10 @@
         <v>15.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="F636" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G636" s="7"/>
       <c r="H636" s="2" t="s">
@@ -19241,7 +19246,7 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>640</v>
@@ -19253,10 +19258,10 @@
         <v>15.0</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="F637" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G637" s="7"/>
       <c r="H637" s="2" t="s">
@@ -19265,7 +19270,7 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>640</v>
@@ -19277,10 +19282,10 @@
         <v>14.0</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="F638" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G638" s="7">
         <v>47331.0</v>
@@ -19289,7 +19294,7 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>32</v>
@@ -19301,10 +19306,10 @@
         <v>7.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F639" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G639" s="7">
         <v>46586.0</v>
@@ -19313,7 +19318,7 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>37</v>
@@ -19325,10 +19330,10 @@
         <v>1.0</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="F640" s="3" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="G640" s="7">
         <v>46836.0</v>
@@ -19337,7 +19342,7 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>37</v>
@@ -19349,10 +19354,10 @@
         <v>21.0</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F641" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G641" s="7">
         <v>46794.0</v>
@@ -19361,7 +19366,7 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>32</v>
@@ -19373,10 +19378,10 @@
         <v>21.0</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="F642" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G642" s="7">
         <v>46509.0</v>
@@ -19385,7 +19390,7 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>32</v>
@@ -19397,7 +19402,7 @@
         <v>21.0</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="F643" s="3" t="s">
         <v>20</v>
@@ -19409,10 +19414,10 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>12</v>
@@ -19421,7 +19426,7 @@
         <v>6.0</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="F644" s="3"/>
       <c r="G644" s="7"/>
@@ -19429,10 +19434,10 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B645" s="2" t="s">
         <v>1273</v>
-      </c>
-      <c r="B645" s="2" t="s">
-        <v>1272</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>12</v>
@@ -19441,7 +19446,7 @@
         <v>6.0</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="F645" s="3"/>
       <c r="G645" s="7"/>
@@ -19449,10 +19454,10 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B646" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>12</v>
@@ -19461,7 +19466,7 @@
         <v>6.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="F646" s="3"/>
       <c r="G646" s="7"/>
@@ -19469,10 +19474,10 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>12</v>
@@ -19481,7 +19486,7 @@
         <v>6.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="F647" s="3"/>
       <c r="G647" s="7"/>
@@ -19489,10 +19494,10 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>12</v>
@@ -19501,7 +19506,7 @@
         <v>6.0</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="F648" s="3"/>
       <c r="G648" s="7"/>
@@ -19509,10 +19514,10 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>12</v>
@@ -19521,7 +19526,7 @@
         <v>6.0</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="F649" s="3"/>
       <c r="G649" s="7"/>
@@ -19529,10 +19534,10 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>12</v>
@@ -19541,7 +19546,7 @@
         <v>6.0</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F650" s="3"/>
       <c r="G650" s="7"/>
@@ -19549,10 +19554,10 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>12</v>
@@ -19561,7 +19566,7 @@
         <v>6.0</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="F651" s="3"/>
       <c r="G651" s="7"/>
@@ -19569,7 +19574,7 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>37</v>
@@ -19581,19 +19586,21 @@
         <v>17.0</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="F652" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G652" s="7">
         <v>46963.0</v>
       </c>
-      <c r="H652" s="2"/>
+      <c r="H652" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>37</v>
@@ -19605,10 +19612,10 @@
         <v>17.0</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="F653" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G653" s="7">
         <v>46963.0</v>
@@ -19617,7 +19624,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>37</v>
@@ -19629,10 +19636,10 @@
         <v>17.0</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="F654" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G654" s="7">
         <v>46995.0</v>
@@ -19641,7 +19648,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>37</v>
@@ -19653,10 +19660,10 @@
         <v>17.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G655" s="7">
         <v>46963.0</v>
@@ -19665,7 +19672,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>37</v>
@@ -19677,10 +19684,10 @@
         <v>17.0</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F656" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G656" s="7">
         <v>46477.0</v>
@@ -19689,7 +19696,7 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>37</v>
@@ -19701,10 +19708,10 @@
         <v>17.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G657" s="7">
         <v>46488.0</v>
@@ -19713,7 +19720,7 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>37</v>
@@ -19725,10 +19732,10 @@
         <v>17.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G658" s="7">
         <v>46488.0</v>
@@ -19737,7 +19744,7 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>37</v>
@@ -19749,10 +19756,10 @@
         <v>12.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G659" s="7">
         <v>46836.0</v>
@@ -19761,7 +19768,7 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>37</v>
@@ -19773,10 +19780,10 @@
         <v>13.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G660" s="7">
         <v>46794.0</v>
@@ -19785,7 +19792,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>37</v>
@@ -19800,7 +19807,7 @@
         <v>879</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G661" s="7">
         <v>46940.0</v>
@@ -19809,7 +19816,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>37</v>
@@ -19821,10 +19828,10 @@
         <v>12.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G662" s="7">
         <v>46940.0</v>
@@ -19833,7 +19840,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>37</v>
@@ -19848,7 +19855,7 @@
         <v>781</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G663" s="7">
         <v>46530.0</v>
@@ -19857,7 +19864,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>37</v>
@@ -19869,10 +19876,10 @@
         <v>13.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G664" s="7">
         <v>46530.0</v>
@@ -19881,7 +19888,7 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>37</v>
@@ -19893,10 +19900,10 @@
         <v>13.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F665" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G665" s="7">
         <v>46487.0</v>
@@ -19905,7 +19912,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>37</v>
@@ -19917,10 +19924,10 @@
         <v>13.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F666" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G666" s="7">
         <v>46792.0</v>
@@ -19929,7 +19936,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>37</v>
@@ -19941,10 +19948,10 @@
         <v>19.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F667" s="3" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="G667" s="7">
         <v>46794.0</v>
@@ -19953,7 +19960,7 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>37</v>
@@ -19965,10 +19972,10 @@
         <v>19.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F668" s="3" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="G668" s="7">
         <v>46793.0</v>
@@ -19977,7 +19984,7 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>37</v>
@@ -19989,10 +19996,10 @@
         <v>18.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G669" s="7">
         <v>46509.0</v>
@@ -20001,10 +20008,10 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>12</v>
@@ -20013,10 +20020,10 @@
         <v>1.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F670" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G670" s="7">
         <v>46530.0</v>
@@ -20025,10 +20032,10 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>12</v>
@@ -20037,10 +20044,10 @@
         <v>1.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="F671" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G671" s="7">
         <v>46792.0</v>
@@ -20049,7 +20056,7 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>37</v>
@@ -20061,7 +20068,7 @@
         <v>21.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F672" s="3" t="s">
         <v>17</v>
@@ -20073,7 +20080,7 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>37</v>
@@ -20085,10 +20092,10 @@
         <v>13.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="F673" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="G673" s="7">
         <v>46530.0</v>
@@ -20097,7 +20104,7 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>37</v>
@@ -20113,7 +20120,7 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>37</v>
@@ -20128,7 +20135,7 @@
         <v>45</v>
       </c>
       <c r="F675" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G675" s="7">
         <v>46758.0</v>
@@ -20137,7 +20144,7 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>640</v>
@@ -20149,16 +20156,16 @@
         <v>13.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="F676" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G676" s="7">
         <v>47231.0</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="677">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3319" uniqueCount="1327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3322" uniqueCount="1329">
   <si>
     <t>ID</t>
   </si>
@@ -3556,10 +3556,16 @@
     <t>PRTDL-YK-C</t>
   </si>
   <si>
+    <t>[產品異常] 轉凍 1151019K6  2028.08.09</t>
+  </si>
+  <si>
     <t>ID1790755399274</t>
   </si>
   <si>
     <t>PRSTL-YK-C</t>
+  </si>
+  <si>
+    <t>【60日】[產品異常] 轉凍 1151019K6  2028.08.09</t>
   </si>
   <si>
     <t>ID1790755409974</t>
@@ -17019,7 +17025,7 @@
         <v>46321.0</v>
       </c>
       <c r="H543" s="2" t="s">
-        <v>605</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="544">
@@ -18146,23 +18152,25 @@
       <c r="G589" s="7">
         <v>46366.0</v>
       </c>
-      <c r="H589" s="2"/>
+      <c r="H589" s="2" t="s">
+        <v>1181</v>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B590" s="2" t="s">
-        <v>602</v>
+        <v>37</v>
       </c>
       <c r="C590" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D590" s="2">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F590" s="3" t="s">
         <v>1178</v>
@@ -18170,11 +18178,13 @@
       <c r="G590" s="7">
         <v>46366.0</v>
       </c>
-      <c r="H590" s="2"/>
+      <c r="H590" s="2" t="s">
+        <v>1184</v>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>602</v>
@@ -18186,7 +18196,7 @@
         <v>5.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F591" s="3" t="s">
         <v>1178</v>
@@ -18194,11 +18204,13 @@
       <c r="G591" s="7">
         <v>46366.0</v>
       </c>
-      <c r="H591" s="2"/>
+      <c r="H591" s="2" t="s">
+        <v>1181</v>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>602</v>
@@ -18210,7 +18222,7 @@
         <v>7.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F592" s="3" t="s">
         <v>1178</v>
@@ -18222,7 +18234,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>32</v>
@@ -18234,7 +18246,7 @@
         <v>20.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="F593" s="3">
         <v>11509.0</v>
@@ -18246,7 +18258,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>37</v>
@@ -18258,7 +18270,7 @@
         <v>1.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="F594" s="3" t="s">
         <v>133</v>
@@ -18270,7 +18282,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>37</v>
@@ -18292,7 +18304,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>640</v>
@@ -18316,7 +18328,7 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>602</v>
@@ -18342,7 +18354,7 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>37</v>
@@ -18354,10 +18366,10 @@
         <v>1.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="F598" s="3" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="G598" s="7">
         <v>46830.0</v>
@@ -18366,7 +18378,7 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>32</v>
@@ -18378,7 +18390,7 @@
         <v>14.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>133</v>
@@ -18390,7 +18402,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>37</v>
@@ -18402,7 +18414,7 @@
         <v>22.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>219</v>
@@ -18414,7 +18426,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>266</v>
@@ -18438,7 +18450,7 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>266</v>
@@ -18462,7 +18474,7 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>266</v>
@@ -18482,7 +18494,7 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>266</v>
@@ -18506,7 +18518,7 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>37</v>
@@ -18530,7 +18542,7 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>37</v>
@@ -18542,7 +18554,7 @@
         <v>7.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>875</v>
@@ -18554,7 +18566,7 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>37</v>
@@ -18578,7 +18590,7 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B608" s="2" t="s">
         <v>37</v>
@@ -18590,7 +18602,7 @@
         <v>5.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="F608" s="3" t="s">
         <v>219</v>
@@ -18600,7 +18612,7 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B609" s="2" t="s">
         <v>32</v>
@@ -18615,7 +18627,7 @@
         <v>1015</v>
       </c>
       <c r="F609" s="3" t="s">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="G609" s="7">
         <v>46725.0</v>
@@ -18624,7 +18636,7 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="B610" s="2" t="s">
         <v>32</v>
@@ -18636,7 +18648,7 @@
         <v>14.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="F610" s="3"/>
       <c r="G610" s="7"/>
@@ -18644,7 +18656,7 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="B611" s="2" t="s">
         <v>32</v>
@@ -18656,7 +18668,7 @@
         <v>6.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="F611" s="3"/>
       <c r="G611" s="7"/>
@@ -18664,7 +18676,7 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="B612" s="2" t="s">
         <v>32</v>
@@ -18688,7 +18700,7 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="B613" s="2" t="s">
         <v>32</v>
@@ -18712,7 +18724,7 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="B614" s="2" t="s">
         <v>32</v>
@@ -18734,7 +18746,7 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="B615" s="2" t="s">
         <v>602</v>
@@ -18746,7 +18758,7 @@
         <v>12.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="F615" s="3" t="s">
         <v>1160</v>
@@ -18758,7 +18770,7 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>602</v>
@@ -18773,7 +18785,7 @@
         <v>512</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="G616" s="7">
         <v>46336.0</v>
@@ -18782,7 +18794,7 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>37</v>
@@ -18804,7 +18816,7 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>640</v>
@@ -18819,7 +18831,7 @@
         <v>1090</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G618" s="7">
         <v>46349.0</v>
@@ -18830,7 +18842,7 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>640</v>
@@ -18845,7 +18857,7 @@
         <v>1163</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="G619" s="7">
         <v>46356.0</v>
@@ -18856,7 +18868,7 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>32</v>
@@ -18868,10 +18880,10 @@
         <v>21.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="G620" s="7"/>
       <c r="H620" s="2" t="s">
@@ -18880,7 +18892,7 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>32</v>
@@ -18892,10 +18904,10 @@
         <v>21.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F621" s="3" t="s">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="G621" s="7"/>
       <c r="H621" s="2" t="s">
@@ -18904,7 +18916,7 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>32</v>
@@ -18916,7 +18928,7 @@
         <v>21.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F622" s="3" t="s">
         <v>69</v>
@@ -18926,7 +18938,7 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>32</v>
@@ -18938,7 +18950,7 @@
         <v>21.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F623" s="3" t="s">
         <v>791</v>
@@ -18948,7 +18960,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>32</v>
@@ -18960,7 +18972,7 @@
         <v>21.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="F624" s="3"/>
       <c r="G624" s="7"/>
@@ -18968,7 +18980,7 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>32</v>
@@ -18980,7 +18992,7 @@
         <v>21.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F625" s="3" t="s">
         <v>791</v>
@@ -18990,7 +19002,7 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>32</v>
@@ -19002,7 +19014,7 @@
         <v>21.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="F626" s="3"/>
       <c r="G626" s="7"/>
@@ -19010,7 +19022,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>32</v>
@@ -19025,7 +19037,7 @@
         <v>1040</v>
       </c>
       <c r="F627" s="3" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="G627" s="7">
         <v>46554.0</v>
@@ -19034,7 +19046,7 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>11</v>
@@ -19046,7 +19058,7 @@
         <v>4.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="F628" s="3"/>
       <c r="G628" s="7"/>
@@ -19054,7 +19066,7 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>640</v>
@@ -19078,7 +19090,7 @@
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1244</v>
+        <v>1246</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>640</v>
@@ -19090,7 +19102,7 @@
         <v>14.0</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>1245</v>
+        <v>1247</v>
       </c>
       <c r="F630" s="3" t="s">
         <v>219</v>
@@ -19102,7 +19114,7 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1246</v>
+        <v>1248</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>640</v>
@@ -19126,7 +19138,7 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>640</v>
@@ -19138,7 +19150,7 @@
         <v>14.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1248</v>
+        <v>1250</v>
       </c>
       <c r="F632" s="3" t="s">
         <v>219</v>
@@ -19150,7 +19162,7 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>640</v>
@@ -19162,7 +19174,7 @@
         <v>14.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="F633" s="3" t="s">
         <v>219</v>
@@ -19174,7 +19186,7 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>640</v>
@@ -19186,7 +19198,7 @@
         <v>14.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="F634" s="3" t="s">
         <v>219</v>
@@ -19198,7 +19210,7 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>640</v>
@@ -19210,7 +19222,7 @@
         <v>15.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="F635" s="3" t="s">
         <v>219</v>
@@ -19222,7 +19234,7 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>640</v>
@@ -19234,7 +19246,7 @@
         <v>15.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="F636" s="3" t="s">
         <v>219</v>
@@ -19246,7 +19258,7 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>640</v>
@@ -19258,7 +19270,7 @@
         <v>15.0</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="F637" s="3" t="s">
         <v>219</v>
@@ -19270,7 +19282,7 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>640</v>
@@ -19282,7 +19294,7 @@
         <v>14.0</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="F638" s="3" t="s">
         <v>219</v>
@@ -19294,7 +19306,7 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>32</v>
@@ -19306,10 +19318,10 @@
         <v>7.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="F639" s="3" t="s">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="G639" s="7">
         <v>46586.0</v>
@@ -19318,7 +19330,7 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>37</v>
@@ -19330,10 +19342,10 @@
         <v>1.0</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="F640" s="3" t="s">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="G640" s="7">
         <v>46836.0</v>
@@ -19342,7 +19354,7 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>37</v>
@@ -19354,7 +19366,7 @@
         <v>21.0</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="F641" s="3" t="s">
         <v>219</v>
@@ -19366,7 +19378,7 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>32</v>
@@ -19378,7 +19390,7 @@
         <v>21.0</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="F642" s="3" t="s">
         <v>206</v>
@@ -19390,7 +19402,7 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>32</v>
@@ -19402,7 +19414,7 @@
         <v>21.0</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="F643" s="3" t="s">
         <v>20</v>
@@ -19414,10 +19426,10 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B644" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C644" s="2" t="s">
         <v>12</v>
@@ -19434,10 +19446,10 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B645" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C645" s="2" t="s">
         <v>12</v>
@@ -19446,7 +19458,7 @@
         <v>6.0</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="F645" s="3"/>
       <c r="G645" s="7"/>
@@ -19454,10 +19466,10 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B646" s="2" t="s">
         <v>1275</v>
-      </c>
-      <c r="B646" s="2" t="s">
-        <v>1273</v>
       </c>
       <c r="C646" s="2" t="s">
         <v>12</v>
@@ -19466,7 +19478,7 @@
         <v>6.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="F646" s="3"/>
       <c r="G646" s="7"/>
@@ -19474,10 +19486,10 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="B647" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C647" s="2" t="s">
         <v>12</v>
@@ -19486,7 +19498,7 @@
         <v>6.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="F647" s="3"/>
       <c r="G647" s="7"/>
@@ -19494,10 +19506,10 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B648" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C648" s="2" t="s">
         <v>12</v>
@@ -19506,7 +19518,7 @@
         <v>6.0</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="F648" s="3"/>
       <c r="G648" s="7"/>
@@ -19514,10 +19526,10 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="B649" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C649" s="2" t="s">
         <v>12</v>
@@ -19526,7 +19538,7 @@
         <v>6.0</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="F649" s="3"/>
       <c r="G649" s="7"/>
@@ -19534,10 +19546,10 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="B650" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C650" s="2" t="s">
         <v>12</v>
@@ -19546,7 +19558,7 @@
         <v>6.0</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="F650" s="3"/>
       <c r="G650" s="7"/>
@@ -19554,10 +19566,10 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B651" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C651" s="2" t="s">
         <v>12</v>
@@ -19566,7 +19578,7 @@
         <v>6.0</v>
       </c>
       <c r="E651" s="2" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="F651" s="3"/>
       <c r="G651" s="7"/>
@@ -19574,7 +19586,7 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>37</v>
@@ -19586,10 +19598,10 @@
         <v>17.0</v>
       </c>
       <c r="E652" s="2" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="F652" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G652" s="7">
         <v>46963.0</v>
@@ -19600,7 +19612,7 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>37</v>
@@ -19612,10 +19624,10 @@
         <v>17.0</v>
       </c>
       <c r="E653" s="2" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F653" s="3" t="s">
         <v>1289</v>
-      </c>
-      <c r="F653" s="3" t="s">
-        <v>1287</v>
       </c>
       <c r="G653" s="7">
         <v>46963.0</v>
@@ -19624,7 +19636,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>37</v>
@@ -19636,10 +19648,10 @@
         <v>17.0</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="F654" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G654" s="7">
         <v>46995.0</v>
@@ -19648,7 +19660,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>37</v>
@@ -19660,10 +19672,10 @@
         <v>17.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="F655" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G655" s="7">
         <v>46963.0</v>
@@ -19672,7 +19684,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>37</v>
@@ -19687,7 +19699,7 @@
         <v>1028</v>
       </c>
       <c r="F656" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G656" s="7">
         <v>46477.0</v>
@@ -19696,7 +19708,7 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>37</v>
@@ -19711,7 +19723,7 @@
         <v>1028</v>
       </c>
       <c r="F657" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G657" s="7">
         <v>46488.0</v>
@@ -19720,7 +19732,7 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>37</v>
@@ -19735,7 +19747,7 @@
         <v>959</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G658" s="7">
         <v>46488.0</v>
@@ -19744,7 +19756,7 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>37</v>
@@ -19756,10 +19768,10 @@
         <v>12.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G659" s="7">
         <v>46836.0</v>
@@ -19768,7 +19780,7 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>37</v>
@@ -19783,7 +19795,7 @@
         <v>287</v>
       </c>
       <c r="F660" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G660" s="7">
         <v>46794.0</v>
@@ -19792,7 +19804,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>37</v>
@@ -19807,7 +19819,7 @@
         <v>879</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G661" s="7">
         <v>46940.0</v>
@@ -19816,7 +19828,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>37</v>
@@ -19828,10 +19840,10 @@
         <v>12.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="F662" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G662" s="7">
         <v>46940.0</v>
@@ -19840,7 +19852,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>37</v>
@@ -19855,7 +19867,7 @@
         <v>781</v>
       </c>
       <c r="F663" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G663" s="7">
         <v>46530.0</v>
@@ -19864,7 +19876,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>37</v>
@@ -19876,10 +19888,10 @@
         <v>13.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1305</v>
+        <v>1307</v>
       </c>
       <c r="F664" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G664" s="7">
         <v>46530.0</v>
@@ -19888,7 +19900,7 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1306</v>
+        <v>1308</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>37</v>
@@ -19900,10 +19912,10 @@
         <v>13.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="F665" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G665" s="7">
         <v>46487.0</v>
@@ -19912,7 +19924,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>37</v>
@@ -19927,7 +19939,7 @@
         <v>980</v>
       </c>
       <c r="F666" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G666" s="7">
         <v>46792.0</v>
@@ -19936,7 +19948,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>37</v>
@@ -19948,10 +19960,10 @@
         <v>19.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="F667" s="3" t="s">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="G667" s="7">
         <v>46794.0</v>
@@ -19960,7 +19972,7 @@
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="B668" s="2" t="s">
         <v>37</v>
@@ -19972,10 +19984,10 @@
         <v>19.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="F668" s="3" t="s">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="G668" s="7">
         <v>46793.0</v>
@@ -19984,7 +19996,7 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="B669" s="2" t="s">
         <v>37</v>
@@ -19999,7 +20011,7 @@
         <v>977</v>
       </c>
       <c r="F669" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G669" s="7">
         <v>46509.0</v>
@@ -20008,10 +20020,10 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="B670" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C670" s="2" t="s">
         <v>12</v>
@@ -20023,7 +20035,7 @@
         <v>1037</v>
       </c>
       <c r="F670" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G670" s="7">
         <v>46530.0</v>
@@ -20032,10 +20044,10 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>12</v>
@@ -20044,10 +20056,10 @@
         <v>1.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="F671" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G671" s="7">
         <v>46792.0</v>
@@ -20056,7 +20068,7 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>37</v>
@@ -20068,7 +20080,7 @@
         <v>21.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="F672" s="3" t="s">
         <v>17</v>
@@ -20080,7 +20092,7 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>37</v>
@@ -20092,10 +20104,10 @@
         <v>13.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="F673" s="3" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="G673" s="7">
         <v>46530.0</v>
@@ -20104,7 +20116,7 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>37</v>
@@ -20120,7 +20132,7 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>37</v>
@@ -20144,7 +20156,7 @@
     </row>
     <row r="676">
       <c r="A676" s="2" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="B676" s="2" t="s">
         <v>640</v>
@@ -20156,7 +20168,7 @@
         <v>13.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="F676" s="3" t="s">
         <v>219</v>
@@ -20165,7 +20177,7 @@
         <v>47231.0</v>
       </c>
       <c r="H676" s="2" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="677">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -23318,16 +23318,6 @@
       <c r="G964" s="7"/>
       <c r="H964" s="2"/>
     </row>
-    <row r="965">
-      <c r="A965" s="2"/>
-      <c r="B965" s="2"/>
-      <c r="C965" s="2"/>
-      <c r="D965" s="2"/>
-      <c r="E965" s="2"/>
-      <c r="F965" s="3"/>
-      <c r="G965" s="7"/>
-      <c r="H965" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3380" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3385" uniqueCount="1346">
   <si>
     <t>ID</t>
   </si>
@@ -625,7 +625,7 @@
     <t>ID39835414951313</t>
   </si>
   <si>
-    <t>EP350 (鴨肝) (9入)</t>
+    <t>EP350 (鴨肝) (9入) --出清</t>
   </si>
   <si>
     <t>ID39835414951314</t>
@@ -970,7 +970,7 @@
     <t>ID1776755702626</t>
   </si>
   <si>
-    <t>PRCER-YK</t>
+    <t>PRCER-YK-K</t>
   </si>
   <si>
     <t>1150409K</t>
@@ -2008,7 +2008,7 @@
     <t>ID1785316769178</t>
   </si>
   <si>
-    <t>ADR81(一般店家)</t>
+    <t>ADR81(一般店家)--出清</t>
   </si>
   <si>
     <t>ID1785316786487</t>
@@ -4043,6 +4043,12 @@
   </si>
   <si>
     <t>G 鴨腱</t>
+  </si>
+  <si>
+    <t>1792547765429708</t>
+  </si>
+  <si>
+    <t>1150416K6</t>
   </si>
 </sst>
 </file>
@@ -20579,13 +20585,27 @@
       <c r="H690" s="2"/>
     </row>
     <row r="691">
-      <c r="A691" s="2"/>
-      <c r="B691" s="2"/>
-      <c r="C691" s="2"/>
-      <c r="D691" s="2"/>
-      <c r="E691" s="2"/>
-      <c r="F691" s="3"/>
-      <c r="G691" s="7"/>
+      <c r="A691" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B691" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C691" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D691" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E691" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="F691" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G691" s="7">
+        <v>46793.0</v>
+      </c>
       <c r="H691" s="2"/>
     </row>
     <row r="692">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3385" uniqueCount="1346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3472" uniqueCount="1374">
   <si>
     <t>ID</t>
   </si>
@@ -4049,6 +4049,90 @@
   </si>
   <si>
     <t>1150416K6</t>
+  </si>
+  <si>
+    <t>M89CER-十字切-KR</t>
+  </si>
+  <si>
+    <t>1151028S</t>
+  </si>
+  <si>
+    <t>1792553014463273</t>
+  </si>
+  <si>
+    <t>1792553039175941</t>
+  </si>
+  <si>
+    <t>PROB-對切-SS</t>
+  </si>
+  <si>
+    <t>1792553054758721</t>
+  </si>
+  <si>
+    <t>1792553074532957</t>
+  </si>
+  <si>
+    <t>1792553085979099</t>
+  </si>
+  <si>
+    <t>PRSRL-280-320-GO-N6</t>
+  </si>
+  <si>
+    <t>1792553104540769</t>
+  </si>
+  <si>
+    <t>1792553137703965</t>
+  </si>
+  <si>
+    <t>1792553285516694</t>
+  </si>
+  <si>
+    <t>PRRERB-580-620-YK</t>
+  </si>
+  <si>
+    <t>1792553294708725</t>
+  </si>
+  <si>
+    <t>PRRERB-580-620-GO</t>
+  </si>
+  <si>
+    <t>BH1-對切</t>
+  </si>
+  <si>
+    <t>1792556755522813</t>
+  </si>
+  <si>
+    <t>10/28 (三) 分切</t>
+  </si>
+  <si>
+    <t>1792564851235232</t>
+  </si>
+  <si>
+    <t>22B</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>1792564886325102</t>
+  </si>
+  <si>
+    <t>1792564908233739</t>
+  </si>
+  <si>
+    <t>1792564928797395</t>
+  </si>
+  <si>
+    <t>1792564973168742</t>
+  </si>
+  <si>
+    <t>ADK</t>
+  </si>
+  <si>
+    <t>1792564994726271</t>
+  </si>
+  <si>
+    <t>10/22(四)</t>
   </si>
 </sst>
 </file>
@@ -20609,191 +20693,439 @@
       <c r="H691" s="2"/>
     </row>
     <row r="692">
-      <c r="A692" s="2"/>
-      <c r="B692" s="2"/>
-      <c r="C692" s="2"/>
-      <c r="D692" s="2"/>
-      <c r="E692" s="2"/>
-      <c r="F692" s="3"/>
+      <c r="A692" s="2">
+        <v>1.79255299094017E15</v>
+      </c>
+      <c r="B692" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C692" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D692" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E692" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="F692" s="3" t="s">
+        <v>1347</v>
+      </c>
       <c r="G692" s="7"/>
       <c r="H692" s="2"/>
     </row>
     <row r="693">
-      <c r="A693" s="2"/>
-      <c r="B693" s="2"/>
-      <c r="C693" s="2"/>
-      <c r="D693" s="2"/>
-      <c r="E693" s="2"/>
-      <c r="F693" s="3"/>
-      <c r="G693" s="7"/>
+      <c r="A693" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B693" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C693" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D693" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E693" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="F693" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G693" s="7">
+        <v>46509.0</v>
+      </c>
       <c r="H693" s="2"/>
     </row>
     <row r="694">
-      <c r="A694" s="2"/>
-      <c r="B694" s="2"/>
-      <c r="C694" s="2"/>
-      <c r="D694" s="2"/>
-      <c r="E694" s="2"/>
-      <c r="F694" s="3"/>
-      <c r="G694" s="7"/>
+      <c r="A694" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B694" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C694" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D694" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E694" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F694" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G694" s="7">
+        <v>46830.0</v>
+      </c>
       <c r="H694" s="2"/>
     </row>
     <row r="695">
-      <c r="A695" s="2"/>
-      <c r="B695" s="2"/>
-      <c r="C695" s="2"/>
-      <c r="D695" s="2"/>
-      <c r="E695" s="2"/>
-      <c r="F695" s="3"/>
-      <c r="G695" s="7"/>
+      <c r="A695" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B695" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C695" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D695" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E695" s="2" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F695" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G695" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H695" s="2"/>
     </row>
     <row r="696">
-      <c r="A696" s="2"/>
-      <c r="B696" s="2"/>
-      <c r="C696" s="2"/>
-      <c r="D696" s="2"/>
-      <c r="E696" s="2"/>
-      <c r="F696" s="3"/>
-      <c r="G696" s="7"/>
+      <c r="A696" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B696" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C696" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D696" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E696" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="F696" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G696" s="7">
+        <v>46530.0</v>
+      </c>
       <c r="H696" s="2"/>
     </row>
     <row r="697">
-      <c r="A697" s="2"/>
-      <c r="B697" s="2"/>
-      <c r="C697" s="2"/>
-      <c r="D697" s="2"/>
-      <c r="E697" s="2"/>
-      <c r="F697" s="3"/>
+      <c r="A697" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B697" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C697" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D697" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E697" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>1347</v>
+      </c>
       <c r="G697" s="7"/>
       <c r="H697" s="2"/>
     </row>
     <row r="698">
-      <c r="A698" s="2"/>
-      <c r="B698" s="2"/>
-      <c r="C698" s="2"/>
-      <c r="D698" s="2"/>
-      <c r="E698" s="2"/>
-      <c r="F698" s="3"/>
-      <c r="G698" s="7"/>
+      <c r="A698" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B698" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C698" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D698" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E698" s="2" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G698" s="7">
+        <v>46487.0</v>
+      </c>
       <c r="H698" s="2"/>
     </row>
     <row r="699">
-      <c r="A699" s="2"/>
-      <c r="B699" s="2"/>
-      <c r="C699" s="2"/>
-      <c r="D699" s="2"/>
-      <c r="E699" s="2"/>
-      <c r="F699" s="3"/>
-      <c r="G699" s="7"/>
+      <c r="A699" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B699" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C699" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D699" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E699" s="2" t="s">
+        <v>970</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G699" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H699" s="2"/>
     </row>
     <row r="700">
-      <c r="A700" s="2"/>
-      <c r="B700" s="2"/>
-      <c r="C700" s="2"/>
-      <c r="D700" s="2"/>
-      <c r="E700" s="2"/>
-      <c r="F700" s="3"/>
-      <c r="G700" s="7"/>
+      <c r="A700" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B700" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C700" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D700" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E700" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G700" s="7">
+        <v>46885.0</v>
+      </c>
       <c r="H700" s="2"/>
     </row>
     <row r="701">
-      <c r="A701" s="2"/>
-      <c r="B701" s="2"/>
-      <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
-      <c r="E701" s="2"/>
-      <c r="F701" s="3"/>
-      <c r="G701" s="7"/>
+      <c r="A701" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D701" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E701" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G701" s="7">
+        <v>46947.0</v>
+      </c>
       <c r="H701" s="2"/>
     </row>
     <row r="702">
-      <c r="A702" s="2"/>
-      <c r="B702" s="2"/>
-      <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
-      <c r="E702" s="2"/>
-      <c r="F702" s="3"/>
-      <c r="G702" s="7"/>
+      <c r="A702" s="2">
+        <v>1.79255331011668E15</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C702" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D702" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E702" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="G702" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H702" s="2"/>
     </row>
     <row r="703">
-      <c r="A703" s="2"/>
-      <c r="B703" s="2"/>
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
-      <c r="E703" s="2"/>
+      <c r="A703" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D703" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E703" s="2" t="s">
+        <v>1363</v>
+      </c>
       <c r="F703" s="3"/>
       <c r="G703" s="7"/>
       <c r="H703" s="2"/>
     </row>
     <row r="704">
-      <c r="A704" s="2"/>
-      <c r="B704" s="2"/>
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
-      <c r="E704" s="2"/>
-      <c r="F704" s="3"/>
+      <c r="A704" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D704" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E704" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F704" s="3">
+        <v>11508.0</v>
+      </c>
       <c r="G704" s="7"/>
       <c r="H704" s="2"/>
     </row>
     <row r="705">
-      <c r="A705" s="2"/>
-      <c r="B705" s="2"/>
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
-      <c r="E705" s="2"/>
-      <c r="F705" s="3"/>
+      <c r="A705" s="2">
+        <v>1.79256485988391E15</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D705" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E705" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F705" s="3">
+        <v>11509.0</v>
+      </c>
       <c r="G705" s="7"/>
       <c r="H705" s="2"/>
     </row>
     <row r="706">
-      <c r="A706" s="2"/>
-      <c r="B706" s="2"/>
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
-      <c r="E706" s="2"/>
-      <c r="F706" s="3"/>
+      <c r="A706" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D706" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E706" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F706" s="3">
+        <v>11509.0</v>
+      </c>
       <c r="G706" s="7"/>
       <c r="H706" s="2"/>
     </row>
     <row r="707">
-      <c r="A707" s="2"/>
-      <c r="B707" s="2"/>
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
-      <c r="E707" s="2"/>
-      <c r="F707" s="3"/>
-      <c r="G707" s="7"/>
+      <c r="A707" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D707" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E707" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G707" s="7">
+        <v>46530.0</v>
+      </c>
       <c r="H707" s="2"/>
     </row>
     <row r="708">
-      <c r="A708" s="2"/>
-      <c r="B708" s="2"/>
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
-      <c r="E708" s="2"/>
-      <c r="F708" s="3"/>
-      <c r="G708" s="7"/>
+      <c r="A708" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D708" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E708" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G708" s="7">
+        <v>46999.0</v>
+      </c>
       <c r="H708" s="2"/>
     </row>
     <row r="709">
-      <c r="A709" s="2"/>
-      <c r="B709" s="2"/>
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
-      <c r="E709" s="2"/>
-      <c r="F709" s="3"/>
-      <c r="G709" s="7"/>
+      <c r="A709" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D709" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E709" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="G709" s="7">
+        <v>46645.0</v>
+      </c>
       <c r="H709" s="2"/>
     </row>
     <row r="710">
-      <c r="A710" s="2"/>
-      <c r="B710" s="2"/>
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
-      <c r="E710" s="2"/>
+      <c r="A710" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>1238</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D710" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E710" s="2" t="s">
+        <v>1373</v>
+      </c>
       <c r="F710" s="3"/>
       <c r="G710" s="7"/>
       <c r="H710" s="2"/>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3437" uniqueCount="1363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="1364">
   <si>
     <t>ID</t>
   </si>
@@ -3782,6 +3782,9 @@
   </si>
   <si>
     <t>TL-4CM-KR</t>
+  </si>
+  <si>
+    <t>[產品出清]</t>
   </si>
   <si>
     <t>ID1791790184915</t>
@@ -19241,11 +19244,13 @@
       <c r="G629" s="7">
         <v>46487.0</v>
       </c>
-      <c r="H629" s="2"/>
+      <c r="H629" s="2" t="s">
+        <v>1257</v>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>38</v>
@@ -19269,7 +19274,7 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>38</v>
@@ -19281,10 +19286,10 @@
         <v>19.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="G631" s="7">
         <v>46794.0</v>
@@ -19293,7 +19298,7 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>38</v>
@@ -19305,10 +19310,10 @@
         <v>19.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="G632" s="7">
         <v>46793.0</v>
@@ -19317,7 +19322,7 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>38</v>
@@ -19341,7 +19346,7 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>1220</v>
@@ -19365,7 +19370,7 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B635" s="2" t="s">
         <v>1220</v>
@@ -19377,7 +19382,7 @@
         <v>1.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="F635" s="3" t="s">
         <v>1236</v>
@@ -19389,7 +19394,7 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>38</v>
@@ -19401,7 +19406,7 @@
         <v>13.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="F636" s="3" t="s">
         <v>1236</v>
@@ -19413,7 +19418,7 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>38</v>
@@ -19437,7 +19442,7 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>38</v>
@@ -19459,7 +19464,7 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>593</v>
@@ -19483,7 +19488,7 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>593</v>
@@ -19507,7 +19512,7 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>593</v>
@@ -19522,7 +19527,7 @@
         <v>1049</v>
       </c>
       <c r="F641" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="G641" s="7">
         <v>46422.0</v>
@@ -19531,7 +19536,7 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>38</v>
@@ -19555,7 +19560,7 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>38</v>
@@ -19579,7 +19584,7 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>38</v>
@@ -19591,7 +19596,7 @@
         <v>21.0</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="F644" s="3">
         <v>11508.0</v>
@@ -19603,7 +19608,7 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>302</v>
@@ -19627,7 +19632,7 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>593</v>
@@ -19639,7 +19644,7 @@
         <v>5.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="F646" s="3" t="s">
         <v>1131</v>
@@ -19651,7 +19656,7 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>593</v>
@@ -19663,7 +19668,7 @@
         <v>5.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="F647" s="3" t="s">
         <v>1131</v>
@@ -19675,7 +19680,7 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>593</v>
@@ -19699,7 +19704,7 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>593</v>
@@ -19723,7 +19728,7 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>593</v>
@@ -19747,7 +19752,7 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>593</v>
@@ -19771,7 +19776,7 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>593</v>
@@ -19795,7 +19800,7 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>593</v>
@@ -19819,7 +19824,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>593</v>
@@ -19834,7 +19839,7 @@
         <v>792</v>
       </c>
       <c r="F654" s="3" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="G654" s="7">
         <v>46352.0</v>
@@ -19845,7 +19850,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>38</v>
@@ -19857,7 +19862,7 @@
         <v>13.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="F655" s="3" t="s">
         <v>210</v>
@@ -19869,7 +19874,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>11</v>
@@ -19881,7 +19886,7 @@
         <v>2.0</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="F656" s="3" t="s">
         <v>23</v>
@@ -19893,7 +19898,7 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>11</v>
@@ -19905,7 +19910,7 @@
         <v>2.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="F657" s="3" t="s">
         <v>23</v>
@@ -19917,7 +19922,7 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>11</v>
@@ -19929,7 +19934,7 @@
         <v>2.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="F658" s="3" t="s">
         <v>23</v>
@@ -19941,7 +19946,7 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>11</v>
@@ -19953,7 +19958,7 @@
         <v>2.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="F659" s="3" t="s">
         <v>23</v>
@@ -19965,7 +19970,7 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>11</v>
@@ -19977,7 +19982,7 @@
         <v>2.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="F660" s="3" t="s">
         <v>23</v>
@@ -19989,7 +19994,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>11</v>
@@ -20001,7 +20006,7 @@
         <v>3.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="F661" s="3" t="s">
         <v>23</v>
@@ -20013,7 +20018,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>11</v>
@@ -20025,7 +20030,7 @@
         <v>5.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="F662" s="3" t="s">
         <v>20</v>
@@ -20037,7 +20042,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>11</v>
@@ -20061,7 +20066,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>11</v>
@@ -20073,7 +20078,7 @@
         <v>5.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="F664" s="3" t="s">
         <v>289</v>
@@ -20085,7 +20090,7 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>11</v>
@@ -20097,7 +20102,7 @@
         <v>4.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="F665" s="3" t="s">
         <v>210</v>
@@ -20109,7 +20114,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>11</v>
@@ -20121,7 +20126,7 @@
         <v>4.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="F666" s="3" t="s">
         <v>210</v>
@@ -20133,7 +20138,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>11</v>
@@ -20193,7 +20198,7 @@
         <v>4.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="F669" s="3" t="s">
         <v>210</v>
@@ -20205,7 +20210,7 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>11</v>
@@ -20217,7 +20222,7 @@
         <v>4.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="F670" s="3" t="s">
         <v>210</v>
@@ -20229,7 +20234,7 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B671" s="2" t="s">
         <v>1220</v>
@@ -20249,7 +20254,7 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B672" s="2" t="s">
         <v>1220</v>
@@ -20261,7 +20266,7 @@
         <v>7.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="F672" s="3"/>
       <c r="G672" s="7"/>
@@ -20269,7 +20274,7 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B673" s="2" t="s">
         <v>1220</v>
@@ -20281,7 +20286,7 @@
         <v>7.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="F673" s="3"/>
       <c r="G673" s="7"/>
@@ -20289,7 +20294,7 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>38</v>
@@ -20301,7 +20306,7 @@
         <v>10.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="F674" s="3"/>
       <c r="G674" s="7">
@@ -20311,7 +20316,7 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>38</v>
@@ -20326,7 +20331,7 @@
         <v>316</v>
       </c>
       <c r="F675" s="3" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="G675" s="7">
         <v>46793.0</v>
@@ -20347,17 +20352,17 @@
         <v>1.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="F676" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G676" s="7"/>
       <c r="H676" s="2"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B677" s="2" t="s">
         <v>1220</v>
@@ -20372,7 +20377,7 @@
         <v>957</v>
       </c>
       <c r="F677" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G677" s="7">
         <v>46509.0</v>
@@ -20381,7 +20386,7 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B678" s="2" t="s">
         <v>1220</v>
@@ -20393,10 +20398,10 @@
         <v>1.0</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G678" s="7">
         <v>46830.0</v>
@@ -20405,7 +20410,7 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B679" s="2" t="s">
         <v>1220</v>
@@ -20420,7 +20425,7 @@
         <v>1251</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G679" s="7">
         <v>46792.0</v>
@@ -20429,7 +20434,7 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B680" s="2" t="s">
         <v>1220</v>
@@ -20444,7 +20449,7 @@
         <v>760</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G680" s="7">
         <v>46530.0</v>
@@ -20453,7 +20458,7 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B681" s="2" t="s">
         <v>1220</v>
@@ -20465,17 +20470,17 @@
         <v>1.0</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G681" s="7"/>
       <c r="H681" s="2"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B682" s="2" t="s">
         <v>1220</v>
@@ -20490,7 +20495,7 @@
         <v>1256</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G682" s="7">
         <v>46487.0</v>
@@ -20499,7 +20504,7 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B683" s="2" t="s">
         <v>1220</v>
@@ -20514,7 +20519,7 @@
         <v>960</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G683" s="7">
         <v>46792.0</v>
@@ -20523,7 +20528,7 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B684" s="2" t="s">
         <v>1220</v>
@@ -20535,10 +20540,10 @@
         <v>1.0</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="F684" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G684" s="7">
         <v>46885.0</v>
@@ -20547,7 +20552,7 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B685" s="2" t="s">
         <v>1220</v>
@@ -20559,10 +20564,10 @@
         <v>1.0</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="F685" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G685" s="7">
         <v>46947.0</v>
@@ -20583,10 +20588,10 @@
         <v>1.0</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F686" s="3" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="G686" s="7">
         <v>46792.0</v>
@@ -20595,7 +20600,7 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B687" s="2" t="s">
         <v>1220</v>
@@ -20607,7 +20612,7 @@
         <v>1.0</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="F687" s="3"/>
       <c r="G687" s="7"/>
@@ -20615,7 +20620,7 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>38</v>
@@ -20627,7 +20632,7 @@
         <v>5.0</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="F688" s="3">
         <v>11508.0</v>
@@ -20651,7 +20656,7 @@
         <v>2.0</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F689" s="3">
         <v>11509.0</v>
@@ -20663,7 +20668,7 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>33</v>
@@ -20675,7 +20680,7 @@
         <v>15.0</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="F690" s="3" t="s">
         <v>199</v>
@@ -20687,7 +20692,7 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>593</v>
@@ -20699,10 +20704,10 @@
         <v>14.0</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="F691" s="3" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="G691" s="7">
         <v>46369.0</v>
@@ -20711,7 +20716,7 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>593</v>
@@ -20726,7 +20731,7 @@
         <v>1120</v>
       </c>
       <c r="F692" s="3" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="G692" s="7">
         <v>46369.0</v>
@@ -20735,7 +20740,7 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>257</v>
@@ -20759,7 +20764,7 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>257</v>
@@ -20783,7 +20788,7 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>257</v>
@@ -20807,7 +20812,7 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>257</v>
@@ -20831,7 +20836,7 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>257</v>
@@ -20855,7 +20860,7 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>257</v>
@@ -20879,7 +20884,7 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>257</v>
@@ -20891,7 +20896,7 @@
         <v>12.0</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="F699" s="3" t="s">
         <v>475</v>
@@ -20901,7 +20906,7 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>257</v>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3438" uniqueCount="1364">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="1376">
   <si>
     <t>ID</t>
   </si>
@@ -3043,6 +3043,9 @@
     <t>1150430K</t>
   </si>
   <si>
+    <t>[產品報廢] 出清</t>
+  </si>
+  <si>
     <t>ID1789701771355</t>
   </si>
   <si>
@@ -4103,6 +4106,39 @@
   </si>
   <si>
     <t>1792640402523436</t>
+  </si>
+  <si>
+    <t>ACSRL-280-320-TY</t>
+  </si>
+  <si>
+    <t>1793074498339778</t>
+  </si>
+  <si>
+    <t>M89BBLD-對切-KR</t>
+  </si>
+  <si>
+    <t>1793074513883664</t>
+  </si>
+  <si>
+    <t>1793074533475602</t>
+  </si>
+  <si>
+    <t>1793074556419135</t>
+  </si>
+  <si>
+    <t>PRCFT-3CM-GO</t>
+  </si>
+  <si>
+    <t>1793074583813722</t>
+  </si>
+  <si>
+    <t>1793074625281361</t>
+  </si>
+  <si>
+    <t>PRSTL-4.5CM-YK</t>
+  </si>
+  <si>
+    <t>1793074686766283</t>
   </si>
 </sst>
 </file>
@@ -16040,11 +16076,13 @@
       <c r="G495" s="7">
         <v>46792.0</v>
       </c>
-      <c r="H495" s="2"/>
+      <c r="H495" s="2" t="s">
+        <v>1010</v>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>38</v>
@@ -16056,7 +16094,7 @@
         <v>12.0</v>
       </c>
       <c r="E496" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F496" s="3" t="s">
         <v>958</v>
@@ -16066,7 +16104,7 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>33</v>
@@ -16078,10 +16116,10 @@
         <v>20.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G497" s="7">
         <v>46926.0</v>
@@ -16090,7 +16128,7 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>33</v>
@@ -16105,7 +16143,7 @@
         <v>922</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G498" s="7">
         <v>46926.0</v>
@@ -16114,7 +16152,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>33</v>
@@ -16126,10 +16164,10 @@
         <v>20.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="G499" s="7">
         <v>46925.0</v>
@@ -16138,7 +16176,7 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>33</v>
@@ -16153,7 +16191,7 @@
         <v>932</v>
       </c>
       <c r="F500" s="3" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="G500" s="7">
         <v>46988.0</v>
@@ -16162,7 +16200,7 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>33</v>
@@ -16184,7 +16222,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>38</v>
@@ -16196,10 +16234,10 @@
         <v>19.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F502" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="G502" s="7">
         <v>46940.0</v>
@@ -16208,7 +16246,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>33</v>
@@ -16220,7 +16258,7 @@
         <v>15.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F503" s="3" t="s">
         <v>676</v>
@@ -16232,7 +16270,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>33</v>
@@ -16244,7 +16282,7 @@
         <v>20.0</v>
       </c>
       <c r="E504" s="2" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F504" s="3"/>
       <c r="G504" s="7"/>
@@ -16252,7 +16290,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>593</v>
@@ -16264,10 +16302,10 @@
         <v>17.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G505" s="7">
         <v>46398.0</v>
@@ -16276,7 +16314,7 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>593</v>
@@ -16288,10 +16326,10 @@
         <v>16.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G506" s="7">
         <v>46398.0</v>
@@ -16300,7 +16338,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>257</v>
@@ -16312,7 +16350,7 @@
         <v>10.0</v>
       </c>
       <c r="E507" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F507" s="3" t="s">
         <v>475</v>
@@ -16324,7 +16362,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>257</v>
@@ -16348,7 +16386,7 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>257</v>
@@ -16372,7 +16410,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>257</v>
@@ -16396,7 +16434,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>257</v>
@@ -16408,7 +16446,7 @@
         <v>10.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F511" s="3" t="s">
         <v>475</v>
@@ -16420,7 +16458,7 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>593</v>
@@ -16432,10 +16470,10 @@
         <v>4.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F512" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G512" s="7">
         <v>46384.0</v>
@@ -16444,7 +16482,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>593</v>
@@ -16456,10 +16494,10 @@
         <v>4.0</v>
       </c>
       <c r="E513" s="2" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F513" s="3" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="G513" s="7">
         <v>46384.0</v>
@@ -16468,7 +16506,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>38</v>
@@ -16480,10 +16518,10 @@
         <v>19.0</v>
       </c>
       <c r="E514" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F514" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G514" s="7">
         <v>46940.0</v>
@@ -16492,7 +16530,7 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>38</v>
@@ -16516,7 +16554,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>593</v>
@@ -16528,7 +16566,7 @@
         <v>16.0</v>
       </c>
       <c r="E516" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F516" s="3" t="s">
         <v>595</v>
@@ -16540,7 +16578,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>33</v>
@@ -16564,7 +16602,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>33</v>
@@ -16576,7 +16614,7 @@
         <v>21.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>923</v>
@@ -16588,7 +16626,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>38</v>
@@ -16600,7 +16638,7 @@
         <v>7.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F519" s="3" t="s">
         <v>853</v>
@@ -16612,7 +16650,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>593</v>
@@ -16624,7 +16662,7 @@
         <v>3.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>926</v>
@@ -16638,7 +16676,7 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>38</v>
@@ -16650,7 +16688,7 @@
         <v>1.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>210</v>
@@ -16662,7 +16700,7 @@
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>302</v>
@@ -16674,7 +16712,7 @@
         <v>4.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>23</v>
@@ -16683,12 +16721,12 @@
         <v>46550.0</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>302</v>
@@ -16700,7 +16738,7 @@
         <v>4.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>23</v>
@@ -16709,12 +16747,12 @@
         <v>46554.0</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>302</v>
@@ -16726,7 +16764,7 @@
         <v>4.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>23</v>
@@ -16735,12 +16773,12 @@
         <v>46549.0</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>302</v>
@@ -16752,7 +16790,7 @@
         <v>2.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>23</v>
@@ -16761,12 +16799,12 @@
         <v>46549.0</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>302</v>
@@ -16778,7 +16816,7 @@
         <v>6.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>23</v>
@@ -16787,12 +16825,12 @@
         <v>46549.0</v>
       </c>
       <c r="H526" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>302</v>
@@ -16804,7 +16842,7 @@
         <v>2.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>23</v>
@@ -16813,12 +16851,12 @@
         <v>46494.0</v>
       </c>
       <c r="H527" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>302</v>
@@ -16830,7 +16868,7 @@
         <v>7.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>23</v>
@@ -16844,7 +16882,7 @@
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>302</v>
@@ -16856,7 +16894,7 @@
         <v>6.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>23</v>
@@ -16865,12 +16903,12 @@
         <v>46707.0</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>302</v>
@@ -16882,7 +16920,7 @@
         <v>6.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>23</v>
@@ -16891,12 +16929,12 @@
         <v>46604.0</v>
       </c>
       <c r="H530" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>302</v>
@@ -16908,7 +16946,7 @@
         <v>5.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>23</v>
@@ -16922,7 +16960,7 @@
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>302</v>
@@ -16934,7 +16972,7 @@
         <v>6.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F532" s="3" t="s">
         <v>23</v>
@@ -16943,12 +16981,12 @@
         <v>46659.0</v>
       </c>
       <c r="H532" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>33</v>
@@ -16960,7 +16998,7 @@
         <v>3.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F533" s="3">
         <v>11508.0</v>
@@ -16970,7 +17008,7 @@
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>302</v>
@@ -16982,7 +17020,7 @@
         <v>4.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>23</v>
@@ -16991,12 +17029,12 @@
         <v>46549.0</v>
       </c>
       <c r="H534" s="2" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>33</v>
@@ -17008,7 +17046,7 @@
         <v>13.0</v>
       </c>
       <c r="E535" s="2" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F535" s="3" t="s">
         <v>199</v>
@@ -17020,7 +17058,7 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>38</v>
@@ -17032,10 +17070,10 @@
         <v>22.0</v>
       </c>
       <c r="E536" s="2" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F536" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G536" s="7">
         <v>46941.0</v>
@@ -17044,7 +17082,7 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>33</v>
@@ -17059,7 +17097,7 @@
         <v>740</v>
       </c>
       <c r="F537" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="G537" s="7">
         <v>46910.0</v>
@@ -17068,7 +17106,7 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>33</v>
@@ -17092,7 +17130,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>33</v>
@@ -17107,7 +17145,7 @@
         <v>833</v>
       </c>
       <c r="F539" s="3" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="G539" s="7">
         <v>46675.0</v>
@@ -17116,7 +17154,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>33</v>
@@ -17140,7 +17178,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>33</v>
@@ -17155,7 +17193,7 @@
         <v>833</v>
       </c>
       <c r="F541" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="G541" s="7">
         <v>46612.0</v>
@@ -17164,7 +17202,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>33</v>
@@ -17176,7 +17214,7 @@
         <v>3.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>815</v>
@@ -17188,7 +17226,7 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>33</v>
@@ -17200,7 +17238,7 @@
         <v>17.0</v>
       </c>
       <c r="E543" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F543" s="3" t="s">
         <v>20</v>
@@ -17212,7 +17250,7 @@
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>38</v>
@@ -17224,17 +17262,17 @@
         <v>7.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F544" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="G544" s="7"/>
       <c r="H544" s="2"/>
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>33</v>
@@ -17246,7 +17284,7 @@
         <v>3.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>332</v>
@@ -17258,7 +17296,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>33</v>
@@ -17270,7 +17308,7 @@
         <v>3.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>815</v>
@@ -17282,7 +17320,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>33</v>
@@ -17294,7 +17332,7 @@
         <v>3.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F547" s="3" t="s">
         <v>332</v>
@@ -17306,7 +17344,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>33</v>
@@ -17318,7 +17356,7 @@
         <v>3.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F548" s="3" t="s">
         <v>815</v>
@@ -17330,7 +17368,7 @@
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>302</v>
@@ -17342,17 +17380,17 @@
         <v>16.0</v>
       </c>
       <c r="E549" s="2" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F549" s="3"/>
       <c r="G549" s="7"/>
       <c r="H549" s="2" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>302</v>
@@ -17364,21 +17402,21 @@
         <v>8.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G550" s="7">
         <v>46376.0</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>302</v>
@@ -17390,21 +17428,21 @@
         <v>8.0</v>
       </c>
       <c r="E551" s="2" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F551" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="G551" s="7">
         <v>46376.0</v>
       </c>
       <c r="H551" s="2" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>257</v>
@@ -17428,7 +17466,7 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>593</v>
@@ -17440,10 +17478,10 @@
         <v>13.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G553" s="7">
         <v>46338.0</v>
@@ -17454,7 +17492,7 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>593</v>
@@ -17466,10 +17504,10 @@
         <v>12.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G554" s="7">
         <v>46348.0</v>
@@ -17480,7 +17518,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>593</v>
@@ -17492,10 +17530,10 @@
         <v>12.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G555" s="7">
         <v>46347.0</v>
@@ -17506,7 +17544,7 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>593</v>
@@ -17518,10 +17556,10 @@
         <v>12.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G556" s="7">
         <v>46349.0</v>
@@ -17532,7 +17570,7 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>593</v>
@@ -17544,10 +17582,10 @@
         <v>15.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G557" s="7">
         <v>46422.0</v>
@@ -17556,7 +17594,7 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>593</v>
@@ -17568,10 +17606,10 @@
         <v>8.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G558" s="7">
         <v>46402.0</v>
@@ -17580,7 +17618,7 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>593</v>
@@ -17592,10 +17630,10 @@
         <v>9.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G559" s="7">
         <v>46405.0</v>
@@ -17604,7 +17642,7 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>593</v>
@@ -17616,10 +17654,10 @@
         <v>10.0</v>
       </c>
       <c r="E560" s="2" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G560" s="7">
         <v>46402.0</v>
@@ -17628,7 +17666,7 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>38</v>
@@ -17652,7 +17690,7 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>593</v>
@@ -17664,10 +17702,10 @@
         <v>6.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G562" s="7">
         <v>46366.0</v>
@@ -17678,7 +17716,7 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>33</v>
@@ -17690,7 +17728,7 @@
         <v>21.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F563" s="3" t="s">
         <v>923</v>
@@ -17702,7 +17740,7 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>33</v>
@@ -17714,7 +17752,7 @@
         <v>21.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F564" s="3" t="s">
         <v>923</v>
@@ -17726,7 +17764,7 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>33</v>
@@ -17738,7 +17776,7 @@
         <v>21.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="F565" s="3" t="s">
         <v>923</v>
@@ -17750,7 +17788,7 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>593</v>
@@ -17762,10 +17800,10 @@
         <v>7.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F566" s="3" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="G566" s="7">
         <v>46366.0</v>
@@ -17776,7 +17814,7 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>38</v>
@@ -17788,7 +17826,7 @@
         <v>1.0</v>
       </c>
       <c r="E567" s="2" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="F567" s="3" t="s">
         <v>23</v>
@@ -17800,7 +17838,7 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>38</v>
@@ -17822,7 +17860,7 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>257</v>
@@ -17846,7 +17884,7 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>593</v>
@@ -17858,10 +17896,10 @@
         <v>13.0</v>
       </c>
       <c r="E570" s="2" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="F570" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G570" s="7">
         <v>46348.0</v>
@@ -17872,7 +17910,7 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>38</v>
@@ -17884,10 +17922,10 @@
         <v>1.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F571" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G571" s="7">
         <v>46830.0</v>
@@ -17896,7 +17934,7 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>33</v>
@@ -17908,7 +17946,7 @@
         <v>14.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="F572" s="3" t="s">
         <v>23</v>
@@ -17920,7 +17958,7 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>38</v>
@@ -17932,7 +17970,7 @@
         <v>22.0</v>
       </c>
       <c r="E573" s="2" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F573" s="3" t="s">
         <v>210</v>
@@ -17944,7 +17982,7 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>257</v>
@@ -17968,7 +18006,7 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>257</v>
@@ -17992,7 +18030,7 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>257</v>
@@ -18016,7 +18054,7 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>38</v>
@@ -18028,7 +18066,7 @@
         <v>7.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F577" s="3" t="s">
         <v>853</v>
@@ -18040,7 +18078,7 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>38</v>
@@ -18052,7 +18090,7 @@
         <v>7.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="F578" s="3" t="s">
         <v>853</v>
@@ -18064,7 +18102,7 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>38</v>
@@ -18076,7 +18114,7 @@
         <v>7.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F579" s="3" t="s">
         <v>853</v>
@@ -18088,7 +18126,7 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>38</v>
@@ -18100,7 +18138,7 @@
         <v>5.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="F580" s="3" t="s">
         <v>210</v>
@@ -18110,7 +18148,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>33</v>
@@ -18125,7 +18163,7 @@
         <v>988</v>
       </c>
       <c r="F581" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="G581" s="7">
         <v>46725.0</v>
@@ -18134,7 +18172,7 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>33</v>
@@ -18146,7 +18184,7 @@
         <v>14.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="F582" s="3"/>
       <c r="G582" s="7"/>
@@ -18154,7 +18192,7 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>33</v>
@@ -18166,7 +18204,7 @@
         <v>6.0</v>
       </c>
       <c r="E583" s="2" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="F583" s="3"/>
       <c r="G583" s="7"/>
@@ -18174,7 +18212,7 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>33</v>
@@ -18198,7 +18236,7 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>33</v>
@@ -18222,7 +18260,7 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>33</v>
@@ -18244,7 +18282,7 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>593</v>
@@ -18256,10 +18294,10 @@
         <v>13.0</v>
       </c>
       <c r="E587" s="2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="F587" s="3" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="G587" s="7">
         <v>46349.0</v>
@@ -18270,7 +18308,7 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>38</v>
@@ -18292,7 +18330,7 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>593</v>
@@ -18304,10 +18342,10 @@
         <v>11.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G589" s="7">
         <v>46349.0</v>
@@ -18318,7 +18356,7 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>302</v>
@@ -18330,10 +18368,10 @@
         <v>11.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="F590" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="G590" s="7">
         <v>46356.0</v>
@@ -18344,7 +18382,7 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>33</v>
@@ -18356,7 +18394,7 @@
         <v>21.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F591" s="3" t="s">
         <v>770</v>
@@ -18366,7 +18404,7 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>33</v>
@@ -18378,10 +18416,10 @@
         <v>20.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F592" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="G592" s="7">
         <v>46554.0</v>
@@ -18390,7 +18428,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>302</v>
@@ -18402,7 +18440,7 @@
         <v>14.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="F593" s="3" t="s">
         <v>210</v>
@@ -18414,7 +18452,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>302</v>
@@ -18426,7 +18464,7 @@
         <v>14.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F594" s="3" t="s">
         <v>210</v>
@@ -18438,7 +18476,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>302</v>
@@ -18450,7 +18488,7 @@
         <v>14.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="F595" s="3" t="s">
         <v>210</v>
@@ -18462,7 +18500,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>302</v>
@@ -18474,7 +18512,7 @@
         <v>14.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F596" s="3" t="s">
         <v>210</v>
@@ -18486,7 +18524,7 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>302</v>
@@ -18498,7 +18536,7 @@
         <v>14.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F597" s="3" t="s">
         <v>210</v>
@@ -18510,7 +18548,7 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>302</v>
@@ -18522,7 +18560,7 @@
         <v>14.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>210</v>
@@ -18534,7 +18572,7 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>302</v>
@@ -18546,7 +18584,7 @@
         <v>15.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>210</v>
@@ -18558,7 +18596,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>302</v>
@@ -18570,7 +18608,7 @@
         <v>15.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>210</v>
@@ -18582,7 +18620,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>302</v>
@@ -18594,7 +18632,7 @@
         <v>15.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>210</v>
@@ -18606,7 +18644,7 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>302</v>
@@ -18618,7 +18656,7 @@
         <v>14.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F602" s="3" t="s">
         <v>210</v>
@@ -18630,7 +18668,7 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>33</v>
@@ -18642,10 +18680,10 @@
         <v>7.0</v>
       </c>
       <c r="E603" s="2" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F603" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="G603" s="7">
         <v>46586.0</v>
@@ -18654,7 +18692,7 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>38</v>
@@ -18666,10 +18704,10 @@
         <v>1.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="F604" s="3" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G604" s="7">
         <v>46836.0</v>
@@ -18678,7 +18716,7 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>38</v>
@@ -18690,7 +18728,7 @@
         <v>21.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>210</v>
@@ -18702,7 +18740,7 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>33</v>
@@ -18714,7 +18752,7 @@
         <v>21.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>199</v>
@@ -18726,7 +18764,7 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B607" s="2" t="s">
         <v>33</v>
@@ -18738,7 +18776,7 @@
         <v>21.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="F607" s="3" t="s">
         <v>20</v>
@@ -18750,10 +18788,10 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>12</v>
@@ -18762,7 +18800,7 @@
         <v>6.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="F608" s="3"/>
       <c r="G608" s="7"/>
@@ -18770,10 +18808,10 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B609" s="2" t="s">
         <v>1221</v>
-      </c>
-      <c r="B609" s="2" t="s">
-        <v>1220</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>12</v>
@@ -18782,7 +18820,7 @@
         <v>6.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="F609" s="3"/>
       <c r="G609" s="7"/>
@@ -18790,10 +18828,10 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>12</v>
@@ -18802,7 +18840,7 @@
         <v>6.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="F610" s="3"/>
       <c r="G610" s="7"/>
@@ -18810,10 +18848,10 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>12</v>
@@ -18822,7 +18860,7 @@
         <v>6.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="F611" s="3"/>
       <c r="G611" s="7"/>
@@ -18830,10 +18868,10 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>12</v>
@@ -18842,7 +18880,7 @@
         <v>6.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F612" s="3"/>
       <c r="G612" s="7"/>
@@ -18850,10 +18888,10 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>12</v>
@@ -18862,7 +18900,7 @@
         <v>6.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="F613" s="3"/>
       <c r="G613" s="7"/>
@@ -18870,10 +18908,10 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B614" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C614" s="2" t="s">
         <v>12</v>
@@ -18882,7 +18920,7 @@
         <v>6.0</v>
       </c>
       <c r="E614" s="2" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="F614" s="3"/>
       <c r="G614" s="7"/>
@@ -18890,10 +18928,10 @@
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B615" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C615" s="2" t="s">
         <v>12</v>
@@ -18902,7 +18940,7 @@
         <v>6.0</v>
       </c>
       <c r="E615" s="2" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="F615" s="3"/>
       <c r="G615" s="7"/>
@@ -18910,7 +18948,7 @@
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>38</v>
@@ -18922,10 +18960,10 @@
         <v>17.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G616" s="7">
         <v>46963.0</v>
@@ -18936,7 +18974,7 @@
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>38</v>
@@ -18948,10 +18986,10 @@
         <v>17.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G617" s="7">
         <v>46963.0</v>
@@ -18960,7 +18998,7 @@
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>38</v>
@@ -18972,10 +19010,10 @@
         <v>17.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G618" s="7">
         <v>46995.0</v>
@@ -18984,7 +19022,7 @@
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>38</v>
@@ -18996,10 +19034,10 @@
         <v>17.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G619" s="7">
         <v>46963.0</v>
@@ -19008,7 +19046,7 @@
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>38</v>
@@ -19023,7 +19061,7 @@
         <v>1001</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G620" s="7">
         <v>46477.0</v>
@@ -19032,7 +19070,7 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>38</v>
@@ -19047,7 +19085,7 @@
         <v>1001</v>
       </c>
       <c r="F621" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G621" s="7">
         <v>46488.0</v>
@@ -19056,7 +19094,7 @@
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>38</v>
@@ -19071,7 +19109,7 @@
         <v>939</v>
       </c>
       <c r="F622" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G622" s="7">
         <v>46488.0</v>
@@ -19080,7 +19118,7 @@
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>38</v>
@@ -19092,10 +19130,10 @@
         <v>12.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="F623" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G623" s="7">
         <v>46836.0</v>
@@ -19104,7 +19142,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>38</v>
@@ -19119,7 +19157,7 @@
         <v>278</v>
       </c>
       <c r="F624" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G624" s="7">
         <v>46794.0</v>
@@ -19128,7 +19166,7 @@
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>38</v>
@@ -19143,7 +19181,7 @@
         <v>857</v>
       </c>
       <c r="F625" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G625" s="7">
         <v>46940.0</v>
@@ -19152,7 +19190,7 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>38</v>
@@ -19164,10 +19202,10 @@
         <v>12.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G626" s="7">
         <v>46940.0</v>
@@ -19176,7 +19214,7 @@
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B627" s="2" t="s">
         <v>38</v>
@@ -19191,7 +19229,7 @@
         <v>760</v>
       </c>
       <c r="F627" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G627" s="7">
         <v>46530.0</v>
@@ -19200,7 +19238,7 @@
     </row>
     <row r="628">
       <c r="A628" s="2" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B628" s="2" t="s">
         <v>38</v>
@@ -19212,10 +19250,10 @@
         <v>13.0</v>
       </c>
       <c r="E628" s="2" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="F628" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G628" s="7">
         <v>46530.0</v>
@@ -19224,7 +19262,7 @@
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>38</v>
@@ -19236,21 +19274,21 @@
         <v>13.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="F629" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G629" s="7">
         <v>46487.0</v>
       </c>
       <c r="H629" s="2" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B630" s="2" t="s">
         <v>38</v>
@@ -19265,7 +19303,7 @@
         <v>960</v>
       </c>
       <c r="F630" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G630" s="7">
         <v>46792.0</v>
@@ -19274,7 +19312,7 @@
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B631" s="2" t="s">
         <v>38</v>
@@ -19286,10 +19324,10 @@
         <v>19.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="G631" s="7">
         <v>46794.0</v>
@@ -19298,7 +19336,7 @@
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B632" s="2" t="s">
         <v>38</v>
@@ -19310,10 +19348,10 @@
         <v>19.0</v>
       </c>
       <c r="E632" s="2" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="F632" s="3" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G632" s="7">
         <v>46793.0</v>
@@ -19322,7 +19360,7 @@
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>38</v>
@@ -19337,7 +19375,7 @@
         <v>957</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G633" s="7">
         <v>46509.0</v>
@@ -19346,10 +19384,10 @@
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B634" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C634" s="2" t="s">
         <v>12</v>
@@ -19358,10 +19396,10 @@
         <v>1.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F634" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G634" s="7">
         <v>46530.0</v>
@@ -19370,10 +19408,10 @@
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C635" s="2" t="s">
         <v>12</v>
@@ -19382,10 +19420,10 @@
         <v>1.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="F635" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G635" s="7">
         <v>46792.0</v>
@@ -19394,7 +19432,7 @@
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>38</v>
@@ -19406,10 +19444,10 @@
         <v>13.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="F636" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="G636" s="7">
         <v>46530.0</v>
@@ -19418,7 +19456,7 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>38</v>
@@ -19442,7 +19480,7 @@
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B638" s="2" t="s">
         <v>38</v>
@@ -19464,7 +19502,7 @@
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>593</v>
@@ -19476,10 +19514,10 @@
         <v>17.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F639" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G639" s="7">
         <v>46420.0</v>
@@ -19488,7 +19526,7 @@
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>593</v>
@@ -19500,10 +19538,10 @@
         <v>16.0</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F640" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G640" s="7">
         <v>46420.0</v>
@@ -19512,7 +19550,7 @@
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B641" s="2" t="s">
         <v>593</v>
@@ -19524,10 +19562,10 @@
         <v>15.0</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F641" s="3" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="G641" s="7">
         <v>46422.0</v>
@@ -19536,7 +19574,7 @@
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B642" s="2" t="s">
         <v>38</v>
@@ -19548,10 +19586,10 @@
         <v>2.0</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F642" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G642" s="7">
         <v>46830.0</v>
@@ -19560,7 +19598,7 @@
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>38</v>
@@ -19584,7 +19622,7 @@
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>38</v>
@@ -19596,7 +19634,7 @@
         <v>21.0</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="F644" s="3">
         <v>11508.0</v>
@@ -19608,7 +19646,7 @@
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>302</v>
@@ -19620,10 +19658,10 @@
         <v>2.0</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="F645" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="G645" s="7">
         <v>46830.0</v>
@@ -19632,7 +19670,7 @@
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>593</v>
@@ -19644,10 +19682,10 @@
         <v>5.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="F646" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G646" s="7">
         <v>46384.0</v>
@@ -19656,7 +19694,7 @@
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>593</v>
@@ -19668,10 +19706,10 @@
         <v>5.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="F647" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="G647" s="7">
         <v>46381.0</v>
@@ -19680,7 +19718,7 @@
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>593</v>
@@ -19704,7 +19742,7 @@
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>593</v>
@@ -19728,7 +19766,7 @@
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>593</v>
@@ -19752,7 +19790,7 @@
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B651" s="2" t="s">
         <v>593</v>
@@ -19776,7 +19814,7 @@
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B652" s="2" t="s">
         <v>593</v>
@@ -19800,7 +19838,7 @@
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>593</v>
@@ -19812,7 +19850,7 @@
         <v>5.0</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F653" s="3" t="s">
         <v>210</v>
@@ -19824,7 +19862,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>593</v>
@@ -19839,7 +19877,7 @@
         <v>792</v>
       </c>
       <c r="F654" s="3" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="G654" s="7">
         <v>46352.0</v>
@@ -19850,7 +19888,7 @@
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>38</v>
@@ -19862,7 +19900,7 @@
         <v>13.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="F655" s="3" t="s">
         <v>210</v>
@@ -19874,7 +19912,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>11</v>
@@ -19886,7 +19924,7 @@
         <v>2.0</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="F656" s="3" t="s">
         <v>23</v>
@@ -19898,7 +19936,7 @@
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>11</v>
@@ -19910,7 +19948,7 @@
         <v>2.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="F657" s="3" t="s">
         <v>23</v>
@@ -19922,7 +19960,7 @@
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>11</v>
@@ -19934,7 +19972,7 @@
         <v>2.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="F658" s="3" t="s">
         <v>23</v>
@@ -19946,7 +19984,7 @@
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>11</v>
@@ -19958,7 +19996,7 @@
         <v>2.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F659" s="3" t="s">
         <v>23</v>
@@ -19970,7 +20008,7 @@
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>11</v>
@@ -19982,7 +20020,7 @@
         <v>2.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="F660" s="3" t="s">
         <v>23</v>
@@ -19994,7 +20032,7 @@
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>11</v>
@@ -20006,7 +20044,7 @@
         <v>3.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="F661" s="3" t="s">
         <v>23</v>
@@ -20018,7 +20056,7 @@
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>11</v>
@@ -20030,7 +20068,7 @@
         <v>5.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="F662" s="3" t="s">
         <v>20</v>
@@ -20042,7 +20080,7 @@
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>11</v>
@@ -20066,7 +20104,7 @@
     </row>
     <row r="664">
       <c r="A664" s="2" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>11</v>
@@ -20078,7 +20116,7 @@
         <v>5.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="F664" s="3" t="s">
         <v>289</v>
@@ -20090,7 +20128,7 @@
     </row>
     <row r="665">
       <c r="A665" s="2" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>11</v>
@@ -20102,7 +20140,7 @@
         <v>4.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="F665" s="3" t="s">
         <v>210</v>
@@ -20114,7 +20152,7 @@
     </row>
     <row r="666">
       <c r="A666" s="2" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>11</v>
@@ -20126,7 +20164,7 @@
         <v>4.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="F666" s="3" t="s">
         <v>210</v>
@@ -20138,7 +20176,7 @@
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B667" s="2" t="s">
         <v>11</v>
@@ -20150,7 +20188,7 @@
         <v>4.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F667" s="3" t="s">
         <v>210</v>
@@ -20174,7 +20212,7 @@
         <v>4.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F668" s="3" t="s">
         <v>210</v>
@@ -20198,7 +20236,7 @@
         <v>4.0</v>
       </c>
       <c r="E669" s="2" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="F669" s="3" t="s">
         <v>210</v>
@@ -20210,7 +20248,7 @@
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B670" s="2" t="s">
         <v>11</v>
@@ -20222,7 +20260,7 @@
         <v>4.0</v>
       </c>
       <c r="E670" s="2" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="F670" s="3" t="s">
         <v>210</v>
@@ -20234,10 +20272,10 @@
     </row>
     <row r="671">
       <c r="A671" s="2" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B671" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C671" s="2" t="s">
         <v>12</v>
@@ -20246,7 +20284,7 @@
         <v>7.0</v>
       </c>
       <c r="E671" s="2" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F671" s="3"/>
       <c r="G671" s="7"/>
@@ -20254,10 +20292,10 @@
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C672" s="2" t="s">
         <v>12</v>
@@ -20266,7 +20304,7 @@
         <v>7.0</v>
       </c>
       <c r="E672" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F672" s="3"/>
       <c r="G672" s="7"/>
@@ -20274,10 +20312,10 @@
     </row>
     <row r="673">
       <c r="A673" s="2" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B673" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C673" s="2" t="s">
         <v>12</v>
@@ -20286,7 +20324,7 @@
         <v>7.0</v>
       </c>
       <c r="E673" s="2" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="F673" s="3"/>
       <c r="G673" s="7"/>
@@ -20294,7 +20332,7 @@
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>38</v>
@@ -20306,7 +20344,7 @@
         <v>10.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="F674" s="3"/>
       <c r="G674" s="7">
@@ -20316,7 +20354,7 @@
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B675" s="2" t="s">
         <v>38</v>
@@ -20331,7 +20369,7 @@
         <v>316</v>
       </c>
       <c r="F675" s="3" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="G675" s="7">
         <v>46793.0</v>
@@ -20343,7 +20381,7 @@
         <v>1.79255299094017E15</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C676" s="2" t="s">
         <v>45</v>
@@ -20352,20 +20390,22 @@
         <v>1.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F676" s="3" t="s">
-        <v>1330</v>
-      </c>
-      <c r="G676" s="7"/>
+        <v>1331</v>
+      </c>
+      <c r="G676" s="7">
+        <v>46995.0</v>
+      </c>
       <c r="H676" s="2"/>
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>45</v>
@@ -20377,7 +20417,7 @@
         <v>957</v>
       </c>
       <c r="F677" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G677" s="7">
         <v>46509.0</v>
@@ -20386,10 +20426,10 @@
     </row>
     <row r="678">
       <c r="A678" s="2" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C678" s="2" t="s">
         <v>45</v>
@@ -20398,10 +20438,10 @@
         <v>1.0</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G678" s="7">
         <v>46830.0</v>
@@ -20410,10 +20450,10 @@
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>45</v>
@@ -20422,10 +20462,10 @@
         <v>1.0</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G679" s="7">
         <v>46792.0</v>
@@ -20434,10 +20474,10 @@
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C680" s="2" t="s">
         <v>45</v>
@@ -20449,7 +20489,7 @@
         <v>760</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G680" s="7">
         <v>46530.0</v>
@@ -20458,10 +20498,10 @@
     </row>
     <row r="681">
       <c r="A681" s="2" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C681" s="2" t="s">
         <v>45</v>
@@ -20470,20 +20510,20 @@
         <v>1.0</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G681" s="7"/>
       <c r="H681" s="2"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C682" s="2" t="s">
         <v>45</v>
@@ -20492,10 +20532,10 @@
         <v>1.0</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G682" s="7">
         <v>46487.0</v>
@@ -20504,10 +20544,10 @@
     </row>
     <row r="683">
       <c r="A683" s="2" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C683" s="2" t="s">
         <v>45</v>
@@ -20519,7 +20559,7 @@
         <v>960</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G683" s="7">
         <v>46792.0</v>
@@ -20528,10 +20568,10 @@
     </row>
     <row r="684">
       <c r="A684" s="2" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C684" s="2" t="s">
         <v>45</v>
@@ -20540,10 +20580,10 @@
         <v>1.0</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F684" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G684" s="7">
         <v>46885.0</v>
@@ -20552,10 +20592,10 @@
     </row>
     <row r="685">
       <c r="A685" s="2" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>45</v>
@@ -20564,10 +20604,10 @@
         <v>1.0</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="F685" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G685" s="7">
         <v>46947.0</v>
@@ -20579,7 +20619,7 @@
         <v>1.79255331011668E15</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C686" s="2" t="s">
         <v>45</v>
@@ -20588,10 +20628,10 @@
         <v>1.0</v>
       </c>
       <c r="E686" s="2" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="F686" s="3" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="G686" s="7">
         <v>46792.0</v>
@@ -20600,10 +20640,10 @@
     </row>
     <row r="687">
       <c r="A687" s="2" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B687" s="2" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C687" s="2" t="s">
         <v>45</v>
@@ -20612,7 +20652,7 @@
         <v>1.0</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F687" s="3"/>
       <c r="G687" s="7"/>
@@ -20620,7 +20660,7 @@
     </row>
     <row r="688">
       <c r="A688" s="2" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B688" s="2" t="s">
         <v>38</v>
@@ -20632,7 +20672,7 @@
         <v>5.0</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="F688" s="3">
         <v>11508.0</v>
@@ -20656,7 +20696,7 @@
         <v>2.0</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="F689" s="3">
         <v>11509.0</v>
@@ -20668,7 +20708,7 @@
     </row>
     <row r="690">
       <c r="A690" s="2" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B690" s="2" t="s">
         <v>33</v>
@@ -20680,7 +20720,7 @@
         <v>15.0</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="F690" s="3" t="s">
         <v>199</v>
@@ -20692,7 +20732,7 @@
     </row>
     <row r="691">
       <c r="A691" s="2" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B691" s="2" t="s">
         <v>593</v>
@@ -20704,10 +20744,10 @@
         <v>14.0</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="F691" s="3" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="G691" s="7">
         <v>46369.0</v>
@@ -20716,7 +20756,7 @@
     </row>
     <row r="692">
       <c r="A692" s="2" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B692" s="2" t="s">
         <v>593</v>
@@ -20728,10 +20768,10 @@
         <v>14.0</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F692" s="3" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="G692" s="7">
         <v>46369.0</v>
@@ -20740,7 +20780,7 @@
     </row>
     <row r="693">
       <c r="A693" s="2" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B693" s="2" t="s">
         <v>257</v>
@@ -20764,7 +20804,7 @@
     </row>
     <row r="694">
       <c r="A694" s="2" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B694" s="2" t="s">
         <v>257</v>
@@ -20788,7 +20828,7 @@
     </row>
     <row r="695">
       <c r="A695" s="2" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B695" s="2" t="s">
         <v>257</v>
@@ -20812,7 +20852,7 @@
     </row>
     <row r="696">
       <c r="A696" s="2" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B696" s="2" t="s">
         <v>257</v>
@@ -20836,7 +20876,7 @@
     </row>
     <row r="697">
       <c r="A697" s="2" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B697" s="2" t="s">
         <v>257</v>
@@ -20860,7 +20900,7 @@
     </row>
     <row r="698">
       <c r="A698" s="2" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B698" s="2" t="s">
         <v>257</v>
@@ -20884,7 +20924,7 @@
     </row>
     <row r="699">
       <c r="A699" s="2" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B699" s="2" t="s">
         <v>257</v>
@@ -20896,7 +20936,7 @@
         <v>12.0</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="F699" s="3" t="s">
         <v>475</v>
@@ -20906,7 +20946,7 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B700" s="2" t="s">
         <v>257</v>
@@ -20929,93 +20969,219 @@
       <c r="H700" s="2"/>
     </row>
     <row r="701">
-      <c r="A701" s="2"/>
-      <c r="B701" s="2"/>
-      <c r="C701" s="2"/>
-      <c r="D701" s="2"/>
-      <c r="E701" s="2"/>
-      <c r="F701" s="3"/>
-      <c r="G701" s="7"/>
+      <c r="A701" s="2">
+        <v>1.79307444508079E15</v>
+      </c>
+      <c r="B701" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C701" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D701" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E701" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G701" s="7">
+        <v>46448.0</v>
+      </c>
       <c r="H701" s="2"/>
     </row>
     <row r="702">
-      <c r="A702" s="2"/>
-      <c r="B702" s="2"/>
-      <c r="C702" s="2"/>
-      <c r="D702" s="2"/>
-      <c r="E702" s="2"/>
-      <c r="F702" s="3"/>
-      <c r="G702" s="7"/>
+      <c r="A702" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B702" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C702" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D702" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E702" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G702" s="7">
+        <v>47020.0</v>
+      </c>
       <c r="H702" s="2"/>
     </row>
     <row r="703">
-      <c r="A703" s="2"/>
-      <c r="B703" s="2"/>
-      <c r="C703" s="2"/>
-      <c r="D703" s="2"/>
-      <c r="E703" s="2"/>
-      <c r="F703" s="3"/>
-      <c r="G703" s="7"/>
+      <c r="A703" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B703" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C703" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D703" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E703" s="2" t="s">
+        <v>1243</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G703" s="7">
+        <v>47020.0</v>
+      </c>
       <c r="H703" s="2"/>
     </row>
     <row r="704">
-      <c r="A704" s="2"/>
-      <c r="B704" s="2"/>
-      <c r="C704" s="2"/>
-      <c r="D704" s="2"/>
-      <c r="E704" s="2"/>
-      <c r="F704" s="3"/>
-      <c r="G704" s="7"/>
+      <c r="A704" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B704" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C704" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D704" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E704" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G704" s="7">
+        <v>46836.0</v>
+      </c>
       <c r="H704" s="2"/>
     </row>
     <row r="705">
-      <c r="A705" s="2"/>
-      <c r="B705" s="2"/>
-      <c r="C705" s="2"/>
-      <c r="D705" s="2"/>
-      <c r="E705" s="2"/>
-      <c r="F705" s="3"/>
-      <c r="G705" s="7"/>
+      <c r="A705" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B705" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C705" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D705" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E705" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G705" s="7">
+        <v>46759.0</v>
+      </c>
       <c r="H705" s="2"/>
     </row>
     <row r="706">
-      <c r="A706" s="2"/>
-      <c r="B706" s="2"/>
-      <c r="C706" s="2"/>
-      <c r="D706" s="2"/>
-      <c r="E706" s="2"/>
-      <c r="F706" s="3"/>
-      <c r="G706" s="7"/>
+      <c r="A706" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B706" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C706" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D706" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E706" s="2" t="s">
+        <v>760</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G706" s="7">
+        <v>46537.0</v>
+      </c>
       <c r="H706" s="2"/>
     </row>
     <row r="707">
-      <c r="A707" s="2"/>
-      <c r="B707" s="2"/>
-      <c r="C707" s="2"/>
-      <c r="D707" s="2"/>
-      <c r="E707" s="2"/>
-      <c r="F707" s="3"/>
-      <c r="G707" s="7"/>
+      <c r="A707" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B707" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C707" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D707" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E707" s="2" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G707" s="7">
+        <v>46612.0</v>
+      </c>
       <c r="H707" s="2"/>
     </row>
     <row r="708">
-      <c r="A708" s="2"/>
-      <c r="B708" s="2"/>
-      <c r="C708" s="2"/>
-      <c r="D708" s="2"/>
-      <c r="E708" s="2"/>
-      <c r="F708" s="3"/>
-      <c r="G708" s="7"/>
+      <c r="A708" s="2">
+        <v>1.79307465042405E15</v>
+      </c>
+      <c r="B708" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C708" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D708" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E708" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G708" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H708" s="2"/>
     </row>
     <row r="709">
-      <c r="A709" s="2"/>
-      <c r="B709" s="2"/>
-      <c r="C709" s="2"/>
-      <c r="D709" s="2"/>
-      <c r="E709" s="2"/>
-      <c r="F709" s="3"/>
-      <c r="G709" s="7"/>
+      <c r="A709" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B709" s="2" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C709" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D709" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E709" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F709" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="G709" s="7">
+        <v>46792.0</v>
+      </c>
       <c r="H709" s="2"/>
     </row>
     <row r="710">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3482" uniqueCount="1376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3496" uniqueCount="1379">
   <si>
     <t>ID</t>
   </si>
@@ -4139,6 +4139,15 @@
   </si>
   <si>
     <t>1793074686766283</t>
+  </si>
+  <si>
+    <t>1793099765258309</t>
+  </si>
+  <si>
+    <t>1793099916869001</t>
+  </si>
+  <si>
+    <t>1793099945721101</t>
   </si>
 </sst>
 </file>
@@ -21185,33 +21194,73 @@
       <c r="H709" s="2"/>
     </row>
     <row r="710">
-      <c r="A710" s="2"/>
-      <c r="B710" s="2"/>
-      <c r="C710" s="2"/>
-      <c r="D710" s="2"/>
-      <c r="E710" s="2"/>
-      <c r="F710" s="3"/>
+      <c r="A710" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B710" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C710" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D710" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E710" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="F710" s="3">
+        <v>11505.0</v>
+      </c>
       <c r="G710" s="7"/>
       <c r="H710" s="2"/>
     </row>
     <row r="711">
-      <c r="A711" s="2"/>
-      <c r="B711" s="2"/>
-      <c r="C711" s="2"/>
-      <c r="D711" s="2"/>
-      <c r="E711" s="2"/>
-      <c r="F711" s="3"/>
-      <c r="G711" s="7"/>
+      <c r="A711" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B711" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C711" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D711" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E711" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F711" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G711" s="7">
+        <v>46595.0</v>
+      </c>
       <c r="H711" s="2"/>
     </row>
     <row r="712">
-      <c r="A712" s="2"/>
-      <c r="B712" s="2"/>
-      <c r="C712" s="2"/>
-      <c r="D712" s="2"/>
-      <c r="E712" s="2"/>
-      <c r="F712" s="3"/>
-      <c r="G712" s="7"/>
+      <c r="A712" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B712" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C712" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D712" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E712" s="2" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F712" s="3" t="s">
+        <v>770</v>
+      </c>
+      <c r="G712" s="7">
+        <v>46608.0</v>
+      </c>
       <c r="H712" s="2"/>
     </row>
     <row r="713">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3496" uniqueCount="1379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3511" uniqueCount="1382">
   <si>
     <t>ID</t>
   </si>
@@ -4148,6 +4148,15 @@
   </si>
   <si>
     <t>1793099945721101</t>
+  </si>
+  <si>
+    <t>1793161555040602</t>
+  </si>
+  <si>
+    <t>1793161583086606</t>
+  </si>
+  <si>
+    <t>1793161597917815</t>
   </si>
 </sst>
 </file>
@@ -21212,7 +21221,9 @@
       <c r="F710" s="3">
         <v>11505.0</v>
       </c>
-      <c r="G710" s="7"/>
+      <c r="G710" s="7">
+        <v>46848.0</v>
+      </c>
       <c r="H710" s="2"/>
     </row>
     <row r="711">
@@ -21235,7 +21246,7 @@
         <v>69</v>
       </c>
       <c r="G711" s="7">
-        <v>46595.0</v>
+        <v>46607.0</v>
       </c>
       <c r="H711" s="2"/>
     </row>
@@ -21259,37 +21270,75 @@
         <v>770</v>
       </c>
       <c r="G712" s="7">
-        <v>46608.0</v>
+        <v>46628.0</v>
       </c>
       <c r="H712" s="2"/>
     </row>
     <row r="713">
-      <c r="A713" s="2"/>
-      <c r="B713" s="2"/>
-      <c r="C713" s="2"/>
-      <c r="D713" s="2"/>
-      <c r="E713" s="2"/>
-      <c r="F713" s="3"/>
-      <c r="G713" s="7"/>
+      <c r="A713" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B713" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C713" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D713" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E713" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="F713" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="G713" s="7">
+        <v>46431.0</v>
+      </c>
       <c r="H713" s="2"/>
     </row>
     <row r="714">
-      <c r="A714" s="2"/>
-      <c r="B714" s="2"/>
-      <c r="C714" s="2"/>
-      <c r="D714" s="2"/>
-      <c r="E714" s="2"/>
-      <c r="F714" s="3"/>
+      <c r="A714" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B714" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C714" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D714" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E714" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F714" s="3" t="s">
+        <v>719</v>
+      </c>
       <c r="G714" s="7"/>
       <c r="H714" s="2"/>
     </row>
     <row r="715">
-      <c r="A715" s="2"/>
-      <c r="B715" s="2"/>
-      <c r="C715" s="2"/>
-      <c r="D715" s="2"/>
-      <c r="E715" s="2"/>
-      <c r="F715" s="3"/>
+      <c r="A715" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B715" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C715" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D715" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E715" s="2" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F715" s="3" t="s">
+        <v>716</v>
+      </c>
       <c r="G715" s="7"/>
       <c r="H715" s="2"/>
     </row>

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3511" uniqueCount="1382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3554" uniqueCount="1394">
   <si>
     <t>ID</t>
   </si>
@@ -4157,6 +4157,42 @@
   </si>
   <si>
     <t>1793161597917815</t>
+  </si>
+  <si>
+    <t>1793186590197003</t>
+  </si>
+  <si>
+    <t>M89BBLD-KR-K</t>
+  </si>
+  <si>
+    <t>1151020K5</t>
+  </si>
+  <si>
+    <t>1793186692676829</t>
+  </si>
+  <si>
+    <t>26#32</t>
+  </si>
+  <si>
+    <t>1793186777788714</t>
+  </si>
+  <si>
+    <t>1793186799011227</t>
+  </si>
+  <si>
+    <t>1793186818215954</t>
+  </si>
+  <si>
+    <t>PRTDL-YK-C</t>
+  </si>
+  <si>
+    <t>1793186850503193</t>
+  </si>
+  <si>
+    <t>1793186860915727</t>
+  </si>
+  <si>
+    <t>PRSRL-YK-C</t>
   </si>
 </sst>
 </file>
@@ -21343,93 +21379,219 @@
       <c r="H715" s="2"/>
     </row>
     <row r="716">
-      <c r="A716" s="2"/>
-      <c r="B716" s="2"/>
-      <c r="C716" s="2"/>
-      <c r="D716" s="2"/>
-      <c r="E716" s="2"/>
-      <c r="F716" s="3"/>
-      <c r="G716" s="7"/>
+      <c r="A716" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B716" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C716" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D716" s="2">
+        <v>20.0</v>
+      </c>
+      <c r="E716" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F716" s="3" t="s">
+        <v>1384</v>
+      </c>
+      <c r="G716" s="7">
+        <v>47020.0</v>
+      </c>
       <c r="H716" s="2"/>
     </row>
     <row r="717">
-      <c r="A717" s="2"/>
-      <c r="B717" s="2"/>
-      <c r="C717" s="2"/>
-      <c r="D717" s="2"/>
-      <c r="E717" s="2"/>
-      <c r="F717" s="3"/>
-      <c r="G717" s="7"/>
+      <c r="A717" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B717" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C717" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D717" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E717" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F717" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G717" s="7">
+        <v>46388.0</v>
+      </c>
       <c r="H717" s="2"/>
     </row>
     <row r="718">
-      <c r="A718" s="2"/>
-      <c r="B718" s="2"/>
-      <c r="C718" s="2"/>
-      <c r="D718" s="2"/>
-      <c r="E718" s="2"/>
-      <c r="F718" s="3"/>
-      <c r="G718" s="7"/>
+      <c r="A718" s="2">
+        <v>1.79318672188573E15</v>
+      </c>
+      <c r="B718" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C718" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D718" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="E718" s="2" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F718" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G718" s="7">
+        <v>46395.0</v>
+      </c>
       <c r="H718" s="2"/>
     </row>
     <row r="719">
-      <c r="A719" s="2"/>
-      <c r="B719" s="2"/>
-      <c r="C719" s="2"/>
-      <c r="D719" s="2"/>
-      <c r="E719" s="2"/>
-      <c r="F719" s="3"/>
-      <c r="G719" s="7"/>
+      <c r="A719" s="2">
+        <v>1.79318674508485E15</v>
+      </c>
+      <c r="B719" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C719" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D719" s="2">
+        <v>6.0</v>
+      </c>
+      <c r="E719" s="2" t="s">
+        <v>1229</v>
+      </c>
+      <c r="F719" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G719" s="7">
+        <v>46396.0</v>
+      </c>
       <c r="H719" s="2"/>
     </row>
     <row r="720">
-      <c r="A720" s="2"/>
-      <c r="B720" s="2"/>
-      <c r="C720" s="2"/>
-      <c r="D720" s="2"/>
-      <c r="E720" s="2"/>
-      <c r="F720" s="3"/>
-      <c r="G720" s="7"/>
+      <c r="A720" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B720" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C720" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D720" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E720" s="2" t="s">
+        <v>1231</v>
+      </c>
+      <c r="F720" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G720" s="7">
+        <v>46389.0</v>
+      </c>
       <c r="H720" s="2"/>
     </row>
     <row r="721">
-      <c r="A721" s="2"/>
-      <c r="B721" s="2"/>
-      <c r="C721" s="2"/>
-      <c r="D721" s="2"/>
-      <c r="E721" s="2"/>
-      <c r="F721" s="3"/>
-      <c r="G721" s="7"/>
+      <c r="A721" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B721" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C721" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D721" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E721" s="2" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F721" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G721" s="7">
+        <v>46387.0</v>
+      </c>
       <c r="H721" s="2"/>
     </row>
     <row r="722">
-      <c r="A722" s="2"/>
-      <c r="B722" s="2"/>
-      <c r="C722" s="2"/>
-      <c r="D722" s="2"/>
-      <c r="E722" s="2"/>
-      <c r="F722" s="3"/>
-      <c r="G722" s="7"/>
+      <c r="A722" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B722" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C722" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D722" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="E722" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F722" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G722" s="7">
+        <v>46395.0</v>
+      </c>
       <c r="H722" s="2"/>
     </row>
     <row r="723">
-      <c r="A723" s="2"/>
-      <c r="B723" s="2"/>
-      <c r="C723" s="2"/>
-      <c r="D723" s="2"/>
-      <c r="E723" s="2"/>
-      <c r="F723" s="3"/>
-      <c r="G723" s="7"/>
+      <c r="A723" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B723" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C723" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D723" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E723" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F723" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G723" s="7">
+        <v>46395.0</v>
+      </c>
       <c r="H723" s="2"/>
     </row>
     <row r="724">
-      <c r="A724" s="2"/>
-      <c r="B724" s="2"/>
-      <c r="C724" s="2"/>
-      <c r="D724" s="2"/>
-      <c r="E724" s="2"/>
-      <c r="F724" s="3"/>
-      <c r="G724" s="7"/>
+      <c r="A724" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B724" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C724" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D724" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="E724" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="F724" s="3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G724" s="7">
+        <v>46396.0</v>
+      </c>
       <c r="H724" s="2"/>
     </row>
     <row r="725">

--- a/擴充凍庫.xlsx
+++ b/擴充凍庫.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3552" uniqueCount="1395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="1370">
   <si>
     <t>ID</t>
   </si>
@@ -2704,9 +2704,6 @@
     <t>PRRERB-800-850-GO</t>
   </si>
   <si>
-    <t>[產品移位] Pollux 退 | [產品移位]</t>
-  </si>
-  <si>
     <t>ID1788618625696</t>
   </si>
   <si>
@@ -3712,12 +3709,6 @@
     <t>ID1791789426484</t>
   </si>
   <si>
-    <t>ID1791789451737</t>
-  </si>
-  <si>
-    <t>YK 進貨 10/27（二）</t>
-  </si>
-  <si>
     <t>ID1791789603351</t>
   </si>
   <si>
@@ -3970,12 +3961,6 @@
     <t>PRSRL-SS-C</t>
   </si>
   <si>
-    <t>ID1792484432046</t>
-  </si>
-  <si>
-    <t>樹森10/27</t>
-  </si>
-  <si>
     <t>ID1792485050574</t>
   </si>
   <si>
@@ -3994,12 +3979,6 @@
     <t>1792553014463273</t>
   </si>
   <si>
-    <t>1792553039175941</t>
-  </si>
-  <si>
-    <t>PROB-對切-SS</t>
-  </si>
-  <si>
     <t>1792553054758721</t>
   </si>
   <si>
@@ -4015,124 +3994,70 @@
     <t>PRSRL-280-320-GO-N6</t>
   </si>
   <si>
-    <t>1792553104540769</t>
+    <t>1792553137703965</t>
+  </si>
+  <si>
+    <t>1792636586542971</t>
+  </si>
+  <si>
+    <t>26#91</t>
+  </si>
+  <si>
+    <t>1792636592739457</t>
+  </si>
+  <si>
+    <t>1792639717227982</t>
+  </si>
+  <si>
+    <t>1792639740754754</t>
+  </si>
+  <si>
+    <t>1792639758035694</t>
+  </si>
+  <si>
+    <t>1792639785933991</t>
+  </si>
+  <si>
+    <t>1792639984281196</t>
+  </si>
+  <si>
+    <t>1792639998724664</t>
+  </si>
+  <si>
+    <t>1792640283550257</t>
+  </si>
+  <si>
+    <t>BY13</t>
+  </si>
+  <si>
+    <t>1792640402523436</t>
+  </si>
+  <si>
+    <t>ACSRL-280-320-TY</t>
+  </si>
+  <si>
+    <t>1793074498339778</t>
+  </si>
+  <si>
+    <t>M89BBLD-對切-KR</t>
+  </si>
+  <si>
+    <t>1793074533475602</t>
+  </si>
+  <si>
+    <t>EMSPL-十字切-SS</t>
+  </si>
+  <si>
+    <t>1793074583813722</t>
+  </si>
+  <si>
+    <t>1793074625281361</t>
   </si>
   <si>
     <t>TL-4CM-KR</t>
   </si>
   <si>
-    <t>1792553137703965</t>
-  </si>
-  <si>
-    <t>1792553285516694</t>
-  </si>
-  <si>
-    <t>PRRERB-580-620-YK</t>
-  </si>
-  <si>
-    <t>1792553294708725</t>
-  </si>
-  <si>
-    <t>PRRERB-580-620-GO</t>
-  </si>
-  <si>
-    <t>BH1-對切</t>
-  </si>
-  <si>
-    <t>1792556755522813</t>
-  </si>
-  <si>
-    <t>10/28 (三) 分切</t>
-  </si>
-  <si>
-    <t>1792564851235232</t>
-  </si>
-  <si>
-    <t>22B(22-24)</t>
-  </si>
-  <si>
-    <t>W</t>
-  </si>
-  <si>
-    <t>1792564973168742</t>
-  </si>
-  <si>
-    <t>ADK</t>
-  </si>
-  <si>
-    <t>1792636586542971</t>
-  </si>
-  <si>
-    <t>26#91</t>
-  </si>
-  <si>
-    <t>1792636592739457</t>
-  </si>
-  <si>
-    <t>1792639717227982</t>
-  </si>
-  <si>
-    <t>1792639740754754</t>
-  </si>
-  <si>
-    <t>1792639758035694</t>
-  </si>
-  <si>
-    <t>1792639785933991</t>
-  </si>
-  <si>
-    <t>1792639984281196</t>
-  </si>
-  <si>
-    <t>1792639998724664</t>
-  </si>
-  <si>
-    <t>1792640283550257</t>
-  </si>
-  <si>
-    <t>BY13</t>
-  </si>
-  <si>
-    <t>1792640402523436</t>
-  </si>
-  <si>
-    <t>ACSRL-280-320-TY</t>
-  </si>
-  <si>
-    <t>1793074498339778</t>
-  </si>
-  <si>
-    <t>M89BBLD-對切-KR</t>
-  </si>
-  <si>
-    <t>1793074513883664</t>
-  </si>
-  <si>
-    <t>[產品出清]</t>
-  </si>
-  <si>
-    <t>1793074533475602</t>
-  </si>
-  <si>
-    <t>EMSPL-十字切-SS</t>
-  </si>
-  <si>
-    <t>1793074556419135</t>
-  </si>
-  <si>
-    <t>PRCFT-3CM-GO</t>
-  </si>
-  <si>
-    <t>1793074583813722</t>
-  </si>
-  <si>
-    <t>1793074625281361</t>
-  </si>
-  <si>
     <t>PRSTL-4.5CM-YK</t>
-  </si>
-  <si>
-    <t>1793074686766283</t>
   </si>
   <si>
     <t>1793099765258309</t>
@@ -8762,7 +8687,7 @@
         <v>30</v>
       </c>
       <c r="D183" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E183" s="2" t="s">
         <v>385</v>
@@ -8786,7 +8711,7 @@
         <v>30</v>
       </c>
       <c r="D184" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E184" s="2" t="s">
         <v>387</v>
@@ -8810,7 +8735,7 @@
         <v>30</v>
       </c>
       <c r="D185" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E185" s="2" t="s">
         <v>389</v>
@@ -14757,10 +14682,10 @@
         <v>38</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D438" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E438" s="2" t="s">
         <v>896</v>
@@ -14771,13 +14696,11 @@
       <c r="G438" s="7">
         <v>46794.0</v>
       </c>
-      <c r="H438" s="2" t="s">
-        <v>897</v>
-      </c>
+      <c r="H438" s="2"/>
     </row>
     <row r="439">
       <c r="A439" s="2" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>33</v>
@@ -14789,7 +14712,7 @@
         <v>18.0</v>
       </c>
       <c r="E439" s="2" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="F439" s="3" t="s">
         <v>17</v>
@@ -14799,7 +14722,7 @@
     </row>
     <row r="440">
       <c r="A440" s="2" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>33</v>
@@ -14811,7 +14734,7 @@
         <v>18.0</v>
       </c>
       <c r="E440" s="2" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="F440" s="3" t="s">
         <v>17</v>
@@ -14821,7 +14744,7 @@
     </row>
     <row r="441">
       <c r="A441" s="2" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>33</v>
@@ -14845,7 +14768,7 @@
     </row>
     <row r="442">
       <c r="A442" s="2" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B442" s="2" t="s">
         <v>38</v>
@@ -14857,10 +14780,10 @@
         <v>19.0</v>
       </c>
       <c r="E442" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="F442" s="3" t="s">
         <v>904</v>
-      </c>
-      <c r="F442" s="3" t="s">
-        <v>905</v>
       </c>
       <c r="G442" s="7">
         <v>46620.0</v>
@@ -14869,7 +14792,7 @@
     </row>
     <row r="443">
       <c r="A443" s="2" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="B443" s="2" t="s">
         <v>38</v>
@@ -14893,7 +14816,7 @@
     </row>
     <row r="444">
       <c r="A444" s="2" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B444" s="2" t="s">
         <v>38</v>
@@ -14905,10 +14828,10 @@
         <v>20.0</v>
       </c>
       <c r="E444" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="F444" s="3" t="s">
         <v>908</v>
-      </c>
-      <c r="F444" s="3" t="s">
-        <v>909</v>
       </c>
       <c r="G444" s="7">
         <v>46670.0</v>
@@ -14917,7 +14840,7 @@
     </row>
     <row r="445">
       <c r="A445" s="2" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B445" s="2" t="s">
         <v>38</v>
@@ -14929,7 +14852,7 @@
         <v>11.0</v>
       </c>
       <c r="E445" s="2" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F445" s="3" t="s">
         <v>210</v>
@@ -14941,7 +14864,7 @@
     </row>
     <row r="446">
       <c r="A446" s="2" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="B446" s="2" t="s">
         <v>38</v>
@@ -14953,7 +14876,7 @@
         <v>11.0</v>
       </c>
       <c r="E446" s="2" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F446" s="3" t="s">
         <v>210</v>
@@ -14965,7 +14888,7 @@
     </row>
     <row r="447">
       <c r="A447" s="2" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B447" s="2" t="s">
         <v>38</v>
@@ -14977,7 +14900,7 @@
         <v>11.0</v>
       </c>
       <c r="E447" s="2" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F447" s="3" t="s">
         <v>210</v>
@@ -14989,7 +14912,7 @@
     </row>
     <row r="448">
       <c r="A448" s="2" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="B448" s="2" t="s">
         <v>38</v>
@@ -15001,7 +14924,7 @@
         <v>11.0</v>
       </c>
       <c r="E448" s="2" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="F448" s="3" t="s">
         <v>210</v>
@@ -15013,7 +14936,7 @@
     </row>
     <row r="449">
       <c r="A449" s="2" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="B449" s="2" t="s">
         <v>33</v>
@@ -15028,7 +14951,7 @@
         <v>262</v>
       </c>
       <c r="F449" s="3" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G449" s="7">
         <v>46461.0</v>
@@ -15037,7 +14960,7 @@
     </row>
     <row r="450">
       <c r="A450" s="2" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B450" s="2" t="s">
         <v>33</v>
@@ -15049,10 +14972,10 @@
         <v>21.0</v>
       </c>
       <c r="E450" s="2" t="s">
+        <v>920</v>
+      </c>
+      <c r="F450" s="3" t="s">
         <v>921</v>
-      </c>
-      <c r="F450" s="3" t="s">
-        <v>922</v>
       </c>
       <c r="G450" s="7">
         <v>46963.0</v>
@@ -15061,7 +14984,7 @@
     </row>
     <row r="451">
       <c r="A451" s="2" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B451" s="2" t="s">
         <v>593</v>
@@ -15073,10 +14996,10 @@
         <v>3.0</v>
       </c>
       <c r="E451" s="2" t="s">
+        <v>923</v>
+      </c>
+      <c r="F451" s="3" t="s">
         <v>924</v>
-      </c>
-      <c r="F451" s="3" t="s">
-        <v>925</v>
       </c>
       <c r="G451" s="7">
         <v>46352.0</v>
@@ -15087,7 +15010,7 @@
     </row>
     <row r="452">
       <c r="A452" s="2" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B452" s="2" t="s">
         <v>593</v>
@@ -15099,10 +15022,10 @@
         <v>3.0</v>
       </c>
       <c r="E452" s="2" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F452" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G452" s="7">
         <v>46352.0</v>
@@ -15113,7 +15036,7 @@
     </row>
     <row r="453">
       <c r="A453" s="2" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B453" s="2" t="s">
         <v>593</v>
@@ -15125,10 +15048,10 @@
         <v>3.0</v>
       </c>
       <c r="E453" s="2" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F453" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G453" s="7">
         <v>46352.0</v>
@@ -15139,7 +15062,7 @@
     </row>
     <row r="454">
       <c r="A454" s="2" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B454" s="2" t="s">
         <v>33</v>
@@ -15151,10 +15074,10 @@
         <v>11.0</v>
       </c>
       <c r="E454" s="2" t="s">
+        <v>930</v>
+      </c>
+      <c r="F454" s="3" t="s">
         <v>931</v>
-      </c>
-      <c r="F454" s="3" t="s">
-        <v>932</v>
       </c>
       <c r="G454" s="7">
         <v>46982.0</v>
@@ -15163,7 +15086,7 @@
     </row>
     <row r="455">
       <c r="A455" s="2" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B455" s="2" t="s">
         <v>33</v>
@@ -15175,10 +15098,10 @@
         <v>10.0</v>
       </c>
       <c r="E455" s="2" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F455" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G455" s="7">
         <v>46914.0</v>
@@ -15187,7 +15110,7 @@
     </row>
     <row r="456">
       <c r="A456" s="2" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B456" s="2" t="s">
         <v>33</v>
@@ -15199,10 +15122,10 @@
         <v>15.0</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F456" s="3" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="G456" s="7">
         <v>46914.0</v>
@@ -15211,7 +15134,7 @@
     </row>
     <row r="457">
       <c r="A457" s="2" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B457" s="2" t="s">
         <v>38</v>
@@ -15223,10 +15146,10 @@
         <v>11.0</v>
       </c>
       <c r="E457" s="2" t="s">
+        <v>937</v>
+      </c>
+      <c r="F457" s="3" t="s">
         <v>938</v>
-      </c>
-      <c r="F457" s="3" t="s">
-        <v>939</v>
       </c>
       <c r="G457" s="7">
         <v>46421.0</v>
@@ -15235,7 +15158,7 @@
     </row>
     <row r="458">
       <c r="A458" s="2" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="B458" s="2" t="s">
         <v>38</v>
@@ -15247,10 +15170,10 @@
         <v>15.0</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F458" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G458" s="7">
         <v>46620.0</v>
@@ -15259,7 +15182,7 @@
     </row>
     <row r="459">
       <c r="A459" s="2" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="B459" s="2" t="s">
         <v>38</v>
@@ -15274,7 +15197,7 @@
         <v>856</v>
       </c>
       <c r="F459" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G459" s="7">
         <v>46757.0</v>
@@ -15283,7 +15206,7 @@
     </row>
     <row r="460">
       <c r="A460" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B460" s="2" t="s">
         <v>38</v>
@@ -15295,10 +15218,10 @@
         <v>15.0</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G460" s="7">
         <v>46480.0</v>
@@ -15307,7 +15230,7 @@
     </row>
     <row r="461">
       <c r="A461" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B461" s="2" t="s">
         <v>38</v>
@@ -15319,10 +15242,10 @@
         <v>15.0</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="F461" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G461" s="7">
         <v>46480.0</v>
@@ -15331,7 +15254,7 @@
     </row>
     <row r="462">
       <c r="A462" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B462" s="2" t="s">
         <v>38</v>
@@ -15343,10 +15266,10 @@
         <v>15.0</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="F462" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G462" s="7">
         <v>46793.0</v>
@@ -15355,7 +15278,7 @@
     </row>
     <row r="463">
       <c r="A463" s="2" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B463" s="2" t="s">
         <v>38</v>
@@ -15370,7 +15293,7 @@
         <v>762</v>
       </c>
       <c r="F463" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G463" s="7">
         <v>46793.0</v>
@@ -15379,33 +15302,31 @@
     </row>
     <row r="464">
       <c r="A464" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="B464" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C464" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D464" s="2">
+        <v>16.0</v>
+      </c>
+      <c r="E464" s="2" t="s">
         <v>950</v>
       </c>
-      <c r="B464" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C464" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D464" s="2">
-        <v>14.0</v>
-      </c>
-      <c r="E464" s="2" t="s">
-        <v>951</v>
-      </c>
       <c r="F464" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G464" s="7">
         <v>46794.0</v>
       </c>
-      <c r="H464" s="2" t="s">
-        <v>630</v>
-      </c>
+      <c r="H464" s="2"/>
     </row>
     <row r="465">
       <c r="A465" s="2" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B465" s="2" t="s">
         <v>38</v>
@@ -15417,10 +15338,10 @@
         <v>15.0</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="F465" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G465" s="7">
         <v>46424.0</v>
@@ -15429,7 +15350,7 @@
     </row>
     <row r="466">
       <c r="A466" s="2" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="B466" s="2" t="s">
         <v>38</v>
@@ -15441,10 +15362,10 @@
         <v>18.0</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F466" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G466" s="7">
         <v>46757.0</v>
@@ -15453,7 +15374,7 @@
     </row>
     <row r="467">
       <c r="A467" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B467" s="2" t="s">
         <v>38</v>
@@ -15465,10 +15386,10 @@
         <v>12.0</v>
       </c>
       <c r="E467" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="F467" s="3" t="s">
         <v>957</v>
-      </c>
-      <c r="F467" s="3" t="s">
-        <v>958</v>
       </c>
       <c r="G467" s="7">
         <v>46670.0</v>
@@ -15477,7 +15398,7 @@
     </row>
     <row r="468">
       <c r="A468" s="2" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="B468" s="2" t="s">
         <v>38</v>
@@ -15489,10 +15410,10 @@
         <v>14.0</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F468" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G468" s="7">
         <v>46792.0</v>
@@ -15501,7 +15422,7 @@
     </row>
     <row r="469">
       <c r="A469" s="2" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B469" s="2" t="s">
         <v>38</v>
@@ -15513,10 +15434,10 @@
         <v>16.0</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F469" s="3" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="G469" s="7">
         <v>46620.0</v>
@@ -15525,7 +15446,7 @@
     </row>
     <row r="470">
       <c r="A470" s="2" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="B470" s="2" t="s">
         <v>33</v>
@@ -15537,10 +15458,10 @@
         <v>16.0</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F470" s="3" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G470" s="7">
         <v>46982.0</v>
@@ -15549,7 +15470,7 @@
     </row>
     <row r="471">
       <c r="A471" s="2" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B471" s="2" t="s">
         <v>11</v>
@@ -15561,7 +15482,7 @@
         <v>2.0</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="F471" s="3" t="s">
         <v>23</v>
@@ -15573,7 +15494,7 @@
     </row>
     <row r="472">
       <c r="A472" s="2" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B472" s="2" t="s">
         <v>11</v>
@@ -15585,7 +15506,7 @@
         <v>2.0</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F472" s="3" t="s">
         <v>23</v>
@@ -15597,7 +15518,7 @@
     </row>
     <row r="473">
       <c r="A473" s="2" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B473" s="2" t="s">
         <v>11</v>
@@ -15609,7 +15530,7 @@
         <v>2.0</v>
       </c>
       <c r="E473" s="2" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F473" s="3" t="s">
         <v>23</v>
@@ -15621,7 +15542,7 @@
     </row>
     <row r="474">
       <c r="A474" s="2" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="B474" s="2" t="s">
         <v>11</v>
@@ -15633,7 +15554,7 @@
         <v>2.0</v>
       </c>
       <c r="E474" s="2" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F474" s="3" t="s">
         <v>23</v>
@@ -15645,7 +15566,7 @@
     </row>
     <row r="475">
       <c r="A475" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B475" s="2" t="s">
         <v>11</v>
@@ -15657,7 +15578,7 @@
         <v>2.0</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="F475" s="3" t="s">
         <v>23</v>
@@ -15669,7 +15590,7 @@
     </row>
     <row r="476">
       <c r="A476" s="2" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="B476" s="2" t="s">
         <v>593</v>
@@ -15681,10 +15602,10 @@
         <v>2.0</v>
       </c>
       <c r="E476" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="F476" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="F476" s="3" t="s">
-        <v>977</v>
       </c>
       <c r="G476" s="7">
         <v>46399.0</v>
@@ -15693,7 +15614,7 @@
     </row>
     <row r="477">
       <c r="A477" s="2" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="B477" s="2" t="s">
         <v>593</v>
@@ -15705,10 +15626,10 @@
         <v>1.0</v>
       </c>
       <c r="E477" s="2" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="F477" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G477" s="7">
         <v>46398.0</v>
@@ -15717,7 +15638,7 @@
     </row>
     <row r="478">
       <c r="A478" s="2" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B478" s="2" t="s">
         <v>593</v>
@@ -15729,10 +15650,10 @@
         <v>1.0</v>
       </c>
       <c r="E478" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="F478" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G478" s="7">
         <v>46398.0</v>
@@ -15741,7 +15662,7 @@
     </row>
     <row r="479">
       <c r="A479" s="2" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B479" s="2" t="s">
         <v>593</v>
@@ -15763,7 +15684,7 @@
     </row>
     <row r="480">
       <c r="A480" s="2" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="B480" s="2" t="s">
         <v>593</v>
@@ -15775,7 +15696,7 @@
         <v>12.0</v>
       </c>
       <c r="E480" s="2" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="F480" s="3" t="s">
         <v>210</v>
@@ -15785,7 +15706,7 @@
     </row>
     <row r="481">
       <c r="A481" s="2" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B481" s="2" t="s">
         <v>257</v>
@@ -15809,7 +15730,7 @@
     </row>
     <row r="482">
       <c r="A482" s="2" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B482" s="2" t="s">
         <v>593</v>
@@ -15831,7 +15752,7 @@
     </row>
     <row r="483">
       <c r="A483" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B483" s="2" t="s">
         <v>33</v>
@@ -15843,10 +15764,10 @@
         <v>15.0</v>
       </c>
       <c r="E483" s="2" t="s">
+        <v>987</v>
+      </c>
+      <c r="F483" s="3" t="s">
         <v>988</v>
-      </c>
-      <c r="F483" s="3" t="s">
-        <v>989</v>
       </c>
       <c r="G483" s="7">
         <v>46432.0</v>
@@ -15855,7 +15776,7 @@
     </row>
     <row r="484">
       <c r="A484" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="B484" s="2" t="s">
         <v>33</v>
@@ -15867,7 +15788,7 @@
         <v>15.0</v>
       </c>
       <c r="E484" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F484" s="3" t="s">
         <v>332</v>
@@ -15879,7 +15800,7 @@
     </row>
     <row r="485">
       <c r="A485" s="2" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B485" s="2" t="s">
         <v>33</v>
@@ -15891,10 +15812,10 @@
         <v>12.0</v>
       </c>
       <c r="E485" s="2" t="s">
+        <v>991</v>
+      </c>
+      <c r="F485" s="3" t="s">
         <v>992</v>
-      </c>
-      <c r="F485" s="3" t="s">
-        <v>993</v>
       </c>
       <c r="G485" s="7">
         <v>46949.0</v>
@@ -15905,7 +15826,7 @@
     </row>
     <row r="486">
       <c r="A486" s="2" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B486" s="2" t="s">
         <v>33</v>
@@ -15917,7 +15838,7 @@
         <v>13.0</v>
       </c>
       <c r="E486" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F486" s="3"/>
       <c r="G486" s="7"/>
@@ -15927,7 +15848,7 @@
     </row>
     <row r="487">
       <c r="A487" s="2" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="B487" s="2" t="s">
         <v>33</v>
@@ -15951,7 +15872,7 @@
     </row>
     <row r="488">
       <c r="A488" s="2" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B488" s="2" t="s">
         <v>33</v>
@@ -15975,7 +15896,7 @@
     </row>
     <row r="489">
       <c r="A489" s="2" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B489" s="2" t="s">
         <v>33</v>
@@ -15987,7 +15908,7 @@
         <v>22.0</v>
       </c>
       <c r="E489" s="2" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F489" s="3"/>
       <c r="G489" s="7"/>
@@ -15995,7 +15916,7 @@
     </row>
     <row r="490">
       <c r="A490" s="2" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="B490" s="2" t="s">
         <v>38</v>
@@ -16007,10 +15928,10 @@
         <v>16.0</v>
       </c>
       <c r="E490" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F490" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G490" s="7">
         <v>46432.0</v>
@@ -16019,7 +15940,7 @@
     </row>
     <row r="491">
       <c r="A491" s="2" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B491" s="2" t="s">
         <v>38</v>
@@ -16031,10 +15952,10 @@
         <v>15.0</v>
       </c>
       <c r="E491" s="2" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F491" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G491" s="7">
         <v>46913.0</v>
@@ -16043,7 +15964,7 @@
     </row>
     <row r="492">
       <c r="A492" s="2" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B492" s="2" t="s">
         <v>38</v>
@@ -16055,21 +15976,21 @@
         <v>21.0</v>
       </c>
       <c r="E492" s="2" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F492" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G492" s="7">
         <v>46641.0</v>
       </c>
       <c r="H492" s="2" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B493" s="2" t="s">
         <v>38</v>
@@ -16093,7 +16014,7 @@
     </row>
     <row r="494">
       <c r="A494" s="2" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="B494" s="2" t="s">
         <v>38</v>
@@ -16108,18 +16029,18 @@
         <v>717</v>
       </c>
       <c r="F494" s="3" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G494" s="7">
         <v>46792.0</v>
       </c>
       <c r="H494" s="2" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="2" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B495" s="2" t="s">
         <v>38</v>
@@ -16131,17 +16052,17 @@
         <v>12.0</v>
       </c>
       <c r="E495" s="2" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="F495" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G495" s="7"/>
       <c r="H495" s="2"/>
     </row>
     <row r="496">
       <c r="A496" s="2" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B496" s="2" t="s">
         <v>33</v>
@@ -16153,10 +16074,10 @@
         <v>20.0</v>
       </c>
       <c r="E496" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F496" s="3" t="s">
         <v>1014</v>
-      </c>
-      <c r="F496" s="3" t="s">
-        <v>1015</v>
       </c>
       <c r="G496" s="7">
         <v>46926.0</v>
@@ -16165,7 +16086,7 @@
     </row>
     <row r="497">
       <c r="A497" s="2" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B497" s="2" t="s">
         <v>33</v>
@@ -16177,10 +16098,10 @@
         <v>20.0</v>
       </c>
       <c r="E497" s="2" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F497" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G497" s="7">
         <v>46926.0</v>
@@ -16189,7 +16110,7 @@
     </row>
     <row r="498">
       <c r="A498" s="2" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B498" s="2" t="s">
         <v>33</v>
@@ -16201,10 +16122,10 @@
         <v>20.0</v>
       </c>
       <c r="E498" s="2" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="F498" s="3" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G498" s="7">
         <v>46925.0</v>
@@ -16213,7 +16134,7 @@
     </row>
     <row r="499">
       <c r="A499" s="2" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="B499" s="2" t="s">
         <v>33</v>
@@ -16225,10 +16146,10 @@
         <v>17.0</v>
       </c>
       <c r="E499" s="2" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F499" s="3" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="G499" s="7">
         <v>46988.0</v>
@@ -16237,7 +16158,7 @@
     </row>
     <row r="500">
       <c r="A500" s="2" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B500" s="2" t="s">
         <v>33</v>
@@ -16249,7 +16170,7 @@
         <v>13.0</v>
       </c>
       <c r="E500" s="2" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F500" s="3"/>
       <c r="G500" s="7"/>
@@ -16259,7 +16180,7 @@
     </row>
     <row r="501">
       <c r="A501" s="2" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B501" s="2" t="s">
         <v>38</v>
@@ -16271,10 +16192,10 @@
         <v>19.0</v>
       </c>
       <c r="E501" s="2" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F501" s="3" t="s">
         <v>1023</v>
-      </c>
-      <c r="F501" s="3" t="s">
-        <v>1024</v>
       </c>
       <c r="G501" s="7">
         <v>46940.0</v>
@@ -16283,7 +16204,7 @@
     </row>
     <row r="502">
       <c r="A502" s="2" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="B502" s="2" t="s">
         <v>33</v>
@@ -16295,7 +16216,7 @@
         <v>15.0</v>
       </c>
       <c r="E502" s="2" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="F502" s="3" t="s">
         <v>677</v>
@@ -16307,7 +16228,7 @@
     </row>
     <row r="503">
       <c r="A503" s="2" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="B503" s="2" t="s">
         <v>33</v>
@@ -16319,7 +16240,7 @@
         <v>20.0</v>
       </c>
       <c r="E503" s="2" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="F503" s="3"/>
       <c r="G503" s="7"/>
@@ -16327,7 +16248,7 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B504" s="2" t="s">
         <v>593</v>
@@ -16339,10 +16260,10 @@
         <v>17.0</v>
       </c>
       <c r="E504" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F504" s="3" t="s">
         <v>1030</v>
-      </c>
-      <c r="F504" s="3" t="s">
-        <v>1031</v>
       </c>
       <c r="G504" s="7">
         <v>46398.0</v>
@@ -16351,7 +16272,7 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="B505" s="2" t="s">
         <v>593</v>
@@ -16363,10 +16284,10 @@
         <v>16.0</v>
       </c>
       <c r="E505" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F505" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G505" s="7">
         <v>46398.0</v>
@@ -16375,7 +16296,7 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B506" s="2" t="s">
         <v>257</v>
@@ -16387,7 +16308,7 @@
         <v>10.0</v>
       </c>
       <c r="E506" s="2" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="F506" s="3" t="s">
         <v>475</v>
@@ -16399,7 +16320,7 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B507" s="2" t="s">
         <v>257</v>
@@ -16423,7 +16344,7 @@
     </row>
     <row r="508">
       <c r="A508" s="2" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="B508" s="2" t="s">
         <v>257</v>
@@ -16447,7 +16368,7 @@
     </row>
     <row r="509">
       <c r="A509" s="2" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="B509" s="2" t="s">
         <v>257</v>
@@ -16471,7 +16392,7 @@
     </row>
     <row r="510">
       <c r="A510" s="2" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B510" s="2" t="s">
         <v>257</v>
@@ -16483,7 +16404,7 @@
         <v>10.0</v>
       </c>
       <c r="E510" s="2" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="F510" s="3" t="s">
         <v>475</v>
@@ -16495,7 +16416,7 @@
     </row>
     <row r="511">
       <c r="A511" s="2" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="B511" s="2" t="s">
         <v>593</v>
@@ -16507,10 +16428,10 @@
         <v>4.0</v>
       </c>
       <c r="E511" s="2" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="F511" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G511" s="7">
         <v>46384.0</v>
@@ -16519,7 +16440,7 @@
     </row>
     <row r="512">
       <c r="A512" s="2" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="B512" s="2" t="s">
         <v>593</v>
@@ -16531,10 +16452,10 @@
         <v>4.0</v>
       </c>
       <c r="E512" s="2" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F512" s="3" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="G512" s="7">
         <v>46384.0</v>
@@ -16543,7 +16464,7 @@
     </row>
     <row r="513">
       <c r="A513" s="2" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B513" s="2" t="s">
         <v>38</v>
@@ -16555,10 +16476,10 @@
         <v>19.0</v>
       </c>
       <c r="E513" s="2" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F513" s="3" t="s">
         <v>1046</v>
-      </c>
-      <c r="F513" s="3" t="s">
-        <v>1047</v>
       </c>
       <c r="G513" s="7">
         <v>46940.0</v>
@@ -16567,7 +16488,7 @@
     </row>
     <row r="514">
       <c r="A514" s="2" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B514" s="2" t="s">
         <v>38</v>
@@ -16591,7 +16512,7 @@
     </row>
     <row r="515">
       <c r="A515" s="2" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="B515" s="2" t="s">
         <v>593</v>
@@ -16603,7 +16524,7 @@
         <v>16.0</v>
       </c>
       <c r="E515" s="2" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F515" s="3" t="s">
         <v>595</v>
@@ -16615,7 +16536,7 @@
     </row>
     <row r="516">
       <c r="A516" s="2" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B516" s="2" t="s">
         <v>33</v>
@@ -16630,7 +16551,7 @@
         <v>739</v>
       </c>
       <c r="F516" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G516" s="7">
         <v>46964.0</v>
@@ -16639,7 +16560,7 @@
     </row>
     <row r="517">
       <c r="A517" s="2" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B517" s="2" t="s">
         <v>33</v>
@@ -16651,10 +16572,10 @@
         <v>21.0</v>
       </c>
       <c r="E517" s="2" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="F517" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G517" s="7">
         <v>46964.0</v>
@@ -16663,7 +16584,7 @@
     </row>
     <row r="518">
       <c r="A518" s="2" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B518" s="2" t="s">
         <v>38</v>
@@ -16675,7 +16596,7 @@
         <v>7.0</v>
       </c>
       <c r="E518" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F518" s="3" t="s">
         <v>852</v>
@@ -16687,7 +16608,7 @@
     </row>
     <row r="519">
       <c r="A519" s="2" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B519" s="2" t="s">
         <v>593</v>
@@ -16699,10 +16620,10 @@
         <v>3.0</v>
       </c>
       <c r="E519" s="2" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="F519" s="3" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G519" s="7">
         <v>46352.0</v>
@@ -16713,7 +16634,7 @@
     </row>
     <row r="520">
       <c r="A520" s="2" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B520" s="2" t="s">
         <v>38</v>
@@ -16725,7 +16646,7 @@
         <v>1.0</v>
       </c>
       <c r="E520" s="2" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="F520" s="3" t="s">
         <v>210</v>
@@ -16737,7 +16658,7 @@
     </row>
     <row r="521">
       <c r="A521" s="2" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B521" s="2" t="s">
         <v>302</v>
@@ -16749,7 +16670,7 @@
         <v>4.0</v>
       </c>
       <c r="E521" s="2" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F521" s="3" t="s">
         <v>23</v>
@@ -16758,12 +16679,12 @@
         <v>46550.0</v>
       </c>
       <c r="H521" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="2" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B522" s="2" t="s">
         <v>302</v>
@@ -16775,7 +16696,7 @@
         <v>4.0</v>
       </c>
       <c r="E522" s="2" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>23</v>
@@ -16784,12 +16705,12 @@
         <v>46554.0</v>
       </c>
       <c r="H522" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="2" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="B523" s="2" t="s">
         <v>302</v>
@@ -16801,7 +16722,7 @@
         <v>4.0</v>
       </c>
       <c r="E523" s="2" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="F523" s="3" t="s">
         <v>23</v>
@@ -16810,12 +16731,12 @@
         <v>46549.0</v>
       </c>
       <c r="H523" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="2" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B524" s="2" t="s">
         <v>302</v>
@@ -16827,7 +16748,7 @@
         <v>2.0</v>
       </c>
       <c r="E524" s="2" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="F524" s="3" t="s">
         <v>23</v>
@@ -16836,12 +16757,12 @@
         <v>46549.0</v>
       </c>
       <c r="H524" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="2" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="B525" s="2" t="s">
         <v>302</v>
@@ -16853,7 +16774,7 @@
         <v>6.0</v>
       </c>
       <c r="E525" s="2" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="F525" s="3" t="s">
         <v>23</v>
@@ -16862,12 +16783,12 @@
         <v>46549.0</v>
       </c>
       <c r="H525" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="2" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B526" s="2" t="s">
         <v>302</v>
@@ -16879,7 +16800,7 @@
         <v>2.0</v>
       </c>
       <c r="E526" s="2" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="F526" s="3" t="s">
         <v>23</v>
@@ -16888,12 +16809,12 @@
         <v>46494.0</v>
       </c>
       <c r="H526" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="2" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B527" s="2" t="s">
         <v>302</v>
@@ -16905,7 +16826,7 @@
         <v>7.0</v>
       </c>
       <c r="E527" s="2" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="F527" s="3" t="s">
         <v>23</v>
@@ -16919,7 +16840,7 @@
     </row>
     <row r="528">
       <c r="A528" s="2" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B528" s="2" t="s">
         <v>302</v>
@@ -16931,7 +16852,7 @@
         <v>6.0</v>
       </c>
       <c r="E528" s="2" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="F528" s="3" t="s">
         <v>23</v>
@@ -16940,12 +16861,12 @@
         <v>46707.0</v>
       </c>
       <c r="H528" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="2" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B529" s="2" t="s">
         <v>302</v>
@@ -16957,7 +16878,7 @@
         <v>6.0</v>
       </c>
       <c r="E529" s="2" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F529" s="3" t="s">
         <v>23</v>
@@ -16966,12 +16887,12 @@
         <v>46604.0</v>
       </c>
       <c r="H529" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="2" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B530" s="2" t="s">
         <v>302</v>
@@ -16983,7 +16904,7 @@
         <v>5.0</v>
       </c>
       <c r="E530" s="2" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="F530" s="3" t="s">
         <v>23</v>
@@ -16997,7 +16918,7 @@
     </row>
     <row r="531">
       <c r="A531" s="2" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B531" s="2" t="s">
         <v>302</v>
@@ -17009,7 +16930,7 @@
         <v>6.0</v>
       </c>
       <c r="E531" s="2" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="F531" s="3" t="s">
         <v>23</v>
@@ -17018,12 +16939,12 @@
         <v>46659.0</v>
       </c>
       <c r="H531" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="2" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B532" s="2" t="s">
         <v>33</v>
@@ -17035,7 +16956,7 @@
         <v>3.0</v>
       </c>
       <c r="E532" s="2" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F532" s="3">
         <v>11508.0</v>
@@ -17045,7 +16966,7 @@
     </row>
     <row r="533">
       <c r="A533" s="2" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B533" s="2" t="s">
         <v>302</v>
@@ -17057,7 +16978,7 @@
         <v>4.0</v>
       </c>
       <c r="E533" s="2" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F533" s="3" t="s">
         <v>23</v>
@@ -17066,12 +16987,12 @@
         <v>46549.0</v>
       </c>
       <c r="H533" s="2" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="2" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B534" s="2" t="s">
         <v>33</v>
@@ -17083,7 +17004,7 @@
         <v>13.0</v>
       </c>
       <c r="E534" s="2" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="F534" s="3" t="s">
         <v>199</v>
@@ -17095,7 +17016,7 @@
     </row>
     <row r="535">
       <c r="A535" s="2" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B535" s="2" t="s">
         <v>38</v>
@@ -17107,10 +17028,10 @@
         <v>22.0</v>
       </c>
       <c r="E535" s="2" t="s">
+        <v>1088</v>
+      </c>
+      <c r="F535" s="3" t="s">
         <v>1089</v>
-      </c>
-      <c r="F535" s="3" t="s">
-        <v>1090</v>
       </c>
       <c r="G535" s="7">
         <v>46941.0</v>
@@ -17119,7 +17040,7 @@
     </row>
     <row r="536">
       <c r="A536" s="2" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B536" s="2" t="s">
         <v>33</v>
@@ -17134,7 +17055,7 @@
         <v>739</v>
       </c>
       <c r="F536" s="3" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G536" s="7">
         <v>46910.0</v>
@@ -17143,7 +17064,7 @@
     </row>
     <row r="537">
       <c r="A537" s="2" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>33</v>
@@ -17167,7 +17088,7 @@
     </row>
     <row r="538">
       <c r="A538" s="2" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B538" s="2" t="s">
         <v>33</v>
@@ -17182,7 +17103,7 @@
         <v>832</v>
       </c>
       <c r="F538" s="3" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G538" s="7">
         <v>46675.0</v>
@@ -17191,7 +17112,7 @@
     </row>
     <row r="539">
       <c r="A539" s="2" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B539" s="2" t="s">
         <v>33</v>
@@ -17215,7 +17136,7 @@
     </row>
     <row r="540">
       <c r="A540" s="2" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B540" s="2" t="s">
         <v>33</v>
@@ -17230,7 +17151,7 @@
         <v>832</v>
       </c>
       <c r="F540" s="3" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="G540" s="7">
         <v>46612.0</v>
@@ -17239,7 +17160,7 @@
     </row>
     <row r="541">
       <c r="A541" s="2" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B541" s="2" t="s">
         <v>33</v>
@@ -17251,7 +17172,7 @@
         <v>3.0</v>
       </c>
       <c r="E541" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F541" s="3" t="s">
         <v>814</v>
@@ -17263,7 +17184,7 @@
     </row>
     <row r="542">
       <c r="A542" s="2" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B542" s="2" t="s">
         <v>33</v>
@@ -17275,7 +17196,7 @@
         <v>17.0</v>
       </c>
       <c r="E542" s="2" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="F542" s="3" t="s">
         <v>20</v>
@@ -17287,7 +17208,7 @@
     </row>
     <row r="543">
       <c r="A543" s="2" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B543" s="2" t="s">
         <v>38</v>
@@ -17299,17 +17220,17 @@
         <v>7.0</v>
       </c>
       <c r="E543" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F543" s="3" t="s">
         <v>1103</v>
-      </c>
-      <c r="F543" s="3" t="s">
-        <v>1104</v>
       </c>
       <c r="G543" s="7"/>
       <c r="H543" s="2"/>
     </row>
     <row r="544">
       <c r="A544" s="2" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B544" s="2" t="s">
         <v>33</v>
@@ -17321,7 +17242,7 @@
         <v>3.0</v>
       </c>
       <c r="E544" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F544" s="3" t="s">
         <v>332</v>
@@ -17333,7 +17254,7 @@
     </row>
     <row r="545">
       <c r="A545" s="2" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B545" s="2" t="s">
         <v>33</v>
@@ -17345,7 +17266,7 @@
         <v>3.0</v>
       </c>
       <c r="E545" s="2" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="F545" s="3" t="s">
         <v>814</v>
@@ -17357,7 +17278,7 @@
     </row>
     <row r="546">
       <c r="A546" s="2" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B546" s="2" t="s">
         <v>33</v>
@@ -17369,7 +17290,7 @@
         <v>3.0</v>
       </c>
       <c r="E546" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>332</v>
@@ -17381,7 +17302,7 @@
     </row>
     <row r="547">
       <c r="A547" s="2" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B547" s="2" t="s">
         <v>33</v>
@@ -17393,7 +17314,7 @@
         <v>3.0</v>
       </c>
       <c r="E547" s="2" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="F547" s="3" t="s">
         <v>814</v>
@@ -17405,7 +17326,7 @@
     </row>
     <row r="548">
       <c r="A548" s="2" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B548" s="2" t="s">
         <v>302</v>
@@ -17417,17 +17338,17 @@
         <v>16.0</v>
       </c>
       <c r="E548" s="2" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="F548" s="3"/>
       <c r="G548" s="7"/>
       <c r="H548" s="2" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="2" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>302</v>
@@ -17439,21 +17360,21 @@
         <v>8.0</v>
       </c>
       <c r="E549" s="2" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F549" s="3" t="s">
         <v>1114</v>
-      </c>
-      <c r="F549" s="3" t="s">
-        <v>1115</v>
       </c>
       <c r="G549" s="7">
         <v>46376.0</v>
       </c>
       <c r="H549" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="2" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B550" s="2" t="s">
         <v>302</v>
@@ -17465,21 +17386,21 @@
         <v>8.0</v>
       </c>
       <c r="E550" s="2" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="F550" s="3" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="G550" s="7">
         <v>46376.0</v>
       </c>
       <c r="H550" s="2" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="2" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B551" s="2" t="s">
         <v>257</v>
@@ -17503,7 +17424,7 @@
     </row>
     <row r="552">
       <c r="A552" s="2" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B552" s="2" t="s">
         <v>593</v>
@@ -17515,10 +17436,10 @@
         <v>13.0</v>
       </c>
       <c r="E552" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F552" s="3" t="s">
         <v>1121</v>
-      </c>
-      <c r="F552" s="3" t="s">
-        <v>1122</v>
       </c>
       <c r="G552" s="7">
         <v>46338.0</v>
@@ -17529,7 +17450,7 @@
     </row>
     <row r="553">
       <c r="A553" s="2" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B553" s="2" t="s">
         <v>593</v>
@@ -17541,10 +17462,10 @@
         <v>12.0</v>
       </c>
       <c r="E553" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F553" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G553" s="7">
         <v>46348.0</v>
@@ -17555,7 +17476,7 @@
     </row>
     <row r="554">
       <c r="A554" s="2" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B554" s="2" t="s">
         <v>593</v>
@@ -17567,10 +17488,10 @@
         <v>12.0</v>
       </c>
       <c r="E554" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F554" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G554" s="7">
         <v>46347.0</v>
@@ -17581,7 +17502,7 @@
     </row>
     <row r="555">
       <c r="A555" s="2" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B555" s="2" t="s">
         <v>593</v>
@@ -17593,10 +17514,10 @@
         <v>12.0</v>
       </c>
       <c r="E555" s="2" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="F555" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G555" s="7">
         <v>46349.0</v>
@@ -17607,7 +17528,7 @@
     </row>
     <row r="556">
       <c r="A556" s="2" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B556" s="2" t="s">
         <v>593</v>
@@ -17619,10 +17540,10 @@
         <v>15.0</v>
       </c>
       <c r="E556" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F556" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G556" s="7">
         <v>46422.0</v>
@@ -17631,7 +17552,7 @@
     </row>
     <row r="557">
       <c r="A557" s="2" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B557" s="2" t="s">
         <v>593</v>
@@ -17643,10 +17564,10 @@
         <v>8.0</v>
       </c>
       <c r="E557" s="2" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="F557" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G557" s="7">
         <v>46402.0</v>
@@ -17655,7 +17576,7 @@
     </row>
     <row r="558">
       <c r="A558" s="2" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B558" s="2" t="s">
         <v>593</v>
@@ -17667,10 +17588,10 @@
         <v>9.0</v>
       </c>
       <c r="E558" s="2" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="F558" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G558" s="7">
         <v>46405.0</v>
@@ -17679,7 +17600,7 @@
     </row>
     <row r="559">
       <c r="A559" s="2" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B559" s="2" t="s">
         <v>593</v>
@@ -17691,10 +17612,10 @@
         <v>10.0</v>
       </c>
       <c r="E559" s="2" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="F559" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G559" s="7">
         <v>46402.0</v>
@@ -17703,7 +17624,7 @@
     </row>
     <row r="560">
       <c r="A560" s="2" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B560" s="2" t="s">
         <v>38</v>
@@ -17712,13 +17633,13 @@
         <v>30</v>
       </c>
       <c r="D560" s="2">
-        <v>14.0</v>
+        <v>16.0</v>
       </c>
       <c r="E560" s="2" t="s">
         <v>700</v>
       </c>
       <c r="F560" s="3" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G560" s="7">
         <v>46792.0</v>
@@ -17727,7 +17648,7 @@
     </row>
     <row r="561">
       <c r="A561" s="2" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B561" s="2" t="s">
         <v>593</v>
@@ -17739,10 +17660,10 @@
         <v>6.0</v>
       </c>
       <c r="E561" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F561" s="3" t="s">
         <v>1139</v>
-      </c>
-      <c r="F561" s="3" t="s">
-        <v>1140</v>
       </c>
       <c r="G561" s="7">
         <v>46366.0</v>
@@ -17753,7 +17674,7 @@
     </row>
     <row r="562">
       <c r="A562" s="2" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B562" s="2" t="s">
         <v>33</v>
@@ -17765,10 +17686,10 @@
         <v>21.0</v>
       </c>
       <c r="E562" s="2" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="F562" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G562" s="7">
         <v>46974.0</v>
@@ -17777,7 +17698,7 @@
     </row>
     <row r="563">
       <c r="A563" s="2" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B563" s="2" t="s">
         <v>33</v>
@@ -17789,10 +17710,10 @@
         <v>21.0</v>
       </c>
       <c r="E563" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="F563" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G563" s="7">
         <v>46974.0</v>
@@ -17801,7 +17722,7 @@
     </row>
     <row r="564">
       <c r="A564" s="2" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B564" s="2" t="s">
         <v>33</v>
@@ -17813,10 +17734,10 @@
         <v>21.0</v>
       </c>
       <c r="E564" s="2" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F564" s="3" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G564" s="7">
         <v>46974.0</v>
@@ -17825,7 +17746,7 @@
     </row>
     <row r="565">
       <c r="A565" s="2" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="B565" s="2" t="s">
         <v>593</v>
@@ -17837,10 +17758,10 @@
         <v>7.0</v>
       </c>
       <c r="E565" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F565" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="G565" s="7">
         <v>46366.0</v>
@@ -17851,7 +17772,7 @@
     </row>
     <row r="566">
       <c r="A566" s="2" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="B566" s="2" t="s">
         <v>38</v>
@@ -17863,7 +17784,7 @@
         <v>1.0</v>
       </c>
       <c r="E566" s="2" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="F566" s="3" t="s">
         <v>23</v>
@@ -17875,7 +17796,7 @@
     </row>
     <row r="567">
       <c r="A567" s="2" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B567" s="2" t="s">
         <v>38</v>
@@ -17897,7 +17818,7 @@
     </row>
     <row r="568">
       <c r="A568" s="2" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B568" s="2" t="s">
         <v>257</v>
@@ -17921,7 +17842,7 @@
     </row>
     <row r="569">
       <c r="A569" s="2" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="B569" s="2" t="s">
         <v>593</v>
@@ -17933,10 +17854,10 @@
         <v>13.0</v>
       </c>
       <c r="E569" s="2" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
       <c r="F569" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G569" s="7">
         <v>46348.0</v>
@@ -17947,7 +17868,7 @@
     </row>
     <row r="570">
       <c r="A570" s="2" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="B570" s="2" t="s">
         <v>38</v>
@@ -17959,10 +17880,10 @@
         <v>1.0</v>
       </c>
       <c r="E570" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F570" s="3" t="s">
         <v>1155</v>
-      </c>
-      <c r="F570" s="3" t="s">
-        <v>1156</v>
       </c>
       <c r="G570" s="7">
         <v>46830.0</v>
@@ -17971,7 +17892,7 @@
     </row>
     <row r="571">
       <c r="A571" s="2" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="B571" s="2" t="s">
         <v>33</v>
@@ -17983,7 +17904,7 @@
         <v>14.0</v>
       </c>
       <c r="E571" s="2" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="F571" s="3" t="s">
         <v>23</v>
@@ -17995,7 +17916,7 @@
     </row>
     <row r="572">
       <c r="A572" s="2" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="B572" s="2" t="s">
         <v>38</v>
@@ -18007,7 +17928,7 @@
         <v>22.0</v>
       </c>
       <c r="E572" s="2" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="F572" s="3" t="s">
         <v>210</v>
@@ -18019,7 +17940,7 @@
     </row>
     <row r="573">
       <c r="A573" s="2" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="B573" s="2" t="s">
         <v>257</v>
@@ -18043,7 +17964,7 @@
     </row>
     <row r="574">
       <c r="A574" s="2" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B574" s="2" t="s">
         <v>257</v>
@@ -18067,7 +17988,7 @@
     </row>
     <row r="575">
       <c r="A575" s="2" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="B575" s="2" t="s">
         <v>257</v>
@@ -18091,7 +18012,7 @@
     </row>
     <row r="576">
       <c r="A576" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B576" s="2" t="s">
         <v>38</v>
@@ -18103,7 +18024,7 @@
         <v>7.0</v>
       </c>
       <c r="E576" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F576" s="3" t="s">
         <v>852</v>
@@ -18115,7 +18036,7 @@
     </row>
     <row r="577">
       <c r="A577" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B577" s="2" t="s">
         <v>38</v>
@@ -18127,7 +18048,7 @@
         <v>7.0</v>
       </c>
       <c r="E577" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="F577" s="3" t="s">
         <v>852</v>
@@ -18139,7 +18060,7 @@
     </row>
     <row r="578">
       <c r="A578" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B578" s="2" t="s">
         <v>38</v>
@@ -18151,7 +18072,7 @@
         <v>7.0</v>
       </c>
       <c r="E578" s="2" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="F578" s="3" t="s">
         <v>852</v>
@@ -18163,7 +18084,7 @@
     </row>
     <row r="579">
       <c r="A579" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="B579" s="2" t="s">
         <v>38</v>
@@ -18175,7 +18096,7 @@
         <v>5.0</v>
       </c>
       <c r="E579" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="F579" s="3" t="s">
         <v>210</v>
@@ -18185,7 +18106,7 @@
     </row>
     <row r="580">
       <c r="A580" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="B580" s="2" t="s">
         <v>33</v>
@@ -18197,10 +18118,10 @@
         <v>15.0</v>
       </c>
       <c r="E580" s="2" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="F580" s="3" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="G580" s="7">
         <v>46725.0</v>
@@ -18209,7 +18130,7 @@
     </row>
     <row r="581">
       <c r="A581" s="2" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B581" s="2" t="s">
         <v>33</v>
@@ -18221,7 +18142,7 @@
         <v>14.0</v>
       </c>
       <c r="E581" s="2" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="F581" s="3"/>
       <c r="G581" s="7"/>
@@ -18229,7 +18150,7 @@
     </row>
     <row r="582">
       <c r="A582" s="2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="B582" s="2" t="s">
         <v>33</v>
@@ -18241,7 +18162,7 @@
         <v>6.0</v>
       </c>
       <c r="E582" s="2" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="F582" s="3"/>
       <c r="G582" s="7"/>
@@ -18249,7 +18170,7 @@
     </row>
     <row r="583">
       <c r="A583" s="2" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="B583" s="2" t="s">
         <v>33</v>
@@ -18273,7 +18194,7 @@
     </row>
     <row r="584">
       <c r="A584" s="2" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="B584" s="2" t="s">
         <v>33</v>
@@ -18297,7 +18218,7 @@
     </row>
     <row r="585">
       <c r="A585" s="2" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B585" s="2" t="s">
         <v>33</v>
@@ -18319,7 +18240,7 @@
     </row>
     <row r="586">
       <c r="A586" s="2" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="B586" s="2" t="s">
         <v>593</v>
@@ -18331,10 +18252,10 @@
         <v>13.0</v>
       </c>
       <c r="E586" s="2" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="F586" s="3" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="G586" s="7">
         <v>46349.0</v>
@@ -18345,7 +18266,7 @@
     </row>
     <row r="587">
       <c r="A587" s="2" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B587" s="2" t="s">
         <v>38</v>
@@ -18367,7 +18288,7 @@
     </row>
     <row r="588">
       <c r="A588" s="2" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="B588" s="2" t="s">
         <v>593</v>
@@ -18379,10 +18300,10 @@
         <v>11.0</v>
       </c>
       <c r="E588" s="2" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="F588" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G588" s="7">
         <v>46349.0</v>
@@ -18393,7 +18314,7 @@
     </row>
     <row r="589">
       <c r="A589" s="2" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="B589" s="2" t="s">
         <v>302</v>
@@ -18405,10 +18326,10 @@
         <v>11.0</v>
       </c>
       <c r="E589" s="2" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F589" s="3" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="G589" s="7">
         <v>46356.0</v>
@@ -18419,7 +18340,7 @@
     </row>
     <row r="590">
       <c r="A590" s="2" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B590" s="2" t="s">
         <v>33</v>
@@ -18431,7 +18352,7 @@
         <v>21.0</v>
       </c>
       <c r="E590" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F590" s="3" t="s">
         <v>769</v>
@@ -18441,7 +18362,7 @@
     </row>
     <row r="591">
       <c r="A591" s="2" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="B591" s="2" t="s">
         <v>33</v>
@@ -18453,10 +18374,10 @@
         <v>20.0</v>
       </c>
       <c r="E591" s="2" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="F591" s="3" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="G591" s="7">
         <v>46554.0</v>
@@ -18465,7 +18386,7 @@
     </row>
     <row r="592">
       <c r="A592" s="2" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="B592" s="2" t="s">
         <v>302</v>
@@ -18477,7 +18398,7 @@
         <v>14.0</v>
       </c>
       <c r="E592" s="2" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="F592" s="3" t="s">
         <v>210</v>
@@ -18489,7 +18410,7 @@
     </row>
     <row r="593">
       <c r="A593" s="2" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B593" s="2" t="s">
         <v>302</v>
@@ -18501,7 +18422,7 @@
         <v>14.0</v>
       </c>
       <c r="E593" s="2" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="F593" s="3" t="s">
         <v>210</v>
@@ -18513,7 +18434,7 @@
     </row>
     <row r="594">
       <c r="A594" s="2" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B594" s="2" t="s">
         <v>302</v>
@@ -18525,7 +18446,7 @@
         <v>14.0</v>
       </c>
       <c r="E594" s="2" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F594" s="3" t="s">
         <v>210</v>
@@ -18537,7 +18458,7 @@
     </row>
     <row r="595">
       <c r="A595" s="2" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="B595" s="2" t="s">
         <v>302</v>
@@ -18549,7 +18470,7 @@
         <v>14.0</v>
       </c>
       <c r="E595" s="2" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="F595" s="3" t="s">
         <v>210</v>
@@ -18561,7 +18482,7 @@
     </row>
     <row r="596">
       <c r="A596" s="2" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="B596" s="2" t="s">
         <v>302</v>
@@ -18573,7 +18494,7 @@
         <v>14.0</v>
       </c>
       <c r="E596" s="2" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="F596" s="3" t="s">
         <v>210</v>
@@ -18585,7 +18506,7 @@
     </row>
     <row r="597">
       <c r="A597" s="2" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B597" s="2" t="s">
         <v>302</v>
@@ -18597,7 +18518,7 @@
         <v>14.0</v>
       </c>
       <c r="E597" s="2" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="F597" s="3" t="s">
         <v>210</v>
@@ -18609,7 +18530,7 @@
     </row>
     <row r="598">
       <c r="A598" s="2" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B598" s="2" t="s">
         <v>302</v>
@@ -18621,7 +18542,7 @@
         <v>15.0</v>
       </c>
       <c r="E598" s="2" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
       <c r="F598" s="3" t="s">
         <v>210</v>
@@ -18633,7 +18554,7 @@
     </row>
     <row r="599">
       <c r="A599" s="2" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B599" s="2" t="s">
         <v>302</v>
@@ -18645,7 +18566,7 @@
         <v>15.0</v>
       </c>
       <c r="E599" s="2" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F599" s="3" t="s">
         <v>210</v>
@@ -18657,7 +18578,7 @@
     </row>
     <row r="600">
       <c r="A600" s="2" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B600" s="2" t="s">
         <v>302</v>
@@ -18669,7 +18590,7 @@
         <v>15.0</v>
       </c>
       <c r="E600" s="2" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="F600" s="3" t="s">
         <v>210</v>
@@ -18681,7 +18602,7 @@
     </row>
     <row r="601">
       <c r="A601" s="2" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="B601" s="2" t="s">
         <v>302</v>
@@ -18693,7 +18614,7 @@
         <v>14.0</v>
       </c>
       <c r="E601" s="2" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="F601" s="3" t="s">
         <v>210</v>
@@ -18705,7 +18626,7 @@
     </row>
     <row r="602">
       <c r="A602" s="2" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B602" s="2" t="s">
         <v>33</v>
@@ -18717,10 +18638,10 @@
         <v>7.0</v>
       </c>
       <c r="E602" s="2" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="F602" s="3" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
       <c r="G602" s="7">
         <v>46586.0</v>
@@ -18729,7 +18650,7 @@
     </row>
     <row r="603">
       <c r="A603" s="2" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
       <c r="B603" s="2" t="s">
         <v>38</v>
@@ -18741,10 +18662,10 @@
         <v>1.0</v>
       </c>
       <c r="E603" s="2" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F603" s="3" t="s">
         <v>1212</v>
-      </c>
-      <c r="F603" s="3" t="s">
-        <v>1213</v>
       </c>
       <c r="G603" s="7">
         <v>46836.0</v>
@@ -18753,7 +18674,7 @@
     </row>
     <row r="604">
       <c r="A604" s="2" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
       <c r="B604" s="2" t="s">
         <v>38</v>
@@ -18765,7 +18686,7 @@
         <v>21.0</v>
       </c>
       <c r="E604" s="2" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="F604" s="3" t="s">
         <v>210</v>
@@ -18777,7 +18698,7 @@
     </row>
     <row r="605">
       <c r="A605" s="2" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B605" s="2" t="s">
         <v>33</v>
@@ -18789,7 +18710,7 @@
         <v>21.0</v>
       </c>
       <c r="E605" s="2" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="F605" s="3" t="s">
         <v>199</v>
@@ -18801,7 +18722,7 @@
     </row>
     <row r="606">
       <c r="A606" s="2" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="B606" s="2" t="s">
         <v>33</v>
@@ -18813,7 +18734,7 @@
         <v>21.0</v>
       </c>
       <c r="E606" s="2" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="F606" s="3" t="s">
         <v>20</v>
@@ -18825,10 +18746,10 @@
     </row>
     <row r="607">
       <c r="A607" s="2" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B607" s="2" t="s">
         <v>1220</v>
-      </c>
-      <c r="B607" s="2" t="s">
-        <v>1221</v>
       </c>
       <c r="C607" s="2" t="s">
         <v>12</v>
@@ -18837,7 +18758,7 @@
         <v>6.0</v>
       </c>
       <c r="E607" s="2" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="F607" s="3"/>
       <c r="G607" s="7"/>
@@ -18845,10 +18766,10 @@
     </row>
     <row r="608">
       <c r="A608" s="2" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
       <c r="B608" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C608" s="2" t="s">
         <v>12</v>
@@ -18857,7 +18778,7 @@
         <v>6.0</v>
       </c>
       <c r="E608" s="2" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
       <c r="F608" s="3"/>
       <c r="G608" s="7"/>
@@ -18865,10 +18786,10 @@
     </row>
     <row r="609">
       <c r="A609" s="2" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="B609" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C609" s="2" t="s">
         <v>12</v>
@@ -18877,7 +18798,7 @@
         <v>6.0</v>
       </c>
       <c r="E609" s="2" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F609" s="3"/>
       <c r="G609" s="7"/>
@@ -18885,10 +18806,10 @@
     </row>
     <row r="610">
       <c r="A610" s="2" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="B610" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C610" s="2" t="s">
         <v>12</v>
@@ -18897,7 +18818,7 @@
         <v>6.0</v>
       </c>
       <c r="E610" s="2" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="F610" s="3"/>
       <c r="G610" s="7"/>
@@ -18905,10 +18826,10 @@
     </row>
     <row r="611">
       <c r="A611" s="2" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B611" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C611" s="2" t="s">
         <v>12</v>
@@ -18917,7 +18838,7 @@
         <v>6.0</v>
       </c>
       <c r="E611" s="2" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="F611" s="3"/>
       <c r="G611" s="7"/>
@@ -18925,10 +18846,10 @@
     </row>
     <row r="612">
       <c r="A612" s="2" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B612" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C612" s="2" t="s">
         <v>12</v>
@@ -18937,7 +18858,7 @@
         <v>6.0</v>
       </c>
       <c r="E612" s="2" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="F612" s="3"/>
       <c r="G612" s="7"/>
@@ -18945,10 +18866,10 @@
     </row>
     <row r="613">
       <c r="A613" s="2" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B613" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C613" s="2" t="s">
         <v>12</v>
@@ -18957,7 +18878,7 @@
         <v>6.0</v>
       </c>
       <c r="E613" s="2" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="F613" s="3"/>
       <c r="G613" s="7"/>
@@ -18965,23 +18886,29 @@
     </row>
     <row r="614">
       <c r="A614" s="2" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B614" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C614" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D614" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="E614" s="2" t="s">
         <v>1233</v>
       </c>
-      <c r="B614" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C614" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D614" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E614" s="2" t="s">
+      <c r="F614" s="3" t="s">
         <v>1234</v>
       </c>
-      <c r="F614" s="3"/>
-      <c r="G614" s="7"/>
-      <c r="H614" s="2"/>
+      <c r="G614" s="7">
+        <v>46963.0</v>
+      </c>
+      <c r="H614" s="2" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="615">
       <c r="A615" s="2" t="s">
@@ -19000,18 +18927,16 @@
         <v>1236</v>
       </c>
       <c r="F615" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G615" s="7">
         <v>46963.0</v>
       </c>
-      <c r="H615" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="H615" s="2"/>
     </row>
     <row r="616">
       <c r="A616" s="2" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B616" s="2" t="s">
         <v>38</v>
@@ -19023,19 +18948,19 @@
         <v>17.0</v>
       </c>
       <c r="E616" s="2" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="F616" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G616" s="7">
-        <v>46963.0</v>
+        <v>46995.0</v>
       </c>
       <c r="H616" s="2"/>
     </row>
     <row r="617">
       <c r="A617" s="2" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B617" s="2" t="s">
         <v>38</v>
@@ -19047,19 +18972,19 @@
         <v>17.0</v>
       </c>
       <c r="E617" s="2" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="F617" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G617" s="7">
-        <v>46995.0</v>
+        <v>46963.0</v>
       </c>
       <c r="H617" s="2"/>
     </row>
     <row r="618">
       <c r="A618" s="2" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B618" s="2" t="s">
         <v>38</v>
@@ -19071,19 +18996,19 @@
         <v>17.0</v>
       </c>
       <c r="E618" s="2" t="s">
-        <v>1243</v>
+        <v>1000</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G618" s="7">
-        <v>46963.0</v>
+        <v>46477.0</v>
       </c>
       <c r="H618" s="2"/>
     </row>
     <row r="619">
       <c r="A619" s="2" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B619" s="2" t="s">
         <v>38</v>
@@ -19095,19 +19020,19 @@
         <v>17.0</v>
       </c>
       <c r="E619" s="2" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F619" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G619" s="7">
-        <v>46477.0</v>
+        <v>46488.0</v>
       </c>
       <c r="H619" s="2"/>
     </row>
     <row r="620">
       <c r="A620" s="2" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B620" s="2" t="s">
         <v>38</v>
@@ -19119,10 +19044,10 @@
         <v>17.0</v>
       </c>
       <c r="E620" s="2" t="s">
-        <v>1001</v>
+        <v>937</v>
       </c>
       <c r="F620" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G620" s="7">
         <v>46488.0</v>
@@ -19131,7 +19056,7 @@
     </row>
     <row r="621">
       <c r="A621" s="2" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B621" s="2" t="s">
         <v>38</v>
@@ -19140,22 +19065,22 @@
         <v>30</v>
       </c>
       <c r="D621" s="2">
-        <v>17.0</v>
+        <v>19.0</v>
       </c>
       <c r="E621" s="2" t="s">
-        <v>938</v>
+        <v>278</v>
       </c>
       <c r="F621" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G621" s="7">
-        <v>46488.0</v>
+        <v>46794.0</v>
       </c>
       <c r="H621" s="2"/>
     </row>
     <row r="622">
       <c r="A622" s="2" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B622" s="2" t="s">
         <v>38</v>
@@ -19164,37 +19089,37 @@
         <v>30</v>
       </c>
       <c r="D622" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E622" s="2" t="s">
-        <v>278</v>
+        <v>856</v>
       </c>
       <c r="F622" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G622" s="7">
-        <v>46794.0</v>
+        <v>46940.0</v>
       </c>
       <c r="H622" s="2"/>
     </row>
     <row r="623">
       <c r="A623" s="2" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B623" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C623" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D623" s="2">
-        <v>18.0</v>
+        <v>12.0</v>
       </c>
       <c r="E623" s="2" t="s">
-        <v>856</v>
+        <v>1247</v>
       </c>
       <c r="F623" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G623" s="7">
         <v>46940.0</v>
@@ -19203,7 +19128,7 @@
     </row>
     <row r="624">
       <c r="A624" s="2" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B624" s="2" t="s">
         <v>38</v>
@@ -19212,22 +19137,22 @@
         <v>12</v>
       </c>
       <c r="D624" s="2">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E624" s="2" t="s">
-        <v>1250</v>
+        <v>759</v>
       </c>
       <c r="F624" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G624" s="7">
-        <v>46940.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H624" s="2"/>
     </row>
     <row r="625">
       <c r="A625" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B625" s="2" t="s">
         <v>38</v>
@@ -19236,13 +19161,13 @@
         <v>12</v>
       </c>
       <c r="D625" s="2">
-        <v>15.0</v>
+        <v>12.0</v>
       </c>
       <c r="E625" s="2" t="s">
-        <v>759</v>
+        <v>1250</v>
       </c>
       <c r="F625" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G625" s="7">
         <v>46530.0</v>
@@ -19251,7 +19176,7 @@
     </row>
     <row r="626">
       <c r="A626" s="2" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B626" s="2" t="s">
         <v>38</v>
@@ -19260,40 +19185,40 @@
         <v>12</v>
       </c>
       <c r="D626" s="2">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="E626" s="2" t="s">
-        <v>1253</v>
+        <v>959</v>
       </c>
       <c r="F626" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G626" s="7">
-        <v>46530.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H626" s="2"/>
     </row>
     <row r="627">
       <c r="A627" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B627" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C627" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D627" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="E627" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F627" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="B627" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C627" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D627" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E627" s="2" t="s">
-        <v>960</v>
-      </c>
-      <c r="F627" s="3" t="s">
-        <v>1237</v>
-      </c>
       <c r="G627" s="7">
-        <v>46792.0</v>
+        <v>46794.0</v>
       </c>
       <c r="H627" s="2"/>
     </row>
@@ -19311,70 +19236,70 @@
         <v>19.0</v>
       </c>
       <c r="E628" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F628" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="F628" s="3" t="s">
-        <v>1257</v>
-      </c>
       <c r="G628" s="7">
-        <v>46794.0</v>
+        <v>46793.0</v>
       </c>
       <c r="H628" s="2"/>
     </row>
     <row r="629">
       <c r="A629" s="2" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B629" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C629" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D629" s="2">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="E629" s="2" t="s">
-        <v>1256</v>
+        <v>956</v>
       </c>
       <c r="F629" s="3" t="s">
-        <v>1259</v>
+        <v>1234</v>
       </c>
       <c r="G629" s="7">
-        <v>46793.0</v>
+        <v>46509.0</v>
       </c>
       <c r="H629" s="2"/>
     </row>
     <row r="630">
       <c r="A630" s="2" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>38</v>
+        <v>1220</v>
       </c>
       <c r="C630" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D630" s="2">
-        <v>18.0</v>
+        <v>1.0</v>
       </c>
       <c r="E630" s="2" t="s">
-        <v>957</v>
+        <v>1011</v>
       </c>
       <c r="F630" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G630" s="7">
-        <v>46509.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H630" s="2"/>
     </row>
     <row r="631">
       <c r="A631" s="2" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="B631" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C631" s="2" t="s">
         <v>12</v>
@@ -19383,113 +19308,113 @@
         <v>1.0</v>
       </c>
       <c r="E631" s="2" t="s">
-        <v>1012</v>
+        <v>1260</v>
       </c>
       <c r="F631" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G631" s="7">
-        <v>46530.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H631" s="2"/>
     </row>
     <row r="632">
       <c r="A632" s="2" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B632" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C632" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D632" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E632" s="2" t="s">
         <v>1262</v>
       </c>
-      <c r="B632" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C632" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D632" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E632" s="2" t="s">
-        <v>1263</v>
-      </c>
       <c r="F632" s="3" t="s">
-        <v>1237</v>
+        <v>1234</v>
       </c>
       <c r="G632" s="7">
-        <v>46792.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H632" s="2"/>
     </row>
     <row r="633">
       <c r="A633" s="2" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B633" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D633" s="2">
-        <v>13.0</v>
+        <v>20.0</v>
       </c>
       <c r="E633" s="2" t="s">
-        <v>1265</v>
+        <v>46</v>
       </c>
       <c r="F633" s="3" t="s">
-        <v>1237</v>
+        <v>210</v>
       </c>
       <c r="G633" s="7">
-        <v>46530.0</v>
+        <v>46758.0</v>
       </c>
       <c r="H633" s="2"/>
     </row>
     <row r="634">
       <c r="A634" s="2" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="B634" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C634" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D634" s="2">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
       <c r="E634" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F634" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G634" s="7">
-        <v>46758.0</v>
-      </c>
+        <v>849</v>
+      </c>
+      <c r="F634" s="3">
+        <v>11508.0</v>
+      </c>
+      <c r="G634" s="7"/>
       <c r="H634" s="2"/>
     </row>
     <row r="635">
       <c r="A635" s="2" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="B635" s="2" t="s">
-        <v>38</v>
+        <v>593</v>
       </c>
       <c r="C635" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D635" s="2">
-        <v>3.0</v>
+        <v>17.0</v>
       </c>
       <c r="E635" s="2" t="s">
-        <v>849</v>
-      </c>
-      <c r="F635" s="3">
-        <v>11508.0</v>
-      </c>
-      <c r="G635" s="7"/>
+        <v>1029</v>
+      </c>
+      <c r="F635" s="3" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G635" s="7">
+        <v>46420.0</v>
+      </c>
       <c r="H635" s="2"/>
     </row>
     <row r="636">
       <c r="A636" s="2" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="B636" s="2" t="s">
         <v>593</v>
@@ -19498,13 +19423,13 @@
         <v>30</v>
       </c>
       <c r="D636" s="2">
-        <v>17.0</v>
+        <v>16.0</v>
       </c>
       <c r="E636" s="2" t="s">
-        <v>1030</v>
+        <v>1133</v>
       </c>
       <c r="F636" s="3" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="G636" s="7">
         <v>46420.0</v>
@@ -19513,55 +19438,55 @@
     </row>
     <row r="637">
       <c r="A637" s="2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B637" s="2" t="s">
         <v>593</v>
       </c>
       <c r="C637" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D637" s="2">
-        <v>16.0</v>
+        <v>15.0</v>
       </c>
       <c r="E637" s="2" t="s">
-        <v>1134</v>
+        <v>1049</v>
       </c>
       <c r="F637" s="3" t="s">
-        <v>1130</v>
+        <v>1268</v>
       </c>
       <c r="G637" s="7">
-        <v>46420.0</v>
+        <v>46422.0</v>
       </c>
       <c r="H637" s="2"/>
     </row>
     <row r="638">
       <c r="A638" s="2" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B638" s="2" t="s">
-        <v>593</v>
+        <v>38</v>
       </c>
       <c r="C638" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D638" s="2">
-        <v>15.0</v>
+        <v>2.0</v>
       </c>
       <c r="E638" s="2" t="s">
-        <v>1050</v>
+        <v>1154</v>
       </c>
       <c r="F638" s="3" t="s">
-        <v>1271</v>
+        <v>1155</v>
       </c>
       <c r="G638" s="7">
-        <v>46422.0</v>
+        <v>46830.0</v>
       </c>
       <c r="H638" s="2"/>
     </row>
     <row r="639">
       <c r="A639" s="2" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="B639" s="2" t="s">
         <v>38</v>
@@ -19570,22 +19495,22 @@
         <v>30</v>
       </c>
       <c r="D639" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E639" s="2" t="s">
-        <v>1155</v>
-      </c>
-      <c r="F639" s="3" t="s">
-        <v>1156</v>
+        <v>591</v>
+      </c>
+      <c r="F639" s="3">
+        <v>11509.0</v>
       </c>
       <c r="G639" s="7">
-        <v>46830.0</v>
+        <v>47004.0</v>
       </c>
       <c r="H639" s="2"/>
     </row>
     <row r="640">
       <c r="A640" s="2" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B640" s="2" t="s">
         <v>38</v>
@@ -19594,70 +19519,70 @@
         <v>30</v>
       </c>
       <c r="D640" s="2">
-        <v>7.0</v>
+        <v>21.0</v>
       </c>
       <c r="E640" s="2" t="s">
-        <v>591</v>
+        <v>1272</v>
       </c>
       <c r="F640" s="3">
-        <v>11509.0</v>
+        <v>11508.0</v>
       </c>
       <c r="G640" s="7">
-        <v>47004.0</v>
+        <v>46777.0</v>
       </c>
       <c r="H640" s="2"/>
     </row>
     <row r="641">
       <c r="A641" s="2" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B641" s="2" t="s">
-        <v>38</v>
+        <v>302</v>
       </c>
       <c r="C641" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D641" s="2">
-        <v>21.0</v>
+        <v>2.0</v>
       </c>
       <c r="E641" s="2" t="s">
-        <v>1275</v>
-      </c>
-      <c r="F641" s="3">
-        <v>11508.0</v>
+        <v>1154</v>
+      </c>
+      <c r="F641" s="3" t="s">
+        <v>1155</v>
       </c>
       <c r="G641" s="7">
-        <v>46777.0</v>
+        <v>46830.0</v>
       </c>
       <c r="H641" s="2"/>
     </row>
     <row r="642">
       <c r="A642" s="2" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>302</v>
+        <v>593</v>
       </c>
       <c r="C642" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D642" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E642" s="2" t="s">
-        <v>1155</v>
+        <v>1275</v>
       </c>
       <c r="F642" s="3" t="s">
-        <v>1156</v>
+        <v>1131</v>
       </c>
       <c r="G642" s="7">
-        <v>46830.0</v>
+        <v>46384.0</v>
       </c>
       <c r="H642" s="2"/>
     </row>
     <row r="643">
       <c r="A643" s="2" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
       <c r="B643" s="2" t="s">
         <v>593</v>
@@ -19669,19 +19594,19 @@
         <v>5.0</v>
       </c>
       <c r="E643" s="2" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
       <c r="F643" s="3" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="G643" s="7">
-        <v>46384.0</v>
+        <v>46381.0</v>
       </c>
       <c r="H643" s="2"/>
     </row>
     <row r="644">
       <c r="A644" s="2" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="B644" s="2" t="s">
         <v>593</v>
@@ -19693,19 +19618,19 @@
         <v>5.0</v>
       </c>
       <c r="E644" s="2" t="s">
-        <v>1280</v>
+        <v>531</v>
       </c>
       <c r="F644" s="3" t="s">
-        <v>1132</v>
+        <v>210</v>
       </c>
       <c r="G644" s="7">
-        <v>46381.0</v>
+        <v>46578.0</v>
       </c>
       <c r="H644" s="2"/>
     </row>
     <row r="645">
       <c r="A645" s="2" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="B645" s="2" t="s">
         <v>593</v>
@@ -19717,19 +19642,19 @@
         <v>5.0</v>
       </c>
       <c r="E645" s="2" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F645" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G645" s="7">
-        <v>46578.0</v>
+        <v>46583.0</v>
       </c>
       <c r="H645" s="2"/>
     </row>
     <row r="646">
       <c r="A646" s="2" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="B646" s="2" t="s">
         <v>593</v>
@@ -19741,19 +19666,19 @@
         <v>5.0</v>
       </c>
       <c r="E646" s="2" t="s">
-        <v>525</v>
+        <v>463</v>
       </c>
       <c r="F646" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G646" s="7">
-        <v>46583.0</v>
+        <v>46564.0</v>
       </c>
       <c r="H646" s="2"/>
     </row>
     <row r="647">
       <c r="A647" s="2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="B647" s="2" t="s">
         <v>593</v>
@@ -19765,19 +19690,19 @@
         <v>5.0</v>
       </c>
       <c r="E647" s="2" t="s">
-        <v>463</v>
+        <v>527</v>
       </c>
       <c r="F647" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G647" s="7">
-        <v>46564.0</v>
+        <v>46521.0</v>
       </c>
       <c r="H647" s="2"/>
     </row>
     <row r="648">
       <c r="A648" s="2" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="B648" s="2" t="s">
         <v>593</v>
@@ -19789,19 +19714,19 @@
         <v>5.0</v>
       </c>
       <c r="E648" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="F648" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G648" s="7">
-        <v>46521.0</v>
+        <v>46572.0</v>
       </c>
       <c r="H648" s="2"/>
     </row>
     <row r="649">
       <c r="A649" s="2" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="B649" s="2" t="s">
         <v>593</v>
@@ -19813,19 +19738,19 @@
         <v>5.0</v>
       </c>
       <c r="E649" s="2" t="s">
-        <v>529</v>
+        <v>1034</v>
       </c>
       <c r="F649" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G649" s="7">
-        <v>46572.0</v>
+        <v>46333.0</v>
       </c>
       <c r="H649" s="2"/>
     </row>
     <row r="650">
       <c r="A650" s="2" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="B650" s="2" t="s">
         <v>593</v>
@@ -19834,72 +19759,72 @@
         <v>12</v>
       </c>
       <c r="D650" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E650" s="2" t="s">
-        <v>1035</v>
+        <v>791</v>
       </c>
       <c r="F650" s="3" t="s">
-        <v>210</v>
+        <v>1285</v>
       </c>
       <c r="G650" s="7">
-        <v>46333.0</v>
-      </c>
-      <c r="H650" s="2"/>
+        <v>46352.0</v>
+      </c>
+      <c r="H650" s="2" t="s">
+        <v>541</v>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="2" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B651" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C651" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D651" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E651" s="2" t="s">
         <v>1287</v>
       </c>
-      <c r="B651" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="C651" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D651" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E651" s="2" t="s">
-        <v>791</v>
-      </c>
       <c r="F651" s="3" t="s">
-        <v>1288</v>
+        <v>210</v>
       </c>
       <c r="G651" s="7">
-        <v>46352.0</v>
-      </c>
-      <c r="H651" s="2" t="s">
-        <v>541</v>
-      </c>
+        <v>47231.0</v>
+      </c>
+      <c r="H651" s="2"/>
     </row>
     <row r="652">
       <c r="A652" s="2" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B652" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C652" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D652" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="E652" s="2" t="s">
         <v>1289</v>
       </c>
-      <c r="B652" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C652" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D652" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E652" s="2" t="s">
-        <v>1290</v>
-      </c>
       <c r="F652" s="3" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="G652" s="7">
-        <v>47231.0</v>
+        <v>47173.0</v>
       </c>
       <c r="H652" s="2"/>
     </row>
     <row r="653">
       <c r="A653" s="2" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B653" s="2" t="s">
         <v>11</v>
@@ -19911,7 +19836,7 @@
         <v>2.0</v>
       </c>
       <c r="E653" s="2" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="F653" s="3" t="s">
         <v>23</v>
@@ -19923,7 +19848,7 @@
     </row>
     <row r="654">
       <c r="A654" s="2" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="B654" s="2" t="s">
         <v>11</v>
@@ -19935,19 +19860,19 @@
         <v>2.0</v>
       </c>
       <c r="E654" s="2" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
       <c r="F654" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G654" s="7">
-        <v>47173.0</v>
+        <v>47533.0</v>
       </c>
       <c r="H654" s="2"/>
     </row>
     <row r="655">
       <c r="A655" s="2" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="B655" s="2" t="s">
         <v>11</v>
@@ -19959,7 +19884,7 @@
         <v>2.0</v>
       </c>
       <c r="E655" s="2" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="F655" s="3" t="s">
         <v>23</v>
@@ -19971,7 +19896,7 @@
     </row>
     <row r="656">
       <c r="A656" s="2" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="B656" s="2" t="s">
         <v>11</v>
@@ -19983,19 +19908,19 @@
         <v>2.0</v>
       </c>
       <c r="E656" s="2" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="F656" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G656" s="7">
-        <v>47533.0</v>
+        <v>47512.0</v>
       </c>
       <c r="H656" s="2"/>
     </row>
     <row r="657">
       <c r="A657" s="2" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="B657" s="2" t="s">
         <v>11</v>
@@ -20004,22 +19929,22 @@
         <v>12</v>
       </c>
       <c r="D657" s="2">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E657" s="2" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="F657" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G657" s="7">
-        <v>47512.0</v>
+        <v>46843.0</v>
       </c>
       <c r="H657" s="2"/>
     </row>
     <row r="658">
       <c r="A658" s="2" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B658" s="2" t="s">
         <v>11</v>
@@ -20028,22 +19953,22 @@
         <v>12</v>
       </c>
       <c r="D658" s="2">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="E658" s="2" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="F658" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G658" s="7">
-        <v>46843.0</v>
+        <v>46796.0</v>
       </c>
       <c r="H658" s="2"/>
     </row>
     <row r="659">
       <c r="A659" s="2" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
       <c r="B659" s="2" t="s">
         <v>11</v>
@@ -20055,19 +19980,19 @@
         <v>5.0</v>
       </c>
       <c r="E659" s="2" t="s">
-        <v>1304</v>
+        <v>983</v>
       </c>
       <c r="F659" s="3" t="s">
-        <v>20</v>
+        <v>289</v>
       </c>
       <c r="G659" s="7">
-        <v>46796.0</v>
+        <v>47286.0</v>
       </c>
       <c r="H659" s="2"/>
     </row>
     <row r="660">
       <c r="A660" s="2" t="s">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="B660" s="2" t="s">
         <v>11</v>
@@ -20079,43 +20004,43 @@
         <v>5.0</v>
       </c>
       <c r="E660" s="2" t="s">
-        <v>984</v>
+        <v>1304</v>
       </c>
       <c r="F660" s="3" t="s">
         <v>289</v>
       </c>
       <c r="G660" s="7">
-        <v>47286.0</v>
+        <v>47293.0</v>
       </c>
       <c r="H660" s="2"/>
     </row>
     <row r="661">
       <c r="A661" s="2" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
       <c r="B661" s="2" t="s">
         <v>11</v>
       </c>
       <c r="C661" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D661" s="2">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="E661" s="2" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="F661" s="3" t="s">
-        <v>289</v>
+        <v>210</v>
       </c>
       <c r="G661" s="7">
-        <v>47293.0</v>
+        <v>47188.0</v>
       </c>
       <c r="H661" s="2"/>
     </row>
     <row r="662">
       <c r="A662" s="2" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="B662" s="2" t="s">
         <v>11</v>
@@ -20127,19 +20052,19 @@
         <v>4.0</v>
       </c>
       <c r="E662" s="2" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
       <c r="F662" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G662" s="7">
-        <v>47188.0</v>
+        <v>47328.0</v>
       </c>
       <c r="H662" s="2"/>
     </row>
     <row r="663">
       <c r="A663" s="2" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
       <c r="B663" s="2" t="s">
         <v>11</v>
@@ -20151,19 +20076,19 @@
         <v>4.0</v>
       </c>
       <c r="E663" s="2" t="s">
-        <v>1311</v>
+        <v>1197</v>
       </c>
       <c r="F663" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G663" s="7">
-        <v>47328.0</v>
+        <v>46874.0</v>
       </c>
       <c r="H663" s="2"/>
     </row>
     <row r="664">
-      <c r="A664" s="2" t="s">
-        <v>1312</v>
+      <c r="A664" s="2">
+        <v>1.7924816362538E15</v>
       </c>
       <c r="B664" s="2" t="s">
         <v>11</v>
@@ -20175,19 +20100,19 @@
         <v>4.0</v>
       </c>
       <c r="E664" s="2" t="s">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="F664" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G664" s="7">
-        <v>46874.0</v>
+        <v>46997.0</v>
       </c>
       <c r="H664" s="2"/>
     </row>
     <row r="665">
       <c r="A665" s="2">
-        <v>1.7924816362538E15</v>
+        <v>1.7924816629052E15</v>
       </c>
       <c r="B665" s="2" t="s">
         <v>11</v>
@@ -20199,19 +20124,19 @@
         <v>4.0</v>
       </c>
       <c r="E665" s="2" t="s">
-        <v>1196</v>
+        <v>1310</v>
       </c>
       <c r="F665" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G665" s="7">
-        <v>46997.0</v>
+        <v>47328.0</v>
       </c>
       <c r="H665" s="2"/>
     </row>
     <row r="666">
-      <c r="A666" s="2">
-        <v>1.7924816629052E15</v>
+      <c r="A666" s="2" t="s">
+        <v>1311</v>
       </c>
       <c r="B666" s="2" t="s">
         <v>11</v>
@@ -20223,46 +20148,42 @@
         <v>4.0</v>
       </c>
       <c r="E666" s="2" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="F666" s="3" t="s">
         <v>210</v>
       </c>
       <c r="G666" s="7">
-        <v>47328.0</v>
+        <v>47357.0</v>
       </c>
       <c r="H666" s="2"/>
     </row>
     <row r="667">
       <c r="A667" s="2" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B667" s="2" t="s">
-        <v>11</v>
+        <v>1220</v>
       </c>
       <c r="C667" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D667" s="2">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="E667" s="2" t="s">
-        <v>1315</v>
-      </c>
-      <c r="F667" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G667" s="7">
-        <v>47357.0</v>
-      </c>
+        <v>1123</v>
+      </c>
+      <c r="F667" s="3"/>
+      <c r="G667" s="7"/>
       <c r="H667" s="2"/>
     </row>
     <row r="668">
       <c r="A668" s="2" t="s">
-        <v>1316</v>
+        <v>1314</v>
       </c>
       <c r="B668" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C668" s="2" t="s">
         <v>12</v>
@@ -20271,7 +20192,7 @@
         <v>7.0</v>
       </c>
       <c r="E668" s="2" t="s">
-        <v>1124</v>
+        <v>1315</v>
       </c>
       <c r="F668" s="3"/>
       <c r="G668" s="7"/>
@@ -20279,144 +20200,152 @@
     </row>
     <row r="669">
       <c r="A669" s="2" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B669" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C669" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D669" s="2">
+        <v>10.0</v>
+      </c>
+      <c r="E669" s="2" t="s">
         <v>1317</v>
       </c>
-      <c r="B669" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C669" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D669" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E669" s="2" t="s">
-        <v>1318</v>
-      </c>
       <c r="F669" s="3"/>
-      <c r="G669" s="7"/>
+      <c r="G669" s="7">
+        <v>46680.0</v>
+      </c>
       <c r="H669" s="2"/>
     </row>
     <row r="670">
       <c r="A670" s="2" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B670" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C670" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D670" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="E670" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F670" s="3" t="s">
         <v>1319</v>
       </c>
-      <c r="B670" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C670" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D670" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E670" s="2" t="s">
+      <c r="G670" s="7">
+        <v>46793.0</v>
+      </c>
+      <c r="H670" s="2"/>
+    </row>
+    <row r="671">
+      <c r="A671" s="2">
+        <v>1.79255299094017E15</v>
+      </c>
+      <c r="B671" s="2" t="s">
+        <v>1220</v>
+      </c>
+      <c r="C671" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D671" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="E671" s="2" t="s">
         <v>1320</v>
       </c>
-      <c r="F670" s="3"/>
-      <c r="G670" s="7"/>
-      <c r="H670" s="2"/>
-    </row>
-    <row r="671">
-      <c r="A671" s="2" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B671" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C671" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D671" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="E671" s="2" t="s">
-        <v>1322</v>
-      </c>
-      <c r="F671" s="3"/>
+      <c r="F671" s="3" t="s">
+        <v>236</v>
+      </c>
       <c r="G671" s="7">
-        <v>46680.0</v>
+        <v>46995.0</v>
       </c>
       <c r="H671" s="2"/>
     </row>
     <row r="672">
       <c r="A672" s="2" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B672" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C672" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D672" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E672" s="2" t="s">
+        <v>956</v>
+      </c>
+      <c r="F672" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G672" s="7">
+        <v>46509.0</v>
+      </c>
+      <c r="H672" s="2"/>
+    </row>
+    <row r="673">
+      <c r="A673" s="2" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B673" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C673" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D673" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="E673" s="2" t="s">
         <v>1323</v>
-      </c>
-      <c r="B672" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C672" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D672" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E672" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F672" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="G672" s="7">
-        <v>46793.0</v>
-      </c>
-      <c r="H672" s="2"/>
-    </row>
-    <row r="673">
-      <c r="A673" s="2">
-        <v>1.79255299094017E15</v>
-      </c>
-      <c r="B673" s="2" t="s">
-        <v>1221</v>
-      </c>
-      <c r="C673" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D673" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="E673" s="2" t="s">
-        <v>1325</v>
       </c>
       <c r="F673" s="3" t="s">
         <v>236</v>
       </c>
       <c r="G673" s="7">
-        <v>46995.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H673" s="2"/>
     </row>
     <row r="674">
       <c r="A674" s="2" t="s">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="B674" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C674" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D674" s="2">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="E674" s="2" t="s">
-        <v>957</v>
+        <v>759</v>
       </c>
       <c r="F674" s="3" t="s">
         <v>236</v>
       </c>
       <c r="G674" s="7">
-        <v>46509.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H674" s="2"/>
     </row>
     <row r="675">
       <c r="A675" s="2" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="B675" s="2" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C675" s="2" t="s">
         <v>45</v>
@@ -20425,31 +20354,29 @@
         <v>1.0</v>
       </c>
       <c r="E675" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="F675" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="G675" s="7">
-        <v>46830.0</v>
-      </c>
+      <c r="G675" s="7"/>
       <c r="H675" s="2"/>
     </row>
     <row r="676">
       <c r="A676" s="2" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>38</v>
+        <v>1220</v>
       </c>
       <c r="C676" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D676" s="2">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="E676" s="2" t="s">
-        <v>1330</v>
+        <v>959</v>
       </c>
       <c r="F676" s="3" t="s">
         <v>236</v>
@@ -20461,542 +20388,544 @@
     </row>
     <row r="677">
       <c r="A677" s="2" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
       <c r="B677" s="2" t="s">
-        <v>38</v>
+        <v>593</v>
       </c>
       <c r="C677" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D677" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="E677" s="2" t="s">
-        <v>759</v>
+        <v>1315</v>
       </c>
       <c r="F677" s="3" t="s">
-        <v>236</v>
+        <v>1329</v>
       </c>
       <c r="G677" s="7">
-        <v>46530.0</v>
+        <v>46369.0</v>
       </c>
       <c r="H677" s="2"/>
     </row>
     <row r="678">
       <c r="A678" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="B678" s="2" t="s">
-        <v>1221</v>
+        <v>593</v>
       </c>
       <c r="C678" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D678" s="2">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="E678" s="2" t="s">
-        <v>1333</v>
+        <v>1120</v>
       </c>
       <c r="F678" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G678" s="7"/>
+        <v>1329</v>
+      </c>
+      <c r="G678" s="7">
+        <v>46369.0</v>
+      </c>
       <c r="H678" s="2"/>
     </row>
     <row r="679">
       <c r="A679" s="2" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="B679" s="2" t="s">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="C679" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D679" s="2">
-        <v>15.0</v>
+        <v>9.0</v>
       </c>
       <c r="E679" s="2" t="s">
-        <v>1335</v>
+        <v>547</v>
       </c>
       <c r="F679" s="3" t="s">
-        <v>236</v>
+        <v>466</v>
       </c>
       <c r="G679" s="7">
-        <v>46487.0</v>
+        <v>46472.0</v>
       </c>
       <c r="H679" s="2"/>
     </row>
     <row r="680">
       <c r="A680" s="2" t="s">
-        <v>1336</v>
+        <v>1332</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>1221</v>
+        <v>257</v>
       </c>
       <c r="C680" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D680" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E680" s="2" t="s">
-        <v>960</v>
+        <v>540</v>
       </c>
       <c r="F680" s="3" t="s">
-        <v>236</v>
+        <v>466</v>
       </c>
       <c r="G680" s="7">
-        <v>46792.0</v>
+        <v>46476.0</v>
       </c>
       <c r="H680" s="2"/>
     </row>
     <row r="681">
       <c r="A681" s="2" t="s">
-        <v>1337</v>
+        <v>1333</v>
       </c>
       <c r="B681" s="2" t="s">
-        <v>1221</v>
+        <v>257</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D681" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E681" s="2" t="s">
-        <v>1338</v>
+        <v>549</v>
       </c>
       <c r="F681" s="3" t="s">
-        <v>236</v>
+        <v>466</v>
       </c>
       <c r="G681" s="7">
-        <v>46885.0</v>
+        <v>46475.0</v>
       </c>
       <c r="H681" s="2"/>
     </row>
     <row r="682">
       <c r="A682" s="2" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="B682" s="2" t="s">
-        <v>1221</v>
+        <v>257</v>
       </c>
       <c r="C682" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D682" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E682" s="2" t="s">
-        <v>1340</v>
+        <v>545</v>
       </c>
       <c r="F682" s="3" t="s">
-        <v>236</v>
+        <v>466</v>
       </c>
       <c r="G682" s="7">
-        <v>46947.0</v>
+        <v>46457.0</v>
       </c>
       <c r="H682" s="2"/>
     </row>
     <row r="683">
-      <c r="A683" s="2">
-        <v>1.79255331011668E15</v>
+      <c r="A683" s="2" t="s">
+        <v>1335</v>
       </c>
       <c r="B683" s="2" t="s">
-        <v>1221</v>
+        <v>257</v>
       </c>
       <c r="C683" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D683" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E683" s="2" t="s">
-        <v>1341</v>
+        <v>451</v>
       </c>
       <c r="F683" s="3" t="s">
-        <v>236</v>
+        <v>466</v>
       </c>
       <c r="G683" s="7">
-        <v>46792.0</v>
+        <v>46644.0</v>
       </c>
       <c r="H683" s="2"/>
     </row>
     <row r="684">
       <c r="A684" s="2" t="s">
-        <v>1342</v>
+        <v>1336</v>
       </c>
       <c r="B684" s="2" t="s">
-        <v>1221</v>
+        <v>257</v>
       </c>
       <c r="C684" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D684" s="2">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="E684" s="2" t="s">
-        <v>1343</v>
-      </c>
-      <c r="F684" s="3"/>
-      <c r="G684" s="7"/>
+        <v>538</v>
+      </c>
+      <c r="F684" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="G684" s="7">
+        <v>46641.0</v>
+      </c>
       <c r="H684" s="2"/>
     </row>
     <row r="685">
       <c r="A685" s="2" t="s">
-        <v>1344</v>
+        <v>1337</v>
       </c>
       <c r="B685" s="2" t="s">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="C685" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D685" s="2">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="E685" s="2" t="s">
-        <v>1345</v>
-      </c>
-      <c r="F685" s="3">
-        <v>11508.0</v>
-      </c>
-      <c r="G685" s="7">
-        <v>46961.0</v>
-      </c>
+        <v>1338</v>
+      </c>
+      <c r="F685" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="G685" s="7"/>
       <c r="H685" s="2"/>
     </row>
     <row r="686">
-      <c r="A686" s="2">
-        <v>1.79256485988391E15</v>
+      <c r="A686" s="2" t="s">
+        <v>1339</v>
       </c>
       <c r="B686" s="2" t="s">
-        <v>38</v>
+        <v>257</v>
       </c>
       <c r="C686" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D686" s="2">
+        <v>14.0</v>
+      </c>
+      <c r="E686" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="F686" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="G686" s="7">
+        <v>46409.0</v>
+      </c>
+      <c r="H686" s="2"/>
+    </row>
+    <row r="687">
+      <c r="A687" s="2">
+        <v>1.79307444508079E15</v>
+      </c>
+      <c r="B687" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C687" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D686" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="E686" s="2" t="s">
-        <v>1346</v>
-      </c>
-      <c r="F686" s="3">
-        <v>11509.0</v>
-      </c>
-      <c r="G686" s="7">
-        <v>47003.0</v>
-      </c>
-      <c r="H686" s="2"/>
-    </row>
-    <row r="687">
-      <c r="A687" s="2" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B687" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C687" s="2" t="s">
-        <v>12</v>
-      </c>
       <c r="D687" s="2">
-        <v>15.0</v>
+        <v>14.0</v>
       </c>
       <c r="E687" s="2" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="F687" s="3" t="s">
-        <v>199</v>
+        <v>236</v>
       </c>
       <c r="G687" s="7">
-        <v>46645.0</v>
+        <v>46448.0</v>
       </c>
       <c r="H687" s="2"/>
     </row>
     <row r="688">
       <c r="A688" s="2" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="B688" s="2" t="s">
-        <v>593</v>
+        <v>1220</v>
       </c>
       <c r="C688" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D688" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E688" s="2" t="s">
-        <v>1318</v>
+        <v>1342</v>
       </c>
       <c r="F688" s="3" t="s">
-        <v>1350</v>
+        <v>236</v>
       </c>
       <c r="G688" s="7">
-        <v>46369.0</v>
+        <v>47020.0</v>
       </c>
       <c r="H688" s="2"/>
     </row>
     <row r="689">
       <c r="A689" s="2" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="B689" s="2" t="s">
-        <v>593</v>
+        <v>1220</v>
       </c>
       <c r="C689" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D689" s="2">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="E689" s="2" t="s">
-        <v>1121</v>
+        <v>1344</v>
       </c>
       <c r="F689" s="3" t="s">
-        <v>1350</v>
+        <v>236</v>
       </c>
       <c r="G689" s="7">
-        <v>46369.0</v>
+        <v>46836.0</v>
       </c>
       <c r="H689" s="2"/>
     </row>
     <row r="690">
       <c r="A690" s="2" t="s">
-        <v>1352</v>
+        <v>1345</v>
       </c>
       <c r="B690" s="2" t="s">
-        <v>257</v>
+        <v>1220</v>
       </c>
       <c r="C690" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D690" s="2">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="E690" s="2" t="s">
-        <v>547</v>
+        <v>759</v>
       </c>
       <c r="F690" s="3" t="s">
-        <v>466</v>
+        <v>236</v>
       </c>
       <c r="G690" s="7">
-        <v>46472.0</v>
+        <v>46537.0</v>
       </c>
       <c r="H690" s="2"/>
     </row>
     <row r="691">
       <c r="A691" s="2" t="s">
-        <v>1353</v>
+        <v>1346</v>
       </c>
       <c r="B691" s="2" t="s">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="C691" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D691" s="2">
-        <v>9.0</v>
+        <v>15.0</v>
       </c>
       <c r="E691" s="2" t="s">
-        <v>540</v>
+        <v>1347</v>
       </c>
       <c r="F691" s="3" t="s">
-        <v>466</v>
+        <v>236</v>
       </c>
       <c r="G691" s="7">
-        <v>46476.0</v>
+        <v>46612.0</v>
       </c>
       <c r="H691" s="2"/>
     </row>
     <row r="692">
-      <c r="A692" s="2" t="s">
-        <v>1354</v>
+      <c r="A692" s="2">
+        <v>1.79307465042405E15</v>
       </c>
       <c r="B692" s="2" t="s">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="C692" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D692" s="2">
-        <v>9.0</v>
+        <v>12.0</v>
       </c>
       <c r="E692" s="2" t="s">
-        <v>549</v>
+        <v>1348</v>
       </c>
       <c r="F692" s="3" t="s">
-        <v>466</v>
+        <v>236</v>
       </c>
       <c r="G692" s="7">
-        <v>46475.0</v>
+        <v>46792.0</v>
       </c>
       <c r="H692" s="2"/>
     </row>
     <row r="693">
       <c r="A693" s="2" t="s">
-        <v>1355</v>
+        <v>1349</v>
       </c>
       <c r="B693" s="2" t="s">
-        <v>257</v>
+        <v>38</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D693" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E693" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="F693" s="3" t="s">
-        <v>466</v>
+        <v>722</v>
+      </c>
+      <c r="F693" s="3">
+        <v>11505.0</v>
       </c>
       <c r="G693" s="7">
-        <v>46457.0</v>
+        <v>46848.0</v>
       </c>
       <c r="H693" s="2"/>
     </row>
     <row r="694">
       <c r="A694" s="2" t="s">
-        <v>1356</v>
+        <v>1350</v>
       </c>
       <c r="B694" s="2" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="C694" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D694" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E694" s="2" t="s">
-        <v>451</v>
+        <v>1185</v>
       </c>
       <c r="F694" s="3" t="s">
-        <v>466</v>
+        <v>69</v>
       </c>
       <c r="G694" s="7">
-        <v>46644.0</v>
+        <v>46607.0</v>
       </c>
       <c r="H694" s="2"/>
     </row>
     <row r="695">
       <c r="A695" s="2" t="s">
-        <v>1357</v>
+        <v>1351</v>
       </c>
       <c r="B695" s="2" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="C695" s="2" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="D695" s="2">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="E695" s="2" t="s">
-        <v>538</v>
+        <v>1185</v>
       </c>
       <c r="F695" s="3" t="s">
-        <v>466</v>
+        <v>769</v>
       </c>
       <c r="G695" s="7">
-        <v>46641.0</v>
+        <v>46628.0</v>
       </c>
       <c r="H695" s="2"/>
     </row>
     <row r="696">
       <c r="A696" s="2" t="s">
-        <v>1358</v>
+        <v>1352</v>
       </c>
       <c r="B696" s="2" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="C696" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D696" s="2">
-        <v>12.0</v>
+        <v>7.0</v>
       </c>
       <c r="E696" s="2" t="s">
-        <v>1359</v>
+        <v>742</v>
       </c>
       <c r="F696" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="G696" s="7"/>
+        <v>782</v>
+      </c>
+      <c r="G696" s="7">
+        <v>46431.0</v>
+      </c>
       <c r="H696" s="2"/>
     </row>
     <row r="697">
       <c r="A697" s="2" t="s">
-        <v>1360</v>
+        <v>1353</v>
       </c>
       <c r="B697" s="2" t="s">
-        <v>257</v>
+        <v>33</v>
       </c>
       <c r="C697" s="2" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D697" s="2">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="E697" s="2" t="s">
-        <v>477</v>
+        <v>1022</v>
       </c>
       <c r="F697" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="G697" s="7">
-        <v>46409.0</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="G697" s="7"/>
       <c r="H697" s="2"/>
     </row>
     <row r="698">
-      <c r="A698" s="2">
-        <v>1.79307444508079E15</v>
+      <c r="A698" s="2" t="s">
+        <v>1354</v>
       </c>
       <c r="B698" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C698" s="2" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D698" s="2">
-        <v>14.0</v>
+        <v>7.0</v>
       </c>
       <c r="E698" s="2" t="s">
-        <v>1361</v>
+        <v>1022</v>
       </c>
       <c r="F698" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G698" s="7">
-        <v>46448.0</v>
-      </c>
+        <v>715</v>
+      </c>
+      <c r="G698" s="7"/>
       <c r="H698" s="2"/>
     </row>
     <row r="699">
       <c r="A699" s="2" t="s">
-        <v>1362</v>
+        <v>1355</v>
       </c>
       <c r="B699" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C699" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D699" s="2">
-        <v>2.0</v>
+        <v>20.0</v>
       </c>
       <c r="E699" s="2" t="s">
-        <v>1363</v>
+        <v>1356</v>
       </c>
       <c r="F699" s="3" t="s">
-        <v>236</v>
+        <v>1357</v>
       </c>
       <c r="G699" s="7">
         <v>47020.0</v>
@@ -21005,107 +20934,103 @@
     </row>
     <row r="700">
       <c r="A700" s="2" t="s">
-        <v>1364</v>
+        <v>1358</v>
       </c>
       <c r="B700" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C700" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D700" s="2">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
       <c r="E700" s="2" t="s">
-        <v>1243</v>
+        <v>1138</v>
       </c>
       <c r="F700" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G700" s="7">
-        <v>47020.0</v>
-      </c>
-      <c r="H700" s="2" t="s">
-        <v>1365</v>
-      </c>
+        <v>46388.0</v>
+      </c>
+      <c r="H700" s="2"/>
     </row>
     <row r="701">
-      <c r="A701" s="2" t="s">
-        <v>1366</v>
+      <c r="A701" s="2">
+        <v>1.79318672188573E15</v>
       </c>
       <c r="B701" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C701" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D701" s="2">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="E701" s="2" t="s">
-        <v>1367</v>
+        <v>1222</v>
       </c>
       <c r="F701" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G701" s="7">
-        <v>46836.0</v>
+        <v>46395.0</v>
       </c>
       <c r="H701" s="2"/>
     </row>
     <row r="702">
-      <c r="A702" s="2" t="s">
-        <v>1368</v>
+      <c r="A702" s="2">
+        <v>1.79318674508485E15</v>
       </c>
       <c r="B702" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C702" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D702" s="2">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="E702" s="2" t="s">
-        <v>1369</v>
+        <v>1228</v>
       </c>
       <c r="F702" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G702" s="7">
-        <v>46759.0</v>
-      </c>
-      <c r="H702" s="2" t="s">
-        <v>1365</v>
-      </c>
+        <v>46396.0</v>
+      </c>
+      <c r="H702" s="2"/>
     </row>
     <row r="703">
       <c r="A703" s="2" t="s">
-        <v>1370</v>
+        <v>1360</v>
       </c>
       <c r="B703" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C703" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D703" s="2">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="E703" s="2" t="s">
-        <v>759</v>
+        <v>1230</v>
       </c>
       <c r="F703" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G703" s="7">
-        <v>46537.0</v>
+        <v>46389.0</v>
       </c>
       <c r="H703" s="2"/>
     </row>
     <row r="704">
       <c r="A704" s="2" t="s">
-        <v>1371</v>
+        <v>1361</v>
       </c>
       <c r="B704" s="2" t="s">
         <v>38</v>
@@ -21114,22 +21039,22 @@
         <v>12</v>
       </c>
       <c r="D704" s="2">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="E704" s="2" t="s">
-        <v>1335</v>
+        <v>1146</v>
       </c>
       <c r="F704" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G704" s="7">
-        <v>46612.0</v>
+        <v>46387.0</v>
       </c>
       <c r="H704" s="2"/>
     </row>
     <row r="705">
-      <c r="A705" s="2">
-        <v>1.79307465042405E15</v>
+      <c r="A705" s="2" t="s">
+        <v>1362</v>
       </c>
       <c r="B705" s="2" t="s">
         <v>38</v>
@@ -21138,445 +21063,253 @@
         <v>12</v>
       </c>
       <c r="D705" s="2">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="E705" s="2" t="s">
-        <v>1372</v>
+        <v>1363</v>
       </c>
       <c r="F705" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G705" s="7">
-        <v>46792.0</v>
+        <v>46395.0</v>
       </c>
       <c r="H705" s="2"/>
     </row>
     <row r="706">
       <c r="A706" s="2" t="s">
-        <v>1373</v>
+        <v>1364</v>
       </c>
       <c r="B706" s="2" t="s">
-        <v>1221</v>
+        <v>38</v>
       </c>
       <c r="C706" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="D706" s="2">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="E706" s="2" t="s">
-        <v>1341</v>
+        <v>1363</v>
       </c>
       <c r="F706" s="3" t="s">
-        <v>236</v>
+        <v>1359</v>
       </c>
       <c r="G706" s="7">
-        <v>46792.0</v>
+        <v>46395.0</v>
       </c>
       <c r="H706" s="2"/>
     </row>
     <row r="707">
       <c r="A707" s="2" t="s">
-        <v>1374</v>
+        <v>1365</v>
       </c>
       <c r="B707" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C707" s="2" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D707" s="2">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="E707" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="F707" s="3">
-        <v>11505.0</v>
+        <v>1366</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>1359</v>
       </c>
       <c r="G707" s="7">
-        <v>46848.0</v>
+        <v>46396.0</v>
       </c>
       <c r="H707" s="2"/>
     </row>
     <row r="708">
       <c r="A708" s="2" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="B708" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C708" s="2" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="D708" s="2">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="E708" s="2" t="s">
-        <v>1186</v>
+        <v>1368</v>
       </c>
       <c r="F708" s="3" t="s">
-        <v>69</v>
+        <v>236</v>
       </c>
       <c r="G708" s="7">
-        <v>46607.0</v>
+        <v>46537.0</v>
       </c>
       <c r="H708" s="2"/>
     </row>
     <row r="709">
       <c r="A709" s="2" t="s">
-        <v>1376</v>
+        <v>1369</v>
       </c>
       <c r="B709" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C709" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D709" s="2">
-        <v>6.0</v>
+        <v>13.0</v>
       </c>
       <c r="E709" s="2" t="s">
-        <v>1186</v>
+        <v>1344</v>
       </c>
       <c r="F709" s="3" t="s">
-        <v>769</v>
+        <v>236</v>
       </c>
       <c r="G709" s="7">
-        <v>46628.0</v>
+        <v>46530.0</v>
       </c>
       <c r="H709" s="2"/>
     </row>
     <row r="710">
-      <c r="A710" s="2" t="s">
-        <v>1377</v>
-      </c>
-      <c r="B710" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C710" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D710" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E710" s="2" t="s">
-        <v>742</v>
-      </c>
-      <c r="F710" s="3" t="s">
-        <v>782</v>
-      </c>
-      <c r="G710" s="7">
-        <v>46431.0</v>
-      </c>
+      <c r="A710" s="2"/>
+      <c r="B710" s="2"/>
+      <c r="C710" s="2"/>
+      <c r="D710" s="2"/>
+      <c r="E710" s="2"/>
+      <c r="F710" s="3"/>
+      <c r="G710" s="7"/>
       <c r="H710" s="2"/>
     </row>
     <row r="711">
-      <c r="A711" s="2" t="s">
-        <v>1378</v>
-      </c>
-      <c r="B711" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C711" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D711" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E711" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F711" s="3" t="s">
-        <v>718</v>
-      </c>
+      <c r="A711" s="2"/>
+      <c r="B711" s="2"/>
+      <c r="C711" s="2"/>
+      <c r="D711" s="2"/>
+      <c r="E711" s="2"/>
+      <c r="F711" s="3"/>
       <c r="G711" s="7"/>
       <c r="H711" s="2"/>
     </row>
     <row r="712">
-      <c r="A712" s="2" t="s">
-        <v>1379</v>
-      </c>
-      <c r="B712" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C712" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D712" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E712" s="2" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F712" s="3" t="s">
-        <v>715</v>
-      </c>
+      <c r="A712" s="2"/>
+      <c r="B712" s="2"/>
+      <c r="C712" s="2"/>
+      <c r="D712" s="2"/>
+      <c r="E712" s="2"/>
+      <c r="F712" s="3"/>
       <c r="G712" s="7"/>
       <c r="H712" s="2"/>
     </row>
     <row r="713">
-      <c r="A713" s="2" t="s">
-        <v>1380</v>
-      </c>
-      <c r="B713" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C713" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D713" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="E713" s="2" t="s">
-        <v>1381</v>
-      </c>
-      <c r="F713" s="3" t="s">
-        <v>1382</v>
-      </c>
-      <c r="G713" s="7">
-        <v>47020.0</v>
-      </c>
+      <c r="A713" s="2"/>
+      <c r="B713" s="2"/>
+      <c r="C713" s="2"/>
+      <c r="D713" s="2"/>
+      <c r="E713" s="2"/>
+      <c r="F713" s="3"/>
+      <c r="G713" s="7"/>
       <c r="H713" s="2"/>
     </row>
     <row r="714">
-      <c r="A714" s="2" t="s">
-        <v>1383</v>
-      </c>
-      <c r="B714" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C714" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D714" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="E714" s="2" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F714" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G714" s="7">
-        <v>46388.0</v>
-      </c>
+      <c r="A714" s="2"/>
+      <c r="B714" s="2"/>
+      <c r="C714" s="2"/>
+      <c r="D714" s="2"/>
+      <c r="E714" s="2"/>
+      <c r="F714" s="3"/>
+      <c r="G714" s="7"/>
       <c r="H714" s="2"/>
     </row>
     <row r="715">
-      <c r="A715" s="2">
-        <v>1.79318672188573E15</v>
-      </c>
-      <c r="B715" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C715" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D715" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="E715" s="2" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F715" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G715" s="7">
-        <v>46395.0</v>
-      </c>
+      <c r="A715" s="2"/>
+      <c r="B715" s="2"/>
+      <c r="C715" s="2"/>
+      <c r="D715" s="2"/>
+      <c r="E715" s="2"/>
+      <c r="F715" s="3"/>
+      <c r="G715" s="7"/>
       <c r="H715" s="2"/>
     </row>
     <row r="716">
-      <c r="A716" s="2">
-        <v>1.79318674508485E15</v>
-      </c>
-      <c r="B716" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C716" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D716" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="E716" s="2" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F716" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G716" s="7">
-        <v>46396.0</v>
-      </c>
+      <c r="A716" s="2"/>
+      <c r="B716" s="2"/>
+      <c r="C716" s="2"/>
+      <c r="D716" s="2"/>
+      <c r="E716" s="2"/>
+      <c r="F716" s="3"/>
+      <c r="G716" s="7"/>
       <c r="H716" s="2"/>
     </row>
     <row r="717">
-      <c r="A717" s="2" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B717" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C717" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D717" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E717" s="2" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F717" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G717" s="7">
-        <v>46389.0</v>
-      </c>
+      <c r="A717" s="2"/>
+      <c r="B717" s="2"/>
+      <c r="C717" s="2"/>
+      <c r="D717" s="2"/>
+      <c r="E717" s="2"/>
+      <c r="F717" s="3"/>
+      <c r="G717" s="7"/>
       <c r="H717" s="2"/>
     </row>
     <row r="718">
-      <c r="A718" s="2" t="s">
-        <v>1386</v>
-      </c>
-      <c r="B718" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C718" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D718" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E718" s="2" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F718" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G718" s="7">
-        <v>46387.0</v>
-      </c>
+      <c r="A718" s="2"/>
+      <c r="B718" s="2"/>
+      <c r="C718" s="2"/>
+      <c r="D718" s="2"/>
+      <c r="E718" s="2"/>
+      <c r="F718" s="3"/>
+      <c r="G718" s="7"/>
       <c r="H718" s="2"/>
     </row>
     <row r="719">
-      <c r="A719" s="2" t="s">
-        <v>1387</v>
-      </c>
-      <c r="B719" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C719" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D719" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="E719" s="2" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F719" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G719" s="7">
-        <v>46395.0</v>
-      </c>
+      <c r="A719" s="2"/>
+      <c r="B719" s="2"/>
+      <c r="C719" s="2"/>
+      <c r="D719" s="2"/>
+      <c r="E719" s="2"/>
+      <c r="F719" s="3"/>
+      <c r="G719" s="7"/>
       <c r="H719" s="2"/>
     </row>
     <row r="720">
-      <c r="A720" s="2" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B720" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C720" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D720" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E720" s="2" t="s">
-        <v>1388</v>
-      </c>
-      <c r="F720" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G720" s="7">
-        <v>46395.0</v>
-      </c>
+      <c r="A720" s="2"/>
+      <c r="B720" s="2"/>
+      <c r="C720" s="2"/>
+      <c r="D720" s="2"/>
+      <c r="E720" s="2"/>
+      <c r="F720" s="3"/>
+      <c r="G720" s="7"/>
       <c r="H720" s="2"/>
     </row>
     <row r="721">
-      <c r="A721" s="2" t="s">
-        <v>1390</v>
-      </c>
-      <c r="B721" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C721" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D721" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="E721" s="2" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F721" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="G721" s="7">
-        <v>46396.0</v>
-      </c>
+      <c r="A721" s="2"/>
+      <c r="B721" s="2"/>
+      <c r="C721" s="2"/>
+      <c r="D721" s="2"/>
+      <c r="E721" s="2"/>
+      <c r="F721" s="3"/>
+      <c r="G721" s="7"/>
       <c r="H721" s="2"/>
     </row>
     <row r="722">
-      <c r="A722" s="2" t="s">
-        <v>1392</v>
-      </c>
-      <c r="B722" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C722" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D722" s="2">
-        <v>16.0</v>
-      </c>
-      <c r="E722" s="2" t="s">
-        <v>1393</v>
-      </c>
-      <c r="F722" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G722" s="7">
-        <v>46537.0</v>
-      </c>
+      <c r="A722" s="2"/>
+      <c r="B722" s="2"/>
+      <c r="C722" s="2"/>
+      <c r="D722" s="2"/>
+      <c r="E722" s="2"/>
+      <c r="F722" s="3"/>
+      <c r="G722" s="7"/>
       <c r="H722" s="2"/>
     </row>
     <row r="723">
-      <c r="A723" s="2" t="s">
-        <v>1394</v>
-      </c>
-      <c r="B723" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C723" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D723" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="E723" s="2" t="s">
-        <v>1367</v>
-      </c>
-      <c r="F723" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="G723" s="7">
-        <v>46530.0</v>
-      </c>
+      <c r="A723" s="2"/>
+      <c r="B723" s="2"/>
+      <c r="C723" s="2"/>
+      <c r="D723" s="2"/>
+      <c r="E723" s="2"/>
+      <c r="F723" s="3"/>
+      <c r="G723" s="7"/>
       <c r="H723" s="2"/>
     </row>
     <row r="724">
@@ -23599,146 +23332,6 @@
       <c r="G925" s="7"/>
       <c r="H925" s="2"/>
     </row>
-    <row r="926">
-      <c r="A926" s="2"/>
-      <c r="B926" s="2"/>
-      <c r="C926" s="2"/>
-      <c r="D926" s="2"/>
-      <c r="E926" s="2"/>
-      <c r="F926" s="3"/>
-      <c r="G926" s="7"/>
-      <c r="H926" s="2"/>
-    </row>
-    <row r="927">
-      <c r="A927" s="2"/>
-      <c r="B927" s="2"/>
-      <c r="C927" s="2"/>
-      <c r="D927" s="2"/>
-      <c r="E927" s="2"/>
-      <c r="F927" s="3"/>
-      <c r="G927" s="7"/>
-      <c r="H927" s="2"/>
-    </row>
-    <row r="928">
-      <c r="A928" s="2"/>
-      <c r="B928" s="2"/>
-      <c r="C928" s="2"/>
-      <c r="D928" s="2"/>
-      <c r="E928" s="2"/>
-      <c r="F928" s="3"/>
-      <c r="G928" s="7"/>
-      <c r="H928" s="2"/>
-    </row>
-    <row r="929">
-      <c r="A929" s="2"/>
-      <c r="B929" s="2"/>
-      <c r="C929" s="2"/>
-      <c r="D929" s="2"/>
-      <c r="E929" s="2"/>
-      <c r="F929" s="3"/>
-      <c r="G929" s="7"/>
-      <c r="H929" s="2"/>
-    </row>
-    <row r="930">
-      <c r="A930" s="2"/>
-      <c r="B930" s="2"/>
-      <c r="C930" s="2"/>
-      <c r="D930" s="2"/>
-      <c r="E930" s="2"/>
-      <c r="F930" s="3"/>
-      <c r="G930" s="7"/>
-      <c r="H930" s="2"/>
-    </row>
-    <row r="931">
-      <c r="A931" s="2"/>
-      <c r="B931" s="2"/>
-      <c r="C931" s="2"/>
-      <c r="D931" s="2"/>
-      <c r="E931" s="2"/>
-      <c r="F931" s="3"/>
-      <c r="G931" s="7"/>
-      <c r="H931" s="2"/>
-    </row>
-    <row r="932">
-      <c r="A932" s="2"/>
-      <c r="B932" s="2"/>
-      <c r="C932" s="2"/>
-      <c r="D932" s="2"/>
-      <c r="E932" s="2"/>
-      <c r="F932" s="3"/>
-      <c r="G932" s="7"/>
-      <c r="H932" s="2"/>
-    </row>
-    <row r="933">
-      <c r="A933" s="2"/>
-      <c r="B933" s="2"/>
-      <c r="C933" s="2"/>
-      <c r="D933" s="2"/>
-      <c r="E933" s="2"/>
-      <c r="F933" s="3"/>
-      <c r="G933" s="7"/>
-      <c r="H933" s="2"/>
-    </row>
-    <row r="934">
-      <c r="A934" s="2"/>
-      <c r="B934" s="2"/>
-      <c r="C934" s="2"/>
-      <c r="D934" s="2"/>
-      <c r="E934" s="2"/>
-      <c r="F934" s="3"/>
-      <c r="G934" s="7"/>
-      <c r="H934" s="2"/>
-    </row>
-    <row r="935">
-      <c r="A935" s="2"/>
-      <c r="B935" s="2"/>
-      <c r="C935" s="2"/>
-      <c r="D935" s="2"/>
-      <c r="E935" s="2"/>
-      <c r="F935" s="3"/>
-      <c r="G935" s="7"/>
-      <c r="H935" s="2"/>
-    </row>
-    <row r="936">
-      <c r="A936" s="2"/>
-      <c r="B936" s="2"/>
-      <c r="C936" s="2"/>
-      <c r="D936" s="2"/>
-      <c r="E936" s="2"/>
-      <c r="F936" s="3"/>
-      <c r="G936" s="7"/>
-      <c r="H936" s="2"/>
-    </row>
-    <row r="937">
-      <c r="A937" s="2"/>
-      <c r="B937" s="2"/>
-      <c r="C937" s="2"/>
-      <c r="D937" s="2"/>
-      <c r="E937" s="2"/>
-      <c r="F937" s="3"/>
-      <c r="G937" s="7"/>
-      <c r="H937" s="2"/>
-    </row>
-    <row r="938">
-      <c r="A938" s="2"/>
-      <c r="B938" s="2"/>
-      <c r="C938" s="2"/>
-      <c r="D938" s="2"/>
-      <c r="E938" s="2"/>
-      <c r="F938" s="3"/>
-      <c r="G938" s="7"/>
-      <c r="H938" s="2"/>
-    </row>
-    <row r="939">
-      <c r="A939" s="2"/>
-      <c r="B939" s="2"/>
-      <c r="C939" s="2"/>
-      <c r="D939" s="2"/>
-      <c r="E939" s="2"/>
-      <c r="F939" s="3"/>
-      <c r="G939" s="7"/>
-      <c r="H939" s="2"/>
-    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
